--- a/static/TALENKAART_DATA/talenkaart_data.xlsx
+++ b/static/TALENKAART_DATA/talenkaart_data.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1243">
   <si>
     <t>Locatie</t>
   </si>
@@ -536,7 +536,7 @@
     <t>fra,spa,dui</t>
   </si>
   <si>
-    <t>nld,tw,eng</t>
+    <t>nld,twi,eng</t>
   </si>
   <si>
     <t>twi,eng</t>
@@ -2232,9 +2232,6 @@
   </si>
   <si>
     <t>Spinoza Lyceum</t>
-  </si>
-  <si>
-    <t>nld,twi,eng</t>
   </si>
   <si>
     <t>nld,pol,eng</t>
@@ -18734,7 +18731,7 @@
       </c>
       <c r="C938" s="3"/>
       <c r="D938" t="s" s="3">
-        <v>731</v>
+        <v>165</v>
       </c>
       <c r="E938" s="4"/>
       <c r="F938" s="4"/>
@@ -18748,7 +18745,7 @@
       </c>
       <c r="C939" s="3"/>
       <c r="D939" t="s" s="3">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E939" s="4"/>
       <c r="F939" s="4"/>
@@ -18860,7 +18857,7 @@
       </c>
       <c r="C947" s="3"/>
       <c r="D947" t="s" s="3">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E947" s="4"/>
       <c r="F947" s="4"/>
@@ -18874,7 +18871,7 @@
       </c>
       <c r="C948" s="3"/>
       <c r="D948" t="s" s="3">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E948" s="4"/>
       <c r="F948" s="4"/>
@@ -18895,7 +18892,7 @@
     </row>
     <row r="950" ht="13.65" customHeight="1">
       <c r="A950" t="s" s="3">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B950" t="s" s="3">
         <v>178</v>
@@ -18909,21 +18906,21 @@
     </row>
     <row r="951" ht="13.65" customHeight="1">
       <c r="A951" t="s" s="3">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B951" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C951" s="3"/>
       <c r="D951" t="s" s="3">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E951" s="4"/>
       <c r="F951" s="4"/>
     </row>
     <row r="952" ht="13.65" customHeight="1">
       <c r="A952" t="s" s="3">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B952" t="s" s="3">
         <v>178</v>
@@ -18937,7 +18934,7 @@
     </row>
     <row r="953" ht="13.65" customHeight="1">
       <c r="A953" t="s" s="3">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B953" t="s" s="3">
         <v>178</v>
@@ -18951,7 +18948,7 @@
     </row>
     <row r="954" ht="13.65" customHeight="1">
       <c r="A954" t="s" s="3">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B954" t="s" s="3">
         <v>444</v>
@@ -18965,10 +18962,10 @@
     </row>
     <row r="955" ht="13.65" customHeight="1">
       <c r="A955" t="s" s="3">
+        <v>737</v>
+      </c>
+      <c r="B955" t="s" s="3">
         <v>738</v>
-      </c>
-      <c r="B955" t="s" s="3">
-        <v>739</v>
       </c>
       <c r="C955" s="3"/>
       <c r="D955" t="s" s="3">
@@ -18979,10 +18976,10 @@
     </row>
     <row r="956" ht="13.65" customHeight="1">
       <c r="A956" t="s" s="3">
+        <v>737</v>
+      </c>
+      <c r="B956" t="s" s="3">
         <v>738</v>
-      </c>
-      <c r="B956" t="s" s="3">
-        <v>739</v>
       </c>
       <c r="C956" s="3"/>
       <c r="D956" t="s" s="3">
@@ -18993,10 +18990,10 @@
     </row>
     <row r="957" ht="13.65" customHeight="1">
       <c r="A957" t="s" s="3">
+        <v>737</v>
+      </c>
+      <c r="B957" t="s" s="3">
         <v>738</v>
-      </c>
-      <c r="B957" t="s" s="3">
-        <v>739</v>
       </c>
       <c r="C957" s="3"/>
       <c r="D957" t="s" s="3">
@@ -19007,38 +19004,38 @@
     </row>
     <row r="958" ht="13.65" customHeight="1">
       <c r="A958" t="s" s="3">
+        <v>737</v>
+      </c>
+      <c r="B958" t="s" s="3">
         <v>738</v>
-      </c>
-      <c r="B958" t="s" s="3">
-        <v>739</v>
       </c>
       <c r="C958" s="3"/>
       <c r="D958" t="s" s="3">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E958" s="4"/>
       <c r="F958" s="4"/>
     </row>
     <row r="959" ht="13.65" customHeight="1">
       <c r="A959" t="s" s="3">
+        <v>737</v>
+      </c>
+      <c r="B959" t="s" s="3">
         <v>738</v>
-      </c>
-      <c r="B959" t="s" s="3">
-        <v>739</v>
       </c>
       <c r="C959" s="3"/>
       <c r="D959" t="s" s="3">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E959" s="4"/>
       <c r="F959" s="4"/>
     </row>
     <row r="960" ht="13.65" customHeight="1">
       <c r="A960" t="s" s="3">
+        <v>737</v>
+      </c>
+      <c r="B960" t="s" s="3">
         <v>738</v>
-      </c>
-      <c r="B960" t="s" s="3">
-        <v>739</v>
       </c>
       <c r="C960" s="3"/>
       <c r="D960" t="s" s="3">
@@ -19049,38 +19046,38 @@
     </row>
     <row r="961" ht="13.65" customHeight="1">
       <c r="A961" t="s" s="3">
+        <v>737</v>
+      </c>
+      <c r="B961" t="s" s="3">
         <v>738</v>
-      </c>
-      <c r="B961" t="s" s="3">
-        <v>739</v>
       </c>
       <c r="C961" s="3"/>
       <c r="D961" t="s" s="3">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E961" s="4"/>
       <c r="F961" s="4"/>
     </row>
     <row r="962" ht="13.65" customHeight="1">
       <c r="A962" t="s" s="3">
+        <v>737</v>
+      </c>
+      <c r="B962" t="s" s="3">
         <v>738</v>
-      </c>
-      <c r="B962" t="s" s="3">
-        <v>739</v>
       </c>
       <c r="C962" s="3"/>
       <c r="D962" t="s" s="3">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E962" s="4"/>
       <c r="F962" s="4"/>
     </row>
     <row r="963" ht="13.65" customHeight="1">
       <c r="A963" t="s" s="3">
+        <v>737</v>
+      </c>
+      <c r="B963" t="s" s="3">
         <v>738</v>
-      </c>
-      <c r="B963" t="s" s="3">
-        <v>739</v>
       </c>
       <c r="C963" s="3"/>
       <c r="D963" t="s" s="3">
@@ -19091,10 +19088,10 @@
     </row>
     <row r="964" ht="13.65" customHeight="1">
       <c r="A964" t="s" s="3">
+        <v>737</v>
+      </c>
+      <c r="B964" t="s" s="3">
         <v>738</v>
-      </c>
-      <c r="B964" t="s" s="3">
-        <v>739</v>
       </c>
       <c r="C964" s="3"/>
       <c r="D964" t="s" s="3">
@@ -19105,24 +19102,24 @@
     </row>
     <row r="965" ht="13.65" customHeight="1">
       <c r="A965" t="s" s="3">
+        <v>737</v>
+      </c>
+      <c r="B965" t="s" s="3">
         <v>738</v>
-      </c>
-      <c r="B965" t="s" s="3">
-        <v>739</v>
       </c>
       <c r="C965" s="3"/>
       <c r="D965" t="s" s="3">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E965" s="4"/>
       <c r="F965" s="4"/>
     </row>
     <row r="966" ht="13.65" customHeight="1">
       <c r="A966" t="s" s="3">
+        <v>737</v>
+      </c>
+      <c r="B966" t="s" s="3">
         <v>738</v>
-      </c>
-      <c r="B966" t="s" s="3">
-        <v>739</v>
       </c>
       <c r="C966" s="3"/>
       <c r="D966" t="s" s="3">
@@ -19133,21 +19130,21 @@
     </row>
     <row r="967" ht="13.65" customHeight="1">
       <c r="A967" t="s" s="3">
+        <v>737</v>
+      </c>
+      <c r="B967" t="s" s="3">
         <v>738</v>
-      </c>
-      <c r="B967" t="s" s="3">
-        <v>739</v>
       </c>
       <c r="C967" s="3"/>
       <c r="D967" t="s" s="3">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E967" s="4"/>
       <c r="F967" s="4"/>
     </row>
     <row r="968" ht="13.65" customHeight="1">
       <c r="A968" t="s" s="3">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B968" t="s" s="3">
         <v>7</v>
@@ -19161,21 +19158,21 @@
     </row>
     <row r="969" ht="13.65" customHeight="1">
       <c r="A969" t="s" s="3">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B969" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C969" s="3"/>
       <c r="D969" t="s" s="3">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E969" s="4"/>
       <c r="F969" s="4"/>
     </row>
     <row r="970" ht="13.65" customHeight="1">
       <c r="A970" t="s" s="3">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B970" t="s" s="3">
         <v>444</v>
@@ -19189,35 +19186,35 @@
     </row>
     <row r="971" ht="13.65" customHeight="1">
       <c r="A971" t="s" s="3">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B971" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C971" s="3"/>
       <c r="D971" t="s" s="3">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E971" s="4"/>
       <c r="F971" s="4"/>
     </row>
     <row r="972" ht="13.65" customHeight="1">
       <c r="A972" t="s" s="3">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B972" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C972" s="3"/>
       <c r="D972" t="s" s="3">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E972" s="4"/>
       <c r="F972" s="4"/>
     </row>
     <row r="973" ht="13.65" customHeight="1">
       <c r="A973" t="s" s="3">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B973" t="s" s="3">
         <v>444</v>
@@ -19231,35 +19228,35 @@
     </row>
     <row r="974" ht="13.65" customHeight="1">
       <c r="A974" t="s" s="3">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B974" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C974" s="3"/>
       <c r="D974" t="s" s="3">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E974" s="4"/>
       <c r="F974" s="4"/>
     </row>
     <row r="975" ht="13.65" customHeight="1">
       <c r="A975" t="s" s="3">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B975" t="s" s="3">
         <v>444</v>
       </c>
       <c r="C975" s="3"/>
       <c r="D975" t="s" s="3">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E975" s="4"/>
       <c r="F975" s="4"/>
     </row>
     <row r="976" ht="13.65" customHeight="1">
       <c r="A976" t="s" s="3">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B976" t="s" s="3">
         <v>444</v>
@@ -19273,7 +19270,7 @@
     </row>
     <row r="977" ht="13.65" customHeight="1">
       <c r="A977" t="s" s="3">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B977" t="s" s="3">
         <v>178</v>
@@ -19287,21 +19284,21 @@
     </row>
     <row r="978" ht="13.65" customHeight="1">
       <c r="A978" t="s" s="3">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B978" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C978" s="3"/>
       <c r="D978" t="s" s="3">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E978" s="4"/>
       <c r="F978" s="4"/>
     </row>
     <row r="979" ht="13.65" customHeight="1">
       <c r="A979" t="s" s="3">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B979" t="s" s="3">
         <v>178</v>
@@ -19315,14 +19312,14 @@
     </row>
     <row r="980" ht="13.65" customHeight="1">
       <c r="A980" t="s" s="3">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B980" t="s" s="3">
         <v>178</v>
       </c>
       <c r="C980" s="3"/>
       <c r="D980" t="s" s="3">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E980" s="4"/>
       <c r="F980" s="4"/>
@@ -19336,7 +19333,7 @@
       </c>
       <c r="C981" s="3"/>
       <c r="D981" t="s" s="3">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E981" s="4"/>
       <c r="F981" s="4"/>
@@ -19366,16 +19363,16 @@
   <sheetData>
     <row r="1" ht="13.65" customHeight="1">
       <c r="A1" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="B1" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="B1" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="C1" t="s" s="2">
         <v>1</v>
       </c>
       <c r="D1" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E1" s="4"/>
     </row>
@@ -19384,13 +19381,13 @@
         <v>6</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C2" t="s" s="3">
         <v>7</v>
       </c>
       <c r="D2" t="s" s="3">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E2" s="4"/>
     </row>
@@ -19399,43 +19396,43 @@
         <v>177</v>
       </c>
       <c r="B3" t="s" s="3">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C3" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D3" t="s" s="3">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E3" s="4"/>
     </row>
     <row r="4" ht="13.65" customHeight="1">
       <c r="A4" t="s" s="3">
+        <v>764</v>
+      </c>
+      <c r="B4" t="s" s="6">
         <v>765</v>
-      </c>
-      <c r="B4" t="s" s="6">
-        <v>766</v>
       </c>
       <c r="C4" t="s" s="3">
         <v>447</v>
       </c>
       <c r="D4" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E4" s="4"/>
     </row>
     <row r="5" ht="13.65" customHeight="1">
       <c r="A5" t="s" s="3">
+        <v>767</v>
+      </c>
+      <c r="B5" t="s" s="3">
         <v>768</v>
-      </c>
-      <c r="B5" t="s" s="3">
-        <v>769</v>
       </c>
       <c r="C5" t="s" s="3">
         <v>447</v>
       </c>
       <c r="D5" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E5" s="4"/>
     </row>
@@ -19444,13 +19441,13 @@
         <v>614</v>
       </c>
       <c r="B6" t="s" s="7">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C6" t="s" s="7">
         <v>447</v>
       </c>
       <c r="D6" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E6" s="4"/>
     </row>
@@ -19459,88 +19456,88 @@
         <v>614</v>
       </c>
       <c r="B7" t="s" s="3">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C7" t="s" s="3">
         <v>447</v>
       </c>
       <c r="D7" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E7" s="4"/>
     </row>
     <row r="8" ht="13.65" customHeight="1">
       <c r="A8" t="s" s="7">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B8" t="s" s="7">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C8" t="s" s="7">
         <v>447</v>
       </c>
       <c r="D8" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E8" s="4"/>
     </row>
     <row r="9" ht="13.65" customHeight="1">
       <c r="A9" t="s" s="7">
+        <v>767</v>
+      </c>
+      <c r="B9" t="s" s="7">
         <v>768</v>
-      </c>
-      <c r="B9" t="s" s="7">
-        <v>769</v>
       </c>
       <c r="C9" t="s" s="7">
         <v>447</v>
       </c>
       <c r="D9" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" ht="13.65" customHeight="1">
       <c r="A10" t="s" s="6">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B10" t="s" s="3">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C10" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D10" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E10" s="4"/>
     </row>
     <row r="11" ht="13.65" customHeight="1">
       <c r="A11" t="s" s="3">
+        <v>773</v>
+      </c>
+      <c r="B11" t="s" s="3">
         <v>774</v>
       </c>
-      <c r="B11" t="s" s="3">
-        <v>775</v>
-      </c>
       <c r="C11" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D11" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E11" s="4"/>
     </row>
     <row r="12" ht="13.65" customHeight="1">
       <c r="A12" t="s" s="3">
+        <v>775</v>
+      </c>
+      <c r="B12" t="s" s="3">
         <v>776</v>
       </c>
-      <c r="B12" t="s" s="3">
-        <v>777</v>
-      </c>
       <c r="C12" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D12" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E12" s="4"/>
     </row>
@@ -19549,13 +19546,13 @@
         <v>620</v>
       </c>
       <c r="B13" t="s" s="3">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C13" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D13" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E13" s="4"/>
     </row>
@@ -19564,43 +19561,43 @@
         <v>451</v>
       </c>
       <c r="B14" t="s" s="3">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C14" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D14" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E14" s="4"/>
     </row>
     <row r="15" ht="13.65" customHeight="1">
       <c r="A15" t="s" s="3">
+        <v>779</v>
+      </c>
+      <c r="B15" t="s" s="3">
         <v>780</v>
       </c>
-      <c r="B15" t="s" s="3">
-        <v>781</v>
-      </c>
       <c r="C15" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D15" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E15" s="4"/>
     </row>
     <row r="16" ht="13.65" customHeight="1">
       <c r="A16" t="s" s="3">
+        <v>781</v>
+      </c>
+      <c r="B16" t="s" s="3">
         <v>782</v>
       </c>
-      <c r="B16" t="s" s="3">
-        <v>783</v>
-      </c>
       <c r="C16" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D16" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E16" s="4"/>
     </row>
@@ -19609,13 +19606,13 @@
         <v>520</v>
       </c>
       <c r="B17" t="s" s="3">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C17" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D17" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E17" s="4"/>
     </row>
@@ -19624,43 +19621,43 @@
         <v>546</v>
       </c>
       <c r="B18" t="s" s="3">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C18" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D18" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E18" s="4"/>
     </row>
     <row r="19" ht="13.65" customHeight="1">
       <c r="A19" t="s" s="3">
+        <v>785</v>
+      </c>
+      <c r="B19" t="s" s="3">
         <v>786</v>
       </c>
-      <c r="B19" t="s" s="3">
-        <v>787</v>
-      </c>
       <c r="C19" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D19" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E19" s="4"/>
     </row>
     <row r="20" ht="13.65" customHeight="1">
       <c r="A20" t="s" s="7">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B20" t="s" s="7">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C20" t="s" s="7">
         <v>178</v>
       </c>
       <c r="D20" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E20" s="4"/>
     </row>
@@ -19669,13 +19666,13 @@
         <v>668</v>
       </c>
       <c r="B21" t="s" s="3">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C21" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D21" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E21" s="4"/>
     </row>
@@ -19684,133 +19681,133 @@
         <v>727</v>
       </c>
       <c r="B22" t="s" s="3">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C22" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D22" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E22" s="4"/>
     </row>
     <row r="23" ht="13.65" customHeight="1">
       <c r="A23" t="s" s="3">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B23" t="s" s="3">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C23" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D23" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E23" s="4"/>
     </row>
     <row r="24" ht="13.65" customHeight="1">
       <c r="A24" t="s" s="7">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B24" t="s" s="7">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C24" t="s" s="7">
         <v>178</v>
       </c>
       <c r="D24" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E24" s="4"/>
     </row>
     <row r="25" ht="13.65" customHeight="1">
       <c r="A25" t="s" s="8">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B25" t="s" s="8">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C25" t="s" s="8">
         <v>178</v>
       </c>
       <c r="D25" t="s" s="8">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E25" s="4"/>
     </row>
     <row r="26" ht="13.65" customHeight="1">
       <c r="A26" t="s" s="3">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B26" t="s" s="3">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C26" t="s" s="3">
         <v>178</v>
       </c>
       <c r="D26" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E26" s="4"/>
     </row>
     <row r="27" ht="13.65" customHeight="1">
       <c r="A27" t="s" s="7">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B27" t="s" s="7">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C27" t="s" s="7">
         <v>178</v>
       </c>
       <c r="D27" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E27" s="4"/>
     </row>
     <row r="28" ht="13.65" customHeight="1">
       <c r="A28" t="s" s="3">
+        <v>794</v>
+      </c>
+      <c r="B28" t="s" s="3">
         <v>795</v>
-      </c>
-      <c r="B28" t="s" s="3">
-        <v>796</v>
       </c>
       <c r="C28" t="s" s="3">
         <v>514</v>
       </c>
       <c r="D28" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E28" s="4"/>
     </row>
     <row r="29" ht="13.65" customHeight="1">
       <c r="A29" t="s" s="3">
+        <v>796</v>
+      </c>
+      <c r="B29" t="s" s="3">
         <v>797</v>
-      </c>
-      <c r="B29" t="s" s="3">
-        <v>798</v>
       </c>
       <c r="C29" t="s" s="3">
         <v>514</v>
       </c>
       <c r="D29" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E29" s="4"/>
     </row>
     <row r="30" ht="13.65" customHeight="1">
       <c r="A30" t="s" s="3">
+        <v>798</v>
+      </c>
+      <c r="B30" t="s" s="3">
         <v>799</v>
-      </c>
-      <c r="B30" t="s" s="3">
-        <v>800</v>
       </c>
       <c r="C30" t="s" s="3">
         <v>514</v>
       </c>
       <c r="D30" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E30" s="4"/>
     </row>
@@ -19819,13 +19816,13 @@
         <v>624</v>
       </c>
       <c r="B31" t="s" s="6">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C31" t="s" s="6">
         <v>514</v>
       </c>
       <c r="D31" t="s" s="6">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E31" s="4"/>
     </row>
@@ -19834,28 +19831,28 @@
         <v>705</v>
       </c>
       <c r="B32" t="s" s="3">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C32" t="s" s="3">
         <v>514</v>
       </c>
       <c r="D32" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E32" s="4"/>
     </row>
     <row r="33" ht="13.65" customHeight="1">
       <c r="A33" t="s" s="3">
+        <v>802</v>
+      </c>
+      <c r="B33" t="s" s="3">
         <v>803</v>
-      </c>
-      <c r="B33" t="s" s="3">
-        <v>804</v>
       </c>
       <c r="C33" t="s" s="3">
         <v>514</v>
       </c>
       <c r="D33" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E33" s="4"/>
     </row>
@@ -19864,28 +19861,28 @@
         <v>619</v>
       </c>
       <c r="B34" t="s" s="3">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C34" t="s" s="3">
         <v>514</v>
       </c>
       <c r="D34" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E34" s="4"/>
     </row>
     <row r="35" ht="13.65" customHeight="1">
       <c r="A35" t="s" s="3">
+        <v>805</v>
+      </c>
+      <c r="B35" t="s" s="3">
         <v>806</v>
-      </c>
-      <c r="B35" t="s" s="3">
-        <v>807</v>
       </c>
       <c r="C35" t="s" s="3">
         <v>514</v>
       </c>
       <c r="D35" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E35" s="4"/>
     </row>
@@ -19894,28 +19891,28 @@
         <v>513</v>
       </c>
       <c r="B36" t="s" s="3">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C36" t="s" s="3">
         <v>514</v>
       </c>
       <c r="D36" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E36" s="4"/>
     </row>
     <row r="37" ht="13.65" customHeight="1">
       <c r="A37" t="s" s="7">
+        <v>808</v>
+      </c>
+      <c r="B37" t="s" s="7">
         <v>809</v>
-      </c>
-      <c r="B37" t="s" s="7">
-        <v>810</v>
       </c>
       <c r="C37" t="s" s="7">
         <v>514</v>
       </c>
       <c r="D37" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E37" s="4"/>
     </row>
@@ -19924,13 +19921,13 @@
         <v>576</v>
       </c>
       <c r="B38" t="s" s="3">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C38" t="s" s="3">
         <v>514</v>
       </c>
       <c r="D38" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E38" s="4"/>
     </row>
@@ -19939,13 +19936,13 @@
         <v>624</v>
       </c>
       <c r="B39" t="s" s="7">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C39" t="s" s="7">
         <v>514</v>
       </c>
       <c r="D39" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E39" s="4"/>
     </row>
@@ -19954,13 +19951,13 @@
         <v>699</v>
       </c>
       <c r="B40" t="s" s="3">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C40" t="s" s="3">
         <v>514</v>
       </c>
       <c r="D40" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E40" s="4"/>
     </row>
@@ -19969,118 +19966,118 @@
         <v>705</v>
       </c>
       <c r="B41" t="s" s="7">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C41" t="s" s="7">
         <v>514</v>
       </c>
       <c r="D41" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E41" s="4"/>
     </row>
     <row r="42" ht="13.65" customHeight="1">
       <c r="A42" t="s" s="7">
+        <v>802</v>
+      </c>
+      <c r="B42" t="s" s="7">
         <v>803</v>
-      </c>
-      <c r="B42" t="s" s="7">
-        <v>804</v>
       </c>
       <c r="C42" t="s" s="7">
         <v>514</v>
       </c>
       <c r="D42" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E42" s="4"/>
     </row>
     <row r="43" ht="13.65" customHeight="1">
       <c r="A43" t="s" s="6">
+        <v>814</v>
+      </c>
+      <c r="B43" t="s" s="6">
         <v>815</v>
-      </c>
-      <c r="B43" t="s" s="6">
-        <v>816</v>
       </c>
       <c r="C43" t="s" s="6">
         <v>514</v>
       </c>
       <c r="D43" t="s" s="6">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E43" s="4"/>
     </row>
     <row r="44" ht="13.65" customHeight="1">
       <c r="A44" t="s" s="3">
+        <v>816</v>
+      </c>
+      <c r="B44" t="s" s="3">
         <v>817</v>
-      </c>
-      <c r="B44" t="s" s="3">
-        <v>818</v>
       </c>
       <c r="C44" t="s" s="3">
         <v>514</v>
       </c>
       <c r="D44" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E44" s="4"/>
     </row>
     <row r="45" ht="13.65" customHeight="1">
       <c r="A45" t="s" s="3">
+        <v>818</v>
+      </c>
+      <c r="B45" t="s" s="3">
         <v>819</v>
-      </c>
-      <c r="B45" t="s" s="3">
-        <v>820</v>
       </c>
       <c r="C45" t="s" s="3">
         <v>514</v>
       </c>
       <c r="D45" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E45" s="4"/>
     </row>
     <row r="46" ht="13.65" customHeight="1">
       <c r="A46" t="s" s="7">
+        <v>820</v>
+      </c>
+      <c r="B46" t="s" s="7">
         <v>821</v>
-      </c>
-      <c r="B46" t="s" s="7">
-        <v>822</v>
       </c>
       <c r="C46" t="s" s="7">
         <v>514</v>
       </c>
       <c r="D46" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E46" s="4"/>
     </row>
     <row r="47" ht="13.65" customHeight="1">
       <c r="A47" t="s" s="7">
+        <v>816</v>
+      </c>
+      <c r="B47" t="s" s="7">
         <v>817</v>
-      </c>
-      <c r="B47" t="s" s="7">
-        <v>818</v>
       </c>
       <c r="C47" t="s" s="7">
         <v>514</v>
       </c>
       <c r="D47" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E47" s="4"/>
     </row>
     <row r="48" ht="13.65" customHeight="1">
       <c r="A48" t="s" s="3">
+        <v>822</v>
+      </c>
+      <c r="B48" t="s" s="3">
         <v>823</v>
       </c>
-      <c r="B48" t="s" s="3">
-        <v>824</v>
-      </c>
       <c r="C48" t="s" s="3">
         <v>347</v>
       </c>
       <c r="D48" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E48" s="4"/>
     </row>
@@ -20089,43 +20086,43 @@
         <v>346</v>
       </c>
       <c r="B49" t="s" s="3">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C49" t="s" s="3">
         <v>347</v>
       </c>
       <c r="D49" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E49" s="4"/>
     </row>
     <row r="50" ht="13.65" customHeight="1">
       <c r="A50" t="s" s="3">
+        <v>825</v>
+      </c>
+      <c r="B50" t="s" s="3">
         <v>826</v>
       </c>
-      <c r="B50" t="s" s="3">
-        <v>827</v>
-      </c>
       <c r="C50" t="s" s="3">
         <v>347</v>
       </c>
       <c r="D50" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E50" s="4"/>
     </row>
     <row r="51" ht="13.65" customHeight="1">
       <c r="A51" t="s" s="3">
+        <v>827</v>
+      </c>
+      <c r="B51" t="s" s="3">
         <v>828</v>
       </c>
-      <c r="B51" t="s" s="3">
-        <v>829</v>
-      </c>
       <c r="C51" t="s" s="3">
         <v>347</v>
       </c>
       <c r="D51" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E51" s="4"/>
     </row>
@@ -20134,13 +20131,13 @@
         <v>459</v>
       </c>
       <c r="B52" t="s" s="3">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C52" t="s" s="3">
         <v>347</v>
       </c>
       <c r="D52" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E52" s="4"/>
     </row>
@@ -20149,13 +20146,13 @@
         <v>544</v>
       </c>
       <c r="B53" t="s" s="3">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C53" t="s" s="3">
         <v>347</v>
       </c>
       <c r="D53" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E53" s="4"/>
     </row>
@@ -20164,13 +20161,13 @@
         <v>617</v>
       </c>
       <c r="B54" t="s" s="3">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C54" t="s" s="3">
         <v>347</v>
       </c>
       <c r="D54" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E54" s="4"/>
     </row>
@@ -20179,13 +20176,13 @@
         <v>622</v>
       </c>
       <c r="B55" t="s" s="3">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C55" t="s" s="3">
         <v>347</v>
       </c>
       <c r="D55" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E55" s="4"/>
     </row>
@@ -20194,13 +20191,13 @@
         <v>623</v>
       </c>
       <c r="B56" t="s" s="3">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C56" t="s" s="3">
         <v>347</v>
       </c>
       <c r="D56" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E56" s="4"/>
     </row>
@@ -20209,13 +20206,13 @@
         <v>665</v>
       </c>
       <c r="B57" t="s" s="6">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C57" t="s" s="6">
         <v>347</v>
       </c>
       <c r="D57" t="s" s="6">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E57" s="4"/>
     </row>
@@ -20224,13 +20221,13 @@
         <v>631</v>
       </c>
       <c r="B58" t="s" s="6">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C58" t="s" s="6">
         <v>347</v>
       </c>
       <c r="D58" t="s" s="6">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E58" s="4"/>
     </row>
@@ -20239,58 +20236,58 @@
         <v>667</v>
       </c>
       <c r="B59" t="s" s="6">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C59" t="s" s="6">
         <v>347</v>
       </c>
       <c r="D59" t="s" s="6">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E59" s="4"/>
     </row>
     <row r="60" ht="13.65" customHeight="1">
       <c r="A60" t="s" s="6">
+        <v>837</v>
+      </c>
+      <c r="B60" t="s" s="6">
         <v>838</v>
       </c>
-      <c r="B60" t="s" s="6">
-        <v>839</v>
-      </c>
       <c r="C60" t="s" s="6">
         <v>347</v>
       </c>
       <c r="D60" t="s" s="6">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E60" s="4"/>
     </row>
     <row r="61" ht="13.65" customHeight="1">
       <c r="A61" t="s" s="6">
+        <v>839</v>
+      </c>
+      <c r="B61" t="s" s="3">
         <v>840</v>
       </c>
-      <c r="B61" t="s" s="3">
-        <v>841</v>
-      </c>
       <c r="C61" t="s" s="3">
         <v>347</v>
       </c>
       <c r="D61" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E61" s="4"/>
     </row>
     <row r="62" ht="13.65" customHeight="1">
       <c r="A62" t="s" s="6">
+        <v>841</v>
+      </c>
+      <c r="B62" t="s" s="6">
         <v>842</v>
       </c>
-      <c r="B62" t="s" s="6">
-        <v>843</v>
-      </c>
       <c r="C62" t="s" s="6">
         <v>347</v>
       </c>
       <c r="D62" t="s" s="6">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E62" s="4"/>
     </row>
@@ -20299,13 +20296,13 @@
         <v>711</v>
       </c>
       <c r="B63" t="s" s="3">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C63" t="s" s="3">
         <v>347</v>
       </c>
       <c r="D63" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E63" s="4"/>
     </row>
@@ -20314,28 +20311,28 @@
         <v>696</v>
       </c>
       <c r="B64" t="s" s="3">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C64" t="s" s="3">
         <v>347</v>
       </c>
       <c r="D64" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E64" s="4"/>
     </row>
     <row r="65" ht="13.65" customHeight="1">
       <c r="A65" t="s" s="3">
+        <v>845</v>
+      </c>
+      <c r="B65" t="s" s="3">
         <v>846</v>
       </c>
-      <c r="B65" t="s" s="3">
-        <v>847</v>
-      </c>
       <c r="C65" t="s" s="3">
         <v>347</v>
       </c>
       <c r="D65" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E65" s="4"/>
     </row>
@@ -20344,13 +20341,13 @@
         <v>696</v>
       </c>
       <c r="B66" t="s" s="7">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C66" t="s" s="7">
         <v>347</v>
       </c>
       <c r="D66" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E66" s="4"/>
     </row>
@@ -20359,13 +20356,13 @@
         <v>711</v>
       </c>
       <c r="B67" t="s" s="7">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C67" t="s" s="7">
         <v>347</v>
       </c>
       <c r="D67" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E67" s="4"/>
     </row>
@@ -20374,28 +20371,28 @@
         <v>574</v>
       </c>
       <c r="B68" t="s" s="3">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C68" t="s" s="3">
         <v>457</v>
       </c>
       <c r="D68" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E68" s="4"/>
     </row>
     <row r="69" ht="13.65" customHeight="1">
       <c r="A69" t="s" s="6">
+        <v>850</v>
+      </c>
+      <c r="B69" t="s" s="6">
         <v>851</v>
       </c>
-      <c r="B69" t="s" s="6">
+      <c r="C69" t="s" s="6">
         <v>852</v>
       </c>
-      <c r="C69" t="s" s="6">
-        <v>853</v>
-      </c>
       <c r="D69" t="s" s="6">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E69" s="4"/>
     </row>
@@ -20404,118 +20401,118 @@
         <v>456</v>
       </c>
       <c r="B70" t="s" s="3">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C70" t="s" s="3">
         <v>457</v>
       </c>
       <c r="D70" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E70" s="4"/>
     </row>
     <row r="71" ht="13.65" customHeight="1">
       <c r="A71" t="s" s="3">
+        <v>854</v>
+      </c>
+      <c r="B71" t="s" s="3">
         <v>855</v>
-      </c>
-      <c r="B71" t="s" s="3">
-        <v>856</v>
       </c>
       <c r="C71" t="s" s="3">
         <v>457</v>
       </c>
       <c r="D71" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E71" s="4"/>
     </row>
     <row r="72" ht="13.65" customHeight="1">
       <c r="A72" t="s" s="3">
+        <v>856</v>
+      </c>
+      <c r="B72" t="s" s="3">
         <v>857</v>
-      </c>
-      <c r="B72" t="s" s="3">
-        <v>858</v>
       </c>
       <c r="C72" t="s" s="3">
         <v>457</v>
       </c>
       <c r="D72" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E72" s="4"/>
     </row>
     <row r="73" ht="13.65" customHeight="1">
       <c r="A73" t="s" s="3">
+        <v>858</v>
+      </c>
+      <c r="B73" t="s" s="3">
         <v>859</v>
-      </c>
-      <c r="B73" t="s" s="3">
-        <v>860</v>
       </c>
       <c r="C73" t="s" s="3">
         <v>457</v>
       </c>
       <c r="D73" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E73" s="4"/>
     </row>
     <row r="74" ht="13.65" customHeight="1">
       <c r="A74" t="s" s="3">
+        <v>737</v>
+      </c>
+      <c r="B74" t="s" s="3">
+        <v>860</v>
+      </c>
+      <c r="C74" t="s" s="3">
         <v>738</v>
       </c>
-      <c r="B74" t="s" s="3">
-        <v>861</v>
-      </c>
-      <c r="C74" t="s" s="3">
-        <v>739</v>
-      </c>
       <c r="D74" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E74" s="4"/>
     </row>
     <row r="75" ht="13.65" customHeight="1">
       <c r="A75" t="s" s="3">
+        <v>861</v>
+      </c>
+      <c r="B75" t="s" s="3">
         <v>862</v>
       </c>
-      <c r="B75" t="s" s="3">
-        <v>863</v>
-      </c>
       <c r="C75" t="s" s="3">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D75" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E75" s="4"/>
     </row>
     <row r="76" ht="13.65" customHeight="1">
       <c r="A76" t="s" s="3">
+        <v>863</v>
+      </c>
+      <c r="B76" t="s" s="3">
         <v>864</v>
       </c>
-      <c r="B76" t="s" s="3">
-        <v>865</v>
-      </c>
       <c r="C76" t="s" s="3">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D76" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E76" s="4"/>
     </row>
     <row r="77" ht="13.65" customHeight="1">
       <c r="A77" t="s" s="7">
+        <v>737</v>
+      </c>
+      <c r="B77" t="s" s="7">
+        <v>860</v>
+      </c>
+      <c r="C77" t="s" s="7">
         <v>738</v>
       </c>
-      <c r="B77" t="s" s="7">
-        <v>861</v>
-      </c>
-      <c r="C77" t="s" s="7">
-        <v>739</v>
-      </c>
       <c r="D77" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E77" s="4"/>
     </row>
@@ -20524,28 +20521,28 @@
         <v>618</v>
       </c>
       <c r="B78" t="s" s="3">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C78" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D78" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E78" s="4"/>
     </row>
     <row r="79" ht="13.65" customHeight="1">
       <c r="A79" t="s" s="8">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B79" t="s" s="8">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C79" t="s" s="8">
         <v>444</v>
       </c>
       <c r="D79" t="s" s="8">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E79" s="4"/>
     </row>
@@ -20554,43 +20551,43 @@
         <v>443</v>
       </c>
       <c r="B80" t="s" s="3">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C80" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D80" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E80" s="4"/>
     </row>
     <row r="81" ht="13.65" customHeight="1">
       <c r="A81" t="s" s="3">
+        <v>868</v>
+      </c>
+      <c r="B81" t="s" s="3">
         <v>869</v>
-      </c>
-      <c r="B81" t="s" s="3">
-        <v>870</v>
       </c>
       <c r="C81" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D81" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E81" s="4"/>
     </row>
     <row r="82" ht="13.65" customHeight="1">
       <c r="A82" t="s" s="3">
+        <v>870</v>
+      </c>
+      <c r="B82" t="s" s="3">
         <v>871</v>
-      </c>
-      <c r="B82" t="s" s="3">
-        <v>872</v>
       </c>
       <c r="C82" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D82" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E82" s="4"/>
     </row>
@@ -20599,28 +20596,28 @@
         <v>627</v>
       </c>
       <c r="B83" t="s" s="6">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C83" t="s" s="6">
         <v>444</v>
       </c>
       <c r="D83" t="s" s="6">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E83" s="4"/>
     </row>
     <row r="84" ht="13.65" customHeight="1">
       <c r="A84" t="s" s="3">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B84" t="s" s="3">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C84" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D84" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E84" s="4"/>
     </row>
@@ -20629,13 +20626,13 @@
         <v>449</v>
       </c>
       <c r="B85" t="s" s="3">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C85" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D85" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E85" s="4"/>
     </row>
@@ -20644,43 +20641,43 @@
         <v>454</v>
       </c>
       <c r="B86" t="s" s="3">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C86" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D86" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E86" s="4"/>
     </row>
     <row r="87" ht="13.65" customHeight="1">
       <c r="A87" t="s" s="3">
+        <v>876</v>
+      </c>
+      <c r="B87" t="s" s="3">
         <v>877</v>
-      </c>
-      <c r="B87" t="s" s="3">
-        <v>878</v>
       </c>
       <c r="C87" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D87" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E87" s="4"/>
     </row>
     <row r="88" ht="13.65" customHeight="1">
       <c r="A88" t="s" s="3">
+        <v>878</v>
+      </c>
+      <c r="B88" t="s" s="3">
         <v>879</v>
-      </c>
-      <c r="B88" t="s" s="3">
-        <v>880</v>
       </c>
       <c r="C88" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D88" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E88" s="4"/>
     </row>
@@ -20689,13 +20686,13 @@
         <v>572</v>
       </c>
       <c r="B89" t="s" s="3">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C89" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D89" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E89" s="4"/>
     </row>
@@ -20704,13 +20701,13 @@
         <v>555</v>
       </c>
       <c r="B90" t="s" s="3">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C90" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D90" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E90" s="4"/>
     </row>
@@ -20719,13 +20716,13 @@
         <v>573</v>
       </c>
       <c r="B91" t="s" s="3">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C91" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D91" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E91" s="4"/>
     </row>
@@ -20734,28 +20731,28 @@
         <v>611</v>
       </c>
       <c r="B92" t="s" s="3">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C92" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D92" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E92" s="4"/>
     </row>
     <row r="93" ht="13.65" customHeight="1">
       <c r="A93" t="s" s="3">
+        <v>884</v>
+      </c>
+      <c r="B93" t="s" s="3">
         <v>885</v>
-      </c>
-      <c r="B93" t="s" s="3">
-        <v>886</v>
       </c>
       <c r="C93" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D93" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E93" s="4"/>
     </row>
@@ -20764,13 +20761,13 @@
         <v>629</v>
       </c>
       <c r="B94" t="s" s="6">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C94" t="s" s="6">
         <v>444</v>
       </c>
       <c r="D94" t="s" s="6">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E94" s="4"/>
     </row>
@@ -20779,58 +20776,58 @@
         <v>663</v>
       </c>
       <c r="B95" t="s" s="6">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C95" t="s" s="6">
         <v>444</v>
       </c>
       <c r="D95" t="s" s="6">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E95" s="4"/>
     </row>
     <row r="96" ht="13.65" customHeight="1">
       <c r="A96" t="s" s="3">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B96" t="s" s="3">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C96" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D96" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E96" s="4"/>
     </row>
     <row r="97" ht="13.65" customHeight="1">
       <c r="A97" t="s" s="3">
+        <v>889</v>
+      </c>
+      <c r="B97" t="s" s="3">
         <v>890</v>
-      </c>
-      <c r="B97" t="s" s="3">
-        <v>891</v>
       </c>
       <c r="C97" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D97" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E97" s="4"/>
     </row>
     <row r="98" ht="13.65" customHeight="1">
       <c r="A98" t="s" s="3">
+        <v>891</v>
+      </c>
+      <c r="B98" t="s" s="3">
         <v>892</v>
-      </c>
-      <c r="B98" t="s" s="3">
-        <v>893</v>
       </c>
       <c r="C98" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D98" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E98" s="4"/>
     </row>
@@ -20839,88 +20836,88 @@
         <v>729</v>
       </c>
       <c r="B99" t="s" s="3">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C99" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D99" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E99" s="4"/>
     </row>
     <row r="100" ht="13.65" customHeight="1">
       <c r="A100" t="s" s="7">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B100" t="s" s="7">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C100" t="s" s="7">
         <v>444</v>
       </c>
       <c r="D100" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E100" s="4"/>
     </row>
     <row r="101" ht="13.65" customHeight="1">
       <c r="A101" t="s" s="3">
+        <v>895</v>
+      </c>
+      <c r="B101" t="s" s="3">
         <v>896</v>
-      </c>
-      <c r="B101" t="s" s="3">
-        <v>897</v>
       </c>
       <c r="C101" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D101" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E101" s="4"/>
     </row>
     <row r="102" ht="13.65" customHeight="1">
       <c r="A102" t="s" s="3">
+        <v>897</v>
+      </c>
+      <c r="B102" t="s" s="3">
         <v>898</v>
-      </c>
-      <c r="B102" t="s" s="3">
-        <v>899</v>
       </c>
       <c r="C102" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D102" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E102" s="4"/>
     </row>
     <row r="103" ht="13.65" customHeight="1">
       <c r="A103" t="s" s="3">
+        <v>899</v>
+      </c>
+      <c r="B103" t="s" s="3">
         <v>900</v>
-      </c>
-      <c r="B103" t="s" s="3">
-        <v>901</v>
       </c>
       <c r="C103" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D103" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E103" s="4"/>
     </row>
     <row r="104" ht="13.65" customHeight="1">
       <c r="A104" t="s" s="3">
+        <v>901</v>
+      </c>
+      <c r="B104" t="s" s="3">
         <v>902</v>
-      </c>
-      <c r="B104" t="s" s="3">
-        <v>903</v>
       </c>
       <c r="C104" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D104" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E104" s="4"/>
     </row>
@@ -20929,13 +20926,13 @@
         <v>523</v>
       </c>
       <c r="B105" t="s" s="3">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C105" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D105" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E105" s="4"/>
     </row>
@@ -20944,208 +20941,208 @@
         <v>730</v>
       </c>
       <c r="B106" t="s" s="3">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C106" t="s" s="3">
         <v>444</v>
       </c>
       <c r="D106" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E106" s="4"/>
     </row>
     <row r="107" ht="13.65" customHeight="1">
       <c r="A107" t="s" s="7">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B107" t="s" s="7">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C107" t="s" s="7">
         <v>444</v>
       </c>
       <c r="D107" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E107" s="4"/>
     </row>
     <row r="108" ht="13.65" customHeight="1">
       <c r="A108" t="s" s="3">
+        <v>906</v>
+      </c>
+      <c r="B108" t="s" s="3">
         <v>907</v>
-      </c>
-      <c r="B108" t="s" s="3">
-        <v>908</v>
       </c>
       <c r="C108" t="s" s="3">
         <v>7</v>
       </c>
       <c r="D108" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E108" s="4"/>
     </row>
     <row r="109" ht="13.65" customHeight="1">
       <c r="A109" t="s" s="6">
+        <v>908</v>
+      </c>
+      <c r="B109" t="s" s="3">
         <v>909</v>
-      </c>
-      <c r="B109" t="s" s="3">
-        <v>910</v>
       </c>
       <c r="C109" t="s" s="3">
         <v>7</v>
       </c>
       <c r="D109" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E109" s="4"/>
     </row>
     <row r="110" ht="13.65" customHeight="1">
       <c r="A110" t="s" s="7">
+        <v>910</v>
+      </c>
+      <c r="B110" t="s" s="7">
         <v>911</v>
-      </c>
-      <c r="B110" t="s" s="7">
-        <v>912</v>
       </c>
       <c r="C110" t="s" s="7">
         <v>7</v>
       </c>
       <c r="D110" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E110" s="4"/>
     </row>
     <row r="111" ht="13.65" customHeight="1">
       <c r="A111" t="s" s="3">
+        <v>912</v>
+      </c>
+      <c r="B111" t="s" s="3">
         <v>913</v>
-      </c>
-      <c r="B111" t="s" s="3">
-        <v>914</v>
       </c>
       <c r="C111" t="s" s="3">
         <v>7</v>
       </c>
       <c r="D111" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E111" s="4"/>
     </row>
     <row r="112" ht="13.65" customHeight="1">
       <c r="A112" t="s" s="3">
+        <v>914</v>
+      </c>
+      <c r="B112" t="s" s="3">
         <v>915</v>
-      </c>
-      <c r="B112" t="s" s="3">
-        <v>916</v>
       </c>
       <c r="C112" t="s" s="3">
         <v>7</v>
       </c>
       <c r="D112" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E112" s="4"/>
     </row>
     <row r="113" ht="13.65" customHeight="1">
       <c r="A113" t="s" s="3">
+        <v>916</v>
+      </c>
+      <c r="B113" t="s" s="3">
         <v>917</v>
-      </c>
-      <c r="B113" t="s" s="3">
-        <v>918</v>
       </c>
       <c r="C113" t="s" s="3">
         <v>7</v>
       </c>
       <c r="D113" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E113" s="4"/>
     </row>
     <row r="114" ht="13.65" customHeight="1">
       <c r="A114" t="s" s="7">
+        <v>906</v>
+      </c>
+      <c r="B114" t="s" s="7">
         <v>907</v>
-      </c>
-      <c r="B114" t="s" s="7">
-        <v>908</v>
       </c>
       <c r="C114" t="s" s="7">
         <v>7</v>
       </c>
       <c r="D114" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E114" s="4"/>
     </row>
     <row r="115" ht="13.65" customHeight="1">
       <c r="A115" t="s" s="3">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B115" t="s" s="3">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C115" t="s" s="3">
         <v>7</v>
       </c>
       <c r="D115" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E115" s="4"/>
     </row>
     <row r="116" ht="13.65" customHeight="1">
       <c r="A116" t="s" s="3">
+        <v>919</v>
+      </c>
+      <c r="B116" t="s" s="3">
         <v>920</v>
-      </c>
-      <c r="B116" t="s" s="3">
-        <v>921</v>
       </c>
       <c r="C116" t="s" s="3">
         <v>7</v>
       </c>
       <c r="D116" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E116" s="4"/>
     </row>
     <row r="117" ht="13.65" customHeight="1">
       <c r="A117" t="s" s="3">
+        <v>921</v>
+      </c>
+      <c r="B117" t="s" s="3">
         <v>922</v>
-      </c>
-      <c r="B117" t="s" s="3">
-        <v>923</v>
       </c>
       <c r="C117" t="s" s="3">
         <v>7</v>
       </c>
       <c r="D117" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E117" s="4"/>
     </row>
     <row r="118" ht="13.65" customHeight="1">
       <c r="A118" t="s" s="6">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B118" t="s" s="6">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="C118" t="s" s="6">
         <v>7</v>
       </c>
       <c r="D118" t="s" s="6">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E118" s="4"/>
     </row>
     <row r="119" ht="13.65" customHeight="1">
       <c r="A119" t="s" s="7">
+        <v>924</v>
+      </c>
+      <c r="B119" t="s" s="7">
         <v>925</v>
-      </c>
-      <c r="B119" t="s" s="7">
-        <v>926</v>
       </c>
       <c r="C119" t="s" s="7">
         <v>7</v>
       </c>
       <c r="D119" t="s" s="7">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E119" s="4"/>
     </row>
@@ -21154,13 +21151,13 @@
         <v>701</v>
       </c>
       <c r="B120" t="s" s="3">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C120" t="s" s="3">
         <v>7</v>
       </c>
       <c r="D120" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E120" s="4"/>
     </row>
@@ -21169,13 +21166,13 @@
         <v>703</v>
       </c>
       <c r="B121" t="s" s="3">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C121" t="s" s="3">
         <v>7</v>
       </c>
       <c r="D121" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E121" s="4"/>
     </row>
@@ -21184,13 +21181,13 @@
         <v>446</v>
       </c>
       <c r="B122" t="s" s="3">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C122" t="s" s="3">
         <v>447</v>
       </c>
       <c r="D122" t="s" s="3">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E122" s="4"/>
     </row>
@@ -21217,13 +21214,13 @@
   <sheetData>
     <row r="1" ht="13.65" customHeight="1">
       <c r="A1" t="s" s="2">
+        <v>929</v>
+      </c>
+      <c r="B1" t="s" s="2">
         <v>930</v>
       </c>
-      <c r="B1" t="s" s="2">
+      <c r="C1" t="s" s="2">
         <v>931</v>
-      </c>
-      <c r="C1" t="s" s="2">
-        <v>932</v>
       </c>
       <c r="D1" s="10"/>
       <c r="E1" s="11"/>
@@ -21233,10 +21230,10 @@
         <v>13</v>
       </c>
       <c r="B2" t="s" s="3">
+        <v>932</v>
+      </c>
+      <c r="C2" t="s" s="3">
         <v>933</v>
-      </c>
-      <c r="C2" t="s" s="3">
-        <v>934</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="13"/>
@@ -21246,10 +21243,10 @@
         <v>86</v>
       </c>
       <c r="B3" t="s" s="3">
+        <v>934</v>
+      </c>
+      <c r="C3" t="s" s="3">
         <v>935</v>
-      </c>
-      <c r="C3" t="s" s="3">
-        <v>936</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="13"/>
@@ -21259,10 +21256,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s" s="3">
+        <v>936</v>
+      </c>
+      <c r="C4" t="s" s="3">
         <v>937</v>
-      </c>
-      <c r="C4" t="s" s="3">
-        <v>938</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="13"/>
@@ -21272,23 +21269,23 @@
         <v>10</v>
       </c>
       <c r="B5" t="s" s="3">
+        <v>938</v>
+      </c>
+      <c r="C5" t="s" s="3">
         <v>939</v>
-      </c>
-      <c r="C5" t="s" s="3">
-        <v>940</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="13"/>
     </row>
     <row r="6" ht="13.65" customHeight="1">
       <c r="A6" t="s" s="3">
+        <v>940</v>
+      </c>
+      <c r="B6" t="s" s="3">
         <v>941</v>
       </c>
-      <c r="B6" t="s" s="3">
+      <c r="C6" t="s" s="3">
         <v>942</v>
-      </c>
-      <c r="C6" t="s" s="3">
-        <v>943</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="13"/>
@@ -21298,10 +21295,10 @@
         <v>17</v>
       </c>
       <c r="B7" t="s" s="3">
+        <v>943</v>
+      </c>
+      <c r="C7" t="s" s="3">
         <v>944</v>
-      </c>
-      <c r="C7" t="s" s="3">
-        <v>945</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="13"/>
@@ -21311,10 +21308,10 @@
         <v>33</v>
       </c>
       <c r="B8" t="s" s="3">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C8" t="s" s="3">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="13"/>
@@ -21324,23 +21321,23 @@
         <v>19</v>
       </c>
       <c r="B9" t="s" s="3">
+        <v>946</v>
+      </c>
+      <c r="C9" t="s" s="3">
         <v>947</v>
-      </c>
-      <c r="C9" t="s" s="3">
-        <v>948</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="13"/>
     </row>
     <row r="10" ht="13.65" customHeight="1">
       <c r="A10" t="s" s="3">
+        <v>948</v>
+      </c>
+      <c r="B10" t="s" s="3">
         <v>949</v>
       </c>
-      <c r="B10" t="s" s="3">
+      <c r="C10" t="s" s="3">
         <v>950</v>
-      </c>
-      <c r="C10" t="s" s="3">
-        <v>951</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="13"/>
@@ -21350,49 +21347,49 @@
         <v>132</v>
       </c>
       <c r="B11" t="s" s="3">
+        <v>951</v>
+      </c>
+      <c r="C11" t="s" s="3">
         <v>952</v>
-      </c>
-      <c r="C11" t="s" s="3">
-        <v>953</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="13"/>
     </row>
     <row r="12" ht="13.65" customHeight="1">
       <c r="A12" t="s" s="3">
+        <v>953</v>
+      </c>
+      <c r="B12" t="s" s="3">
         <v>954</v>
       </c>
-      <c r="B12" t="s" s="3">
+      <c r="C12" t="s" s="3">
         <v>955</v>
-      </c>
-      <c r="C12" t="s" s="3">
-        <v>956</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="13"/>
     </row>
     <row r="13" ht="13.65" customHeight="1">
       <c r="A13" t="s" s="3">
+        <v>956</v>
+      </c>
+      <c r="B13" t="s" s="3">
         <v>957</v>
       </c>
-      <c r="B13" t="s" s="3">
+      <c r="C13" t="s" s="3">
         <v>958</v>
-      </c>
-      <c r="C13" t="s" s="3">
-        <v>959</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="13"/>
     </row>
     <row r="14" ht="13.65" customHeight="1">
       <c r="A14" t="s" s="3">
+        <v>959</v>
+      </c>
+      <c r="B14" t="s" s="3">
         <v>960</v>
       </c>
-      <c r="B14" t="s" s="3">
-        <v>961</v>
-      </c>
       <c r="C14" t="s" s="3">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="13"/>
@@ -21402,10 +21399,10 @@
         <v>150</v>
       </c>
       <c r="B15" t="s" s="3">
+        <v>961</v>
+      </c>
+      <c r="C15" t="s" s="3">
         <v>962</v>
-      </c>
-      <c r="C15" t="s" s="3">
-        <v>963</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="13"/>
@@ -21415,10 +21412,10 @@
         <v>25</v>
       </c>
       <c r="B16" t="s" s="3">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="C16" t="s" s="3">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="D16" s="12"/>
       <c r="E16" s="13"/>
@@ -21428,10 +21425,10 @@
         <v>27</v>
       </c>
       <c r="B17" t="s" s="3">
+        <v>964</v>
+      </c>
+      <c r="C17" t="s" s="3">
         <v>965</v>
-      </c>
-      <c r="C17" t="s" s="3">
-        <v>966</v>
       </c>
       <c r="D17" s="12"/>
       <c r="E17" s="13"/>
@@ -21441,23 +21438,23 @@
         <v>198</v>
       </c>
       <c r="B18" t="s" s="3">
+        <v>966</v>
+      </c>
+      <c r="C18" t="s" s="3">
         <v>967</v>
-      </c>
-      <c r="C18" t="s" s="3">
-        <v>968</v>
       </c>
       <c r="D18" s="12"/>
       <c r="E18" s="13"/>
     </row>
     <row r="19" ht="13.65" customHeight="1">
       <c r="A19" t="s" s="3">
+        <v>968</v>
+      </c>
+      <c r="B19" t="s" s="3">
         <v>969</v>
       </c>
-      <c r="B19" t="s" s="3">
+      <c r="C19" t="s" s="3">
         <v>970</v>
-      </c>
-      <c r="C19" t="s" s="3">
-        <v>971</v>
       </c>
       <c r="D19" s="12"/>
       <c r="E19" s="13"/>
@@ -21467,10 +21464,10 @@
         <v>85</v>
       </c>
       <c r="B20" t="s" s="3">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C20" t="s" s="3">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D20" s="12"/>
       <c r="E20" s="13"/>
@@ -21480,23 +21477,23 @@
         <v>126</v>
       </c>
       <c r="B21" t="s" s="3">
+        <v>972</v>
+      </c>
+      <c r="C21" t="s" s="3">
         <v>973</v>
-      </c>
-      <c r="C21" t="s" s="3">
-        <v>974</v>
       </c>
       <c r="D21" s="12"/>
       <c r="E21" s="13"/>
     </row>
     <row r="22" ht="13.65" customHeight="1">
       <c r="A22" t="s" s="3">
+        <v>974</v>
+      </c>
+      <c r="B22" t="s" s="3">
         <v>975</v>
       </c>
-      <c r="B22" t="s" s="3">
+      <c r="C22" t="s" s="3">
         <v>976</v>
-      </c>
-      <c r="C22" t="s" s="3">
-        <v>977</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="13"/>
@@ -21506,10 +21503,10 @@
         <v>99</v>
       </c>
       <c r="B23" t="s" s="3">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C23" t="s" s="3">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="13"/>
@@ -21519,23 +21516,23 @@
         <v>38</v>
       </c>
       <c r="B24" t="s" s="3">
+        <v>978</v>
+      </c>
+      <c r="C24" t="s" s="3">
         <v>979</v>
-      </c>
-      <c r="C24" t="s" s="3">
-        <v>980</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="13"/>
     </row>
     <row r="25" ht="13.65" customHeight="1">
       <c r="A25" t="s" s="3">
+        <v>980</v>
+      </c>
+      <c r="B25" t="s" s="3">
         <v>981</v>
       </c>
-      <c r="B25" t="s" s="3">
+      <c r="C25" t="s" s="3">
         <v>982</v>
-      </c>
-      <c r="C25" t="s" s="3">
-        <v>983</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="13"/>
@@ -21545,10 +21542,10 @@
         <v>79</v>
       </c>
       <c r="B26" t="s" s="3">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C26" t="s" s="3">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="13"/>
@@ -21558,75 +21555,75 @@
         <v>155</v>
       </c>
       <c r="B27" t="s" s="3">
+        <v>984</v>
+      </c>
+      <c r="C27" t="s" s="3">
         <v>985</v>
-      </c>
-      <c r="C27" t="s" s="3">
-        <v>986</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="13"/>
     </row>
     <row r="28" ht="13.65" customHeight="1">
       <c r="A28" t="s" s="3">
+        <v>986</v>
+      </c>
+      <c r="B28" t="s" s="3">
         <v>987</v>
       </c>
-      <c r="B28" t="s" s="3">
+      <c r="C28" t="s" s="3">
         <v>988</v>
-      </c>
-      <c r="C28" t="s" s="3">
-        <v>989</v>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="13"/>
     </row>
     <row r="29" ht="13.65" customHeight="1">
       <c r="A29" t="s" s="3">
+        <v>989</v>
+      </c>
+      <c r="B29" t="s" s="3">
         <v>990</v>
       </c>
-      <c r="B29" t="s" s="3">
+      <c r="C29" t="s" s="3">
         <v>991</v>
-      </c>
-      <c r="C29" t="s" s="3">
-        <v>992</v>
       </c>
       <c r="D29" s="12"/>
       <c r="E29" s="13"/>
     </row>
     <row r="30" ht="13.65" customHeight="1">
       <c r="A30" t="s" s="3">
+        <v>992</v>
+      </c>
+      <c r="B30" t="s" s="3">
         <v>993</v>
       </c>
-      <c r="B30" t="s" s="3">
+      <c r="C30" t="s" s="3">
         <v>994</v>
-      </c>
-      <c r="C30" t="s" s="3">
-        <v>995</v>
       </c>
       <c r="D30" s="12"/>
       <c r="E30" s="13"/>
     </row>
     <row r="31" ht="13.65" customHeight="1">
       <c r="A31" t="s" s="3">
+        <v>995</v>
+      </c>
+      <c r="B31" t="s" s="3">
         <v>996</v>
       </c>
-      <c r="B31" t="s" s="3">
+      <c r="C31" t="s" s="3">
         <v>997</v>
-      </c>
-      <c r="C31" t="s" s="3">
-        <v>998</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="13"/>
     </row>
     <row r="32" ht="13.65" customHeight="1">
       <c r="A32" t="s" s="3">
+        <v>998</v>
+      </c>
+      <c r="B32" t="s" s="3">
         <v>999</v>
       </c>
-      <c r="B32" t="s" s="3">
+      <c r="C32" t="s" s="3">
         <v>1000</v>
-      </c>
-      <c r="C32" t="s" s="3">
-        <v>1001</v>
       </c>
       <c r="D32" s="12"/>
       <c r="E32" s="13"/>
@@ -21636,23 +21633,23 @@
         <v>192</v>
       </c>
       <c r="B33" t="s" s="3">
+        <v>1001</v>
+      </c>
+      <c r="C33" t="s" s="3">
         <v>1002</v>
-      </c>
-      <c r="C33" t="s" s="3">
-        <v>1003</v>
       </c>
       <c r="D33" s="12"/>
       <c r="E33" s="13"/>
     </row>
     <row r="34" ht="13.65" customHeight="1">
       <c r="A34" t="s" s="3">
+        <v>1003</v>
+      </c>
+      <c r="B34" t="s" s="3">
         <v>1004</v>
       </c>
-      <c r="B34" t="s" s="3">
-        <v>1005</v>
-      </c>
       <c r="C34" t="s" s="3">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D34" s="12"/>
       <c r="E34" s="13"/>
@@ -21662,10 +21659,10 @@
         <v>87</v>
       </c>
       <c r="B35" t="s" s="3">
+        <v>1005</v>
+      </c>
+      <c r="C35" t="s" s="3">
         <v>1006</v>
-      </c>
-      <c r="C35" t="s" s="3">
-        <v>1007</v>
       </c>
       <c r="D35" s="12"/>
       <c r="E35" s="13"/>
@@ -21675,49 +21672,49 @@
         <v>278</v>
       </c>
       <c r="B36" t="s" s="3">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="C36" t="s" s="3">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D36" s="12"/>
       <c r="E36" s="13"/>
     </row>
     <row r="37" ht="13.65" customHeight="1">
       <c r="A37" t="s" s="3">
+        <v>1008</v>
+      </c>
+      <c r="B37" t="s" s="3">
         <v>1009</v>
       </c>
-      <c r="B37" t="s" s="3">
-        <v>1010</v>
-      </c>
       <c r="C37" t="s" s="3">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="D37" s="12"/>
       <c r="E37" s="13"/>
     </row>
     <row r="38" ht="13.65" customHeight="1">
       <c r="A38" t="s" s="3">
+        <v>1010</v>
+      </c>
+      <c r="B38" t="s" s="3">
         <v>1011</v>
       </c>
-      <c r="B38" t="s" s="3">
-        <v>1012</v>
-      </c>
       <c r="C38" t="s" s="3">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D38" s="12"/>
       <c r="E38" s="13"/>
     </row>
     <row r="39" ht="13.65" customHeight="1">
       <c r="A39" t="s" s="3">
+        <v>1012</v>
+      </c>
+      <c r="B39" t="s" s="3">
         <v>1013</v>
       </c>
-      <c r="B39" t="s" s="3">
-        <v>1014</v>
-      </c>
       <c r="C39" t="s" s="3">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="D39" s="12"/>
       <c r="E39" s="13"/>
@@ -21727,75 +21724,75 @@
         <v>205</v>
       </c>
       <c r="B40" t="s" s="3">
+        <v>1014</v>
+      </c>
+      <c r="C40" t="s" s="3">
         <v>1015</v>
-      </c>
-      <c r="C40" t="s" s="3">
-        <v>1016</v>
       </c>
       <c r="D40" s="12"/>
       <c r="E40" s="13"/>
     </row>
     <row r="41" ht="13.65" customHeight="1">
       <c r="A41" t="s" s="3">
+        <v>1016</v>
+      </c>
+      <c r="B41" t="s" s="3">
         <v>1017</v>
       </c>
-      <c r="B41" t="s" s="3">
+      <c r="C41" t="s" s="3">
         <v>1018</v>
-      </c>
-      <c r="C41" t="s" s="3">
-        <v>1019</v>
       </c>
       <c r="D41" s="12"/>
       <c r="E41" s="13"/>
     </row>
     <row r="42" ht="13.65" customHeight="1">
       <c r="A42" t="s" s="3">
+        <v>1019</v>
+      </c>
+      <c r="B42" t="s" s="3">
         <v>1020</v>
       </c>
-      <c r="B42" t="s" s="3">
+      <c r="C42" t="s" s="3">
         <v>1021</v>
-      </c>
-      <c r="C42" t="s" s="3">
-        <v>1022</v>
       </c>
       <c r="D42" s="12"/>
       <c r="E42" s="13"/>
     </row>
     <row r="43" ht="13.65" customHeight="1">
       <c r="A43" t="s" s="3">
+        <v>1022</v>
+      </c>
+      <c r="B43" t="s" s="3">
         <v>1023</v>
       </c>
-      <c r="B43" t="s" s="3">
+      <c r="C43" t="s" s="3">
         <v>1024</v>
-      </c>
-      <c r="C43" t="s" s="3">
-        <v>1025</v>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="13"/>
     </row>
     <row r="44" ht="13.65" customHeight="1">
       <c r="A44" t="s" s="3">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B44" t="s" s="3">
+        <v>1005</v>
+      </c>
+      <c r="C44" t="s" s="3">
         <v>1006</v>
-      </c>
-      <c r="C44" t="s" s="3">
-        <v>1007</v>
       </c>
       <c r="D44" s="12"/>
       <c r="E44" s="13"/>
     </row>
     <row r="45" ht="13.65" customHeight="1">
       <c r="A45" t="s" s="3">
+        <v>1026</v>
+      </c>
+      <c r="B45" t="s" s="3">
         <v>1027</v>
       </c>
-      <c r="B45" t="s" s="3">
+      <c r="C45" t="s" s="3">
         <v>1028</v>
-      </c>
-      <c r="C45" t="s" s="3">
-        <v>1029</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="13"/>
@@ -21805,10 +21802,10 @@
         <v>76</v>
       </c>
       <c r="B46" t="s" s="3">
+        <v>1029</v>
+      </c>
+      <c r="C46" t="s" s="3">
         <v>1030</v>
-      </c>
-      <c r="C46" t="s" s="3">
-        <v>1031</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="13"/>
@@ -21818,23 +21815,23 @@
         <v>82</v>
       </c>
       <c r="B47" t="s" s="3">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C47" t="s" s="3">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D47" s="12"/>
       <c r="E47" s="13"/>
     </row>
     <row r="48" ht="13.65" customHeight="1">
       <c r="A48" t="s" s="3">
+        <v>1032</v>
+      </c>
+      <c r="B48" t="s" s="3">
         <v>1033</v>
       </c>
-      <c r="B48" t="s" s="3">
-        <v>1034</v>
-      </c>
       <c r="C48" t="s" s="3">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D48" s="12"/>
       <c r="E48" s="13"/>
@@ -21844,49 +21841,49 @@
         <v>90</v>
       </c>
       <c r="B49" t="s" s="3">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C49" t="s" s="3">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="D49" s="12"/>
       <c r="E49" s="13"/>
     </row>
     <row r="50" ht="13.65" customHeight="1">
       <c r="A50" t="s" s="3">
+        <v>1035</v>
+      </c>
+      <c r="B50" t="s" s="3">
         <v>1036</v>
       </c>
-      <c r="B50" t="s" s="3">
-        <v>1037</v>
-      </c>
       <c r="C50" t="s" s="3">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="D50" s="12"/>
       <c r="E50" s="13"/>
     </row>
     <row r="51" ht="13.65" customHeight="1">
       <c r="A51" t="s" s="3">
+        <v>1037</v>
+      </c>
+      <c r="B51" t="s" s="3">
         <v>1038</v>
       </c>
-      <c r="B51" t="s" s="3">
-        <v>1039</v>
-      </c>
       <c r="C51" t="s" s="3">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D51" s="12"/>
       <c r="E51" s="13"/>
     </row>
     <row r="52" ht="13.65" customHeight="1">
       <c r="A52" t="s" s="3">
+        <v>1039</v>
+      </c>
+      <c r="B52" t="s" s="3">
         <v>1040</v>
       </c>
-      <c r="B52" t="s" s="3">
+      <c r="C52" t="s" s="3">
         <v>1041</v>
-      </c>
-      <c r="C52" t="s" s="3">
-        <v>1042</v>
       </c>
       <c r="D52" s="12"/>
       <c r="E52" s="13"/>
@@ -21896,36 +21893,36 @@
         <v>89</v>
       </c>
       <c r="B53" t="s" s="3">
+        <v>1042</v>
+      </c>
+      <c r="C53" t="s" s="3">
         <v>1043</v>
-      </c>
-      <c r="C53" t="s" s="3">
-        <v>1044</v>
       </c>
       <c r="D53" s="12"/>
       <c r="E53" s="13"/>
     </row>
     <row r="54" ht="13.65" customHeight="1">
       <c r="A54" t="s" s="3">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B54" t="s" s="3">
+        <v>946</v>
+      </c>
+      <c r="C54" t="s" s="3">
         <v>947</v>
-      </c>
-      <c r="C54" t="s" s="3">
-        <v>948</v>
       </c>
       <c r="D54" s="12"/>
       <c r="E54" s="13"/>
     </row>
     <row r="55" ht="13.65" customHeight="1">
       <c r="A55" t="s" s="3">
+        <v>1045</v>
+      </c>
+      <c r="B55" t="s" s="3">
         <v>1046</v>
       </c>
-      <c r="B55" t="s" s="3">
-        <v>1047</v>
-      </c>
       <c r="C55" t="s" s="3">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D55" s="12"/>
       <c r="E55" s="13"/>
@@ -21935,23 +21932,23 @@
         <v>97</v>
       </c>
       <c r="B56" t="s" s="3">
+        <v>1047</v>
+      </c>
+      <c r="C56" t="s" s="3">
         <v>1048</v>
-      </c>
-      <c r="C56" t="s" s="3">
-        <v>1049</v>
       </c>
       <c r="D56" s="12"/>
       <c r="E56" s="13"/>
     </row>
     <row r="57" ht="13.65" customHeight="1">
       <c r="A57" t="s" s="3">
+        <v>1049</v>
+      </c>
+      <c r="B57" t="s" s="3">
         <v>1050</v>
       </c>
-      <c r="B57" t="s" s="3">
+      <c r="C57" t="s" s="3">
         <v>1051</v>
-      </c>
-      <c r="C57" t="s" s="3">
-        <v>1052</v>
       </c>
       <c r="D57" s="12"/>
       <c r="E57" s="13"/>
@@ -21961,153 +21958,153 @@
         <v>102</v>
       </c>
       <c r="B58" t="s" s="3">
+        <v>1052</v>
+      </c>
+      <c r="C58" t="s" s="3">
         <v>1053</v>
-      </c>
-      <c r="C58" t="s" s="3">
-        <v>1054</v>
       </c>
       <c r="D58" s="12"/>
       <c r="E58" s="13"/>
     </row>
     <row r="59" ht="13.65" customHeight="1">
       <c r="A59" t="s" s="3">
+        <v>1054</v>
+      </c>
+      <c r="B59" t="s" s="3">
         <v>1055</v>
       </c>
-      <c r="B59" t="s" s="3">
-        <v>1056</v>
-      </c>
       <c r="C59" t="s" s="3">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D59" s="12"/>
       <c r="E59" s="13"/>
     </row>
     <row r="60" ht="13.65" customHeight="1">
       <c r="A60" t="s" s="3">
+        <v>1056</v>
+      </c>
+      <c r="B60" t="s" s="3">
         <v>1057</v>
       </c>
-      <c r="B60" t="s" s="3">
-        <v>1058</v>
-      </c>
       <c r="C60" t="s" s="3">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="D60" s="12"/>
       <c r="E60" s="13"/>
     </row>
     <row r="61" ht="13.65" customHeight="1">
       <c r="A61" t="s" s="3">
+        <v>1058</v>
+      </c>
+      <c r="B61" t="s" s="3">
         <v>1059</v>
       </c>
-      <c r="B61" t="s" s="3">
-        <v>1060</v>
-      </c>
       <c r="C61" t="s" s="3">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D61" s="12"/>
       <c r="E61" s="13"/>
     </row>
     <row r="62" ht="13.65" customHeight="1">
       <c r="A62" t="s" s="3">
+        <v>1060</v>
+      </c>
+      <c r="B62" t="s" s="3">
         <v>1061</v>
       </c>
-      <c r="B62" t="s" s="3">
+      <c r="C62" t="s" s="3">
         <v>1062</v>
-      </c>
-      <c r="C62" t="s" s="3">
-        <v>1063</v>
       </c>
       <c r="D62" s="12"/>
       <c r="E62" s="13"/>
     </row>
     <row r="63" ht="13.65" customHeight="1">
       <c r="A63" t="s" s="3">
+        <v>1063</v>
+      </c>
+      <c r="B63" t="s" s="3">
         <v>1064</v>
       </c>
-      <c r="B63" t="s" s="3">
+      <c r="C63" t="s" s="3">
         <v>1065</v>
-      </c>
-      <c r="C63" t="s" s="3">
-        <v>1066</v>
       </c>
       <c r="D63" s="12"/>
       <c r="E63" s="13"/>
     </row>
     <row r="64" ht="13.65" customHeight="1">
       <c r="A64" t="s" s="3">
+        <v>1066</v>
+      </c>
+      <c r="B64" t="s" s="3">
         <v>1067</v>
       </c>
-      <c r="B64" t="s" s="3">
+      <c r="C64" t="s" s="3">
         <v>1068</v>
-      </c>
-      <c r="C64" t="s" s="3">
-        <v>1069</v>
       </c>
       <c r="D64" s="12"/>
       <c r="E64" s="13"/>
     </row>
     <row r="65" ht="13.65" customHeight="1">
       <c r="A65" t="s" s="3">
+        <v>1069</v>
+      </c>
+      <c r="B65" t="s" s="3">
         <v>1070</v>
       </c>
-      <c r="B65" t="s" s="3">
-        <v>1071</v>
-      </c>
       <c r="C65" t="s" s="3">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="D65" s="12"/>
       <c r="E65" s="13"/>
     </row>
     <row r="66" ht="13.65" customHeight="1">
       <c r="A66" t="s" s="3">
+        <v>1071</v>
+      </c>
+      <c r="B66" t="s" s="3">
         <v>1072</v>
       </c>
-      <c r="B66" t="s" s="3">
-        <v>1073</v>
-      </c>
       <c r="C66" t="s" s="3">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D66" s="12"/>
       <c r="E66" s="13"/>
     </row>
     <row r="67" ht="13.65" customHeight="1">
       <c r="A67" t="s" s="3">
+        <v>1073</v>
+      </c>
+      <c r="B67" t="s" s="3">
         <v>1074</v>
       </c>
-      <c r="B67" t="s" s="3">
-        <v>1075</v>
-      </c>
       <c r="C67" t="s" s="3">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="D67" s="12"/>
       <c r="E67" s="13"/>
     </row>
     <row r="68" ht="13.65" customHeight="1">
       <c r="A68" t="s" s="3">
+        <v>1075</v>
+      </c>
+      <c r="B68" t="s" s="3">
         <v>1076</v>
       </c>
-      <c r="B68" t="s" s="3">
+      <c r="C68" t="s" s="3">
         <v>1077</v>
-      </c>
-      <c r="C68" t="s" s="3">
-        <v>1078</v>
       </c>
       <c r="D68" s="12"/>
       <c r="E68" s="13"/>
     </row>
     <row r="69" ht="13.65" customHeight="1">
       <c r="A69" t="s" s="3">
+        <v>1078</v>
+      </c>
+      <c r="B69" t="s" s="3">
         <v>1079</v>
       </c>
-      <c r="B69" t="s" s="3">
-        <v>1080</v>
-      </c>
       <c r="C69" t="s" s="3">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="D69" s="12"/>
       <c r="E69" s="13"/>
@@ -22117,49 +22114,49 @@
         <v>168</v>
       </c>
       <c r="B70" t="s" s="3">
+        <v>1080</v>
+      </c>
+      <c r="C70" t="s" s="3">
         <v>1081</v>
-      </c>
-      <c r="C70" t="s" s="3">
-        <v>1082</v>
       </c>
       <c r="D70" s="12"/>
       <c r="E70" s="13"/>
     </row>
     <row r="71" ht="13.65" customHeight="1">
       <c r="A71" t="s" s="3">
+        <v>1082</v>
+      </c>
+      <c r="B71" t="s" s="3">
         <v>1083</v>
       </c>
-      <c r="B71" t="s" s="3">
-        <v>1084</v>
-      </c>
       <c r="C71" t="s" s="3">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="D71" s="12"/>
       <c r="E71" s="13"/>
     </row>
     <row r="72" ht="13.65" customHeight="1">
       <c r="A72" t="s" s="3">
+        <v>1084</v>
+      </c>
+      <c r="B72" t="s" s="3">
         <v>1085</v>
       </c>
-      <c r="B72" t="s" s="3">
-        <v>1086</v>
-      </c>
       <c r="C72" t="s" s="3">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D72" s="12"/>
       <c r="E72" s="13"/>
     </row>
     <row r="73" ht="13.65" customHeight="1">
       <c r="A73" t="s" s="3">
+        <v>1086</v>
+      </c>
+      <c r="B73" t="s" s="3">
         <v>1087</v>
       </c>
-      <c r="B73" t="s" s="3">
-        <v>1088</v>
-      </c>
       <c r="C73" t="s" s="3">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D73" s="12"/>
       <c r="E73" s="13"/>
@@ -22169,49 +22166,49 @@
         <v>195</v>
       </c>
       <c r="B74" t="s" s="3">
+        <v>1088</v>
+      </c>
+      <c r="C74" t="s" s="3">
         <v>1089</v>
-      </c>
-      <c r="C74" t="s" s="3">
-        <v>1090</v>
       </c>
       <c r="D74" s="12"/>
       <c r="E74" s="13"/>
     </row>
     <row r="75" ht="13.65" customHeight="1">
       <c r="A75" t="s" s="3">
+        <v>1090</v>
+      </c>
+      <c r="B75" t="s" s="3">
         <v>1091</v>
       </c>
-      <c r="B75" t="s" s="3">
+      <c r="C75" t="s" s="3">
         <v>1092</v>
-      </c>
-      <c r="C75" t="s" s="3">
-        <v>1093</v>
       </c>
       <c r="D75" s="12"/>
       <c r="E75" s="13"/>
     </row>
     <row r="76" ht="13.65" customHeight="1">
       <c r="A76" t="s" s="3">
+        <v>1093</v>
+      </c>
+      <c r="B76" t="s" s="3">
         <v>1094</v>
       </c>
-      <c r="B76" t="s" s="3">
+      <c r="C76" t="s" s="3">
         <v>1095</v>
-      </c>
-      <c r="C76" t="s" s="3">
-        <v>1096</v>
       </c>
       <c r="D76" s="12"/>
       <c r="E76" s="13"/>
     </row>
     <row r="77" ht="13.65" customHeight="1">
       <c r="A77" t="s" s="3">
+        <v>1096</v>
+      </c>
+      <c r="B77" t="s" s="3">
         <v>1097</v>
       </c>
-      <c r="B77" t="s" s="3">
-        <v>1098</v>
-      </c>
       <c r="C77" t="s" s="3">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D77" s="12"/>
       <c r="E77" s="13"/>
@@ -22221,543 +22218,543 @@
         <v>238</v>
       </c>
       <c r="B78" t="s" s="3">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="C78" t="s" s="3">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="D78" s="12"/>
       <c r="E78" s="13"/>
     </row>
     <row r="79" ht="13.65" customHeight="1">
       <c r="A79" t="s" s="3">
+        <v>1099</v>
+      </c>
+      <c r="B79" t="s" s="3">
         <v>1100</v>
       </c>
-      <c r="B79" t="s" s="3">
-        <v>1101</v>
-      </c>
       <c r="C79" t="s" s="3">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D79" s="12"/>
       <c r="E79" s="13"/>
     </row>
     <row r="80" ht="13.65" customHeight="1">
       <c r="A80" t="s" s="3">
+        <v>1101</v>
+      </c>
+      <c r="B80" t="s" s="3">
         <v>1102</v>
       </c>
-      <c r="B80" t="s" s="3">
+      <c r="C80" t="s" s="3">
         <v>1103</v>
-      </c>
-      <c r="C80" t="s" s="3">
-        <v>1104</v>
       </c>
       <c r="D80" s="12"/>
       <c r="E80" s="13"/>
     </row>
     <row r="81" ht="13.65" customHeight="1">
       <c r="A81" t="s" s="3">
+        <v>1104</v>
+      </c>
+      <c r="B81" t="s" s="3">
         <v>1105</v>
       </c>
-      <c r="B81" t="s" s="3">
+      <c r="C81" t="s" s="3">
         <v>1106</v>
-      </c>
-      <c r="C81" t="s" s="3">
-        <v>1107</v>
       </c>
       <c r="D81" s="12"/>
       <c r="E81" s="13"/>
     </row>
     <row r="82" ht="13.65" customHeight="1">
       <c r="A82" t="s" s="3">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B82" t="s" s="3">
+        <v>941</v>
+      </c>
+      <c r="C82" t="s" s="3">
         <v>942</v>
-      </c>
-      <c r="C82" t="s" s="3">
-        <v>943</v>
       </c>
       <c r="D82" s="12"/>
       <c r="E82" s="13"/>
     </row>
     <row r="83" ht="13.65" customHeight="1">
       <c r="A83" t="s" s="3">
+        <v>1108</v>
+      </c>
+      <c r="B83" t="s" s="3">
         <v>1109</v>
       </c>
-      <c r="B83" t="s" s="3">
+      <c r="C83" t="s" s="3">
         <v>1110</v>
-      </c>
-      <c r="C83" t="s" s="3">
-        <v>1111</v>
       </c>
       <c r="D83" s="12"/>
       <c r="E83" s="13"/>
     </row>
     <row r="84" ht="13.65" customHeight="1">
       <c r="A84" t="s" s="6">
+        <v>1111</v>
+      </c>
+      <c r="B84" t="s" s="6">
         <v>1112</v>
       </c>
-      <c r="B84" t="s" s="6">
+      <c r="C84" t="s" s="6">
         <v>1113</v>
-      </c>
-      <c r="C84" t="s" s="6">
-        <v>1114</v>
       </c>
       <c r="D84" s="12"/>
       <c r="E84" s="13"/>
     </row>
     <row r="85" ht="13.65" customHeight="1">
       <c r="A85" t="s" s="6">
+        <v>1114</v>
+      </c>
+      <c r="B85" t="s" s="6">
         <v>1115</v>
       </c>
-      <c r="B85" t="s" s="6">
+      <c r="C85" t="s" s="6">
         <v>1116</v>
-      </c>
-      <c r="C85" t="s" s="6">
-        <v>1117</v>
       </c>
       <c r="D85" s="12"/>
       <c r="E85" s="13"/>
     </row>
     <row r="86" ht="13.65" customHeight="1">
       <c r="A86" t="s" s="6">
+        <v>1117</v>
+      </c>
+      <c r="B86" t="s" s="6">
         <v>1118</v>
       </c>
-      <c r="B86" t="s" s="6">
+      <c r="C86" t="s" s="6">
         <v>1119</v>
-      </c>
-      <c r="C86" t="s" s="6">
-        <v>1120</v>
       </c>
       <c r="D86" s="12"/>
       <c r="E86" s="13"/>
     </row>
     <row r="87" ht="13.65" customHeight="1">
       <c r="A87" t="s" s="6">
+        <v>1120</v>
+      </c>
+      <c r="B87" t="s" s="6">
         <v>1121</v>
       </c>
-      <c r="B87" t="s" s="6">
+      <c r="C87" t="s" s="6">
         <v>1122</v>
-      </c>
-      <c r="C87" t="s" s="6">
-        <v>1123</v>
       </c>
       <c r="D87" s="12"/>
       <c r="E87" s="13"/>
     </row>
     <row r="88" ht="13.65" customHeight="1">
       <c r="A88" t="s" s="6">
+        <v>1123</v>
+      </c>
+      <c r="B88" t="s" s="6">
         <v>1124</v>
       </c>
-      <c r="B88" t="s" s="6">
+      <c r="C88" t="s" s="6">
         <v>1125</v>
-      </c>
-      <c r="C88" t="s" s="6">
-        <v>1126</v>
       </c>
       <c r="D88" s="12"/>
       <c r="E88" s="13"/>
     </row>
     <row r="89" ht="13.65" customHeight="1">
       <c r="A89" t="s" s="6">
+        <v>1126</v>
+      </c>
+      <c r="B89" t="s" s="6">
         <v>1127</v>
       </c>
-      <c r="B89" t="s" s="6">
+      <c r="C89" t="s" s="6">
         <v>1128</v>
-      </c>
-      <c r="C89" t="s" s="6">
-        <v>1129</v>
       </c>
       <c r="D89" s="12"/>
       <c r="E89" s="13"/>
     </row>
     <row r="90" ht="13.65" customHeight="1">
       <c r="A90" t="s" s="6">
+        <v>1129</v>
+      </c>
+      <c r="B90" t="s" s="6">
         <v>1130</v>
       </c>
-      <c r="B90" t="s" s="6">
+      <c r="C90" t="s" s="6">
         <v>1131</v>
-      </c>
-      <c r="C90" t="s" s="6">
-        <v>1132</v>
       </c>
       <c r="D90" s="12"/>
       <c r="E90" s="13"/>
     </row>
     <row r="91" ht="13.65" customHeight="1">
       <c r="A91" t="s" s="6">
+        <v>1132</v>
+      </c>
+      <c r="B91" t="s" s="6">
         <v>1133</v>
       </c>
-      <c r="B91" t="s" s="6">
+      <c r="C91" t="s" s="6">
         <v>1134</v>
-      </c>
-      <c r="C91" t="s" s="6">
-        <v>1135</v>
       </c>
       <c r="D91" s="12"/>
       <c r="E91" s="13"/>
     </row>
     <row r="92" ht="13.65" customHeight="1">
       <c r="A92" t="s" s="6">
+        <v>1135</v>
+      </c>
+      <c r="B92" t="s" s="6">
         <v>1136</v>
       </c>
-      <c r="B92" t="s" s="6">
+      <c r="C92" t="s" s="6">
         <v>1137</v>
-      </c>
-      <c r="C92" t="s" s="6">
-        <v>1138</v>
       </c>
       <c r="D92" s="12"/>
       <c r="E92" s="13"/>
     </row>
     <row r="93" ht="13.65" customHeight="1">
       <c r="A93" t="s" s="6">
+        <v>1138</v>
+      </c>
+      <c r="B93" t="s" s="6">
         <v>1139</v>
       </c>
-      <c r="B93" t="s" s="6">
-        <v>1140</v>
-      </c>
       <c r="C93" t="s" s="6">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D93" s="12"/>
       <c r="E93" s="13"/>
     </row>
     <row r="94" ht="13.65" customHeight="1">
       <c r="A94" t="s" s="6">
+        <v>1140</v>
+      </c>
+      <c r="B94" t="s" s="6">
         <v>1141</v>
       </c>
-      <c r="B94" t="s" s="6">
+      <c r="C94" t="s" s="6">
         <v>1142</v>
-      </c>
-      <c r="C94" t="s" s="6">
-        <v>1143</v>
       </c>
       <c r="D94" s="12"/>
       <c r="E94" s="13"/>
     </row>
     <row r="95" ht="13.65" customHeight="1">
       <c r="A95" t="s" s="6">
+        <v>1143</v>
+      </c>
+      <c r="B95" t="s" s="6">
         <v>1144</v>
       </c>
-      <c r="B95" t="s" s="6">
-        <v>1145</v>
-      </c>
       <c r="C95" t="s" s="6">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D95" s="12"/>
       <c r="E95" s="13"/>
     </row>
     <row r="96" ht="13.65" customHeight="1">
       <c r="A96" t="s" s="6">
+        <v>1145</v>
+      </c>
+      <c r="B96" t="s" s="6">
         <v>1146</v>
       </c>
-      <c r="B96" t="s" s="6">
+      <c r="C96" t="s" s="6">
         <v>1147</v>
-      </c>
-      <c r="C96" t="s" s="6">
-        <v>1148</v>
       </c>
       <c r="D96" s="12"/>
       <c r="E96" s="13"/>
     </row>
     <row r="97" ht="13.65" customHeight="1">
       <c r="A97" t="s" s="6">
+        <v>1148</v>
+      </c>
+      <c r="B97" t="s" s="6">
         <v>1149</v>
       </c>
-      <c r="B97" t="s" s="6">
+      <c r="C97" t="s" s="6">
         <v>1150</v>
-      </c>
-      <c r="C97" t="s" s="6">
-        <v>1151</v>
       </c>
       <c r="D97" s="12"/>
       <c r="E97" s="13"/>
     </row>
     <row r="98" ht="13.65" customHeight="1">
       <c r="A98" t="s" s="6">
+        <v>1151</v>
+      </c>
+      <c r="B98" t="s" s="6">
         <v>1152</v>
       </c>
-      <c r="B98" t="s" s="6">
+      <c r="C98" t="s" s="6">
         <v>1153</v>
-      </c>
-      <c r="C98" t="s" s="6">
-        <v>1154</v>
       </c>
       <c r="D98" s="12"/>
       <c r="E98" s="13"/>
     </row>
     <row r="99" ht="13.65" customHeight="1">
       <c r="A99" t="s" s="6">
+        <v>1154</v>
+      </c>
+      <c r="B99" t="s" s="6">
         <v>1155</v>
       </c>
-      <c r="B99" t="s" s="6">
-        <v>1156</v>
-      </c>
       <c r="C99" t="s" s="6">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="D99" s="12"/>
       <c r="E99" s="13"/>
     </row>
     <row r="100" ht="13.65" customHeight="1">
       <c r="A100" t="s" s="6">
+        <v>1156</v>
+      </c>
+      <c r="B100" t="s" s="6">
         <v>1157</v>
       </c>
-      <c r="B100" t="s" s="6">
+      <c r="C100" t="s" s="6">
         <v>1158</v>
-      </c>
-      <c r="C100" t="s" s="6">
-        <v>1159</v>
       </c>
       <c r="D100" s="12"/>
       <c r="E100" s="13"/>
     </row>
     <row r="101" ht="13.65" customHeight="1">
       <c r="A101" t="s" s="6">
+        <v>1159</v>
+      </c>
+      <c r="B101" t="s" s="6">
         <v>1160</v>
       </c>
-      <c r="B101" t="s" s="6">
+      <c r="C101" t="s" s="6">
         <v>1161</v>
-      </c>
-      <c r="C101" t="s" s="6">
-        <v>1162</v>
       </c>
       <c r="D101" s="12"/>
       <c r="E101" s="13"/>
     </row>
     <row r="102" ht="13.65" customHeight="1">
       <c r="A102" t="s" s="6">
+        <v>1162</v>
+      </c>
+      <c r="B102" t="s" s="6">
         <v>1163</v>
       </c>
-      <c r="B102" t="s" s="6">
+      <c r="C102" t="s" s="6">
         <v>1164</v>
-      </c>
-      <c r="C102" t="s" s="6">
-        <v>1165</v>
       </c>
       <c r="D102" s="12"/>
       <c r="E102" s="13"/>
     </row>
     <row r="103" ht="13.65" customHeight="1">
       <c r="A103" t="s" s="6">
+        <v>1165</v>
+      </c>
+      <c r="B103" t="s" s="6">
         <v>1166</v>
       </c>
-      <c r="B103" t="s" s="6">
+      <c r="C103" t="s" s="6">
         <v>1167</v>
-      </c>
-      <c r="C103" t="s" s="6">
-        <v>1168</v>
       </c>
       <c r="D103" s="12"/>
       <c r="E103" s="13"/>
     </row>
     <row r="104" ht="13.65" customHeight="1">
       <c r="A104" t="s" s="6">
+        <v>1168</v>
+      </c>
+      <c r="B104" t="s" s="6">
         <v>1169</v>
       </c>
-      <c r="B104" t="s" s="6">
+      <c r="C104" t="s" s="6">
         <v>1170</v>
-      </c>
-      <c r="C104" t="s" s="6">
-        <v>1171</v>
       </c>
       <c r="D104" s="12"/>
       <c r="E104" s="13"/>
     </row>
     <row r="105" ht="13.65" customHeight="1">
       <c r="A105" t="s" s="6">
+        <v>1171</v>
+      </c>
+      <c r="B105" t="s" s="6">
         <v>1172</v>
       </c>
-      <c r="B105" t="s" s="6">
-        <v>1173</v>
-      </c>
       <c r="C105" t="s" s="6">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D105" s="12"/>
       <c r="E105" s="13"/>
     </row>
     <row r="106" ht="13.65" customHeight="1">
       <c r="A106" t="s" s="6">
+        <v>1173</v>
+      </c>
+      <c r="B106" t="s" s="6">
         <v>1174</v>
       </c>
-      <c r="B106" t="s" s="6">
+      <c r="C106" t="s" s="6">
         <v>1175</v>
-      </c>
-      <c r="C106" t="s" s="6">
-        <v>1176</v>
       </c>
       <c r="D106" s="12"/>
       <c r="E106" s="13"/>
     </row>
     <row r="107" ht="13.65" customHeight="1">
       <c r="A107" t="s" s="6">
+        <v>1176</v>
+      </c>
+      <c r="B107" t="s" s="6">
         <v>1177</v>
       </c>
-      <c r="B107" t="s" s="6">
+      <c r="C107" t="s" s="6">
         <v>1178</v>
-      </c>
-      <c r="C107" t="s" s="6">
-        <v>1179</v>
       </c>
       <c r="D107" s="12"/>
       <c r="E107" s="13"/>
     </row>
     <row r="108" ht="13.65" customHeight="1">
       <c r="A108" t="s" s="6">
+        <v>1179</v>
+      </c>
+      <c r="B108" t="s" s="6">
         <v>1180</v>
       </c>
-      <c r="B108" t="s" s="6">
-        <v>1181</v>
-      </c>
       <c r="C108" t="s" s="6">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="D108" s="12"/>
       <c r="E108" s="13"/>
     </row>
     <row r="109" ht="13.65" customHeight="1">
       <c r="A109" t="s" s="6">
+        <v>1181</v>
+      </c>
+      <c r="B109" t="s" s="6">
         <v>1182</v>
       </c>
-      <c r="B109" t="s" s="6">
-        <v>1183</v>
-      </c>
       <c r="C109" t="s" s="6">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="D109" s="12"/>
       <c r="E109" s="13"/>
     </row>
     <row r="110" ht="13.65" customHeight="1">
       <c r="A110" t="s" s="6">
+        <v>1183</v>
+      </c>
+      <c r="B110" t="s" s="6">
         <v>1184</v>
       </c>
-      <c r="B110" t="s" s="6">
-        <v>1185</v>
-      </c>
       <c r="C110" t="s" s="6">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D110" s="12"/>
       <c r="E110" s="13"/>
     </row>
     <row r="111" ht="13.65" customHeight="1">
       <c r="A111" t="s" s="6">
+        <v>1185</v>
+      </c>
+      <c r="B111" t="s" s="6">
         <v>1186</v>
       </c>
-      <c r="B111" t="s" s="6">
+      <c r="C111" t="s" s="6">
         <v>1187</v>
-      </c>
-      <c r="C111" t="s" s="6">
-        <v>1188</v>
       </c>
       <c r="D111" s="12"/>
       <c r="E111" s="13"/>
     </row>
     <row r="112" ht="13.65" customHeight="1">
       <c r="A112" t="s" s="6">
+        <v>1188</v>
+      </c>
+      <c r="B112" t="s" s="6">
         <v>1189</v>
       </c>
-      <c r="B112" t="s" s="6">
-        <v>1190</v>
-      </c>
       <c r="C112" t="s" s="6">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="D112" s="12"/>
       <c r="E112" s="13"/>
     </row>
     <row r="113" ht="13.65" customHeight="1">
       <c r="A113" t="s" s="6">
+        <v>1190</v>
+      </c>
+      <c r="B113" t="s" s="6">
         <v>1191</v>
       </c>
-      <c r="B113" t="s" s="6">
+      <c r="C113" t="s" s="6">
         <v>1192</v>
-      </c>
-      <c r="C113" t="s" s="6">
-        <v>1193</v>
       </c>
       <c r="D113" s="12"/>
       <c r="E113" s="13"/>
     </row>
     <row r="114" ht="13.65" customHeight="1">
       <c r="A114" t="s" s="6">
+        <v>1193</v>
+      </c>
+      <c r="B114" t="s" s="6">
         <v>1194</v>
       </c>
-      <c r="B114" t="s" s="6">
-        <v>1195</v>
-      </c>
       <c r="C114" t="s" s="6">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="D114" s="12"/>
       <c r="E114" s="13"/>
     </row>
     <row r="115" ht="13.65" customHeight="1">
       <c r="A115" t="s" s="6">
+        <v>1195</v>
+      </c>
+      <c r="B115" t="s" s="6">
         <v>1196</v>
       </c>
-      <c r="B115" t="s" s="6">
-        <v>1197</v>
-      </c>
       <c r="C115" t="s" s="6">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D115" s="12"/>
       <c r="E115" s="13"/>
     </row>
     <row r="116" ht="13.65" customHeight="1">
       <c r="A116" t="s" s="6">
+        <v>1197</v>
+      </c>
+      <c r="B116" t="s" s="6">
         <v>1198</v>
       </c>
-      <c r="B116" t="s" s="6">
-        <v>1199</v>
-      </c>
       <c r="C116" t="s" s="6">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D116" s="12"/>
       <c r="E116" s="13"/>
     </row>
     <row r="117" ht="13.65" customHeight="1">
       <c r="A117" t="s" s="6">
+        <v>1199</v>
+      </c>
+      <c r="B117" t="s" s="6">
         <v>1200</v>
       </c>
-      <c r="B117" t="s" s="6">
+      <c r="C117" t="s" s="6">
         <v>1201</v>
-      </c>
-      <c r="C117" t="s" s="6">
-        <v>1202</v>
       </c>
       <c r="D117" s="12"/>
       <c r="E117" s="13"/>
     </row>
     <row r="118" ht="13.65" customHeight="1">
       <c r="A118" t="s" s="6">
+        <v>1202</v>
+      </c>
+      <c r="B118" t="s" s="6">
         <v>1203</v>
       </c>
-      <c r="B118" t="s" s="6">
-        <v>1204</v>
-      </c>
       <c r="C118" t="s" s="6">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D118" s="12"/>
       <c r="E118" s="13"/>
     </row>
     <row r="119" ht="13.65" customHeight="1">
       <c r="A119" t="s" s="6">
+        <v>1204</v>
+      </c>
+      <c r="B119" t="s" s="6">
         <v>1205</v>
       </c>
-      <c r="B119" t="s" s="6">
-        <v>1206</v>
-      </c>
       <c r="C119" t="s" s="6">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="D119" s="12"/>
       <c r="E119" s="13"/>
@@ -22767,192 +22764,192 @@
         <v>205</v>
       </c>
       <c r="B120" t="s" s="6">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="C120" t="s" s="6">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="D120" s="12"/>
       <c r="E120" s="13"/>
     </row>
     <row r="121" ht="13.65" customHeight="1">
       <c r="A121" t="s" s="6">
+        <v>1206</v>
+      </c>
+      <c r="B121" t="s" s="6">
         <v>1207</v>
       </c>
-      <c r="B121" t="s" s="6">
+      <c r="C121" t="s" s="6">
         <v>1208</v>
-      </c>
-      <c r="C121" t="s" s="6">
-        <v>1209</v>
       </c>
       <c r="D121" s="12"/>
       <c r="E121" s="13"/>
     </row>
     <row r="122" ht="13.65" customHeight="1">
       <c r="A122" t="s" s="6">
+        <v>1209</v>
+      </c>
+      <c r="B122" t="s" s="6">
         <v>1210</v>
       </c>
-      <c r="B122" t="s" s="6">
+      <c r="C122" t="s" s="6">
         <v>1211</v>
-      </c>
-      <c r="C122" t="s" s="6">
-        <v>1212</v>
       </c>
       <c r="D122" s="12"/>
       <c r="E122" s="13"/>
     </row>
     <row r="123" ht="13.65" customHeight="1">
       <c r="A123" t="s" s="6">
+        <v>1212</v>
+      </c>
+      <c r="B123" t="s" s="6">
         <v>1213</v>
       </c>
-      <c r="B123" t="s" s="6">
+      <c r="C123" t="s" s="6">
         <v>1214</v>
-      </c>
-      <c r="C123" t="s" s="6">
-        <v>1215</v>
       </c>
       <c r="D123" s="12"/>
       <c r="E123" s="13"/>
     </row>
     <row r="124" ht="13.65" customHeight="1">
       <c r="A124" t="s" s="6">
+        <v>1215</v>
+      </c>
+      <c r="B124" t="s" s="6">
         <v>1216</v>
       </c>
-      <c r="B124" t="s" s="6">
+      <c r="C124" t="s" s="6">
         <v>1217</v>
-      </c>
-      <c r="C124" t="s" s="6">
-        <v>1218</v>
       </c>
       <c r="D124" s="12"/>
       <c r="E124" s="13"/>
     </row>
     <row r="125" ht="13.65" customHeight="1">
       <c r="A125" t="s" s="6">
+        <v>1218</v>
+      </c>
+      <c r="B125" t="s" s="6">
         <v>1219</v>
       </c>
-      <c r="B125" t="s" s="6">
+      <c r="C125" t="s" s="6">
         <v>1220</v>
-      </c>
-      <c r="C125" t="s" s="6">
-        <v>1221</v>
       </c>
       <c r="D125" s="12"/>
       <c r="E125" s="13"/>
     </row>
     <row r="126" ht="13.65" customHeight="1">
       <c r="A126" t="s" s="6">
+        <v>1221</v>
+      </c>
+      <c r="B126" t="s" s="6">
         <v>1222</v>
       </c>
-      <c r="B126" t="s" s="6">
+      <c r="C126" t="s" s="6">
         <v>1223</v>
-      </c>
-      <c r="C126" t="s" s="6">
-        <v>1224</v>
       </c>
       <c r="D126" s="12"/>
       <c r="E126" s="13"/>
     </row>
     <row r="127" ht="13.65" customHeight="1">
       <c r="A127" t="s" s="6">
+        <v>1224</v>
+      </c>
+      <c r="B127" t="s" s="14">
         <v>1225</v>
       </c>
-      <c r="B127" t="s" s="14">
+      <c r="C127" t="s" s="6">
         <v>1226</v>
-      </c>
-      <c r="C127" t="s" s="6">
-        <v>1227</v>
       </c>
       <c r="D127" s="12"/>
       <c r="E127" s="13"/>
     </row>
     <row r="128" ht="13.65" customHeight="1">
       <c r="A128" t="s" s="6">
+        <v>1227</v>
+      </c>
+      <c r="B128" t="s" s="6">
         <v>1228</v>
       </c>
-      <c r="B128" t="s" s="6">
-        <v>1229</v>
-      </c>
       <c r="C128" t="s" s="6">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="D128" s="12"/>
       <c r="E128" s="13"/>
     </row>
     <row r="129" ht="13.65" customHeight="1">
       <c r="A129" t="s" s="6">
+        <v>1229</v>
+      </c>
+      <c r="B129" t="s" s="6">
         <v>1230</v>
       </c>
-      <c r="B129" t="s" s="6">
+      <c r="C129" t="s" s="6">
         <v>1231</v>
-      </c>
-      <c r="C129" t="s" s="6">
-        <v>1232</v>
       </c>
       <c r="D129" s="12"/>
       <c r="E129" s="13"/>
     </row>
     <row r="130" ht="13.65" customHeight="1">
       <c r="A130" t="s" s="6">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B130" t="s" s="6">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="C130" t="s" s="6">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="D130" s="12"/>
       <c r="E130" s="13"/>
     </row>
     <row r="131" ht="13.65" customHeight="1">
       <c r="A131" t="s" s="6">
+        <v>1233</v>
+      </c>
+      <c r="B131" t="s" s="6">
         <v>1234</v>
       </c>
-      <c r="B131" t="s" s="6">
-        <v>1235</v>
-      </c>
       <c r="C131" t="s" s="6">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="D131" s="12"/>
       <c r="E131" s="13"/>
     </row>
     <row r="132" ht="13.65" customHeight="1">
       <c r="A132" t="s" s="6">
+        <v>1235</v>
+      </c>
+      <c r="B132" t="s" s="6">
         <v>1236</v>
       </c>
-      <c r="B132" t="s" s="6">
-        <v>1237</v>
-      </c>
       <c r="C132" t="s" s="6">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="D132" s="12"/>
       <c r="E132" s="13"/>
     </row>
     <row r="133" ht="13.65" customHeight="1">
       <c r="A133" t="s" s="6">
+        <v>1237</v>
+      </c>
+      <c r="B133" t="s" s="6">
         <v>1238</v>
       </c>
-      <c r="B133" t="s" s="6">
+      <c r="C133" t="s" s="6">
         <v>1239</v>
-      </c>
-      <c r="C133" t="s" s="6">
-        <v>1240</v>
       </c>
       <c r="D133" s="12"/>
       <c r="E133" s="13"/>
     </row>
     <row r="134" ht="13.65" customHeight="1">
       <c r="A134" t="s" s="6">
+        <v>1240</v>
+      </c>
+      <c r="B134" t="s" s="6">
         <v>1241</v>
       </c>
-      <c r="B134" t="s" s="6">
+      <c r="C134" t="s" s="6">
         <v>1242</v>
-      </c>
-      <c r="C134" t="s" s="6">
-        <v>1243</v>
       </c>
       <c r="D134" s="15"/>
       <c r="E134" s="16"/>

--- a/static/TALENKAART_DATA/talenkaart_data.xlsx
+++ b/static/TALENKAART_DATA/talenkaart_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amsuni-my.sharepoint.com/personal/kylie_mansour_student_uva_nl/Documents/Documents/MA/Internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{D6D6DB9B-1825-0E4C-A6B9-EC4CA1933FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CB7B743-DE3A-D440-ABBE-0AB15E380274}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{D6D6DB9B-1825-0E4C-A6B9-EC4CA1933FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F211D1BA-A2D1-5544-9701-826E6BB76B96}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respondenten" sheetId="2" r:id="rId1"/>
@@ -3416,9 +3416,6 @@
     <t>OBA Buitenveldert</t>
   </si>
   <si>
-    <t>52.33250504203255</t>
-  </si>
-  <si>
     <t>OBA Van der Pek</t>
   </si>
   <si>
@@ -4433,6 +4430,9 @@
   </si>
   <si>
     <t>eng,spa,ita</t>
+  </si>
+  <si>
+    <t>52.332498330642814, 4.876000881281019</t>
   </si>
 </sst>
 </file>
@@ -4992,6 +4992,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15037,7 +15041,7 @@
       </c>
       <c r="C475" s="2"/>
       <c r="D475" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E475" s="6"/>
       <c r="F475" s="3"/>
@@ -15163,7 +15167,7 @@
       </c>
       <c r="C482" s="2"/>
       <c r="D482" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="E482" s="6"/>
       <c r="F482" s="3"/>
@@ -18655,7 +18659,7 @@
       </c>
       <c r="C676" s="2"/>
       <c r="D676" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E676" s="6"/>
       <c r="F676" s="3"/>
@@ -21823,7 +21827,7 @@
       </c>
       <c r="C852" s="2"/>
       <c r="D852" s="2" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E852" s="6"/>
       <c r="F852" s="3"/>
@@ -24091,7 +24095,7 @@
       </c>
       <c r="C978" s="2"/>
       <c r="D978" s="2" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E978" s="6"/>
       <c r="F978" s="3"/>
@@ -24552,13 +24556,13 @@
     </row>
     <row r="999" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A999" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B999" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C999" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D999" s="25" t="s">
         <v>227</v>
@@ -24582,13 +24586,13 @@
     </row>
     <row r="1000" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1000" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1000" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1000" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1000" s="25" t="s">
         <v>227</v>
@@ -24600,7 +24604,7 @@
         <v>218</v>
       </c>
       <c r="G1000" s="25" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H1000" s="25" t="s">
         <v>34</v>
@@ -24612,16 +24616,16 @@
     </row>
     <row r="1001" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1001" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1001" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1001" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1001" s="25" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="E1001" s="25" t="s">
         <v>89</v>
@@ -24633,10 +24637,10 @@
         <v>204</v>
       </c>
       <c r="H1001" s="25" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I1001" s="25" t="s">
         <v>1182</v>
-      </c>
-      <c r="I1001" s="25" t="s">
-        <v>1183</v>
       </c>
       <c r="J1001" s="25" t="s">
         <v>108</v>
@@ -24644,13 +24648,13 @@
     </row>
     <row r="1002" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1002" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1002" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1002" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1002" s="25" t="s">
         <v>140</v>
@@ -24662,28 +24666,28 @@
         <v>141</v>
       </c>
       <c r="G1002" s="25" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1002" s="25" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1002" s="25" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1002" s="25"/>
     </row>
     <row r="1003" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1003" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1003" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1003" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1003" s="25" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E1003" s="25" t="s">
         <v>89</v>
@@ -24704,16 +24708,16 @@
     </row>
     <row r="1004" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1004" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1004" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1004" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1004" s="25" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E1004" s="25" t="s">
         <v>242</v>
@@ -24722,28 +24726,28 @@
         <v>242</v>
       </c>
       <c r="G1004" s="25" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H1004" s="25" t="s">
+        <v>1185</v>
+      </c>
+      <c r="I1004" s="25" t="s">
         <v>1186</v>
-      </c>
-      <c r="H1004" s="25" t="s">
-        <v>1186</v>
-      </c>
-      <c r="I1004" s="25" t="s">
-        <v>1187</v>
       </c>
       <c r="J1004" s="25"/>
     </row>
     <row r="1005" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1005" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1005" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1005" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1005" s="25" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="E1005" s="25" t="s">
         <v>219</v>
@@ -24752,10 +24756,10 @@
         <v>218</v>
       </c>
       <c r="G1005" s="25" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H1005" s="25" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="I1005" s="25" t="s">
         <v>218</v>
@@ -24764,16 +24768,16 @@
     </row>
     <row r="1006" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1006" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1006" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1006" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1006" s="26" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E1006" s="26" t="s">
         <v>81</v>
@@ -24794,16 +24798,16 @@
     </row>
     <row r="1007" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1007" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1007" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1007" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1007" s="26" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E1007" s="27" t="s">
         <v>284</v>
@@ -24815,7 +24819,7 @@
         <v>108</v>
       </c>
       <c r="H1007" s="27" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1007" s="27" t="s">
         <v>81</v>
@@ -24824,19 +24828,19 @@
     </row>
     <row r="1008" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1008" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1008" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1008" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1008" s="26" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E1008" s="27" t="s">
         <v>1192</v>
-      </c>
-      <c r="E1008" s="27" t="s">
-        <v>1193</v>
       </c>
       <c r="F1008" s="27" t="s">
         <v>1005</v>
@@ -24845,22 +24849,22 @@
         <v>81</v>
       </c>
       <c r="H1008" s="27" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="I1008" s="27" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="J1008" s="26"/>
     </row>
     <row r="1009" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1009" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1009" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1009" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1009" s="26" t="s">
         <v>34</v>
@@ -24884,13 +24888,13 @@
     </row>
     <row r="1010" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1010" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1010" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1010" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1010" s="26" t="s">
         <v>108</v>
@@ -24902,7 +24906,7 @@
         <v>89</v>
       </c>
       <c r="G1010" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1010" s="26" t="s">
         <v>89</v>
@@ -24914,13 +24918,13 @@
     </row>
     <row r="1011" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1011" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1011" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1011" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1011" s="26" t="s">
         <v>204</v>
@@ -24938,22 +24942,22 @@
         <v>89</v>
       </c>
       <c r="I1011" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1011" s="26"/>
     </row>
     <row r="1012" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1012" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1012" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1012" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1012" s="26" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="E1012" s="26" t="s">
         <v>969</v>
@@ -24962,7 +24966,7 @@
         <v>969</v>
       </c>
       <c r="G1012" s="26" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="H1012" s="26" t="s">
         <v>81</v>
@@ -24974,16 +24978,16 @@
     </row>
     <row r="1013" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1013" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1013" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1013" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1013" s="27" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E1013" s="27" t="s">
         <v>143</v>
@@ -24995,24 +24999,24 @@
         <v>108</v>
       </c>
       <c r="H1013" s="27" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1013" s="27" t="s">
         <v>81</v>
       </c>
       <c r="J1013" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="1014" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1014" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1014" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1014" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1014" s="26" t="s">
         <v>338</v>
@@ -25038,16 +25042,16 @@
     </row>
     <row r="1015" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1015" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1015" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1015" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1015" s="26" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="E1015" s="26" t="s">
         <v>108</v>
@@ -25074,7 +25078,7 @@
         <v>155</v>
       </c>
       <c r="C1016" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1016" s="28" t="s">
         <v>232</v>
@@ -25106,13 +25110,13 @@
         <v>155</v>
       </c>
       <c r="C1017" s="28" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D1017" s="28" t="s">
         <v>1199</v>
       </c>
-      <c r="D1017" s="28" t="s">
-        <v>1200</v>
-      </c>
       <c r="E1017" s="28" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F1017" s="28" t="s">
         <v>219</v>
@@ -25136,7 +25140,7 @@
         <v>155</v>
       </c>
       <c r="C1018" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1018" s="29" t="s">
         <v>796</v>
@@ -25148,13 +25152,13 @@
         <v>89</v>
       </c>
       <c r="G1018" s="29" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1018" s="29" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1018" s="29" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1018" s="28"/>
     </row>
@@ -25166,7 +25170,7 @@
         <v>155</v>
       </c>
       <c r="C1019" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1019" s="28" t="s">
         <v>206</v>
@@ -25194,25 +25198,25 @@
         <v>155</v>
       </c>
       <c r="C1020" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1020" s="28" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E1020" s="28" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="F1020" s="28" t="s">
         <v>89</v>
       </c>
       <c r="G1020" s="28" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1020" s="28" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1020" s="28" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1020" s="28"/>
     </row>
@@ -25224,16 +25228,16 @@
         <v>155</v>
       </c>
       <c r="C1021" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1021" s="28" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="E1021" s="28" t="s">
         <v>82</v>
       </c>
       <c r="F1021" s="28" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G1021" s="28" t="s">
         <v>89</v>
@@ -25242,7 +25246,7 @@
         <v>89</v>
       </c>
       <c r="I1021" s="28" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1021" s="28" t="s">
         <v>281</v>
@@ -25256,7 +25260,7 @@
         <v>155</v>
       </c>
       <c r="C1022" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1022" s="28" t="s">
         <v>31</v>
@@ -25274,7 +25278,7 @@
         <v>89</v>
       </c>
       <c r="I1022" s="28" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1022" s="28" t="s">
         <v>89</v>
@@ -25288,7 +25292,7 @@
         <v>155</v>
       </c>
       <c r="C1023" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1023" s="28" t="s">
         <v>796</v>
@@ -25320,10 +25324,10 @@
         <v>155</v>
       </c>
       <c r="C1024" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1024" s="28" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E1024" s="28" t="s">
         <v>89</v>
@@ -25352,7 +25356,7 @@
         <v>155</v>
       </c>
       <c r="C1025" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1025" s="28" t="s">
         <v>281</v>
@@ -25384,22 +25388,22 @@
         <v>155</v>
       </c>
       <c r="C1026" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1026" s="28" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E1026" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1026" s="28" t="s">
         <v>1202</v>
       </c>
-      <c r="E1026" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1026" s="28" t="s">
+      <c r="G1026" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1026" s="28" t="s">
         <v>1203</v>
-      </c>
-      <c r="G1026" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="H1026" s="28" t="s">
-        <v>1204</v>
       </c>
       <c r="I1026" s="28" t="s">
         <v>89</v>
@@ -25416,25 +25420,25 @@
         <v>155</v>
       </c>
       <c r="C1027" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1027" s="28" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="E1027" s="28" t="s">
         <v>81</v>
       </c>
       <c r="F1027" s="28" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="G1027" s="28" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1027" s="28" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="I1027" s="28" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="J1027" s="28"/>
     </row>
@@ -25446,10 +25450,10 @@
         <v>155</v>
       </c>
       <c r="C1028" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1028" s="28" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="E1028" s="28" t="s">
         <v>16</v>
@@ -25461,10 +25465,10 @@
         <v>89</v>
       </c>
       <c r="H1028" s="28" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="I1028" s="28" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="J1028" s="28" t="s">
         <v>15</v>
@@ -25478,7 +25482,7 @@
         <v>155</v>
       </c>
       <c r="C1029" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1029" s="28" t="s">
         <v>281</v>
@@ -25510,7 +25514,7 @@
         <v>155</v>
       </c>
       <c r="C1030" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1030" s="28" t="s">
         <v>89</v>
@@ -25538,10 +25542,10 @@
         <v>413</v>
       </c>
       <c r="C1031" s="26" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D1031" s="26" t="s">
         <v>1209</v>
-      </c>
-      <c r="D1031" s="26" t="s">
-        <v>1210</v>
       </c>
       <c r="E1031" s="26" t="s">
         <v>902</v>
@@ -25553,10 +25557,10 @@
         <v>81</v>
       </c>
       <c r="H1031" s="26" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="I1031" s="26" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="J1031" s="26"/>
     </row>
@@ -25568,7 +25572,7 @@
         <v>413</v>
       </c>
       <c r="C1032" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1032" s="26" t="s">
         <v>108</v>
@@ -25586,7 +25590,7 @@
         <v>89</v>
       </c>
       <c r="I1032" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1032" s="26" t="s">
         <v>89</v>
@@ -25600,7 +25604,7 @@
         <v>413</v>
       </c>
       <c r="C1033" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1033" s="27" t="s">
         <v>50</v>
@@ -25612,13 +25616,13 @@
         <v>89</v>
       </c>
       <c r="G1033" s="27" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1033" s="27" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1033" s="27" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1033" s="26" t="s">
         <v>89</v>
@@ -25632,7 +25636,7 @@
         <v>413</v>
       </c>
       <c r="C1034" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1034" s="26" t="s">
         <v>204</v>
@@ -25644,7 +25648,7 @@
         <v>89</v>
       </c>
       <c r="G1034" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1034" s="26" t="s">
         <v>89</v>
@@ -25664,7 +25668,7 @@
         <v>413</v>
       </c>
       <c r="C1035" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1035" s="26" t="s">
         <v>81</v>
@@ -25688,10 +25692,10 @@
         <v>413</v>
       </c>
       <c r="C1036" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1036" s="26" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="E1036" s="26" t="s">
         <v>892</v>
@@ -25703,10 +25707,10 @@
         <v>81</v>
       </c>
       <c r="H1036" s="26" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="I1036" s="26" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="J1036" s="26" t="s">
         <v>892</v>
@@ -25720,16 +25724,16 @@
         <v>413</v>
       </c>
       <c r="C1037" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1037" s="26" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="E1037" s="26" t="s">
         <v>89</v>
       </c>
       <c r="F1037" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G1037" s="26" t="s">
         <v>81</v>
@@ -25738,7 +25742,7 @@
         <v>89</v>
       </c>
       <c r="I1037" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1037" s="26" t="s">
         <v>89</v>
@@ -25752,13 +25756,13 @@
         <v>413</v>
       </c>
       <c r="C1038" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1038" s="26" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E1038" s="26" t="s">
         <v>1215</v>
-      </c>
-      <c r="E1038" s="26" t="s">
-        <v>1216</v>
       </c>
       <c r="F1038" s="26" t="s">
         <v>969</v>
@@ -25784,7 +25788,7 @@
         <v>413</v>
       </c>
       <c r="C1039" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1039" s="26" t="s">
         <v>204</v>
@@ -25799,7 +25803,7 @@
         <v>22</v>
       </c>
       <c r="H1039" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1039" s="26" t="s">
         <v>22</v>
@@ -25814,10 +25818,10 @@
         <v>413</v>
       </c>
       <c r="C1040" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1040" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E1040" s="26" t="s">
         <v>89</v>
@@ -25826,13 +25830,13 @@
         <v>89</v>
       </c>
       <c r="G1040" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1040" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1040" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1040" s="26"/>
     </row>
@@ -25844,10 +25848,10 @@
         <v>413</v>
       </c>
       <c r="C1041" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1041" s="30" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="E1041" s="30" t="s">
         <v>89</v>
@@ -25856,16 +25860,16 @@
         <v>153</v>
       </c>
       <c r="G1041" s="30" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1041" s="30" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1041" s="30" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1041" s="30" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="1042" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -25876,10 +25880,10 @@
         <v>413</v>
       </c>
       <c r="C1042" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1042" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E1042" s="26" t="s">
         <v>89</v>
@@ -25906,7 +25910,7 @@
         <v>413</v>
       </c>
       <c r="C1043" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1043" s="26" t="s">
         <v>31</v>
@@ -25936,10 +25940,10 @@
         <v>413</v>
       </c>
       <c r="C1044" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1044" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E1044" s="26" t="s">
         <v>81</v>
@@ -25951,7 +25955,7 @@
         <v>89</v>
       </c>
       <c r="H1044" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1044" s="26" t="s">
         <v>81</v>
@@ -25966,22 +25970,22 @@
         <v>413</v>
       </c>
       <c r="C1045" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1045" s="26" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="E1045" s="26" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F1045" s="26" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="G1045" s="26" t="s">
         <v>108</v>
       </c>
       <c r="H1045" s="26" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="I1045" s="26" t="s">
         <v>81</v>
@@ -25996,7 +26000,7 @@
         <v>413</v>
       </c>
       <c r="C1046" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1046" s="26" t="s">
         <v>1119</v>
@@ -26026,10 +26030,10 @@
         <v>413</v>
       </c>
       <c r="C1047" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1047" s="26" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="E1047" s="26" t="s">
         <v>37</v>
@@ -26056,10 +26060,10 @@
         <v>413</v>
       </c>
       <c r="C1048" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1048" s="26" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E1048" s="26" t="s">
         <v>892</v>
@@ -26071,7 +26075,7 @@
         <v>81</v>
       </c>
       <c r="H1048" s="26" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="I1048" s="26" t="s">
         <v>81</v>
@@ -26088,7 +26092,7 @@
         <v>413</v>
       </c>
       <c r="C1049" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1049" s="26" t="s">
         <v>142</v>
@@ -26120,7 +26124,7 @@
         <v>413</v>
       </c>
       <c r="C1050" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1050" s="26" t="s">
         <v>142</v>
@@ -26152,10 +26156,10 @@
         <v>413</v>
       </c>
       <c r="C1051" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1051" s="26" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="E1051" s="26" t="s">
         <v>865</v>
@@ -26170,7 +26174,7 @@
         <v>81</v>
       </c>
       <c r="I1051" s="26" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="J1051" s="26"/>
     </row>
@@ -26182,10 +26186,10 @@
         <v>413</v>
       </c>
       <c r="C1052" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1052" s="26" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E1052" s="26" t="s">
         <v>81</v>
@@ -26197,7 +26201,7 @@
         <v>81</v>
       </c>
       <c r="H1052" s="26" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="I1052" s="26" t="s">
         <v>81</v>
@@ -26214,10 +26218,10 @@
         <v>413</v>
       </c>
       <c r="C1053" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1053" s="26" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E1053" s="26" t="s">
         <v>81</v>
@@ -26229,7 +26233,7 @@
         <v>81</v>
       </c>
       <c r="H1053" s="26" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="I1053" s="26" t="s">
         <v>81</v>
@@ -26246,10 +26250,10 @@
         <v>413</v>
       </c>
       <c r="C1054" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1054" s="26" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="E1054" s="26" t="s">
         <v>219</v>
@@ -26276,10 +26280,10 @@
         <v>413</v>
       </c>
       <c r="C1055" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1055" s="26" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="E1055" s="26" t="s">
         <v>248</v>
@@ -26288,7 +26292,7 @@
         <v>248</v>
       </c>
       <c r="G1055" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1055" s="26" t="s">
         <v>89</v>
@@ -26308,10 +26312,10 @@
         <v>413</v>
       </c>
       <c r="C1056" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1056" s="26" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E1056" s="26" t="s">
         <v>28</v>
@@ -26320,16 +26324,16 @@
         <v>28</v>
       </c>
       <c r="G1056" s="26" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H1056" s="26" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="I1056" s="26" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="J1056" s="26" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="1057" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -26340,23 +26344,23 @@
         <v>413</v>
       </c>
       <c r="C1057" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1057" s="26" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="E1057" s="26" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F1057" s="26"/>
       <c r="G1057" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1057" s="26" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="I1057" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1057" s="26"/>
     </row>
@@ -26368,10 +26372,10 @@
         <v>413</v>
       </c>
       <c r="C1058" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1058" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E1058" s="26" t="s">
         <v>108</v>
@@ -26386,7 +26390,7 @@
         <v>89</v>
       </c>
       <c r="I1058" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1058" s="26"/>
     </row>
@@ -26398,22 +26402,22 @@
         <v>413</v>
       </c>
       <c r="C1059" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1059" s="26" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="E1059" s="26" t="s">
         <v>81</v>
       </c>
       <c r="F1059" s="26" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="G1059" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1059" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1059" s="26" t="s">
         <v>81</v>
@@ -26428,10 +26432,10 @@
         <v>413</v>
       </c>
       <c r="C1060" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1060" s="26" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="E1060" s="26" t="s">
         <v>1041</v>
@@ -26458,7 +26462,7 @@
         <v>413</v>
       </c>
       <c r="C1061" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1061" s="26" t="s">
         <v>338</v>
@@ -26470,13 +26474,13 @@
         <v>89</v>
       </c>
       <c r="G1061" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1061" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1061" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1061" s="26"/>
     </row>
@@ -26488,7 +26492,7 @@
         <v>413</v>
       </c>
       <c r="C1062" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1062" s="26" t="s">
         <v>204</v>
@@ -26500,13 +26504,13 @@
         <v>89</v>
       </c>
       <c r="G1062" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1062" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1062" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1062" s="26"/>
     </row>
@@ -26518,7 +26522,7 @@
         <v>413</v>
       </c>
       <c r="C1063" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1063" s="26" t="s">
         <v>108</v>
@@ -26530,13 +26534,13 @@
         <v>89</v>
       </c>
       <c r="G1063" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1063" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1063" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1063" s="26"/>
     </row>
@@ -26548,10 +26552,10 @@
         <v>413</v>
       </c>
       <c r="C1064" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1064" s="26" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="E1064" s="26" t="s">
         <v>859</v>
@@ -26563,10 +26567,10 @@
         <v>81</v>
       </c>
       <c r="H1064" s="26" t="s">
+        <v>1236</v>
+      </c>
+      <c r="I1064" s="26" t="s">
         <v>1237</v>
-      </c>
-      <c r="I1064" s="26" t="s">
-        <v>1238</v>
       </c>
       <c r="J1064" s="26"/>
     </row>
@@ -26578,10 +26582,10 @@
         <v>413</v>
       </c>
       <c r="C1065" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1065" s="26" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="E1065" s="26" t="s">
         <v>19</v>
@@ -26593,10 +26597,10 @@
         <v>81</v>
       </c>
       <c r="H1065" s="26" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="I1065" s="26" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="J1065" s="26"/>
     </row>
@@ -26608,10 +26612,10 @@
         <v>413</v>
       </c>
       <c r="C1066" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1066" s="26" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="E1066" s="26" t="s">
         <v>81</v>
@@ -26626,7 +26630,7 @@
         <v>81</v>
       </c>
       <c r="I1066" s="26" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="J1066" s="26"/>
     </row>
@@ -26638,10 +26642,10 @@
         <v>413</v>
       </c>
       <c r="C1067" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1067" s="26" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="E1067" s="26" t="s">
         <v>89</v>
@@ -26650,7 +26654,7 @@
         <v>89</v>
       </c>
       <c r="G1067" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1067" s="26" t="s">
         <v>108</v>
@@ -26668,7 +26672,7 @@
         <v>413</v>
       </c>
       <c r="C1068" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1068" s="26" t="s">
         <v>796</v>
@@ -26680,7 +26684,7 @@
         <v>89</v>
       </c>
       <c r="G1068" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1068" s="26" t="s">
         <v>108</v>
@@ -26698,22 +26702,22 @@
         <v>413</v>
       </c>
       <c r="C1069" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1069" s="26" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="E1069" s="26" t="s">
         <v>81</v>
       </c>
       <c r="F1069" s="26" t="s">
+        <v>1244</v>
+      </c>
+      <c r="G1069" s="26" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H1069" s="26" t="s">
         <v>1245</v>
-      </c>
-      <c r="G1069" s="26" t="s">
-        <v>1184</v>
-      </c>
-      <c r="H1069" s="26" t="s">
-        <v>1246</v>
       </c>
       <c r="I1069" s="26" t="s">
         <v>81</v>
@@ -26728,10 +26732,10 @@
         <v>413</v>
       </c>
       <c r="C1070" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1070" s="26" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="E1070" s="26" t="s">
         <v>81</v>
@@ -26746,7 +26750,7 @@
         <v>81</v>
       </c>
       <c r="I1070" s="26" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="J1070" s="26"/>
     </row>
@@ -26758,19 +26762,19 @@
         <v>413</v>
       </c>
       <c r="C1071" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1071" s="26" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E1071" s="26" t="s">
         <v>1248</v>
-      </c>
-      <c r="E1071" s="26" t="s">
-        <v>1249</v>
       </c>
       <c r="F1071" s="26" t="s">
         <v>97</v>
       </c>
       <c r="G1071" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1071" s="26" t="s">
         <v>81</v>
@@ -26788,10 +26792,10 @@
         <v>413</v>
       </c>
       <c r="C1072" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1072" s="26" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="E1072" s="26" t="s">
         <v>81</v>
@@ -26806,7 +26810,7 @@
         <v>81</v>
       </c>
       <c r="I1072" s="26" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="J1072" s="26"/>
     </row>
@@ -26818,16 +26822,16 @@
         <v>413</v>
       </c>
       <c r="C1073" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1073" s="31" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="E1073" s="26" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="F1073" s="26" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="G1073" s="26" t="s">
         <v>81</v>
@@ -26848,10 +26852,10 @@
         <v>413</v>
       </c>
       <c r="C1074" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1074" s="26" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E1074" s="26" t="s">
         <v>990</v>
@@ -26878,7 +26882,7 @@
         <v>413</v>
       </c>
       <c r="C1075" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1075" s="26" t="s">
         <v>218</v>
@@ -26908,7 +26912,7 @@
         <v>413</v>
       </c>
       <c r="C1076" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1076" s="26" t="s">
         <v>796</v>
@@ -26938,7 +26942,7 @@
         <v>413</v>
       </c>
       <c r="C1077" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1077" s="26" t="s">
         <v>594</v>
@@ -26970,7 +26974,7 @@
         <v>413</v>
       </c>
       <c r="C1078" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1078" s="26" t="s">
         <v>338</v>
@@ -26988,7 +26992,7 @@
         <v>89</v>
       </c>
       <c r="I1078" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1078" s="26" t="s">
         <v>89</v>
@@ -27002,10 +27006,10 @@
         <v>413</v>
       </c>
       <c r="C1079" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1079" s="26" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E1079" s="26" t="s">
         <v>1021</v>
@@ -27017,10 +27021,10 @@
         <v>81</v>
       </c>
       <c r="H1079" s="26" t="s">
+        <v>1252</v>
+      </c>
+      <c r="I1079" s="26" t="s">
         <v>1253</v>
-      </c>
-      <c r="I1079" s="26" t="s">
-        <v>1254</v>
       </c>
       <c r="J1079" s="26" t="s">
         <v>1021</v>
@@ -27034,13 +27038,13 @@
         <v>413</v>
       </c>
       <c r="C1080" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1080" s="26" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E1080" s="26" t="s">
         <v>1255</v>
-      </c>
-      <c r="E1080" s="26" t="s">
-        <v>1256</v>
       </c>
       <c r="F1080" s="26" t="s">
         <v>924</v>
@@ -27066,10 +27070,10 @@
         <v>413</v>
       </c>
       <c r="C1081" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1081" s="26" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="E1081" s="26" t="s">
         <v>811</v>
@@ -27078,13 +27082,13 @@
         <v>811</v>
       </c>
       <c r="G1081" s="26" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H1081" s="26" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="I1081" s="26" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="J1081" s="26"/>
     </row>
@@ -27096,10 +27100,10 @@
         <v>413</v>
       </c>
       <c r="C1082" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1082" s="26" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="E1082" s="26" t="s">
         <v>28</v>
@@ -27111,10 +27115,10 @@
         <v>28</v>
       </c>
       <c r="H1082" s="26" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="I1082" s="26" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="J1082" s="26"/>
     </row>
@@ -27126,10 +27130,10 @@
         <v>413</v>
       </c>
       <c r="C1083" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1083" s="26" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="E1083" s="26" t="s">
         <v>28</v>
@@ -27156,10 +27160,10 @@
         <v>413</v>
       </c>
       <c r="C1084" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1084" s="26" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="E1084" s="26" t="s">
         <v>808</v>
@@ -27174,7 +27178,7 @@
         <v>81</v>
       </c>
       <c r="I1084" s="26" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="J1084" s="26"/>
     </row>
@@ -27186,7 +27190,7 @@
         <v>413</v>
       </c>
       <c r="C1085" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1085" s="26" t="s">
         <v>108</v>
@@ -27204,7 +27208,7 @@
         <v>89</v>
       </c>
       <c r="I1085" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1085" s="26"/>
     </row>
@@ -27216,10 +27220,10 @@
         <v>413</v>
       </c>
       <c r="C1086" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1086" s="26" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E1086" s="26" t="s">
         <v>946</v>
@@ -27231,7 +27235,7 @@
         <v>81</v>
       </c>
       <c r="H1086" s="26" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="I1086" s="26" t="s">
         <v>81</v>
@@ -27248,10 +27252,10 @@
         <v>413</v>
       </c>
       <c r="C1087" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1087" s="26" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="E1087" s="26" t="s">
         <v>89</v>
@@ -27278,10 +27282,10 @@
         <v>413</v>
       </c>
       <c r="C1088" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1088" s="26" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="E1088" s="26" t="s">
         <v>89</v>
@@ -27308,7 +27312,7 @@
         <v>413</v>
       </c>
       <c r="C1089" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1089" s="26" t="s">
         <v>50</v>
@@ -27317,7 +27321,7 @@
         <v>392</v>
       </c>
       <c r="F1089" s="26" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="G1089" s="26" t="s">
         <v>108</v>
@@ -27338,7 +27342,7 @@
         <v>413</v>
       </c>
       <c r="C1090" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1090" s="26" t="s">
         <v>233</v>
@@ -27364,16 +27368,16 @@
     </row>
     <row r="1091" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1091" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1091" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1091" s="32" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D1091" s="32" t="s">
         <v>1264</v>
-      </c>
-      <c r="D1091" s="32" t="s">
-        <v>1265</v>
       </c>
       <c r="E1091" s="32" t="s">
         <v>89</v>
@@ -27392,22 +27396,22 @@
     </row>
     <row r="1092" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1092" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1092" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1092" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D1092" s="32" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="E1092" s="32" t="s">
         <v>108</v>
       </c>
       <c r="F1092" s="32" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G1092" s="32" t="s">
         <v>89</v>
@@ -27424,43 +27428,43 @@
     </row>
     <row r="1093" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1093" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1093" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1093" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D1093" s="33" t="s">
         <v>348</v>
       </c>
       <c r="E1093" s="33" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="F1093" s="33" t="s">
         <v>89</v>
       </c>
       <c r="G1093" s="33" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1093" s="33" t="s">
         <v>108</v>
       </c>
       <c r="I1093" s="33" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1093" s="32"/>
     </row>
     <row r="1094" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1094" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1094" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1094" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D1094" s="32" t="s">
         <v>50</v>
@@ -27469,31 +27473,31 @@
         <v>808</v>
       </c>
       <c r="F1094" s="32" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G1094" s="32" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1094" s="32" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="I1094" s="32" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="J1094" s="32"/>
     </row>
     <row r="1095" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1095" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1095" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1095" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D1095" s="32" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="E1095" s="32" t="s">
         <v>401</v>
@@ -27511,18 +27515,18 @@
         <v>108</v>
       </c>
       <c r="J1095" s="32" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="1096" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1096" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1096" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1096" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D1096" s="34" t="s">
         <v>34</v>
@@ -27548,16 +27552,16 @@
     </row>
     <row r="1097" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1097" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1097" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1097" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D1097" s="34" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="E1097" s="34" t="s">
         <v>81</v>
@@ -27569,24 +27573,24 @@
         <v>81</v>
       </c>
       <c r="H1097" s="34" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="I1097" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J1097" s="34" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="1098" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1098" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1098" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1098" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D1098" s="34" t="s">
         <v>50</v>
@@ -27612,28 +27616,28 @@
     </row>
     <row r="1099" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1099" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1099" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1099" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D1099" s="34" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="E1099" s="34" t="s">
         <v>50</v>
       </c>
       <c r="F1099" s="34" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="G1099" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1099" s="34" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="I1099" s="34" t="s">
         <v>50</v>
@@ -27642,13 +27646,13 @@
     </row>
     <row r="1100" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1100" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1100" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1100" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D1100" s="34" t="s">
         <v>108</v>
@@ -27672,22 +27676,22 @@
     </row>
     <row r="1101" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1101" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1101" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1101" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D1101" s="34" t="s">
         <v>496</v>
       </c>
       <c r="E1101" s="34" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F1101" s="34" t="s">
         <v>1275</v>
-      </c>
-      <c r="F1101" s="34" t="s">
-        <v>1276</v>
       </c>
       <c r="G1101" s="34" t="s">
         <v>89</v>
@@ -27702,13 +27706,13 @@
     </row>
     <row r="1102" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1102" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1102" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1102" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D1102" s="34" t="s">
         <v>204</v>
@@ -27732,13 +27736,13 @@
     </row>
     <row r="1103" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1103" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1103" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1103" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D1103" s="34" t="s">
         <v>149</v>
@@ -27762,16 +27766,16 @@
     </row>
     <row r="1104" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1104" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1104" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1104" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D1104" s="34" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="E1104" s="34" t="s">
         <v>144</v>
@@ -27780,7 +27784,7 @@
         <v>144</v>
       </c>
       <c r="G1104" s="34" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="H1104" s="34" t="s">
         <v>89</v>
@@ -27789,27 +27793,27 @@
         <v>89</v>
       </c>
       <c r="J1104" s="34" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="1105" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1105" s="32" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B1105" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1105" s="32" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D1105" s="34" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="E1105" s="34" t="s">
         <v>81</v>
       </c>
       <c r="F1105" s="34" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="G1105" s="34" t="s">
         <v>81</v>
@@ -27830,19 +27834,19 @@
         <v>155</v>
       </c>
       <c r="C1106" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1106" s="34" t="s">
         <v>319</v>
       </c>
       <c r="E1106" s="34" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F1106" s="34" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G1106" s="34" t="s">
         <v>1280</v>
-      </c>
-      <c r="F1106" s="34" t="s">
-        <v>1280</v>
-      </c>
-      <c r="G1106" s="34" t="s">
-        <v>1281</v>
       </c>
       <c r="H1106" s="34" t="s">
         <v>143</v>
@@ -27860,28 +27864,28 @@
         <v>155</v>
       </c>
       <c r="C1107" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1107" s="34" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E1107" s="34" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="F1107" s="34" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G1107" s="34" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1107" s="34" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1107" s="34" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1107" s="34" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="1108" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27892,25 +27896,25 @@
         <v>155</v>
       </c>
       <c r="C1108" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1108" s="35" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E1108" s="35" t="s">
         <v>16</v>
       </c>
       <c r="F1108" s="35" t="s">
+        <v>1283</v>
+      </c>
+      <c r="G1108" s="35" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H1108" s="35" t="s">
         <v>1284</v>
       </c>
-      <c r="G1108" s="35" t="s">
-        <v>1283</v>
-      </c>
-      <c r="H1108" s="35" t="s">
-        <v>1285</v>
-      </c>
       <c r="I1108" s="35" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="J1108" s="34"/>
     </row>
@@ -27922,22 +27926,22 @@
         <v>155</v>
       </c>
       <c r="C1109" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1109" s="34" t="s">
         <v>108</v>
       </c>
       <c r="E1109" s="34" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F1109" s="34" t="s">
+        <v>1280</v>
+      </c>
+      <c r="G1109" s="34" t="s">
         <v>1281</v>
       </c>
-      <c r="F1109" s="34" t="s">
+      <c r="H1109" s="34" t="s">
         <v>1281</v>
-      </c>
-      <c r="G1109" s="34" t="s">
-        <v>1282</v>
-      </c>
-      <c r="H1109" s="34" t="s">
-        <v>1282</v>
       </c>
       <c r="I1109" s="34" t="s">
         <v>108</v>
@@ -27952,28 +27956,28 @@
         <v>155</v>
       </c>
       <c r="C1110" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1110" s="34" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E1110" s="34" t="s">
         <v>1286</v>
       </c>
-      <c r="E1110" s="34" t="s">
-        <v>1287</v>
-      </c>
       <c r="F1110" s="34" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="G1110" s="34" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H1110" s="34" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="I1110" s="34" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="J1110" s="34" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="1111" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27984,28 +27988,28 @@
         <v>155</v>
       </c>
       <c r="C1111" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1111" s="34" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E1111" s="34" t="s">
         <v>1286</v>
       </c>
-      <c r="E1111" s="34" t="s">
-        <v>1287</v>
-      </c>
       <c r="F1111" s="34" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="G1111" s="34" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H1111" s="34" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="I1111" s="34" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="J1111" s="34" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="1112" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28016,7 +28020,7 @@
         <v>155</v>
       </c>
       <c r="C1112" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1112" s="34" t="s">
         <v>275</v>
@@ -28025,7 +28029,7 @@
         <v>281</v>
       </c>
       <c r="F1112" s="34" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="G1112" s="34" t="s">
         <v>281</v>
@@ -28037,7 +28041,7 @@
         <v>281</v>
       </c>
       <c r="J1112" s="34" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="1113" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28048,25 +28052,25 @@
         <v>155</v>
       </c>
       <c r="C1113" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1113" s="34" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="E1113" s="34" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="F1113" s="34" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="G1113" s="34" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="H1113" s="34" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="I1113" s="34" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="J1113" s="34"/>
     </row>
@@ -28078,19 +28082,19 @@
         <v>155</v>
       </c>
       <c r="C1114" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1114" s="34" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E1114" s="34" t="s">
         <v>1290</v>
       </c>
-      <c r="E1114" s="34" t="s">
-        <v>1291</v>
-      </c>
       <c r="F1114" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="G1114" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H1114" s="34" t="s">
         <v>227</v>
@@ -28099,7 +28103,7 @@
         <v>227</v>
       </c>
       <c r="J1114" s="34" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="1115" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28110,16 +28114,16 @@
         <v>155</v>
       </c>
       <c r="C1115" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1115" s="34" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E1115" s="34" t="s">
         <v>1292</v>
       </c>
-      <c r="E1115" s="34" t="s">
-        <v>1293</v>
-      </c>
       <c r="F1115" s="34" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="G1115" s="34" t="s">
         <v>281</v>
@@ -28128,10 +28132,10 @@
         <v>157</v>
       </c>
       <c r="I1115" s="34" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="J1115" s="34" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="1116" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28142,28 +28146,28 @@
         <v>155</v>
       </c>
       <c r="C1116" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1116" s="34" t="s">
         <v>337</v>
       </c>
       <c r="E1116" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="F1116" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="G1116" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H1116" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="I1116" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="J1116" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="1117" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28174,28 +28178,28 @@
         <v>155</v>
       </c>
       <c r="C1117" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1117" s="34" t="s">
         <v>337</v>
       </c>
       <c r="E1117" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="F1117" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="G1117" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H1117" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="I1117" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="J1117" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="1118" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28206,28 +28210,28 @@
         <v>155</v>
       </c>
       <c r="C1118" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1118" s="34" t="s">
         <v>437</v>
       </c>
       <c r="E1118" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="F1118" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="G1118" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H1118" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="I1118" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="J1118" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="1119" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28238,28 +28242,28 @@
         <v>155</v>
       </c>
       <c r="C1119" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1119" s="34" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E1119" s="34" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F1119" s="34" t="s">
+        <v>1280</v>
+      </c>
+      <c r="G1119" s="34" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H1119" s="34" t="s">
         <v>1281</v>
       </c>
-      <c r="F1119" s="34" t="s">
-        <v>1281</v>
-      </c>
-      <c r="G1119" s="34" t="s">
-        <v>1281</v>
-      </c>
-      <c r="H1119" s="34" t="s">
-        <v>1282</v>
-      </c>
       <c r="I1119" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="J1119" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="1120" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28270,25 +28274,25 @@
         <v>155</v>
       </c>
       <c r="C1120" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1120" s="34" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="E1120" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="F1120" s="34" t="s">
         <v>108</v>
       </c>
       <c r="G1120" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H1120" s="34" t="s">
         <v>108</v>
       </c>
       <c r="I1120" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="J1120" s="34"/>
     </row>
@@ -28300,19 +28304,19 @@
         <v>155</v>
       </c>
       <c r="C1121" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1121" s="36" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E1121" s="36" t="s">
         <v>1296</v>
       </c>
-      <c r="E1121" s="36" t="s">
-        <v>1297</v>
-      </c>
       <c r="F1121" s="36" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="G1121" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H1121" s="34" t="s">
         <v>108</v>
@@ -28330,28 +28334,28 @@
         <v>155</v>
       </c>
       <c r="C1122" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1122" s="34" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="E1122" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="F1122" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="G1122" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1122" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="I1122" s="34" t="s">
         <v>108</v>
       </c>
       <c r="J1122" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="1123" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28362,28 +28366,28 @@
         <v>155</v>
       </c>
       <c r="C1123" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1123" s="34" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="E1123" s="34" t="s">
         <v>143</v>
       </c>
       <c r="F1123" s="34" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G1123" s="34" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H1123" s="34" t="s">
+        <v>1183</v>
+      </c>
+      <c r="I1123" s="34" t="s">
         <v>1280</v>
       </c>
-      <c r="G1123" s="34" t="s">
-        <v>1184</v>
-      </c>
-      <c r="H1123" s="34" t="s">
-        <v>1184</v>
-      </c>
-      <c r="I1123" s="34" t="s">
-        <v>1281</v>
-      </c>
       <c r="J1123" s="34" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="1124" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28394,28 +28398,28 @@
         <v>155</v>
       </c>
       <c r="C1124" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1124" s="34" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E1124" s="34" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F1124" s="34" t="s">
         <v>1301</v>
-      </c>
-      <c r="E1124" s="34" t="s">
-        <v>1281</v>
-      </c>
-      <c r="F1124" s="34" t="s">
-        <v>1302</v>
       </c>
       <c r="G1124" s="34" t="s">
         <v>228</v>
       </c>
       <c r="H1124" s="34" t="s">
+        <v>1300</v>
+      </c>
+      <c r="I1124" s="34" t="s">
+        <v>1281</v>
+      </c>
+      <c r="J1124" s="34" t="s">
         <v>1301</v>
-      </c>
-      <c r="I1124" s="34" t="s">
-        <v>1282</v>
-      </c>
-      <c r="J1124" s="34" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="1125" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28426,40 +28430,40 @@
         <v>155</v>
       </c>
       <c r="C1125" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D1125" s="34" t="s">
         <v>111</v>
       </c>
       <c r="E1125" s="34" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="F1125" s="34" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="G1125" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1125" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="I1125" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="J1125" s="34"/>
     </row>
     <row r="1126" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1126" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1126" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1126" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1126" s="34" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E1126" s="34" t="s">
         <v>808</v>
@@ -28468,10 +28472,10 @@
         <v>808</v>
       </c>
       <c r="G1126" s="34" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1126" s="34" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1126" s="34" t="s">
         <v>81</v>
@@ -28480,16 +28484,16 @@
     </row>
     <row r="1127" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1127" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1127" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1127" s="34" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D1127" s="34" t="s">
         <v>1303</v>
-      </c>
-      <c r="D1127" s="34" t="s">
-        <v>1304</v>
       </c>
       <c r="E1127" s="34" t="s">
         <v>969</v>
@@ -28510,16 +28514,16 @@
     </row>
     <row r="1128" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1128" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1128" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1128" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1128" s="34" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="E1128" s="34" t="s">
         <v>242</v>
@@ -28542,16 +28546,16 @@
     </row>
     <row r="1129" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1129" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1129" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1129" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1129" s="34" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E1129" s="34" t="s">
         <v>14</v>
@@ -28572,13 +28576,13 @@
     </row>
     <row r="1130" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1130" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1130" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1130" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1130" s="34" t="s">
         <v>142</v>
@@ -28602,16 +28606,16 @@
     </row>
     <row r="1131" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1131" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1131" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1131" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1131" s="34" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="E1131" s="34" t="s">
         <v>19</v>
@@ -28623,7 +28627,7 @@
         <v>81</v>
       </c>
       <c r="H1131" s="34" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="I1131" s="34" t="s">
         <v>34</v>
@@ -28632,16 +28636,16 @@
     </row>
     <row r="1132" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1132" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1132" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1132" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1132" s="34" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="E1132" s="34" t="s">
         <v>242</v>
@@ -28656,19 +28660,19 @@
         <v>98</v>
       </c>
       <c r="I1132" s="34" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="J1132" s="34"/>
     </row>
     <row r="1133" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1133" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1133" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1133" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1133" s="34" t="s">
         <v>321</v>
@@ -28692,13 +28696,13 @@
     </row>
     <row r="1134" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1134" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1134" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1134" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1134" s="34" t="s">
         <v>204</v>
@@ -28722,19 +28726,19 @@
     </row>
     <row r="1135" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1135" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1135" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1135" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1135" s="34" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E1135" s="34" t="s">
         <v>1310</v>
-      </c>
-      <c r="E1135" s="34" t="s">
-        <v>1311</v>
       </c>
       <c r="F1135" s="34" t="s">
         <v>89</v>
@@ -28754,16 +28758,16 @@
     </row>
     <row r="1136" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1136" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1136" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1136" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1136" s="34" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E1136" s="34" t="s">
         <v>34</v>
@@ -28784,13 +28788,13 @@
     </row>
     <row r="1137" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1137" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1137" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1137" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1137" s="34" t="s">
         <v>204</v>
@@ -28814,13 +28818,13 @@
     </row>
     <row r="1138" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1138" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1138" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1138" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1138" s="34" t="s">
         <v>149</v>
@@ -28844,16 +28848,16 @@
     </row>
     <row r="1139" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1139" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1139" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1139" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1139" s="34" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="E1139" s="34" t="s">
         <v>89</v>
@@ -28874,28 +28878,28 @@
     </row>
     <row r="1140" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1140" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1140" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1140" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1140" s="34" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="E1140" s="34" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F1140" s="34" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="G1140" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1140" s="34" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1140" s="34" t="s">
         <v>81</v>
@@ -28904,16 +28908,16 @@
     </row>
     <row r="1141" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1141" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1141" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1141" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1141" s="34" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="E1141" s="34" t="s">
         <v>54</v>
@@ -28934,13 +28938,13 @@
     </row>
     <row r="1142" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1142" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1142" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1142" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1142" s="34" t="s">
         <v>204</v>
@@ -28964,13 +28968,13 @@
     </row>
     <row r="1143" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1143" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1143" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1143" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1143" s="34" t="s">
         <v>206</v>
@@ -28996,16 +29000,16 @@
     </row>
     <row r="1144" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1144" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1144" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1144" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1144" s="34" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="E1144" s="34" t="s">
         <v>242</v>
@@ -29014,7 +29018,7 @@
         <v>89</v>
       </c>
       <c r="G1144" s="34" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1144" s="34" t="s">
         <v>89</v>
@@ -29026,16 +29030,16 @@
     </row>
     <row r="1145" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1145" s="34" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B1145" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1145" s="34" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D1145" s="34" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="E1145" s="34" t="s">
         <v>141</v>
@@ -29058,13 +29062,13 @@
     </row>
     <row r="1146" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1146" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1146" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1146" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1146" s="38" t="s">
         <v>81</v>
@@ -29088,13 +29092,13 @@
     </row>
     <row r="1147" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1147" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1147" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1147" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1147" s="38" t="s">
         <v>81</v>
@@ -29118,13 +29122,13 @@
     </row>
     <row r="1148" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1148" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1148" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1148" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1148" s="38" t="s">
         <v>108</v>
@@ -29148,28 +29152,28 @@
     </row>
     <row r="1149" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1149" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1149" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1149" s="37" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D1149" s="38" t="s">
         <v>1317</v>
       </c>
-      <c r="D1149" s="38" t="s">
-        <v>1318</v>
-      </c>
       <c r="E1149" s="37" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="F1149" s="38" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="G1149" s="37" t="s">
         <v>108</v>
       </c>
       <c r="H1149" s="38" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="I1149" s="37" t="s">
         <v>22</v>
@@ -29180,22 +29184,22 @@
     </row>
     <row r="1150" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1150" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1150" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1150" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1150" s="38" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E1150" s="37" t="s">
         <v>1319</v>
       </c>
-      <c r="E1150" s="37" t="s">
+      <c r="F1150" s="38" t="s">
         <v>1320</v>
-      </c>
-      <c r="F1150" s="38" t="s">
-        <v>1321</v>
       </c>
       <c r="G1150" s="37" t="s">
         <v>89</v>
@@ -29210,16 +29214,16 @@
     </row>
     <row r="1151" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1151" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1151" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1151" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1151" s="38" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="E1151" s="37" t="s">
         <v>141</v>
@@ -29234,22 +29238,22 @@
         <v>54</v>
       </c>
       <c r="I1151" s="37" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="J1151" s="38"/>
     </row>
     <row r="1152" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1152" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1152" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1152" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1152" s="38" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="E1152" s="37" t="s">
         <v>89</v>
@@ -29264,34 +29268,34 @@
         <v>89</v>
       </c>
       <c r="I1152" s="37" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="J1152" s="38"/>
     </row>
     <row r="1153" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1153" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1153" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1153" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1153" s="38" t="s">
         <v>204</v>
       </c>
       <c r="E1153" s="37" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="F1153" s="38" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G1153" s="37" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1153" s="38" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1153" s="37" t="s">
         <v>204</v>
@@ -29300,91 +29304,91 @@
     </row>
     <row r="1154" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1154" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1154" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1154" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1154" s="38" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E1154" s="37" t="s">
         <v>1324</v>
       </c>
-      <c r="E1154" s="37" t="s">
-        <v>1325</v>
-      </c>
       <c r="F1154" s="38" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G1154" s="37" t="s">
         <v>108</v>
       </c>
       <c r="H1154" s="38" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="I1154" s="37" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="J1154" s="38"/>
     </row>
     <row r="1155" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1155" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1155" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1155" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1155" s="38" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="E1155" s="37" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="F1155" s="38" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G1155" s="37" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="H1155" s="38" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="I1155" s="37" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="J1155" s="38"/>
     </row>
     <row r="1156" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1156" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1156" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1156" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1156" s="38" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E1156" s="37" t="s">
         <v>1327</v>
-      </c>
-      <c r="E1156" s="37" t="s">
-        <v>1328</v>
       </c>
       <c r="F1156" s="38" t="s">
         <v>219</v>
       </c>
       <c r="G1156" s="37" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1156" s="38" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="I1156" s="37" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="J1156" s="38" t="s">
         <v>219</v>
@@ -29392,19 +29396,19 @@
     </row>
     <row r="1157" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1157" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1157" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1157" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1157" s="38" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="E1157" s="37" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="F1157" s="38" t="s">
         <v>902</v>
@@ -29413,28 +29417,28 @@
         <v>81</v>
       </c>
       <c r="H1157" s="38" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="I1157" s="37" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="J1157" s="38"/>
     </row>
     <row r="1158" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1158" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1158" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1158" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1158" s="38" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="E1158" s="37" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F1158" s="38" t="s">
         <v>902</v>
@@ -29446,67 +29450,67 @@
         <v>81</v>
       </c>
       <c r="I1158" s="37" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="J1158" s="38"/>
     </row>
     <row r="1159" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1159" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1159" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1159" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1159" s="38" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="E1159" s="37" t="s">
         <v>34</v>
       </c>
       <c r="F1159" s="38" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="G1159" s="37" t="s">
         <v>81</v>
       </c>
       <c r="H1159" s="38" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="I1159" s="37" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="J1159" s="38"/>
     </row>
     <row r="1160" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1160" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1160" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1160" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1160" s="38" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E1160" s="37" t="s">
         <v>1333</v>
-      </c>
-      <c r="E1160" s="37" t="s">
-        <v>1334</v>
       </c>
       <c r="F1160" s="38" t="s">
         <v>832</v>
       </c>
       <c r="G1160" s="37" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H1160" s="38" t="s">
+        <v>1195</v>
+      </c>
+      <c r="I1160" s="37" t="s">
         <v>1335</v>
-      </c>
-      <c r="H1160" s="38" t="s">
-        <v>1196</v>
-      </c>
-      <c r="I1160" s="37" t="s">
-        <v>1336</v>
       </c>
       <c r="J1160" s="38" t="s">
         <v>81</v>
@@ -29514,16 +29518,16 @@
     </row>
     <row r="1161" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1161" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1161" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1161" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1161" s="38" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="E1161" s="37" t="s">
         <v>847</v>
@@ -29532,43 +29536,43 @@
         <v>847</v>
       </c>
       <c r="G1161" s="37" t="s">
+        <v>1337</v>
+      </c>
+      <c r="H1161" s="38" t="s">
         <v>1338</v>
       </c>
-      <c r="H1161" s="38" t="s">
-        <v>1339</v>
-      </c>
       <c r="I1161" s="37" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="J1161" s="38"/>
     </row>
     <row r="1162" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1162" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1162" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1162" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1162" s="38" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E1162" s="37" t="s">
         <v>1340</v>
       </c>
-      <c r="E1162" s="37" t="s">
+      <c r="F1162" s="38" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G1162" s="37" t="s">
         <v>1341</v>
-      </c>
-      <c r="F1162" s="38" t="s">
-        <v>1341</v>
-      </c>
-      <c r="G1162" s="37" t="s">
-        <v>1342</v>
       </c>
       <c r="H1162" s="38" t="s">
         <v>81</v>
       </c>
       <c r="I1162" s="37" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="J1162" s="38" t="s">
         <v>81</v>
@@ -29576,13 +29580,13 @@
     </row>
     <row r="1163" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1163" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1163" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1163" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1163" s="38" t="s">
         <v>108</v>
@@ -29606,13 +29610,13 @@
     </row>
     <row r="1164" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1164" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1164" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1164" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1164" s="38" t="s">
         <v>108</v>
@@ -29636,31 +29640,31 @@
     </row>
     <row r="1165" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1165" s="37" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B1165" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1165" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D1165" s="38" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E1165" s="37" t="s">
         <v>1327</v>
-      </c>
-      <c r="E1165" s="37" t="s">
-        <v>1328</v>
       </c>
       <c r="F1165" s="38" t="s">
         <v>219</v>
       </c>
       <c r="G1165" s="37" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1165" s="38" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="I1165" s="37" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="J1165" s="38" t="s">
         <v>219</v>
@@ -29668,13 +29672,13 @@
     </row>
     <row r="1166" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1166" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1166" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1166" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1166" s="34" t="s">
         <v>108</v>
@@ -29698,16 +29702,16 @@
     </row>
     <row r="1167" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1167" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1167" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1167" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1167" s="34" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="E1167" s="34" t="s">
         <v>143</v>
@@ -29728,19 +29732,19 @@
     </row>
     <row r="1168" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1168" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1168" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1168" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1168" s="35" t="s">
         <v>338</v>
       </c>
       <c r="E1168" s="35" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="F1168" s="35" t="s">
         <v>89</v>
@@ -29758,13 +29762,13 @@
     </row>
     <row r="1169" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1169" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1169" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1169" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1169" s="34" t="s">
         <v>108</v>
@@ -29788,13 +29792,13 @@
     </row>
     <row r="1170" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1170" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1170" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1170" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1170" s="34" t="s">
         <v>114</v>
@@ -29820,19 +29824,19 @@
     </row>
     <row r="1171" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1171" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1171" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1171" s="34" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D1171" s="34" t="s">
         <v>1343</v>
       </c>
-      <c r="D1171" s="34" t="s">
+      <c r="E1171" s="34" t="s">
         <v>1344</v>
-      </c>
-      <c r="E1171" s="34" t="s">
-        <v>1345</v>
       </c>
       <c r="F1171" s="34" t="s">
         <v>832</v>
@@ -29850,13 +29854,13 @@
     </row>
     <row r="1172" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1172" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1172" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1172" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1172" s="34" t="s">
         <v>338</v>
@@ -29880,13 +29884,13 @@
     </row>
     <row r="1173" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1173" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1173" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1173" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1173" s="34" t="s">
         <v>458</v>
@@ -29912,16 +29916,16 @@
     </row>
     <row r="1174" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1174" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1174" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1174" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1174" s="34" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="E1174" s="34" t="s">
         <v>82</v>
@@ -29944,22 +29948,22 @@
     </row>
     <row r="1175" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1175" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1175" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1175" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1175" s="34" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E1175" s="34" t="s">
         <v>1347</v>
       </c>
-      <c r="E1175" s="34" t="s">
-        <v>1348</v>
-      </c>
       <c r="F1175" s="34" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="G1175" s="34" t="s">
         <v>108</v>
@@ -29976,22 +29980,22 @@
     </row>
     <row r="1176" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1176" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1176" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1176" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1176" s="34" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="E1176" s="34" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="F1176" s="34" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="G1176" s="34" t="s">
         <v>81</v>
@@ -30008,16 +30012,16 @@
     </row>
     <row r="1177" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1177" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1177" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1177" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1177" s="34" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="E1177" s="34" t="s">
         <v>89</v>
@@ -30038,13 +30042,13 @@
     </row>
     <row r="1178" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1178" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1178" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1178" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1178" s="34" t="s">
         <v>334</v>
@@ -30068,13 +30072,13 @@
     </row>
     <row r="1179" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1179" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1179" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1179" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1179" s="34" t="s">
         <v>280</v>
@@ -30098,16 +30102,16 @@
     </row>
     <row r="1180" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1180" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1180" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1180" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1180" s="34" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="E1180" s="34" t="s">
         <v>89</v>
@@ -30128,16 +30132,16 @@
     </row>
     <row r="1181" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1181" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1181" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1181" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1181" s="34" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="E1181" s="34" t="s">
         <v>51</v>
@@ -30160,16 +30164,16 @@
     </row>
     <row r="1182" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1182" s="34" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B1182" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1182" s="34" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D1182" s="34" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="E1182" s="34" t="s">
         <v>89</v>
@@ -30181,7 +30185,7 @@
         <v>89</v>
       </c>
       <c r="H1182" s="34" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="I1182" s="34" t="s">
         <v>108</v>
@@ -30190,13 +30194,13 @@
     </row>
     <row r="1183" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1183" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1183" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1183" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1183" s="39" t="s">
         <v>410</v>
@@ -30220,16 +30224,16 @@
     </row>
     <row r="1184" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1184" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1184" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1184" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1184" s="39" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="E1184" s="39" t="s">
         <v>89</v>
@@ -30248,25 +30252,25 @@
     </row>
     <row r="1185" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1185" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1185" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1185" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1185" s="39" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E1185" s="39" t="s">
         <v>1355</v>
       </c>
-      <c r="E1185" s="39" t="s">
-        <v>1356</v>
-      </c>
       <c r="F1185" s="39" t="s">
         <v>89</v>
       </c>
       <c r="G1185" s="39" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="H1185" s="39" t="s">
         <v>89</v>
@@ -30278,43 +30282,43 @@
     </row>
     <row r="1186" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1186" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1186" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1186" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1186" s="39" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E1186" s="39" t="s">
         <v>832</v>
       </c>
       <c r="F1186" s="39" t="s">
+        <v>1357</v>
+      </c>
+      <c r="G1186" s="39" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H1186" s="39" t="s">
         <v>1358</v>
       </c>
-      <c r="G1186" s="39" t="s">
-        <v>1184</v>
-      </c>
-      <c r="H1186" s="39" t="s">
-        <v>1359</v>
-      </c>
       <c r="I1186" s="39" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="J1186" s="39"/>
     </row>
     <row r="1187" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1187" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1187" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1187" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1187" s="40" t="s">
         <v>594</v>
@@ -30338,13 +30342,13 @@
     </row>
     <row r="1188" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1188" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1188" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1188" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1188" s="40" t="s">
         <v>108</v>
@@ -30368,13 +30372,13 @@
     </row>
     <row r="1189" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1189" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1189" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1189" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1189" s="40" t="s">
         <v>204</v>
@@ -30398,19 +30402,19 @@
     </row>
     <row r="1190" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1190" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1190" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1190" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1190" s="40" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="E1190" s="40" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="F1190" s="40" t="s">
         <v>808</v>
@@ -30419,7 +30423,7 @@
         <v>81</v>
       </c>
       <c r="H1190" s="40" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="I1190" s="40" t="s">
         <v>81</v>
@@ -30428,13 +30432,13 @@
     </row>
     <row r="1191" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1191" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1191" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1191" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1191" s="40" t="s">
         <v>108</v>
@@ -30446,7 +30450,7 @@
         <v>89</v>
       </c>
       <c r="G1191" s="40" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1191" s="40" t="s">
         <v>89</v>
@@ -30458,16 +30462,16 @@
     </row>
     <row r="1192" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1192" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1192" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1192" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1192" s="40" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E1192" s="40" t="s">
         <v>169</v>
@@ -30490,13 +30494,13 @@
     </row>
     <row r="1193" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1193" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1193" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1193" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1193" s="40" t="s">
         <v>495</v>
@@ -30522,13 +30526,13 @@
     </row>
     <row r="1194" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1194" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1194" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1194" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1194" s="40" t="s">
         <v>50</v>
@@ -30554,13 +30558,13 @@
     </row>
     <row r="1195" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1195" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1195" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1195" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1195" s="40" t="s">
         <v>393</v>
@@ -30576,25 +30580,25 @@
         <v>108</v>
       </c>
       <c r="I1195" s="40" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1195" s="40"/>
     </row>
     <row r="1196" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1196" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1196" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1196" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1196" s="40" t="s">
         <v>321</v>
       </c>
       <c r="E1196" s="40" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="F1196" s="40" t="s">
         <v>89</v>
@@ -30612,13 +30616,13 @@
     </row>
     <row r="1197" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1197" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1197" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1197" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1197" s="40" t="s">
         <v>108</v>
@@ -30648,7 +30652,7 @@
         <v>413</v>
       </c>
       <c r="C1198" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1198" s="40" t="s">
         <v>204</v>
@@ -30676,10 +30680,10 @@
         <v>413</v>
       </c>
       <c r="C1199" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1199" s="40" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="E1199" s="40" t="s">
         <v>89</v>
@@ -30704,7 +30708,7 @@
         <v>413</v>
       </c>
       <c r="C1200" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1200" s="40" t="s">
         <v>108</v>
@@ -30716,7 +30720,7 @@
         <v>89</v>
       </c>
       <c r="G1200" s="40" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1200" s="40" t="s">
         <v>108</v>
@@ -30734,10 +30738,10 @@
         <v>413</v>
       </c>
       <c r="C1201" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1201" s="40" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="E1201" s="40" t="s">
         <v>16</v>
@@ -30749,7 +30753,7 @@
         <v>81</v>
       </c>
       <c r="H1201" s="40" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="I1201" s="40" t="s">
         <v>81</v>
@@ -30764,10 +30768,10 @@
         <v>413</v>
       </c>
       <c r="C1202" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1202" s="40" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="E1202" s="40" t="s">
         <v>89</v>
@@ -30794,10 +30798,10 @@
         <v>413</v>
       </c>
       <c r="C1203" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1203" s="40" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="E1203" s="40" t="s">
         <v>94</v>
@@ -30826,7 +30830,7 @@
         <v>413</v>
       </c>
       <c r="C1204" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1204" s="40" t="s">
         <v>338</v>
@@ -30838,10 +30842,10 @@
         <v>89</v>
       </c>
       <c r="G1204" s="40" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H1204" s="40" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="I1204" s="40" t="s">
         <v>89</v>
@@ -30856,7 +30860,7 @@
         <v>413</v>
       </c>
       <c r="C1205" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1205" s="40" t="s">
         <v>392</v>
@@ -30884,7 +30888,7 @@
         <v>413</v>
       </c>
       <c r="C1206" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1206" s="40" t="s">
         <v>108</v>
@@ -30912,10 +30916,10 @@
         <v>413</v>
       </c>
       <c r="C1207" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1207" s="40" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="E1207" s="40" t="s">
         <v>89</v>
@@ -30924,13 +30928,13 @@
         <v>89</v>
       </c>
       <c r="G1207" s="40" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1207" s="40" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1207" s="40" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1207" s="40"/>
     </row>
@@ -30942,16 +30946,16 @@
         <v>413</v>
       </c>
       <c r="C1208" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1208" s="40" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E1208" s="40" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F1208" s="40" t="s">
         <v>1366</v>
-      </c>
-      <c r="E1208" s="40" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F1208" s="40" t="s">
-        <v>1367</v>
       </c>
       <c r="G1208" s="40" t="s">
         <v>89</v>
@@ -30960,7 +30964,7 @@
         <v>108</v>
       </c>
       <c r="I1208" s="40" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1208" s="40" t="s">
         <v>955</v>
@@ -30974,10 +30978,10 @@
         <v>413</v>
       </c>
       <c r="C1209" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1209" s="40" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="E1209" s="40" t="s">
         <v>141</v>
@@ -31006,10 +31010,10 @@
         <v>413</v>
       </c>
       <c r="C1210" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1210" s="40" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="E1210" s="40" t="s">
         <v>141</v>
@@ -31036,10 +31040,10 @@
         <v>413</v>
       </c>
       <c r="C1211" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1211" s="40" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="E1211" s="40" t="s">
         <v>847</v>
@@ -31051,10 +31055,10 @@
         <v>81</v>
       </c>
       <c r="H1211" s="40" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="I1211" s="40" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="J1211" s="40"/>
     </row>
@@ -31066,7 +31070,7 @@
         <v>413</v>
       </c>
       <c r="C1212" s="26" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D1212" s="41" t="s">
         <v>676</v>
@@ -31094,7 +31098,7 @@
         <v>11</v>
       </c>
       <c r="C1213" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1213" s="32" t="s">
         <v>108</v>
@@ -31124,10 +31128,10 @@
         <v>11</v>
       </c>
       <c r="C1214" s="32" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D1214" s="32" t="s">
         <v>1368</v>
-      </c>
-      <c r="D1214" s="32" t="s">
-        <v>1369</v>
       </c>
       <c r="E1214" s="32" t="s">
         <v>89</v>
@@ -31156,16 +31160,16 @@
         <v>11</v>
       </c>
       <c r="C1215" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1215" s="32" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="E1215" s="32" t="s">
         <v>847</v>
       </c>
       <c r="F1215" s="32" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="G1215" s="32" t="s">
         <v>89</v>
@@ -31188,16 +31192,16 @@
         <v>11</v>
       </c>
       <c r="C1216" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1216" s="32" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="E1216" s="32" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="F1216" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="G1216" s="32" t="s">
         <v>50</v>
@@ -31218,7 +31222,7 @@
         <v>11</v>
       </c>
       <c r="C1217" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1217" s="32" t="s">
         <v>146</v>
@@ -31250,7 +31254,7 @@
         <v>11</v>
       </c>
       <c r="C1218" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1218" s="32" t="s">
         <v>108</v>
@@ -31280,7 +31284,7 @@
         <v>11</v>
       </c>
       <c r="C1219" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1219" s="32" t="s">
         <v>351</v>
@@ -31289,7 +31293,7 @@
         <v>89</v>
       </c>
       <c r="F1219" s="32" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="G1219" s="32" t="s">
         <v>108</v>
@@ -31310,28 +31314,28 @@
         <v>11</v>
       </c>
       <c r="C1220" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1220" s="32" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="E1220" s="32" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="F1220" s="32" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G1220" s="32" t="s">
         <v>89</v>
       </c>
       <c r="H1220" s="32" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="I1220" s="32" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="J1220" s="32" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="1221" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31342,7 +31346,7 @@
         <v>11</v>
       </c>
       <c r="C1221" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1221" s="32" t="s">
         <v>297</v>
@@ -31374,16 +31378,16 @@
         <v>11</v>
       </c>
       <c r="C1222" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1222" s="32" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E1222" s="32" t="s">
         <v>1375</v>
       </c>
-      <c r="E1222" s="32" t="s">
-        <v>1376</v>
-      </c>
       <c r="F1222" s="32" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G1222" s="32" t="s">
         <v>89</v>
@@ -31404,7 +31408,7 @@
         <v>11</v>
       </c>
       <c r="C1223" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1223" s="32" t="s">
         <v>108</v>
@@ -31434,7 +31438,7 @@
         <v>11</v>
       </c>
       <c r="C1224" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1224" s="32" t="s">
         <v>334</v>
@@ -31464,7 +31468,7 @@
         <v>11</v>
       </c>
       <c r="C1225" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1225" s="32" t="s">
         <v>51</v>
@@ -31485,7 +31489,7 @@
         <v>81</v>
       </c>
       <c r="J1225" s="32" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="1226" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31496,10 +31500,10 @@
         <v>11</v>
       </c>
       <c r="C1226" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1226" s="32" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="E1226" s="32" t="s">
         <v>983</v>
@@ -31526,10 +31530,10 @@
         <v>11</v>
       </c>
       <c r="C1227" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1227" s="32" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="E1227" s="32" t="s">
         <v>16</v>
@@ -31550,13 +31554,13 @@
     </row>
     <row r="1228" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1228" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1228" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1228" s="43" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D1228" s="42" t="s">
         <v>108</v>
@@ -31582,13 +31586,13 @@
     </row>
     <row r="1229" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1229" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1229" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1229" s="43" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D1229" s="42" t="s">
         <v>50</v>
@@ -31612,13 +31616,13 @@
     </row>
     <row r="1230" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1230" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1230" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1230" s="43" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D1230" s="42" t="s">
         <v>411</v>
@@ -31633,22 +31637,22 @@
         <v>108</v>
       </c>
       <c r="H1230" s="42" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="I1230" s="42" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="J1230" s="43"/>
     </row>
     <row r="1231" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1231" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1231" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1231" s="43" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D1231" s="42" t="s">
         <v>351</v>
@@ -31657,7 +31661,7 @@
         <v>89</v>
       </c>
       <c r="F1231" s="42" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="G1231" s="42" t="s">
         <v>108</v>
@@ -31672,13 +31676,13 @@
     </row>
     <row r="1232" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1232" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1232" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1232" s="43" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D1232" s="42" t="s">
         <v>338</v>
@@ -31704,16 +31708,16 @@
     </row>
     <row r="1233" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1233" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1233" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1233" s="43" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D1233" s="42" t="s">
         <v>1379</v>
-      </c>
-      <c r="D1233" s="42" t="s">
-        <v>1380</v>
       </c>
       <c r="E1233" s="42" t="s">
         <v>89</v>
@@ -31736,13 +31740,13 @@
     </row>
     <row r="1234" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1234" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1234" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1234" s="43" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D1234" s="42" t="s">
         <v>458</v>
@@ -31766,22 +31770,22 @@
     </row>
     <row r="1235" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1235" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1235" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1235" s="43" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D1235" s="44" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="E1235" s="42" t="s">
         <v>81</v>
       </c>
       <c r="F1235" s="42" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="G1235" s="42" t="s">
         <v>108</v>
@@ -31791,51 +31795,51 @@
       </c>
       <c r="I1235" s="43"/>
       <c r="J1235" s="42" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="1236" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1236" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1236" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1236" s="43" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D1236" s="45" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="E1236" s="42" t="s">
         <v>325</v>
       </c>
       <c r="F1236" s="42" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="G1236" s="42" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H1236" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1236" s="42" t="s">
         <v>1384</v>
-      </c>
-      <c r="H1236" s="42" t="s">
-        <v>89</v>
-      </c>
-      <c r="I1236" s="42" t="s">
-        <v>1385</v>
       </c>
       <c r="J1236" s="43"/>
     </row>
     <row r="1237" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1237" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1237" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1237" s="43" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D1237" s="46" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="E1237" s="42" t="s">
         <v>108</v>
@@ -31858,22 +31862,22 @@
     </row>
     <row r="1238" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1238" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1238" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1238" s="43" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D1238" s="47" t="s">
+        <v>1386</v>
+      </c>
+      <c r="E1238" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1238" s="42" t="s">
         <v>1387</v>
-      </c>
-      <c r="E1238" s="42" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1238" s="42" t="s">
-        <v>1388</v>
       </c>
       <c r="G1238" s="42" t="s">
         <v>108</v>
@@ -31888,16 +31892,16 @@
     </row>
     <row r="1239" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1239" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1239" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1239" s="43" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D1239" s="42" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E1239" s="42" t="s">
         <v>26</v>
@@ -31918,16 +31922,16 @@
     </row>
     <row r="1240" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1240" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1240" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1240" s="43" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D1240" s="48" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="E1240" s="42" t="s">
         <v>89</v>
@@ -31950,28 +31954,28 @@
     </row>
     <row r="1241" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1241" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1241" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1241" s="43" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D1241" s="42" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="E1241" s="42" t="s">
         <v>847</v>
       </c>
       <c r="F1241" s="42" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="G1241" s="42" t="s">
         <v>81</v>
       </c>
       <c r="H1241" s="42" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="I1241" s="42" t="s">
         <v>81</v>
@@ -31980,16 +31984,16 @@
     </row>
     <row r="1242" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1242" s="42" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B1242" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1242" s="43" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="D1242" s="42" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="E1242" s="42" t="s">
         <v>19</v>
@@ -32001,22 +32005,22 @@
         <v>81</v>
       </c>
       <c r="H1242" s="42" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="I1242" s="42" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="J1242" s="43"/>
     </row>
     <row r="1243" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1243" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1243" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1243" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1243" s="50" t="s">
         <v>50</v>
@@ -32028,7 +32032,7 @@
         <v>89</v>
       </c>
       <c r="G1243" s="50" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H1243" s="50" t="s">
         <v>89</v>
@@ -32040,16 +32044,16 @@
     </row>
     <row r="1244" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1244" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1244" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1244" s="50" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D1244" s="49" t="s">
         <v>1395</v>
-      </c>
-      <c r="D1244" s="49" t="s">
-        <v>1396</v>
       </c>
       <c r="E1244" s="49" t="s">
         <v>89</v>
@@ -32068,19 +32072,19 @@
     </row>
     <row r="1245" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1245" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1245" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1245" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1245" s="49" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="E1245" s="49" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="F1245" s="49" t="s">
         <v>19</v>
@@ -32098,16 +32102,16 @@
     </row>
     <row r="1246" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1246" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1246" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1246" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1246" s="51" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E1246" s="51" t="s">
         <v>89</v>
@@ -32128,13 +32132,13 @@
     </row>
     <row r="1247" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1247" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1247" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1247" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1247" s="49" t="s">
         <v>384</v>
@@ -32146,28 +32150,28 @@
         <v>89</v>
       </c>
       <c r="G1247" s="49" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1247" s="49" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1247" s="49" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1247" s="49"/>
     </row>
     <row r="1248" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1248" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1248" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1248" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1248" s="49" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="E1248" s="49" t="s">
         <v>89</v>
@@ -32176,34 +32180,34 @@
         <v>89</v>
       </c>
       <c r="G1248" s="49" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1248" s="49" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1248" s="49" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1248" s="49"/>
     </row>
     <row r="1249" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1249" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1249" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1249" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1249" s="49" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="E1249" s="49" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F1249" s="49" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="G1249" s="49" t="s">
         <v>89</v>
@@ -32220,28 +32224,28 @@
     </row>
     <row r="1250" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1250" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1250" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1250" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1250" s="49" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E1250" s="49" t="s">
         <v>1400</v>
       </c>
-      <c r="E1250" s="49" t="s">
-        <v>1401</v>
-      </c>
       <c r="F1250" s="49" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="G1250" s="49" t="s">
         <v>81</v>
       </c>
       <c r="H1250" s="49" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="I1250" s="49" t="s">
         <v>81</v>
@@ -32252,19 +32256,19 @@
     </row>
     <row r="1251" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1251" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1251" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1251" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1251" s="49" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E1251" s="49" t="s">
         <v>1403</v>
-      </c>
-      <c r="E1251" s="49" t="s">
-        <v>1404</v>
       </c>
       <c r="F1251" s="49"/>
       <c r="G1251" s="49"/>
@@ -32278,13 +32282,13 @@
     </row>
     <row r="1252" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1252" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1252" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1252" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1252" s="49" t="s">
         <v>242</v>
@@ -32308,16 +32312,16 @@
     </row>
     <row r="1253" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1253" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1253" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1253" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1253" s="49" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="E1253" s="49" t="s">
         <v>89</v>
@@ -32326,28 +32330,28 @@
         <v>89</v>
       </c>
       <c r="G1253" s="49" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1253" s="49" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1253" s="49" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1253" s="49"/>
     </row>
     <row r="1254" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1254" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1254" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1254" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1254" s="49" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="E1254" s="49" t="s">
         <v>218</v>
@@ -32356,10 +32360,10 @@
         <v>219</v>
       </c>
       <c r="G1254" s="49" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1254" s="49" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="I1254" s="49" t="s">
         <v>227</v>
@@ -32370,25 +32374,25 @@
     </row>
     <row r="1255" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1255" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1255" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1255" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1255" s="49" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E1255" s="49" t="s">
         <v>1407</v>
-      </c>
-      <c r="E1255" s="49" t="s">
-        <v>1408</v>
       </c>
       <c r="F1255" s="49" t="s">
         <v>827</v>
       </c>
       <c r="G1255" s="49" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1255" s="49" t="s">
         <v>81</v>
@@ -32402,13 +32406,13 @@
     </row>
     <row r="1256" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1256" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1256" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1256" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1256" s="49" t="s">
         <v>242</v>
@@ -32434,19 +32438,19 @@
     </row>
     <row r="1257" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1257" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1257" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1257" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1257" s="49" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E1257" s="49" t="s">
         <v>1409</v>
-      </c>
-      <c r="E1257" s="49" t="s">
-        <v>1410</v>
       </c>
       <c r="F1257" s="49" t="s">
         <v>999</v>
@@ -32455,7 +32459,7 @@
         <v>89</v>
       </c>
       <c r="H1257" s="49" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="I1257" s="49" t="s">
         <v>89</v>
@@ -32466,16 +32470,16 @@
     </row>
     <row r="1258" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1258" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1258" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1258" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1258" s="49" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="E1258" s="49" t="s">
         <v>977</v>
@@ -32484,10 +32488,10 @@
         <v>81</v>
       </c>
       <c r="G1258" s="49" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="H1258" s="49" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="I1258" s="49" t="s">
         <v>977</v>
@@ -32496,16 +32500,16 @@
     </row>
     <row r="1259" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1259" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1259" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1259" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1259" s="49" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="E1259" s="49" t="s">
         <v>81</v>
@@ -32517,7 +32521,7 @@
         <v>81</v>
       </c>
       <c r="H1259" s="49" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="I1259" s="49" t="s">
         <v>81</v>
@@ -32528,16 +32532,16 @@
     </row>
     <row r="1260" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1260" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1260" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1260" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1260" s="49" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="E1260" s="49" t="s">
         <v>808</v>
@@ -32558,16 +32562,16 @@
     </row>
     <row r="1261" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1261" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1261" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1261" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1261" s="49" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="E1261" s="49" t="s">
         <v>808</v>
@@ -32588,16 +32592,16 @@
     </row>
     <row r="1262" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1262" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1262" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1262" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1262" s="49" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="E1262" s="49" t="s">
         <v>89</v>
@@ -32618,16 +32622,16 @@
     </row>
     <row r="1263" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1263" s="49" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B1263" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1263" s="50" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D1263" s="49" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="E1263" s="49" t="s">
         <v>89</v>
@@ -32654,13 +32658,13 @@
         <v>11</v>
       </c>
       <c r="C1264" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1264" s="32" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="E1264" s="32" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="F1264" s="32" t="s">
         <v>81</v>
@@ -32686,7 +32690,7 @@
         <v>11</v>
       </c>
       <c r="C1265" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1265" s="32" t="s">
         <v>108</v>
@@ -32698,7 +32702,7 @@
         <v>89</v>
       </c>
       <c r="G1265" s="32" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1265" s="32" t="s">
         <v>108</v>
@@ -32718,7 +32722,7 @@
         <v>11</v>
       </c>
       <c r="C1266" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1266" s="33" t="s">
         <v>143</v>
@@ -32750,10 +32754,10 @@
         <v>11</v>
       </c>
       <c r="C1267" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1267" s="32" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="E1267" s="32" t="s">
         <v>108</v>
@@ -32780,7 +32784,7 @@
         <v>11</v>
       </c>
       <c r="C1268" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1268" s="32" t="s">
         <v>50</v>
@@ -32812,7 +32816,7 @@
         <v>11</v>
       </c>
       <c r="C1269" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1269" s="32" t="s">
         <v>409</v>
@@ -32821,7 +32825,7 @@
         <v>847</v>
       </c>
       <c r="F1269" s="32" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="G1269" s="32" t="s">
         <v>89</v>
@@ -32844,7 +32848,7 @@
         <v>11</v>
       </c>
       <c r="C1270" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1270" s="32" t="s">
         <v>20</v>
@@ -32876,10 +32880,10 @@
         <v>11</v>
       </c>
       <c r="C1271" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1271" s="32" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="E1271" s="32" t="s">
         <v>89</v>
@@ -32894,7 +32898,7 @@
         <v>89</v>
       </c>
       <c r="I1271" s="32" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1271" s="32" t="s">
         <v>941</v>
@@ -32908,22 +32912,22 @@
         <v>11</v>
       </c>
       <c r="C1272" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1272" s="32" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E1272" s="32" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="F1272" s="32" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="G1272" s="32" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H1272" s="32" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="I1272" s="32" t="s">
         <v>81</v>
@@ -32940,19 +32944,19 @@
         <v>11</v>
       </c>
       <c r="C1273" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1273" s="32" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E1273" s="32" t="s">
         <v>1422</v>
-      </c>
-      <c r="E1273" s="32" t="s">
-        <v>1423</v>
       </c>
       <c r="F1273" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G1273" s="32" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H1273" s="32" t="s">
         <v>89</v>
@@ -32970,10 +32974,10 @@
         <v>11</v>
       </c>
       <c r="C1274" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1274" s="32" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E1274" s="32" t="s">
         <v>941</v>
@@ -33002,22 +33006,22 @@
         <v>11</v>
       </c>
       <c r="C1275" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1275" s="32" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E1275" s="32" t="s">
         <v>1425</v>
       </c>
-      <c r="E1275" s="32" t="s">
+      <c r="F1275" s="32" t="s">
         <v>1426</v>
       </c>
-      <c r="F1275" s="32" t="s">
+      <c r="G1275" s="32" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H1275" s="32" t="s">
         <v>1427</v>
-      </c>
-      <c r="G1275" s="32" t="s">
-        <v>1184</v>
-      </c>
-      <c r="H1275" s="32" t="s">
-        <v>1428</v>
       </c>
       <c r="I1275" s="32" t="s">
         <v>81</v>
@@ -33034,7 +33038,7 @@
         <v>11</v>
       </c>
       <c r="C1276" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1276" s="32" t="s">
         <v>50</v>
@@ -33064,7 +33068,7 @@
         <v>11</v>
       </c>
       <c r="C1277" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1277" s="32" t="s">
         <v>50</v>
@@ -33094,7 +33098,7 @@
         <v>11</v>
       </c>
       <c r="C1278" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1278" s="32" t="s">
         <v>458</v>
@@ -33112,7 +33116,7 @@
         <v>89</v>
       </c>
       <c r="I1278" s="32" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1278" s="32"/>
     </row>
@@ -33124,7 +33128,7 @@
         <v>11</v>
       </c>
       <c r="C1279" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1279" s="32" t="s">
         <v>149</v>
@@ -33154,7 +33158,7 @@
         <v>11</v>
       </c>
       <c r="C1280" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1280" s="32" t="s">
         <v>20</v>
@@ -33186,7 +33190,7 @@
         <v>11</v>
       </c>
       <c r="C1281" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1281" s="32" t="s">
         <v>108</v>
@@ -33201,7 +33205,7 @@
         <v>89</v>
       </c>
       <c r="H1281" s="32" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1281" s="32" t="s">
         <v>89</v>
@@ -33218,7 +33222,7 @@
         <v>11</v>
       </c>
       <c r="C1282" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1282" s="32" t="s">
         <v>101</v>
@@ -33250,13 +33254,13 @@
         <v>11</v>
       </c>
       <c r="C1283" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1283" s="32" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="E1283" s="32" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="F1283" s="32" t="s">
         <v>938</v>
@@ -33282,28 +33286,28 @@
         <v>11</v>
       </c>
       <c r="C1284" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1284" s="32" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E1284" s="32" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F1284" s="32" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G1284" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1284" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1284" s="32" t="s">
         <v>1430</v>
       </c>
-      <c r="E1284" s="32" t="s">
-        <v>1374</v>
-      </c>
-      <c r="F1284" s="32" t="s">
-        <v>1169</v>
-      </c>
-      <c r="G1284" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="H1284" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="I1284" s="32" t="s">
-        <v>1431</v>
-      </c>
       <c r="J1284" s="32" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="1285" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -33314,7 +33318,7 @@
         <v>11</v>
       </c>
       <c r="C1285" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1285" s="32" t="s">
         <v>108</v>
@@ -33332,7 +33336,7 @@
         <v>89</v>
       </c>
       <c r="I1285" s="32" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1285" s="32" t="s">
         <v>89</v>
@@ -33346,7 +33350,7 @@
         <v>11</v>
       </c>
       <c r="C1286" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1286" s="32" t="s">
         <v>227</v>
@@ -33378,10 +33382,10 @@
         <v>11</v>
       </c>
       <c r="C1287" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1287" s="32" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="E1287" s="32" t="s">
         <v>101</v>
@@ -33410,7 +33414,7 @@
         <v>11</v>
       </c>
       <c r="C1288" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1288" s="32" t="s">
         <v>116</v>
@@ -33442,19 +33446,19 @@
         <v>11</v>
       </c>
       <c r="C1289" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1289" s="32" t="s">
+        <v>1432</v>
+      </c>
+      <c r="E1289" s="32" t="s">
         <v>1433</v>
       </c>
-      <c r="E1289" s="32" t="s">
+      <c r="F1289" s="32" t="s">
         <v>1434</v>
       </c>
-      <c r="F1289" s="32" t="s">
-        <v>1435</v>
-      </c>
       <c r="G1289" s="32" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1289" s="32" t="s">
         <v>81</v>
@@ -33474,7 +33478,7 @@
         <v>11</v>
       </c>
       <c r="C1290" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1290" s="32" t="s">
         <v>108</v>
@@ -33506,22 +33510,22 @@
         <v>11</v>
       </c>
       <c r="C1291" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1291" s="32" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="E1291" s="32" t="s">
         <v>33</v>
       </c>
       <c r="F1291" s="32" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="G1291" s="32" t="s">
         <v>108</v>
       </c>
       <c r="H1291" s="32" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="I1291" s="32"/>
       <c r="J1291" s="32" t="s">
@@ -33536,7 +33540,7 @@
         <v>11</v>
       </c>
       <c r="C1292" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1292" s="32" t="s">
         <v>116</v>
@@ -33568,13 +33572,13 @@
         <v>11</v>
       </c>
       <c r="C1293" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1293" s="32" t="s">
         <v>108</v>
       </c>
       <c r="E1293" s="32" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="F1293" s="32" t="s">
         <v>81</v>
@@ -33586,7 +33590,7 @@
         <v>89</v>
       </c>
       <c r="I1293" s="32" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="J1293" s="32"/>
     </row>
@@ -33598,7 +33602,7 @@
         <v>11</v>
       </c>
       <c r="C1294" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1294" s="32" t="s">
         <v>204</v>
@@ -33610,7 +33614,7 @@
         <v>89</v>
       </c>
       <c r="G1294" s="32" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1294" s="32" t="s">
         <v>204</v>
@@ -33628,7 +33632,7 @@
         <v>11</v>
       </c>
       <c r="C1295" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1295" s="32" t="s">
         <v>108</v>
@@ -33658,10 +33662,10 @@
         <v>11</v>
       </c>
       <c r="C1296" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1296" s="32" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="E1296" s="32" t="s">
         <v>81</v>
@@ -33676,7 +33680,7 @@
         <v>81</v>
       </c>
       <c r="I1296" s="32" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="J1296" s="32"/>
     </row>
@@ -33688,7 +33692,7 @@
         <v>11</v>
       </c>
       <c r="C1297" s="32" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="D1297" s="32" t="s">
         <v>108</v>
@@ -33712,78 +33716,78 @@
     </row>
     <row r="1298" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1298" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1298" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1298" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1298" s="31" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E1298" s="26" t="s">
         <v>1439</v>
       </c>
-      <c r="E1298" s="26" t="s">
+      <c r="F1298" s="26" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G1298" s="31" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H1298" s="26" t="s">
         <v>1440</v>
       </c>
-      <c r="F1298" s="26" t="s">
-        <v>1440</v>
-      </c>
-      <c r="G1298" s="31" t="s">
-        <v>1184</v>
-      </c>
-      <c r="H1298" s="26" t="s">
-        <v>1441</v>
-      </c>
       <c r="I1298" s="26" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="J1298" s="26" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="1299" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1299" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1299" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1299" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1299" s="26" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="E1299" s="26" t="s">
         <v>1088</v>
       </c>
       <c r="F1299" s="26" t="s">
+        <v>1442</v>
+      </c>
+      <c r="G1299" s="26" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H1299" s="26" t="s">
         <v>1443</v>
       </c>
-      <c r="G1299" s="26" t="s">
-        <v>1184</v>
-      </c>
-      <c r="H1299" s="26" t="s">
-        <v>1444</v>
-      </c>
       <c r="I1299" s="26" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="J1299" s="26"/>
     </row>
     <row r="1300" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1300" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1300" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1300" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1300" s="31" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="E1300" s="27" t="s">
         <v>19</v>
@@ -33795,10 +33799,10 @@
         <v>81</v>
       </c>
       <c r="H1300" s="27" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="I1300" s="27" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="J1300" s="26" t="s">
         <v>19</v>
@@ -33806,16 +33810,16 @@
     </row>
     <row r="1301" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1301" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1301" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1301" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1301" s="26" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="E1301" s="26" t="s">
         <v>161</v>
@@ -33830,7 +33834,7 @@
         <v>455</v>
       </c>
       <c r="I1301" s="26" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="J1301" s="26" t="s">
         <v>82</v>
@@ -33838,13 +33842,13 @@
     </row>
     <row r="1302" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1302" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1302" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1302" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1302" s="26" t="s">
         <v>50</v>
@@ -33856,10 +33860,10 @@
         <v>89</v>
       </c>
       <c r="G1302" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1302" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1302" s="26" t="s">
         <v>81</v>
@@ -33868,16 +33872,16 @@
     </row>
     <row r="1303" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1303" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1303" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1303" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1303" s="26" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="E1303" s="26" t="s">
         <v>847</v>
@@ -33892,7 +33896,7 @@
         <v>81</v>
       </c>
       <c r="I1303" s="26" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="J1303" s="26" t="s">
         <v>847</v>
@@ -33900,13 +33904,13 @@
     </row>
     <row r="1304" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1304" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1304" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1304" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1304" s="26" t="s">
         <v>284</v>
@@ -33921,10 +33925,10 @@
         <v>89</v>
       </c>
       <c r="H1304" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I1304" s="26" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="J1304" s="26" t="s">
         <v>141</v>
@@ -33932,16 +33936,16 @@
     </row>
     <row r="1305" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1305" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1305" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1305" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1305" s="26" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="E1305" s="26" t="s">
         <v>1021</v>
@@ -33950,25 +33954,25 @@
         <v>1021</v>
       </c>
       <c r="G1305" s="26" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H1305" s="26" t="s">
         <v>81</v>
       </c>
       <c r="I1305" s="26" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="J1305" s="26"/>
     </row>
     <row r="1306" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1306" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1306" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1306" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1306" s="26" t="s">
         <v>39</v>
@@ -33994,46 +33998,46 @@
     </row>
     <row r="1307" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1307" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1307" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1307" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1307" s="26" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E1307" s="26" t="s">
         <v>1448</v>
       </c>
-      <c r="E1307" s="26" t="s">
-        <v>1449</v>
-      </c>
       <c r="F1307" s="26" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="G1307" s="26" t="s">
         <v>81</v>
       </c>
       <c r="H1307" s="26" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="I1307" s="26" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="J1307" s="26"/>
     </row>
     <row r="1308" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1308" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1308" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1308" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1308" s="31" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="E1308" s="26" t="s">
         <v>847</v>
@@ -34042,13 +34046,13 @@
         <v>847</v>
       </c>
       <c r="G1308" s="26" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="H1308" s="26" t="s">
+        <v>1337</v>
+      </c>
+      <c r="I1308" s="26" t="s">
         <v>1338</v>
-      </c>
-      <c r="I1308" s="26" t="s">
-        <v>1339</v>
       </c>
       <c r="J1308" s="26" t="s">
         <v>847</v>
@@ -34056,16 +34060,16 @@
     </row>
     <row r="1309" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1309" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1309" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1309" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1309" s="26" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="E1309" s="26" t="s">
         <v>841</v>
@@ -34077,25 +34081,25 @@
         <v>81</v>
       </c>
       <c r="H1309" s="26" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="I1309" s="26" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="J1309" s="26"/>
     </row>
     <row r="1310" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1310" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1310" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1310" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1310" s="26" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="E1310" s="26" t="s">
         <v>832</v>
@@ -34104,27 +34108,27 @@
         <v>832</v>
       </c>
       <c r="G1310" s="26" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="H1310" s="26" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="I1310" s="26" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="J1310" s="26" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="1311" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1311" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1311" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1311" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1311" s="26" t="s">
         <v>218</v>
@@ -34148,16 +34152,16 @@
     </row>
     <row r="1312" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1312" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1312" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1312" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1312" s="26" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="E1312" s="26" t="s">
         <v>924</v>
@@ -34169,10 +34173,10 @@
         <v>81</v>
       </c>
       <c r="H1312" s="31" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="I1312" s="26" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="J1312" s="26" t="s">
         <v>924</v>
@@ -34180,31 +34184,31 @@
     </row>
     <row r="1313" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1313" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1313" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1313" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1313" s="31" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E1313" s="26" t="s">
         <v>1455</v>
       </c>
-      <c r="E1313" s="26" t="s">
-        <v>1456</v>
-      </c>
       <c r="F1313" s="26" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="G1313" s="31" t="s">
         <v>81</v>
       </c>
       <c r="H1313" s="26" t="s">
+        <v>1456</v>
+      </c>
+      <c r="I1313" s="26" t="s">
         <v>1457</v>
-      </c>
-      <c r="I1313" s="26" t="s">
-        <v>1458</v>
       </c>
       <c r="J1313" s="26" t="s">
         <v>895</v>
@@ -34212,31 +34216,31 @@
     </row>
     <row r="1314" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1314" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1314" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1314" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1314" s="26" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="E1314" s="26" t="s">
+        <v>1458</v>
+      </c>
+      <c r="F1314" s="26" t="s">
+        <v>1458</v>
+      </c>
+      <c r="G1314" s="26" t="s">
         <v>1459</v>
       </c>
-      <c r="F1314" s="26" t="s">
+      <c r="H1314" s="26" t="s">
         <v>1459</v>
       </c>
-      <c r="G1314" s="26" t="s">
-        <v>1460</v>
-      </c>
-      <c r="H1314" s="26" t="s">
-        <v>1460</v>
-      </c>
       <c r="I1314" s="26" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="J1314" s="26" t="s">
         <v>902</v>
@@ -34244,13 +34248,13 @@
     </row>
     <row r="1315" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1315" s="24" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B1315" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1315" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D1315" s="26" t="s">
         <v>334</v>
@@ -36039,117 +36043,117 @@
     </row>
     <row r="135" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="58" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B135" s="58" t="s">
         <v>1143</v>
       </c>
-      <c r="B135" s="58" t="s">
+      <c r="C135" s="58" t="s">
         <v>1144</v>
-      </c>
-      <c r="C135" s="58" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="22" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B136" s="22" t="s">
         <v>1146</v>
       </c>
-      <c r="B136" s="22" t="s">
+      <c r="C136" s="22" t="s">
         <v>1147</v>
-      </c>
-      <c r="C136" s="22" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="57" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B137" s="57" t="s">
         <v>1149</v>
       </c>
-      <c r="B137" s="57" t="s">
+      <c r="C137" s="57" t="s">
         <v>1150</v>
-      </c>
-      <c r="C137" s="57" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="59" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B138" s="57" t="s">
         <v>1152</v>
       </c>
-      <c r="B138" s="57" t="s">
+      <c r="C138" s="57" t="s">
         <v>1153</v>
-      </c>
-      <c r="C138" s="57" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="22" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B139" s="22" t="s">
         <v>1155</v>
       </c>
-      <c r="B139" s="22" t="s">
+      <c r="C139" s="22" t="s">
         <v>1156</v>
-      </c>
-      <c r="C139" s="22" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="22" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B140" s="22" t="s">
         <v>1158</v>
       </c>
-      <c r="B140" s="22" t="s">
+      <c r="C140" s="22" t="s">
         <v>1159</v>
-      </c>
-      <c r="C140" s="22" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="22" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B141" s="22" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C141" s="22" t="s">
         <v>1161</v>
-      </c>
-      <c r="C141" s="22" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="22" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B142" s="22" t="s">
         <v>1163</v>
       </c>
-      <c r="B142" s="22" t="s">
-        <v>1164</v>
-      </c>
       <c r="C142" s="22" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="22" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B143" s="60" t="s">
         <v>1165</v>
       </c>
-      <c r="B143" s="60" t="s">
-        <v>1166</v>
-      </c>
       <c r="C143" s="60" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="22" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B144" s="22" t="s">
         <v>1167</v>
       </c>
-      <c r="B144" s="22" t="s">
-        <v>1168</v>
-      </c>
       <c r="C144" s="22" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="22" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B145" s="22" t="s">
         <v>1033</v>
@@ -36160,35 +36164,35 @@
     </row>
     <row r="146" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="22" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B146" s="22" t="s">
         <v>1170</v>
       </c>
-      <c r="B146" s="22" t="s">
+      <c r="C146" s="22" t="s">
         <v>1171</v>
-      </c>
-      <c r="C146" s="22" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="22" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B147" s="22" t="s">
         <v>1173</v>
       </c>
-      <c r="B147" s="22" t="s">
+      <c r="C147" s="61" t="s">
         <v>1174</v>
-      </c>
-      <c r="C147" s="61" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="22" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B148" s="22" t="s">
         <v>1176</v>
       </c>
-      <c r="B148" s="22" t="s">
-        <v>1177</v>
-      </c>
       <c r="C148" s="22" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
   </sheetData>
@@ -37042,8 +37046,8 @@
       <c r="A60" s="53" t="s">
         <v>1124</v>
       </c>
-      <c r="B60" s="20" t="s">
-        <v>1125</v>
+      <c r="B60" s="1" t="s">
+        <v>1460</v>
       </c>
       <c r="C60" s="20" t="s">
         <v>413</v>
@@ -37054,10 +37058,10 @@
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="20" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B61" s="20" t="s">
         <v>1126</v>
-      </c>
-      <c r="B61" s="20" t="s">
-        <v>1127</v>
       </c>
       <c r="C61" s="20" t="s">
         <v>482</v>
@@ -37068,10 +37072,10 @@
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="54" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B62" s="20" t="s">
         <v>1128</v>
-      </c>
-      <c r="B62" s="20" t="s">
-        <v>1129</v>
       </c>
       <c r="C62" s="20" t="s">
         <v>317</v>
@@ -37082,10 +37086,10 @@
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="55" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B63" s="55" t="s">
         <v>1130</v>
-      </c>
-      <c r="B63" s="55" t="s">
-        <v>1131</v>
       </c>
       <c r="C63" s="20" t="s">
         <v>155</v>
@@ -37096,10 +37100,10 @@
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="54" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B64" s="20" t="s">
         <v>1132</v>
-      </c>
-      <c r="B64" s="20" t="s">
-        <v>1133</v>
       </c>
       <c r="C64" s="20" t="s">
         <v>317</v>
@@ -37110,10 +37114,10 @@
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="56" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B65" s="56" t="s">
         <v>1134</v>
-      </c>
-      <c r="B65" s="56" t="s">
-        <v>1135</v>
       </c>
       <c r="C65" s="56" t="s">
         <v>425</v>
@@ -37124,10 +37128,10 @@
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="57" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B66" s="20" t="s">
         <v>1136</v>
-      </c>
-      <c r="B66" s="20" t="s">
-        <v>1137</v>
       </c>
       <c r="C66" s="20" t="s">
         <v>413</v>

--- a/static/TALENKAART_DATA/talenkaart_data.xlsx
+++ b/static/TALENKAART_DATA/talenkaart_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amsuni-my.sharepoint.com/personal/kylie_mansour_student_uva_nl/Documents/Documents/MA/Internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{D6D6DB9B-1825-0E4C-A6B9-EC4CA1933FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F211D1BA-A2D1-5544-9701-826E6BB76B96}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{D6D6DB9B-1825-0E4C-A6B9-EC4CA1933FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9582289-DC86-BE47-B4F1-7C39349B2275}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respondenten" sheetId="2" r:id="rId1"/>
@@ -3407,9 +3407,6 @@
     <t xml:space="preserve"> 4.926217857436223</t>
   </si>
   <si>
-    <t xml:space="preserve">OBA  De Hallen </t>
-  </si>
-  <si>
     <t>52.367097743814796, 4.86875051064426</t>
   </si>
   <si>
@@ -4433,6 +4430,9 @@
   </si>
   <si>
     <t>52.332498330642814, 4.876000881281019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBA De Hallen </t>
   </si>
 </sst>
 </file>
@@ -15041,7 +15041,7 @@
       </c>
       <c r="C475" s="2"/>
       <c r="D475" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E475" s="6"/>
       <c r="F475" s="3"/>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="C482" s="2"/>
       <c r="D482" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E482" s="6"/>
       <c r="F482" s="3"/>
@@ -18659,7 +18659,7 @@
       </c>
       <c r="C676" s="2"/>
       <c r="D676" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="E676" s="6"/>
       <c r="F676" s="3"/>
@@ -21827,7 +21827,7 @@
       </c>
       <c r="C852" s="2"/>
       <c r="D852" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E852" s="6"/>
       <c r="F852" s="3"/>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="C978" s="2"/>
       <c r="D978" s="2" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E978" s="6"/>
       <c r="F978" s="3"/>
@@ -24556,13 +24556,13 @@
     </row>
     <row r="999" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A999" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B999" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C999" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D999" s="25" t="s">
         <v>227</v>
@@ -24586,13 +24586,13 @@
     </row>
     <row r="1000" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1000" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1000" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1000" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1000" s="25" t="s">
         <v>227</v>
@@ -24604,7 +24604,7 @@
         <v>218</v>
       </c>
       <c r="G1000" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H1000" s="25" t="s">
         <v>34</v>
@@ -24616,16 +24616,16 @@
     </row>
     <row r="1001" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1001" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1001" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1001" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1001" s="25" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E1001" s="25" t="s">
         <v>89</v>
@@ -24637,10 +24637,10 @@
         <v>204</v>
       </c>
       <c r="H1001" s="25" t="s">
+        <v>1180</v>
+      </c>
+      <c r="I1001" s="25" t="s">
         <v>1181</v>
-      </c>
-      <c r="I1001" s="25" t="s">
-        <v>1182</v>
       </c>
       <c r="J1001" s="25" t="s">
         <v>108</v>
@@ -24648,13 +24648,13 @@
     </row>
     <row r="1002" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1002" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1002" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1002" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1002" s="25" t="s">
         <v>140</v>
@@ -24666,28 +24666,28 @@
         <v>141</v>
       </c>
       <c r="G1002" s="25" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1002" s="25" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1002" s="25" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1002" s="25"/>
     </row>
     <row r="1003" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1003" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1003" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1003" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1003" s="25" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E1003" s="25" t="s">
         <v>89</v>
@@ -24708,16 +24708,16 @@
     </row>
     <row r="1004" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1004" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1004" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1004" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1004" s="25" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E1004" s="25" t="s">
         <v>242</v>
@@ -24726,28 +24726,28 @@
         <v>242</v>
       </c>
       <c r="G1004" s="25" t="s">
+        <v>1184</v>
+      </c>
+      <c r="H1004" s="25" t="s">
+        <v>1184</v>
+      </c>
+      <c r="I1004" s="25" t="s">
         <v>1185</v>
-      </c>
-      <c r="H1004" s="25" t="s">
-        <v>1185</v>
-      </c>
-      <c r="I1004" s="25" t="s">
-        <v>1186</v>
       </c>
       <c r="J1004" s="25"/>
     </row>
     <row r="1005" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1005" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1005" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1005" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1005" s="25" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="E1005" s="25" t="s">
         <v>219</v>
@@ -24756,10 +24756,10 @@
         <v>218</v>
       </c>
       <c r="G1005" s="25" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H1005" s="25" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="I1005" s="25" t="s">
         <v>218</v>
@@ -24768,16 +24768,16 @@
     </row>
     <row r="1006" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1006" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1006" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1006" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1006" s="26" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="E1006" s="26" t="s">
         <v>81</v>
@@ -24798,16 +24798,16 @@
     </row>
     <row r="1007" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1007" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1007" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1007" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1007" s="26" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="E1007" s="27" t="s">
         <v>284</v>
@@ -24819,7 +24819,7 @@
         <v>108</v>
       </c>
       <c r="H1007" s="27" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1007" s="27" t="s">
         <v>81</v>
@@ -24828,19 +24828,19 @@
     </row>
     <row r="1008" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1008" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1008" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1008" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1008" s="26" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E1008" s="27" t="s">
         <v>1191</v>
-      </c>
-      <c r="E1008" s="27" t="s">
-        <v>1192</v>
       </c>
       <c r="F1008" s="27" t="s">
         <v>1005</v>
@@ -24849,22 +24849,22 @@
         <v>81</v>
       </c>
       <c r="H1008" s="27" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="I1008" s="27" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="J1008" s="26"/>
     </row>
     <row r="1009" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1009" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1009" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1009" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1009" s="26" t="s">
         <v>34</v>
@@ -24888,13 +24888,13 @@
     </row>
     <row r="1010" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1010" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1010" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1010" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1010" s="26" t="s">
         <v>108</v>
@@ -24906,7 +24906,7 @@
         <v>89</v>
       </c>
       <c r="G1010" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1010" s="26" t="s">
         <v>89</v>
@@ -24918,13 +24918,13 @@
     </row>
     <row r="1011" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1011" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1011" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1011" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1011" s="26" t="s">
         <v>204</v>
@@ -24942,22 +24942,22 @@
         <v>89</v>
       </c>
       <c r="I1011" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1011" s="26"/>
     </row>
     <row r="1012" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1012" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1012" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1012" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1012" s="26" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="E1012" s="26" t="s">
         <v>969</v>
@@ -24966,7 +24966,7 @@
         <v>969</v>
       </c>
       <c r="G1012" s="26" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="H1012" s="26" t="s">
         <v>81</v>
@@ -24978,16 +24978,16 @@
     </row>
     <row r="1013" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1013" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1013" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1013" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1013" s="27" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="E1013" s="27" t="s">
         <v>143</v>
@@ -24999,24 +24999,24 @@
         <v>108</v>
       </c>
       <c r="H1013" s="27" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1013" s="27" t="s">
         <v>81</v>
       </c>
       <c r="J1013" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="1014" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1014" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1014" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1014" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1014" s="26" t="s">
         <v>338</v>
@@ -25042,16 +25042,16 @@
     </row>
     <row r="1015" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1015" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1015" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1015" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1015" s="26" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E1015" s="26" t="s">
         <v>108</v>
@@ -25078,7 +25078,7 @@
         <v>155</v>
       </c>
       <c r="C1016" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1016" s="28" t="s">
         <v>232</v>
@@ -25110,13 +25110,13 @@
         <v>155</v>
       </c>
       <c r="C1017" s="28" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D1017" s="28" t="s">
         <v>1198</v>
       </c>
-      <c r="D1017" s="28" t="s">
-        <v>1199</v>
-      </c>
       <c r="E1017" s="28" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="F1017" s="28" t="s">
         <v>219</v>
@@ -25140,7 +25140,7 @@
         <v>155</v>
       </c>
       <c r="C1018" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1018" s="29" t="s">
         <v>796</v>
@@ -25152,13 +25152,13 @@
         <v>89</v>
       </c>
       <c r="G1018" s="29" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1018" s="29" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1018" s="29" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1018" s="28"/>
     </row>
@@ -25170,7 +25170,7 @@
         <v>155</v>
       </c>
       <c r="C1019" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1019" s="28" t="s">
         <v>206</v>
@@ -25198,25 +25198,25 @@
         <v>155</v>
       </c>
       <c r="C1020" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1020" s="28" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E1020" s="28" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F1020" s="28" t="s">
         <v>89</v>
       </c>
       <c r="G1020" s="28" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1020" s="28" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1020" s="28" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1020" s="28"/>
     </row>
@@ -25228,16 +25228,16 @@
         <v>155</v>
       </c>
       <c r="C1021" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1021" s="28" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="E1021" s="28" t="s">
         <v>82</v>
       </c>
       <c r="F1021" s="28" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="G1021" s="28" t="s">
         <v>89</v>
@@ -25246,7 +25246,7 @@
         <v>89</v>
       </c>
       <c r="I1021" s="28" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1021" s="28" t="s">
         <v>281</v>
@@ -25260,7 +25260,7 @@
         <v>155</v>
       </c>
       <c r="C1022" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1022" s="28" t="s">
         <v>31</v>
@@ -25278,7 +25278,7 @@
         <v>89</v>
       </c>
       <c r="I1022" s="28" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1022" s="28" t="s">
         <v>89</v>
@@ -25292,7 +25292,7 @@
         <v>155</v>
       </c>
       <c r="C1023" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1023" s="28" t="s">
         <v>796</v>
@@ -25324,10 +25324,10 @@
         <v>155</v>
       </c>
       <c r="C1024" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1024" s="28" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E1024" s="28" t="s">
         <v>89</v>
@@ -25356,7 +25356,7 @@
         <v>155</v>
       </c>
       <c r="C1025" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1025" s="28" t="s">
         <v>281</v>
@@ -25388,22 +25388,22 @@
         <v>155</v>
       </c>
       <c r="C1026" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1026" s="28" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E1026" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1026" s="28" t="s">
         <v>1201</v>
       </c>
-      <c r="E1026" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1026" s="28" t="s">
+      <c r="G1026" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1026" s="28" t="s">
         <v>1202</v>
-      </c>
-      <c r="G1026" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="H1026" s="28" t="s">
-        <v>1203</v>
       </c>
       <c r="I1026" s="28" t="s">
         <v>89</v>
@@ -25420,25 +25420,25 @@
         <v>155</v>
       </c>
       <c r="C1027" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1027" s="28" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="E1027" s="28" t="s">
         <v>81</v>
       </c>
       <c r="F1027" s="28" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="G1027" s="28" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1027" s="28" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="I1027" s="28" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="J1027" s="28"/>
     </row>
@@ -25450,10 +25450,10 @@
         <v>155</v>
       </c>
       <c r="C1028" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1028" s="28" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="E1028" s="28" t="s">
         <v>16</v>
@@ -25465,10 +25465,10 @@
         <v>89</v>
       </c>
       <c r="H1028" s="28" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="I1028" s="28" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="J1028" s="28" t="s">
         <v>15</v>
@@ -25482,7 +25482,7 @@
         <v>155</v>
       </c>
       <c r="C1029" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1029" s="28" t="s">
         <v>281</v>
@@ -25514,7 +25514,7 @@
         <v>155</v>
       </c>
       <c r="C1030" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1030" s="28" t="s">
         <v>89</v>
@@ -25536,16 +25536,16 @@
     </row>
     <row r="1031" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1031" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1031" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1031" s="26" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D1031" s="26" t="s">
         <v>1208</v>
-      </c>
-      <c r="D1031" s="26" t="s">
-        <v>1209</v>
       </c>
       <c r="E1031" s="26" t="s">
         <v>902</v>
@@ -25557,22 +25557,22 @@
         <v>81</v>
       </c>
       <c r="H1031" s="26" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="I1031" s="26" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="J1031" s="26"/>
     </row>
     <row r="1032" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1032" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1032" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1032" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1032" s="26" t="s">
         <v>108</v>
@@ -25590,7 +25590,7 @@
         <v>89</v>
       </c>
       <c r="I1032" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1032" s="26" t="s">
         <v>89</v>
@@ -25598,13 +25598,13 @@
     </row>
     <row r="1033" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1033" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1033" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1033" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1033" s="27" t="s">
         <v>50</v>
@@ -25616,13 +25616,13 @@
         <v>89</v>
       </c>
       <c r="G1033" s="27" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1033" s="27" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1033" s="27" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1033" s="26" t="s">
         <v>89</v>
@@ -25630,13 +25630,13 @@
     </row>
     <row r="1034" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1034" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1034" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1034" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1034" s="26" t="s">
         <v>204</v>
@@ -25648,7 +25648,7 @@
         <v>89</v>
       </c>
       <c r="G1034" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1034" s="26" t="s">
         <v>89</v>
@@ -25662,13 +25662,13 @@
     </row>
     <row r="1035" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1035" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1035" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1035" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1035" s="26" t="s">
         <v>81</v>
@@ -25686,16 +25686,16 @@
     </row>
     <row r="1036" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1036" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1036" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1036" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1036" s="26" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="E1036" s="26" t="s">
         <v>892</v>
@@ -25707,10 +25707,10 @@
         <v>81</v>
       </c>
       <c r="H1036" s="26" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="I1036" s="26" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="J1036" s="26" t="s">
         <v>892</v>
@@ -25718,22 +25718,22 @@
     </row>
     <row r="1037" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1037" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1037" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1037" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1037" s="26" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="E1037" s="26" t="s">
         <v>89</v>
       </c>
       <c r="F1037" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G1037" s="26" t="s">
         <v>81</v>
@@ -25742,7 +25742,7 @@
         <v>89</v>
       </c>
       <c r="I1037" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1037" s="26" t="s">
         <v>89</v>
@@ -25750,19 +25750,19 @@
     </row>
     <row r="1038" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1038" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1038" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1038" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1038" s="26" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E1038" s="26" t="s">
         <v>1214</v>
-      </c>
-      <c r="E1038" s="26" t="s">
-        <v>1215</v>
       </c>
       <c r="F1038" s="26" t="s">
         <v>969</v>
@@ -25782,13 +25782,13 @@
     </row>
     <row r="1039" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1039" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1039" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1039" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1039" s="26" t="s">
         <v>204</v>
@@ -25803,7 +25803,7 @@
         <v>22</v>
       </c>
       <c r="H1039" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1039" s="26" t="s">
         <v>22</v>
@@ -25812,16 +25812,16 @@
     </row>
     <row r="1040" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1040" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1040" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1040" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1040" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E1040" s="26" t="s">
         <v>89</v>
@@ -25830,28 +25830,28 @@
         <v>89</v>
       </c>
       <c r="G1040" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1040" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1040" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1040" s="26"/>
     </row>
     <row r="1041" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1041" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1041" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1041" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1041" s="30" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="E1041" s="30" t="s">
         <v>89</v>
@@ -25860,30 +25860,30 @@
         <v>153</v>
       </c>
       <c r="G1041" s="30" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1041" s="30" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1041" s="30" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1041" s="30" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="1042" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1042" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1042" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1042" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1042" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E1042" s="26" t="s">
         <v>89</v>
@@ -25904,13 +25904,13 @@
     </row>
     <row r="1043" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1043" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1043" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1043" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1043" s="26" t="s">
         <v>31</v>
@@ -25934,16 +25934,16 @@
     </row>
     <row r="1044" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1044" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1044" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1044" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1044" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E1044" s="26" t="s">
         <v>81</v>
@@ -25955,7 +25955,7 @@
         <v>89</v>
       </c>
       <c r="H1044" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1044" s="26" t="s">
         <v>81</v>
@@ -25964,28 +25964,28 @@
     </row>
     <row r="1045" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1045" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1045" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1045" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1045" s="26" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="E1045" s="26" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="F1045" s="26" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G1045" s="26" t="s">
         <v>108</v>
       </c>
       <c r="H1045" s="26" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="I1045" s="26" t="s">
         <v>81</v>
@@ -25994,13 +25994,13 @@
     </row>
     <row r="1046" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1046" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1046" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1046" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1046" s="26" t="s">
         <v>1119</v>
@@ -26024,16 +26024,16 @@
     </row>
     <row r="1047" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1047" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1047" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1047" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1047" s="26" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="E1047" s="26" t="s">
         <v>37</v>
@@ -26054,16 +26054,16 @@
     </row>
     <row r="1048" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1048" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1048" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1048" s="26" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="E1048" s="26" t="s">
         <v>892</v>
@@ -26075,7 +26075,7 @@
         <v>81</v>
       </c>
       <c r="H1048" s="26" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="I1048" s="26" t="s">
         <v>81</v>
@@ -26086,13 +26086,13 @@
     </row>
     <row r="1049" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1049" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1049" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1049" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1049" s="26" t="s">
         <v>142</v>
@@ -26118,13 +26118,13 @@
     </row>
     <row r="1050" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1050" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1050" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1050" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1050" s="26" t="s">
         <v>142</v>
@@ -26150,16 +26150,16 @@
     </row>
     <row r="1051" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1051" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1051" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1051" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1051" s="26" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E1051" s="26" t="s">
         <v>865</v>
@@ -26174,22 +26174,22 @@
         <v>81</v>
       </c>
       <c r="I1051" s="26" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="J1051" s="26"/>
     </row>
     <row r="1052" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1052" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1052" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1052" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1052" s="26" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="E1052" s="26" t="s">
         <v>81</v>
@@ -26201,7 +26201,7 @@
         <v>81</v>
       </c>
       <c r="H1052" s="26" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="I1052" s="26" t="s">
         <v>81</v>
@@ -26212,16 +26212,16 @@
     </row>
     <row r="1053" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1053" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1053" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1053" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1053" s="26" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="E1053" s="26" t="s">
         <v>81</v>
@@ -26233,7 +26233,7 @@
         <v>81</v>
       </c>
       <c r="H1053" s="26" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="I1053" s="26" t="s">
         <v>81</v>
@@ -26244,16 +26244,16 @@
     </row>
     <row r="1054" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1054" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1054" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1054" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1054" s="26" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="E1054" s="26" t="s">
         <v>219</v>
@@ -26274,16 +26274,16 @@
     </row>
     <row r="1055" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1055" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1055" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1055" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1055" s="26" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="E1055" s="26" t="s">
         <v>248</v>
@@ -26292,7 +26292,7 @@
         <v>248</v>
       </c>
       <c r="G1055" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1055" s="26" t="s">
         <v>89</v>
@@ -26306,16 +26306,16 @@
     </row>
     <row r="1056" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1056" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1056" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1056" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1056" s="26" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="E1056" s="26" t="s">
         <v>28</v>
@@ -26324,58 +26324,58 @@
         <v>28</v>
       </c>
       <c r="G1056" s="26" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="H1056" s="26" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="I1056" s="26" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="J1056" s="26" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="1057" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1057" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1057" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1057" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1057" s="26" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="E1057" s="26" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="F1057" s="26"/>
       <c r="G1057" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1057" s="26" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="I1057" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1057" s="26"/>
     </row>
     <row r="1058" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1058" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1058" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1058" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1058" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E1058" s="26" t="s">
         <v>108</v>
@@ -26390,34 +26390,34 @@
         <v>89</v>
       </c>
       <c r="I1058" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1058" s="26"/>
     </row>
     <row r="1059" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1059" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1059" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1059" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1059" s="26" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="E1059" s="26" t="s">
         <v>81</v>
       </c>
       <c r="F1059" s="26" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G1059" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1059" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1059" s="26" t="s">
         <v>81</v>
@@ -26426,16 +26426,16 @@
     </row>
     <row r="1060" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1060" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1060" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1060" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1060" s="26" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="E1060" s="26" t="s">
         <v>1041</v>
@@ -26456,13 +26456,13 @@
     </row>
     <row r="1061" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1061" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1061" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1061" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1061" s="26" t="s">
         <v>338</v>
@@ -26474,25 +26474,25 @@
         <v>89</v>
       </c>
       <c r="G1061" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1061" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1061" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1061" s="26"/>
     </row>
     <row r="1062" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1062" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1062" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1062" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1062" s="26" t="s">
         <v>204</v>
@@ -26504,25 +26504,25 @@
         <v>89</v>
       </c>
       <c r="G1062" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1062" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1062" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1062" s="26"/>
     </row>
     <row r="1063" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1063" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1063" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1063" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1063" s="26" t="s">
         <v>108</v>
@@ -26534,28 +26534,28 @@
         <v>89</v>
       </c>
       <c r="G1063" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1063" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1063" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1063" s="26"/>
     </row>
     <row r="1064" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1064" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1064" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1064" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1064" s="26" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="E1064" s="26" t="s">
         <v>859</v>
@@ -26567,25 +26567,25 @@
         <v>81</v>
       </c>
       <c r="H1064" s="26" t="s">
+        <v>1235</v>
+      </c>
+      <c r="I1064" s="26" t="s">
         <v>1236</v>
-      </c>
-      <c r="I1064" s="26" t="s">
-        <v>1237</v>
       </c>
       <c r="J1064" s="26"/>
     </row>
     <row r="1065" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1065" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1065" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1065" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1065" s="26" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="E1065" s="26" t="s">
         <v>19</v>
@@ -26597,25 +26597,25 @@
         <v>81</v>
       </c>
       <c r="H1065" s="26" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="I1065" s="26" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="J1065" s="26"/>
     </row>
     <row r="1066" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1066" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1066" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1066" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1066" s="26" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="E1066" s="26" t="s">
         <v>81</v>
@@ -26630,22 +26630,22 @@
         <v>81</v>
       </c>
       <c r="I1066" s="26" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="J1066" s="26"/>
     </row>
     <row r="1067" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1067" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1067" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1067" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1067" s="26" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="E1067" s="26" t="s">
         <v>89</v>
@@ -26654,7 +26654,7 @@
         <v>89</v>
       </c>
       <c r="G1067" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1067" s="26" t="s">
         <v>108</v>
@@ -26666,13 +26666,13 @@
     </row>
     <row r="1068" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1068" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1068" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1068" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1068" s="26" t="s">
         <v>796</v>
@@ -26684,7 +26684,7 @@
         <v>89</v>
       </c>
       <c r="G1068" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1068" s="26" t="s">
         <v>108</v>
@@ -26696,28 +26696,28 @@
     </row>
     <row r="1069" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1069" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1069" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1069" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1069" s="26" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="E1069" s="26" t="s">
         <v>81</v>
       </c>
       <c r="F1069" s="26" t="s">
+        <v>1243</v>
+      </c>
+      <c r="G1069" s="26" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H1069" s="26" t="s">
         <v>1244</v>
-      </c>
-      <c r="G1069" s="26" t="s">
-        <v>1183</v>
-      </c>
-      <c r="H1069" s="26" t="s">
-        <v>1245</v>
       </c>
       <c r="I1069" s="26" t="s">
         <v>81</v>
@@ -26726,16 +26726,16 @@
     </row>
     <row r="1070" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1070" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1070" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1070" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1070" s="26" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="E1070" s="26" t="s">
         <v>81</v>
@@ -26750,31 +26750,31 @@
         <v>81</v>
       </c>
       <c r="I1070" s="26" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="J1070" s="26"/>
     </row>
     <row r="1071" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1071" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1071" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1071" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1071" s="26" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E1071" s="26" t="s">
         <v>1247</v>
-      </c>
-      <c r="E1071" s="26" t="s">
-        <v>1248</v>
       </c>
       <c r="F1071" s="26" t="s">
         <v>97</v>
       </c>
       <c r="G1071" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1071" s="26" t="s">
         <v>81</v>
@@ -26786,16 +26786,16 @@
     </row>
     <row r="1072" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1072" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1072" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1072" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1072" s="26" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="E1072" s="26" t="s">
         <v>81</v>
@@ -26810,28 +26810,28 @@
         <v>81</v>
       </c>
       <c r="I1072" s="26" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="J1072" s="26"/>
     </row>
     <row r="1073" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1073" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1073" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1073" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1073" s="31" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="E1073" s="26" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="F1073" s="26" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="G1073" s="26" t="s">
         <v>81</v>
@@ -26846,16 +26846,16 @@
     </row>
     <row r="1074" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1074" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1074" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1074" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1074" s="26" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="E1074" s="26" t="s">
         <v>990</v>
@@ -26876,13 +26876,13 @@
     </row>
     <row r="1075" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1075" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1075" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1075" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1075" s="26" t="s">
         <v>218</v>
@@ -26906,13 +26906,13 @@
     </row>
     <row r="1076" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1076" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1076" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1076" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1076" s="26" t="s">
         <v>796</v>
@@ -26936,13 +26936,13 @@
     </row>
     <row r="1077" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1077" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1077" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1077" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1077" s="26" t="s">
         <v>594</v>
@@ -26968,13 +26968,13 @@
     </row>
     <row r="1078" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1078" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1078" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1078" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1078" s="26" t="s">
         <v>338</v>
@@ -26992,7 +26992,7 @@
         <v>89</v>
       </c>
       <c r="I1078" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1078" s="26" t="s">
         <v>89</v>
@@ -27000,16 +27000,16 @@
     </row>
     <row r="1079" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1079" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1079" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1079" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1079" s="26" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="E1079" s="26" t="s">
         <v>1021</v>
@@ -27021,10 +27021,10 @@
         <v>81</v>
       </c>
       <c r="H1079" s="26" t="s">
+        <v>1251</v>
+      </c>
+      <c r="I1079" s="26" t="s">
         <v>1252</v>
-      </c>
-      <c r="I1079" s="26" t="s">
-        <v>1253</v>
       </c>
       <c r="J1079" s="26" t="s">
         <v>1021</v>
@@ -27032,19 +27032,19 @@
     </row>
     <row r="1080" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1080" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1080" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1080" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1080" s="26" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E1080" s="26" t="s">
         <v>1254</v>
-      </c>
-      <c r="E1080" s="26" t="s">
-        <v>1255</v>
       </c>
       <c r="F1080" s="26" t="s">
         <v>924</v>
@@ -27064,16 +27064,16 @@
     </row>
     <row r="1081" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1081" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1081" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1081" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1081" s="26" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="E1081" s="26" t="s">
         <v>811</v>
@@ -27082,28 +27082,28 @@
         <v>811</v>
       </c>
       <c r="G1081" s="26" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="H1081" s="26" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="I1081" s="26" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="J1081" s="26"/>
     </row>
     <row r="1082" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1082" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1082" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1082" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1082" s="26" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E1082" s="26" t="s">
         <v>28</v>
@@ -27115,25 +27115,25 @@
         <v>28</v>
       </c>
       <c r="H1082" s="26" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="I1082" s="26" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="J1082" s="26"/>
     </row>
     <row r="1083" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1083" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1083" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1083" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1083" s="26" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="E1083" s="26" t="s">
         <v>28</v>
@@ -27154,16 +27154,16 @@
     </row>
     <row r="1084" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1084" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1084" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1084" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1084" s="26" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="E1084" s="26" t="s">
         <v>808</v>
@@ -27178,19 +27178,19 @@
         <v>81</v>
       </c>
       <c r="I1084" s="26" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="J1084" s="26"/>
     </row>
     <row r="1085" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1085" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1085" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1085" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1085" s="26" t="s">
         <v>108</v>
@@ -27208,22 +27208,22 @@
         <v>89</v>
       </c>
       <c r="I1085" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1085" s="26"/>
     </row>
     <row r="1086" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1086" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1086" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1086" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1086" s="26" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="E1086" s="26" t="s">
         <v>946</v>
@@ -27235,7 +27235,7 @@
         <v>81</v>
       </c>
       <c r="H1086" s="26" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="I1086" s="26" t="s">
         <v>81</v>
@@ -27246,16 +27246,16 @@
     </row>
     <row r="1087" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1087" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1087" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1087" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1087" s="26" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E1087" s="26" t="s">
         <v>89</v>
@@ -27276,16 +27276,16 @@
     </row>
     <row r="1088" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1088" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1088" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1088" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1088" s="26" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="E1088" s="26" t="s">
         <v>89</v>
@@ -27306,13 +27306,13 @@
     </row>
     <row r="1089" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1089" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1089" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1089" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1089" s="26" t="s">
         <v>50</v>
@@ -27321,7 +27321,7 @@
         <v>392</v>
       </c>
       <c r="F1089" s="26" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="G1089" s="26" t="s">
         <v>108</v>
@@ -27336,13 +27336,13 @@
     </row>
     <row r="1090" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1090" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1090" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1090" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1090" s="26" t="s">
         <v>233</v>
@@ -27368,16 +27368,16 @@
     </row>
     <row r="1091" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1091" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1091" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1091" s="32" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D1091" s="32" t="s">
         <v>1263</v>
-      </c>
-      <c r="D1091" s="32" t="s">
-        <v>1264</v>
       </c>
       <c r="E1091" s="32" t="s">
         <v>89</v>
@@ -27396,22 +27396,22 @@
     </row>
     <row r="1092" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1092" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1092" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1092" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D1092" s="32" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="E1092" s="32" t="s">
         <v>108</v>
       </c>
       <c r="F1092" s="32" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="G1092" s="32" t="s">
         <v>89</v>
@@ -27428,43 +27428,43 @@
     </row>
     <row r="1093" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1093" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1093" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1093" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D1093" s="33" t="s">
         <v>348</v>
       </c>
       <c r="E1093" s="33" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F1093" s="33" t="s">
         <v>89</v>
       </c>
       <c r="G1093" s="33" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1093" s="33" t="s">
         <v>108</v>
       </c>
       <c r="I1093" s="33" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1093" s="32"/>
     </row>
     <row r="1094" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1094" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1094" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1094" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D1094" s="32" t="s">
         <v>50</v>
@@ -27473,31 +27473,31 @@
         <v>808</v>
       </c>
       <c r="F1094" s="32" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G1094" s="32" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1094" s="32" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="I1094" s="32" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="J1094" s="32"/>
     </row>
     <row r="1095" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1095" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1095" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1095" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D1095" s="32" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="E1095" s="32" t="s">
         <v>401</v>
@@ -27515,18 +27515,18 @@
         <v>108</v>
       </c>
       <c r="J1095" s="32" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="1096" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1096" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1096" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1096" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D1096" s="34" t="s">
         <v>34</v>
@@ -27552,16 +27552,16 @@
     </row>
     <row r="1097" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1097" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1097" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1097" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D1097" s="34" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="E1097" s="34" t="s">
         <v>81</v>
@@ -27573,24 +27573,24 @@
         <v>81</v>
       </c>
       <c r="H1097" s="34" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="I1097" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J1097" s="34" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="1098" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1098" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1098" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1098" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D1098" s="34" t="s">
         <v>50</v>
@@ -27616,28 +27616,28 @@
     </row>
     <row r="1099" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1099" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1099" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1099" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D1099" s="34" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="E1099" s="34" t="s">
         <v>50</v>
       </c>
       <c r="F1099" s="34" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G1099" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1099" s="34" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="I1099" s="34" t="s">
         <v>50</v>
@@ -27646,13 +27646,13 @@
     </row>
     <row r="1100" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1100" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1100" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1100" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D1100" s="34" t="s">
         <v>108</v>
@@ -27676,22 +27676,22 @@
     </row>
     <row r="1101" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1101" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1101" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1101" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D1101" s="34" t="s">
         <v>496</v>
       </c>
       <c r="E1101" s="34" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F1101" s="34" t="s">
         <v>1274</v>
-      </c>
-      <c r="F1101" s="34" t="s">
-        <v>1275</v>
       </c>
       <c r="G1101" s="34" t="s">
         <v>89</v>
@@ -27706,13 +27706,13 @@
     </row>
     <row r="1102" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1102" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1102" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1102" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D1102" s="34" t="s">
         <v>204</v>
@@ -27736,13 +27736,13 @@
     </row>
     <row r="1103" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1103" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1103" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1103" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D1103" s="34" t="s">
         <v>149</v>
@@ -27766,16 +27766,16 @@
     </row>
     <row r="1104" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1104" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1104" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1104" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D1104" s="34" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="E1104" s="34" t="s">
         <v>144</v>
@@ -27784,7 +27784,7 @@
         <v>144</v>
       </c>
       <c r="G1104" s="34" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="H1104" s="34" t="s">
         <v>89</v>
@@ -27793,27 +27793,27 @@
         <v>89</v>
       </c>
       <c r="J1104" s="34" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="1105" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1105" s="32" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B1105" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1105" s="32" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D1105" s="34" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="E1105" s="34" t="s">
         <v>81</v>
       </c>
       <c r="F1105" s="34" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="G1105" s="34" t="s">
         <v>81</v>
@@ -27834,19 +27834,19 @@
         <v>155</v>
       </c>
       <c r="C1106" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1106" s="34" t="s">
         <v>319</v>
       </c>
       <c r="E1106" s="34" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F1106" s="34" t="s">
+        <v>1278</v>
+      </c>
+      <c r="G1106" s="34" t="s">
         <v>1279</v>
-      </c>
-      <c r="F1106" s="34" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G1106" s="34" t="s">
-        <v>1280</v>
       </c>
       <c r="H1106" s="34" t="s">
         <v>143</v>
@@ -27864,28 +27864,28 @@
         <v>155</v>
       </c>
       <c r="C1107" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1107" s="34" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E1107" s="34" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F1107" s="34" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G1107" s="34" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1107" s="34" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1107" s="34" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1107" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="1108" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27896,25 +27896,25 @@
         <v>155</v>
       </c>
       <c r="C1108" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1108" s="35" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="E1108" s="35" t="s">
         <v>16</v>
       </c>
       <c r="F1108" s="35" t="s">
+        <v>1282</v>
+      </c>
+      <c r="G1108" s="35" t="s">
+        <v>1281</v>
+      </c>
+      <c r="H1108" s="35" t="s">
         <v>1283</v>
       </c>
-      <c r="G1108" s="35" t="s">
-        <v>1282</v>
-      </c>
-      <c r="H1108" s="35" t="s">
-        <v>1284</v>
-      </c>
       <c r="I1108" s="35" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="J1108" s="34"/>
     </row>
@@ -27926,22 +27926,22 @@
         <v>155</v>
       </c>
       <c r="C1109" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1109" s="34" t="s">
         <v>108</v>
       </c>
       <c r="E1109" s="34" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F1109" s="34" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G1109" s="34" t="s">
         <v>1280</v>
       </c>
-      <c r="F1109" s="34" t="s">
+      <c r="H1109" s="34" t="s">
         <v>1280</v>
-      </c>
-      <c r="G1109" s="34" t="s">
-        <v>1281</v>
-      </c>
-      <c r="H1109" s="34" t="s">
-        <v>1281</v>
       </c>
       <c r="I1109" s="34" t="s">
         <v>108</v>
@@ -27956,28 +27956,28 @@
         <v>155</v>
       </c>
       <c r="C1110" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1110" s="34" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E1110" s="34" t="s">
         <v>1285</v>
       </c>
-      <c r="E1110" s="34" t="s">
-        <v>1286</v>
-      </c>
       <c r="F1110" s="34" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="G1110" s="34" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H1110" s="34" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="I1110" s="34" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="J1110" s="34" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="1111" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27988,28 +27988,28 @@
         <v>155</v>
       </c>
       <c r="C1111" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1111" s="34" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E1111" s="34" t="s">
         <v>1285</v>
       </c>
-      <c r="E1111" s="34" t="s">
-        <v>1286</v>
-      </c>
       <c r="F1111" s="34" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="G1111" s="34" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H1111" s="34" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="I1111" s="34" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="J1111" s="34" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="1112" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28020,7 +28020,7 @@
         <v>155</v>
       </c>
       <c r="C1112" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1112" s="34" t="s">
         <v>275</v>
@@ -28029,7 +28029,7 @@
         <v>281</v>
       </c>
       <c r="F1112" s="34" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="G1112" s="34" t="s">
         <v>281</v>
@@ -28041,7 +28041,7 @@
         <v>281</v>
       </c>
       <c r="J1112" s="34" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="1113" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28052,25 +28052,25 @@
         <v>155</v>
       </c>
       <c r="C1113" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1113" s="34" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="E1113" s="34" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="F1113" s="34" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="G1113" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H1113" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="I1113" s="34" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="J1113" s="34"/>
     </row>
@@ -28082,19 +28082,19 @@
         <v>155</v>
       </c>
       <c r="C1114" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1114" s="34" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E1114" s="34" t="s">
         <v>1289</v>
       </c>
-      <c r="E1114" s="34" t="s">
-        <v>1290</v>
-      </c>
       <c r="F1114" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="G1114" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H1114" s="34" t="s">
         <v>227</v>
@@ -28103,7 +28103,7 @@
         <v>227</v>
       </c>
       <c r="J1114" s="34" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="1115" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28114,16 +28114,16 @@
         <v>155</v>
       </c>
       <c r="C1115" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1115" s="34" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E1115" s="34" t="s">
         <v>1291</v>
       </c>
-      <c r="E1115" s="34" t="s">
-        <v>1292</v>
-      </c>
       <c r="F1115" s="34" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="G1115" s="34" t="s">
         <v>281</v>
@@ -28132,10 +28132,10 @@
         <v>157</v>
       </c>
       <c r="I1115" s="34" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="J1115" s="34" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="1116" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28146,28 +28146,28 @@
         <v>155</v>
       </c>
       <c r="C1116" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1116" s="34" t="s">
         <v>337</v>
       </c>
       <c r="E1116" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="F1116" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="G1116" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H1116" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="I1116" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J1116" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="1117" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28178,28 +28178,28 @@
         <v>155</v>
       </c>
       <c r="C1117" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1117" s="34" t="s">
         <v>337</v>
       </c>
       <c r="E1117" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="F1117" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="G1117" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H1117" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="I1117" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J1117" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="1118" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28210,28 +28210,28 @@
         <v>155</v>
       </c>
       <c r="C1118" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1118" s="34" t="s">
         <v>437</v>
       </c>
       <c r="E1118" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="F1118" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="G1118" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H1118" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="I1118" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J1118" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="1119" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28242,28 +28242,28 @@
         <v>155</v>
       </c>
       <c r="C1119" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1119" s="34" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="E1119" s="34" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F1119" s="34" t="s">
+        <v>1279</v>
+      </c>
+      <c r="G1119" s="34" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H1119" s="34" t="s">
         <v>1280</v>
       </c>
-      <c r="F1119" s="34" t="s">
-        <v>1280</v>
-      </c>
-      <c r="G1119" s="34" t="s">
-        <v>1280</v>
-      </c>
-      <c r="H1119" s="34" t="s">
-        <v>1281</v>
-      </c>
       <c r="I1119" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J1119" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="1120" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28274,25 +28274,25 @@
         <v>155</v>
       </c>
       <c r="C1120" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1120" s="34" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="E1120" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="F1120" s="34" t="s">
         <v>108</v>
       </c>
       <c r="G1120" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H1120" s="34" t="s">
         <v>108</v>
       </c>
       <c r="I1120" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J1120" s="34"/>
     </row>
@@ -28304,19 +28304,19 @@
         <v>155</v>
       </c>
       <c r="C1121" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1121" s="36" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E1121" s="36" t="s">
         <v>1295</v>
       </c>
-      <c r="E1121" s="36" t="s">
-        <v>1296</v>
-      </c>
       <c r="F1121" s="36" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="G1121" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="H1121" s="34" t="s">
         <v>108</v>
@@ -28334,28 +28334,28 @@
         <v>155</v>
       </c>
       <c r="C1122" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1122" s="34" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="E1122" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="F1122" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="G1122" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1122" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="I1122" s="34" t="s">
         <v>108</v>
       </c>
       <c r="J1122" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="1123" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28366,28 +28366,28 @@
         <v>155</v>
       </c>
       <c r="C1123" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1123" s="34" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="E1123" s="34" t="s">
         <v>143</v>
       </c>
       <c r="F1123" s="34" t="s">
+        <v>1278</v>
+      </c>
+      <c r="G1123" s="34" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H1123" s="34" t="s">
+        <v>1182</v>
+      </c>
+      <c r="I1123" s="34" t="s">
         <v>1279</v>
       </c>
-      <c r="G1123" s="34" t="s">
-        <v>1183</v>
-      </c>
-      <c r="H1123" s="34" t="s">
-        <v>1183</v>
-      </c>
-      <c r="I1123" s="34" t="s">
-        <v>1280</v>
-      </c>
       <c r="J1123" s="34" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="1124" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28398,28 +28398,28 @@
         <v>155</v>
       </c>
       <c r="C1124" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1124" s="34" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E1124" s="34" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F1124" s="34" t="s">
         <v>1300</v>
-      </c>
-      <c r="E1124" s="34" t="s">
-        <v>1280</v>
-      </c>
-      <c r="F1124" s="34" t="s">
-        <v>1301</v>
       </c>
       <c r="G1124" s="34" t="s">
         <v>228</v>
       </c>
       <c r="H1124" s="34" t="s">
+        <v>1299</v>
+      </c>
+      <c r="I1124" s="34" t="s">
+        <v>1280</v>
+      </c>
+      <c r="J1124" s="34" t="s">
         <v>1300</v>
-      </c>
-      <c r="I1124" s="34" t="s">
-        <v>1281</v>
-      </c>
-      <c r="J1124" s="34" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="1125" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28430,40 +28430,40 @@
         <v>155</v>
       </c>
       <c r="C1125" s="28" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D1125" s="34" t="s">
         <v>111</v>
       </c>
       <c r="E1125" s="34" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="F1125" s="34" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="G1125" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1125" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="I1125" s="34" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J1125" s="34"/>
     </row>
     <row r="1126" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1126" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1126" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1126" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1126" s="34" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E1126" s="34" t="s">
         <v>808</v>
@@ -28472,10 +28472,10 @@
         <v>808</v>
       </c>
       <c r="G1126" s="34" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1126" s="34" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1126" s="34" t="s">
         <v>81</v>
@@ -28484,16 +28484,16 @@
     </row>
     <row r="1127" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1127" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1127" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1127" s="34" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D1127" s="34" t="s">
         <v>1302</v>
-      </c>
-      <c r="D1127" s="34" t="s">
-        <v>1303</v>
       </c>
       <c r="E1127" s="34" t="s">
         <v>969</v>
@@ -28514,16 +28514,16 @@
     </row>
     <row r="1128" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1128" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1128" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1128" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1128" s="34" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="E1128" s="34" t="s">
         <v>242</v>
@@ -28546,16 +28546,16 @@
     </row>
     <row r="1129" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1129" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1129" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1129" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1129" s="34" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="E1129" s="34" t="s">
         <v>14</v>
@@ -28576,13 +28576,13 @@
     </row>
     <row r="1130" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1130" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1130" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1130" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1130" s="34" t="s">
         <v>142</v>
@@ -28606,16 +28606,16 @@
     </row>
     <row r="1131" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1131" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1131" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1131" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1131" s="34" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E1131" s="34" t="s">
         <v>19</v>
@@ -28627,7 +28627,7 @@
         <v>81</v>
       </c>
       <c r="H1131" s="34" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="I1131" s="34" t="s">
         <v>34</v>
@@ -28636,16 +28636,16 @@
     </row>
     <row r="1132" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1132" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1132" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1132" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1132" s="34" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="E1132" s="34" t="s">
         <v>242</v>
@@ -28660,19 +28660,19 @@
         <v>98</v>
       </c>
       <c r="I1132" s="34" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="J1132" s="34"/>
     </row>
     <row r="1133" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1133" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1133" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1133" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1133" s="34" t="s">
         <v>321</v>
@@ -28696,13 +28696,13 @@
     </row>
     <row r="1134" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1134" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1134" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1134" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1134" s="34" t="s">
         <v>204</v>
@@ -28726,19 +28726,19 @@
     </row>
     <row r="1135" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1135" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1135" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1135" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1135" s="34" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E1135" s="34" t="s">
         <v>1309</v>
-      </c>
-      <c r="E1135" s="34" t="s">
-        <v>1310</v>
       </c>
       <c r="F1135" s="34" t="s">
         <v>89</v>
@@ -28758,16 +28758,16 @@
     </row>
     <row r="1136" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1136" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1136" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1136" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1136" s="34" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="E1136" s="34" t="s">
         <v>34</v>
@@ -28788,13 +28788,13 @@
     </row>
     <row r="1137" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1137" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1137" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1137" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1137" s="34" t="s">
         <v>204</v>
@@ -28818,13 +28818,13 @@
     </row>
     <row r="1138" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1138" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1138" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1138" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1138" s="34" t="s">
         <v>149</v>
@@ -28848,16 +28848,16 @@
     </row>
     <row r="1139" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1139" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1139" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1139" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1139" s="34" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="E1139" s="34" t="s">
         <v>89</v>
@@ -28878,28 +28878,28 @@
     </row>
     <row r="1140" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1140" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1140" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1140" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1140" s="34" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="E1140" s="34" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="F1140" s="34" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="G1140" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1140" s="34" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1140" s="34" t="s">
         <v>81</v>
@@ -28908,16 +28908,16 @@
     </row>
     <row r="1141" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1141" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1141" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1141" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1141" s="34" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="E1141" s="34" t="s">
         <v>54</v>
@@ -28938,13 +28938,13 @@
     </row>
     <row r="1142" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1142" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1142" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1142" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1142" s="34" t="s">
         <v>204</v>
@@ -28968,13 +28968,13 @@
     </row>
     <row r="1143" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1143" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1143" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1143" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1143" s="34" t="s">
         <v>206</v>
@@ -29000,16 +29000,16 @@
     </row>
     <row r="1144" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1144" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1144" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1144" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1144" s="34" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="E1144" s="34" t="s">
         <v>242</v>
@@ -29018,7 +29018,7 @@
         <v>89</v>
       </c>
       <c r="G1144" s="34" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1144" s="34" t="s">
         <v>89</v>
@@ -29030,16 +29030,16 @@
     </row>
     <row r="1145" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1145" s="34" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B1145" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1145" s="34" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D1145" s="34" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="E1145" s="34" t="s">
         <v>141</v>
@@ -29062,13 +29062,13 @@
     </row>
     <row r="1146" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1146" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1146" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1146" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1146" s="38" t="s">
         <v>81</v>
@@ -29092,13 +29092,13 @@
     </row>
     <row r="1147" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1147" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1147" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1147" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1147" s="38" t="s">
         <v>81</v>
@@ -29122,13 +29122,13 @@
     </row>
     <row r="1148" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1148" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1148" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1148" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1148" s="38" t="s">
         <v>108</v>
@@ -29152,28 +29152,28 @@
     </row>
     <row r="1149" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1149" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1149" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1149" s="37" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D1149" s="38" t="s">
         <v>1316</v>
       </c>
-      <c r="D1149" s="38" t="s">
-        <v>1317</v>
-      </c>
       <c r="E1149" s="37" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="F1149" s="38" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="G1149" s="37" t="s">
         <v>108</v>
       </c>
       <c r="H1149" s="38" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="I1149" s="37" t="s">
         <v>22</v>
@@ -29184,22 +29184,22 @@
     </row>
     <row r="1150" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1150" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1150" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1150" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1150" s="38" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E1150" s="37" t="s">
         <v>1318</v>
       </c>
-      <c r="E1150" s="37" t="s">
+      <c r="F1150" s="38" t="s">
         <v>1319</v>
-      </c>
-      <c r="F1150" s="38" t="s">
-        <v>1320</v>
       </c>
       <c r="G1150" s="37" t="s">
         <v>89</v>
@@ -29214,16 +29214,16 @@
     </row>
     <row r="1151" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1151" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1151" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1151" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1151" s="38" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="E1151" s="37" t="s">
         <v>141</v>
@@ -29238,22 +29238,22 @@
         <v>54</v>
       </c>
       <c r="I1151" s="37" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="J1151" s="38"/>
     </row>
     <row r="1152" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1152" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1152" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1152" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1152" s="38" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="E1152" s="37" t="s">
         <v>89</v>
@@ -29268,34 +29268,34 @@
         <v>89</v>
       </c>
       <c r="I1152" s="37" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="J1152" s="38"/>
     </row>
     <row r="1153" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1153" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1153" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1153" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1153" s="38" t="s">
         <v>204</v>
       </c>
       <c r="E1153" s="37" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F1153" s="38" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G1153" s="37" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1153" s="38" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1153" s="37" t="s">
         <v>204</v>
@@ -29304,91 +29304,91 @@
     </row>
     <row r="1154" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1154" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1154" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1154" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1154" s="38" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E1154" s="37" t="s">
         <v>1323</v>
       </c>
-      <c r="E1154" s="37" t="s">
-        <v>1324</v>
-      </c>
       <c r="F1154" s="38" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G1154" s="37" t="s">
         <v>108</v>
       </c>
       <c r="H1154" s="38" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="I1154" s="37" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="J1154" s="38"/>
     </row>
     <row r="1155" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1155" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1155" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1155" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1155" s="38" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="E1155" s="37" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="F1155" s="38" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G1155" s="37" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="H1155" s="38" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="I1155" s="37" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="J1155" s="38"/>
     </row>
     <row r="1156" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1156" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1156" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1156" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1156" s="38" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E1156" s="37" t="s">
         <v>1326</v>
-      </c>
-      <c r="E1156" s="37" t="s">
-        <v>1327</v>
       </c>
       <c r="F1156" s="38" t="s">
         <v>219</v>
       </c>
       <c r="G1156" s="37" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1156" s="38" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I1156" s="37" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="J1156" s="38" t="s">
         <v>219</v>
@@ -29396,19 +29396,19 @@
     </row>
     <row r="1157" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1157" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1157" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1157" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1157" s="38" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="E1157" s="37" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="F1157" s="38" t="s">
         <v>902</v>
@@ -29417,28 +29417,28 @@
         <v>81</v>
       </c>
       <c r="H1157" s="38" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="I1157" s="37" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="J1157" s="38"/>
     </row>
     <row r="1158" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1158" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1158" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1158" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1158" s="38" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="E1158" s="37" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="F1158" s="38" t="s">
         <v>902</v>
@@ -29450,67 +29450,67 @@
         <v>81</v>
       </c>
       <c r="I1158" s="37" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="J1158" s="38"/>
     </row>
     <row r="1159" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1159" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1159" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1159" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1159" s="38" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="E1159" s="37" t="s">
         <v>34</v>
       </c>
       <c r="F1159" s="38" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="G1159" s="37" t="s">
         <v>81</v>
       </c>
       <c r="H1159" s="38" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="I1159" s="37" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="J1159" s="38"/>
     </row>
     <row r="1160" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1160" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1160" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1160" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1160" s="38" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E1160" s="37" t="s">
         <v>1332</v>
-      </c>
-      <c r="E1160" s="37" t="s">
-        <v>1333</v>
       </c>
       <c r="F1160" s="38" t="s">
         <v>832</v>
       </c>
       <c r="G1160" s="37" t="s">
+        <v>1333</v>
+      </c>
+      <c r="H1160" s="38" t="s">
+        <v>1194</v>
+      </c>
+      <c r="I1160" s="37" t="s">
         <v>1334</v>
-      </c>
-      <c r="H1160" s="38" t="s">
-        <v>1195</v>
-      </c>
-      <c r="I1160" s="37" t="s">
-        <v>1335</v>
       </c>
       <c r="J1160" s="38" t="s">
         <v>81</v>
@@ -29518,16 +29518,16 @@
     </row>
     <row r="1161" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1161" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1161" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1161" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1161" s="38" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="E1161" s="37" t="s">
         <v>847</v>
@@ -29536,43 +29536,43 @@
         <v>847</v>
       </c>
       <c r="G1161" s="37" t="s">
+        <v>1336</v>
+      </c>
+      <c r="H1161" s="38" t="s">
         <v>1337</v>
       </c>
-      <c r="H1161" s="38" t="s">
-        <v>1338</v>
-      </c>
       <c r="I1161" s="37" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="J1161" s="38"/>
     </row>
     <row r="1162" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1162" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1162" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1162" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1162" s="38" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E1162" s="37" t="s">
         <v>1339</v>
       </c>
-      <c r="E1162" s="37" t="s">
+      <c r="F1162" s="38" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G1162" s="37" t="s">
         <v>1340</v>
-      </c>
-      <c r="F1162" s="38" t="s">
-        <v>1340</v>
-      </c>
-      <c r="G1162" s="37" t="s">
-        <v>1341</v>
       </c>
       <c r="H1162" s="38" t="s">
         <v>81</v>
       </c>
       <c r="I1162" s="37" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="J1162" s="38" t="s">
         <v>81</v>
@@ -29580,13 +29580,13 @@
     </row>
     <row r="1163" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1163" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1163" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1163" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1163" s="38" t="s">
         <v>108</v>
@@ -29610,13 +29610,13 @@
     </row>
     <row r="1164" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1164" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1164" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1164" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1164" s="38" t="s">
         <v>108</v>
@@ -29640,31 +29640,31 @@
     </row>
     <row r="1165" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1165" s="37" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B1165" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1165" s="37" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="D1165" s="38" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E1165" s="37" t="s">
         <v>1326</v>
-      </c>
-      <c r="E1165" s="37" t="s">
-        <v>1327</v>
       </c>
       <c r="F1165" s="38" t="s">
         <v>219</v>
       </c>
       <c r="G1165" s="37" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1165" s="38" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="I1165" s="37" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="J1165" s="38" t="s">
         <v>219</v>
@@ -29672,13 +29672,13 @@
     </row>
     <row r="1166" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1166" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1166" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1166" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1166" s="34" t="s">
         <v>108</v>
@@ -29702,16 +29702,16 @@
     </row>
     <row r="1167" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1167" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1167" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1167" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1167" s="34" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="E1167" s="34" t="s">
         <v>143</v>
@@ -29732,19 +29732,19 @@
     </row>
     <row r="1168" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1168" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1168" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1168" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1168" s="35" t="s">
         <v>338</v>
       </c>
       <c r="E1168" s="35" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F1168" s="35" t="s">
         <v>89</v>
@@ -29762,13 +29762,13 @@
     </row>
     <row r="1169" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1169" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1169" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1169" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1169" s="34" t="s">
         <v>108</v>
@@ -29792,13 +29792,13 @@
     </row>
     <row r="1170" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1170" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1170" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1170" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1170" s="34" t="s">
         <v>114</v>
@@ -29824,19 +29824,19 @@
     </row>
     <row r="1171" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1171" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1171" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1171" s="34" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D1171" s="34" t="s">
         <v>1342</v>
       </c>
-      <c r="D1171" s="34" t="s">
+      <c r="E1171" s="34" t="s">
         <v>1343</v>
-      </c>
-      <c r="E1171" s="34" t="s">
-        <v>1344</v>
       </c>
       <c r="F1171" s="34" t="s">
         <v>832</v>
@@ -29854,13 +29854,13 @@
     </row>
     <row r="1172" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1172" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1172" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1172" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1172" s="34" t="s">
         <v>338</v>
@@ -29884,13 +29884,13 @@
     </row>
     <row r="1173" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1173" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1173" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1173" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1173" s="34" t="s">
         <v>458</v>
@@ -29916,16 +29916,16 @@
     </row>
     <row r="1174" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1174" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1174" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1174" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1174" s="34" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="E1174" s="34" t="s">
         <v>82</v>
@@ -29948,22 +29948,22 @@
     </row>
     <row r="1175" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1175" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1175" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1175" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1175" s="34" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E1175" s="34" t="s">
         <v>1346</v>
       </c>
-      <c r="E1175" s="34" t="s">
-        <v>1347</v>
-      </c>
       <c r="F1175" s="34" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="G1175" s="34" t="s">
         <v>108</v>
@@ -29980,22 +29980,22 @@
     </row>
     <row r="1176" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1176" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1176" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1176" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1176" s="34" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="E1176" s="34" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F1176" s="34" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="G1176" s="34" t="s">
         <v>81</v>
@@ -30012,16 +30012,16 @@
     </row>
     <row r="1177" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1177" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1177" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1177" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1177" s="34" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="E1177" s="34" t="s">
         <v>89</v>
@@ -30042,13 +30042,13 @@
     </row>
     <row r="1178" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1178" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1178" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1178" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1178" s="34" t="s">
         <v>334</v>
@@ -30072,13 +30072,13 @@
     </row>
     <row r="1179" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1179" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1179" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1179" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1179" s="34" t="s">
         <v>280</v>
@@ -30102,16 +30102,16 @@
     </row>
     <row r="1180" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1180" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1180" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1180" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1180" s="34" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="E1180" s="34" t="s">
         <v>89</v>
@@ -30132,16 +30132,16 @@
     </row>
     <row r="1181" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1181" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1181" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1181" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1181" s="34" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="E1181" s="34" t="s">
         <v>51</v>
@@ -30164,16 +30164,16 @@
     </row>
     <row r="1182" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1182" s="34" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B1182" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1182" s="34" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D1182" s="34" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="E1182" s="34" t="s">
         <v>89</v>
@@ -30185,7 +30185,7 @@
         <v>89</v>
       </c>
       <c r="H1182" s="34" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="I1182" s="34" t="s">
         <v>108</v>
@@ -30194,13 +30194,13 @@
     </row>
     <row r="1183" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1183" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1183" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1183" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1183" s="39" t="s">
         <v>410</v>
@@ -30224,16 +30224,16 @@
     </row>
     <row r="1184" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1184" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1184" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1184" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1184" s="39" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="E1184" s="39" t="s">
         <v>89</v>
@@ -30252,25 +30252,25 @@
     </row>
     <row r="1185" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1185" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1185" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1185" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1185" s="39" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E1185" s="39" t="s">
         <v>1354</v>
       </c>
-      <c r="E1185" s="39" t="s">
-        <v>1355</v>
-      </c>
       <c r="F1185" s="39" t="s">
         <v>89</v>
       </c>
       <c r="G1185" s="39" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="H1185" s="39" t="s">
         <v>89</v>
@@ -30282,43 +30282,43 @@
     </row>
     <row r="1186" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1186" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1186" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1186" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1186" s="39" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="E1186" s="39" t="s">
         <v>832</v>
       </c>
       <c r="F1186" s="39" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G1186" s="39" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H1186" s="39" t="s">
         <v>1357</v>
       </c>
-      <c r="G1186" s="39" t="s">
-        <v>1183</v>
-      </c>
-      <c r="H1186" s="39" t="s">
-        <v>1358</v>
-      </c>
       <c r="I1186" s="39" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="J1186" s="39"/>
     </row>
     <row r="1187" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1187" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1187" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1187" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1187" s="40" t="s">
         <v>594</v>
@@ -30342,13 +30342,13 @@
     </row>
     <row r="1188" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1188" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1188" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1188" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1188" s="40" t="s">
         <v>108</v>
@@ -30372,13 +30372,13 @@
     </row>
     <row r="1189" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1189" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1189" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1189" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1189" s="40" t="s">
         <v>204</v>
@@ -30402,19 +30402,19 @@
     </row>
     <row r="1190" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1190" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1190" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1190" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1190" s="40" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="E1190" s="40" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="F1190" s="40" t="s">
         <v>808</v>
@@ -30423,7 +30423,7 @@
         <v>81</v>
       </c>
       <c r="H1190" s="40" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="I1190" s="40" t="s">
         <v>81</v>
@@ -30432,13 +30432,13 @@
     </row>
     <row r="1191" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1191" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1191" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1191" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1191" s="40" t="s">
         <v>108</v>
@@ -30450,7 +30450,7 @@
         <v>89</v>
       </c>
       <c r="G1191" s="40" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1191" s="40" t="s">
         <v>89</v>
@@ -30462,16 +30462,16 @@
     </row>
     <row r="1192" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1192" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1192" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1192" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1192" s="40" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="E1192" s="40" t="s">
         <v>169</v>
@@ -30494,13 +30494,13 @@
     </row>
     <row r="1193" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1193" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1193" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1193" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1193" s="40" t="s">
         <v>495</v>
@@ -30526,13 +30526,13 @@
     </row>
     <row r="1194" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1194" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1194" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1194" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1194" s="40" t="s">
         <v>50</v>
@@ -30558,13 +30558,13 @@
     </row>
     <row r="1195" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1195" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1195" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1195" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1195" s="40" t="s">
         <v>393</v>
@@ -30580,25 +30580,25 @@
         <v>108</v>
       </c>
       <c r="I1195" s="40" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1195" s="40"/>
     </row>
     <row r="1196" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1196" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1196" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1196" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1196" s="40" t="s">
         <v>321</v>
       </c>
       <c r="E1196" s="40" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F1196" s="40" t="s">
         <v>89</v>
@@ -30616,13 +30616,13 @@
     </row>
     <row r="1197" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1197" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1197" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1197" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1197" s="40" t="s">
         <v>108</v>
@@ -30646,13 +30646,13 @@
     </row>
     <row r="1198" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1198" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1198" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1198" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1198" s="40" t="s">
         <v>204</v>
@@ -30674,16 +30674,16 @@
     </row>
     <row r="1199" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1199" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1199" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1199" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1199" s="40" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E1199" s="40" t="s">
         <v>89</v>
@@ -30702,13 +30702,13 @@
     </row>
     <row r="1200" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1200" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1200" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1200" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1200" s="40" t="s">
         <v>108</v>
@@ -30720,7 +30720,7 @@
         <v>89</v>
       </c>
       <c r="G1200" s="40" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1200" s="40" t="s">
         <v>108</v>
@@ -30732,16 +30732,16 @@
     </row>
     <row r="1201" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1201" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1201" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1201" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1201" s="40" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="E1201" s="40" t="s">
         <v>16</v>
@@ -30753,7 +30753,7 @@
         <v>81</v>
       </c>
       <c r="H1201" s="40" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="I1201" s="40" t="s">
         <v>81</v>
@@ -30762,16 +30762,16 @@
     </row>
     <row r="1202" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1202" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1202" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1202" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1202" s="40" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E1202" s="40" t="s">
         <v>89</v>
@@ -30792,16 +30792,16 @@
     </row>
     <row r="1203" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1203" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1203" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1203" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1203" s="40" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="E1203" s="40" t="s">
         <v>94</v>
@@ -30824,13 +30824,13 @@
     </row>
     <row r="1204" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1204" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1204" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1204" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1204" s="40" t="s">
         <v>338</v>
@@ -30842,10 +30842,10 @@
         <v>89</v>
       </c>
       <c r="G1204" s="40" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="H1204" s="40" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="I1204" s="40" t="s">
         <v>89</v>
@@ -30854,13 +30854,13 @@
     </row>
     <row r="1205" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1205" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1205" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1205" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1205" s="40" t="s">
         <v>392</v>
@@ -30882,13 +30882,13 @@
     </row>
     <row r="1206" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1206" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1206" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1206" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1206" s="40" t="s">
         <v>108</v>
@@ -30910,16 +30910,16 @@
     </row>
     <row r="1207" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1207" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1207" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1207" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1207" s="40" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="E1207" s="40" t="s">
         <v>89</v>
@@ -30928,34 +30928,34 @@
         <v>89</v>
       </c>
       <c r="G1207" s="40" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1207" s="40" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1207" s="40" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1207" s="40"/>
     </row>
     <row r="1208" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1208" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1208" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1208" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1208" s="40" t="s">
+        <v>1364</v>
+      </c>
+      <c r="E1208" s="40" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F1208" s="40" t="s">
         <v>1365</v>
-      </c>
-      <c r="E1208" s="40" t="s">
-        <v>1183</v>
-      </c>
-      <c r="F1208" s="40" t="s">
-        <v>1366</v>
       </c>
       <c r="G1208" s="40" t="s">
         <v>89</v>
@@ -30964,7 +30964,7 @@
         <v>108</v>
       </c>
       <c r="I1208" s="40" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1208" s="40" t="s">
         <v>955</v>
@@ -30972,16 +30972,16 @@
     </row>
     <row r="1209" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1209" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1209" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1209" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1209" s="40" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="E1209" s="40" t="s">
         <v>141</v>
@@ -31004,16 +31004,16 @@
     </row>
     <row r="1210" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1210" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1210" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1210" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1210" s="40" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="E1210" s="40" t="s">
         <v>141</v>
@@ -31034,16 +31034,16 @@
     </row>
     <row r="1211" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1211" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1211" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1211" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1211" s="40" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="E1211" s="40" t="s">
         <v>847</v>
@@ -31055,22 +31055,22 @@
         <v>81</v>
       </c>
       <c r="H1211" s="40" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="I1211" s="40" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="J1211" s="40"/>
     </row>
     <row r="1212" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1212" s="27" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B1212" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1212" s="26" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D1212" s="41" t="s">
         <v>676</v>
@@ -31098,7 +31098,7 @@
         <v>11</v>
       </c>
       <c r="C1213" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1213" s="32" t="s">
         <v>108</v>
@@ -31128,10 +31128,10 @@
         <v>11</v>
       </c>
       <c r="C1214" s="32" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D1214" s="32" t="s">
         <v>1367</v>
-      </c>
-      <c r="D1214" s="32" t="s">
-        <v>1368</v>
       </c>
       <c r="E1214" s="32" t="s">
         <v>89</v>
@@ -31160,16 +31160,16 @@
         <v>11</v>
       </c>
       <c r="C1215" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1215" s="32" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="E1215" s="32" t="s">
         <v>847</v>
       </c>
       <c r="F1215" s="32" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="G1215" s="32" t="s">
         <v>89</v>
@@ -31192,16 +31192,16 @@
         <v>11</v>
       </c>
       <c r="C1216" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1216" s="32" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="E1216" s="32" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="F1216" s="32" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="G1216" s="32" t="s">
         <v>50</v>
@@ -31222,7 +31222,7 @@
         <v>11</v>
       </c>
       <c r="C1217" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1217" s="32" t="s">
         <v>146</v>
@@ -31254,7 +31254,7 @@
         <v>11</v>
       </c>
       <c r="C1218" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1218" s="32" t="s">
         <v>108</v>
@@ -31284,7 +31284,7 @@
         <v>11</v>
       </c>
       <c r="C1219" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1219" s="32" t="s">
         <v>351</v>
@@ -31293,7 +31293,7 @@
         <v>89</v>
       </c>
       <c r="F1219" s="32" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="G1219" s="32" t="s">
         <v>108</v>
@@ -31314,28 +31314,28 @@
         <v>11</v>
       </c>
       <c r="C1220" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1220" s="32" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="E1220" s="32" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="F1220" s="32" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G1220" s="32" t="s">
         <v>89</v>
       </c>
       <c r="H1220" s="32" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="I1220" s="32" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="J1220" s="32" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="1221" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31346,7 +31346,7 @@
         <v>11</v>
       </c>
       <c r="C1221" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1221" s="32" t="s">
         <v>297</v>
@@ -31378,16 +31378,16 @@
         <v>11</v>
       </c>
       <c r="C1222" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1222" s="32" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E1222" s="32" t="s">
         <v>1374</v>
       </c>
-      <c r="E1222" s="32" t="s">
-        <v>1375</v>
-      </c>
       <c r="F1222" s="32" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="G1222" s="32" t="s">
         <v>89</v>
@@ -31408,7 +31408,7 @@
         <v>11</v>
       </c>
       <c r="C1223" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1223" s="32" t="s">
         <v>108</v>
@@ -31438,7 +31438,7 @@
         <v>11</v>
       </c>
       <c r="C1224" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1224" s="32" t="s">
         <v>334</v>
@@ -31468,7 +31468,7 @@
         <v>11</v>
       </c>
       <c r="C1225" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1225" s="32" t="s">
         <v>51</v>
@@ -31489,7 +31489,7 @@
         <v>81</v>
       </c>
       <c r="J1225" s="32" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="1226" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31500,10 +31500,10 @@
         <v>11</v>
       </c>
       <c r="C1226" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1226" s="32" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="E1226" s="32" t="s">
         <v>983</v>
@@ -31530,10 +31530,10 @@
         <v>11</v>
       </c>
       <c r="C1227" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1227" s="32" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="E1227" s="32" t="s">
         <v>16</v>
@@ -31554,13 +31554,13 @@
     </row>
     <row r="1228" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1228" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1228" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1228" s="43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D1228" s="42" t="s">
         <v>108</v>
@@ -31586,13 +31586,13 @@
     </row>
     <row r="1229" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1229" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1229" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1229" s="43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D1229" s="42" t="s">
         <v>50</v>
@@ -31616,13 +31616,13 @@
     </row>
     <row r="1230" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1230" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1230" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1230" s="43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D1230" s="42" t="s">
         <v>411</v>
@@ -31637,22 +31637,22 @@
         <v>108</v>
       </c>
       <c r="H1230" s="42" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="I1230" s="42" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="J1230" s="43"/>
     </row>
     <row r="1231" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1231" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1231" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1231" s="43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D1231" s="42" t="s">
         <v>351</v>
@@ -31661,7 +31661,7 @@
         <v>89</v>
       </c>
       <c r="F1231" s="42" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="G1231" s="42" t="s">
         <v>108</v>
@@ -31676,13 +31676,13 @@
     </row>
     <row r="1232" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1232" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1232" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1232" s="43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D1232" s="42" t="s">
         <v>338</v>
@@ -31708,16 +31708,16 @@
     </row>
     <row r="1233" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1233" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1233" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1233" s="43" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D1233" s="42" t="s">
         <v>1378</v>
-      </c>
-      <c r="D1233" s="42" t="s">
-        <v>1379</v>
       </c>
       <c r="E1233" s="42" t="s">
         <v>89</v>
@@ -31740,13 +31740,13 @@
     </row>
     <row r="1234" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1234" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1234" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1234" s="43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D1234" s="42" t="s">
         <v>458</v>
@@ -31770,22 +31770,22 @@
     </row>
     <row r="1235" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1235" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1235" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1235" s="43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D1235" s="44" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="E1235" s="42" t="s">
         <v>81</v>
       </c>
       <c r="F1235" s="42" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="G1235" s="42" t="s">
         <v>108</v>
@@ -31795,51 +31795,51 @@
       </c>
       <c r="I1235" s="43"/>
       <c r="J1235" s="42" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="1236" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1236" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1236" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1236" s="43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D1236" s="45" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="E1236" s="42" t="s">
         <v>325</v>
       </c>
       <c r="F1236" s="42" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="G1236" s="42" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H1236" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1236" s="42" t="s">
         <v>1383</v>
-      </c>
-      <c r="H1236" s="42" t="s">
-        <v>89</v>
-      </c>
-      <c r="I1236" s="42" t="s">
-        <v>1384</v>
       </c>
       <c r="J1236" s="43"/>
     </row>
     <row r="1237" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1237" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1237" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1237" s="43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D1237" s="46" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="E1237" s="42" t="s">
         <v>108</v>
@@ -31862,22 +31862,22 @@
     </row>
     <row r="1238" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1238" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1238" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1238" s="43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D1238" s="47" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E1238" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1238" s="42" t="s">
         <v>1386</v>
-      </c>
-      <c r="E1238" s="42" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1238" s="42" t="s">
-        <v>1387</v>
       </c>
       <c r="G1238" s="42" t="s">
         <v>108</v>
@@ -31892,16 +31892,16 @@
     </row>
     <row r="1239" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1239" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1239" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1239" s="43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D1239" s="42" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="E1239" s="42" t="s">
         <v>26</v>
@@ -31922,16 +31922,16 @@
     </row>
     <row r="1240" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1240" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1240" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1240" s="43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D1240" s="48" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E1240" s="42" t="s">
         <v>89</v>
@@ -31954,28 +31954,28 @@
     </row>
     <row r="1241" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1241" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1241" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1241" s="43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D1241" s="42" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="E1241" s="42" t="s">
         <v>847</v>
       </c>
       <c r="F1241" s="42" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="G1241" s="42" t="s">
         <v>81</v>
       </c>
       <c r="H1241" s="42" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="I1241" s="42" t="s">
         <v>81</v>
@@ -31984,16 +31984,16 @@
     </row>
     <row r="1242" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1242" s="42" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B1242" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1242" s="43" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D1242" s="42" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="E1242" s="42" t="s">
         <v>19</v>
@@ -32005,22 +32005,22 @@
         <v>81</v>
       </c>
       <c r="H1242" s="42" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="I1242" s="42" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J1242" s="43"/>
     </row>
     <row r="1243" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1243" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1243" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1243" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1243" s="50" t="s">
         <v>50</v>
@@ -32032,7 +32032,7 @@
         <v>89</v>
       </c>
       <c r="G1243" s="50" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H1243" s="50" t="s">
         <v>89</v>
@@ -32044,16 +32044,16 @@
     </row>
     <row r="1244" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1244" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1244" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1244" s="50" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D1244" s="49" t="s">
         <v>1394</v>
-      </c>
-      <c r="D1244" s="49" t="s">
-        <v>1395</v>
       </c>
       <c r="E1244" s="49" t="s">
         <v>89</v>
@@ -32072,19 +32072,19 @@
     </row>
     <row r="1245" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1245" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1245" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1245" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1245" s="49" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="E1245" s="49" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F1245" s="49" t="s">
         <v>19</v>
@@ -32102,16 +32102,16 @@
     </row>
     <row r="1246" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1246" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1246" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1246" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1246" s="51" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E1246" s="51" t="s">
         <v>89</v>
@@ -32132,13 +32132,13 @@
     </row>
     <row r="1247" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1247" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1247" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1247" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1247" s="49" t="s">
         <v>384</v>
@@ -32150,28 +32150,28 @@
         <v>89</v>
       </c>
       <c r="G1247" s="49" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1247" s="49" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1247" s="49" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1247" s="49"/>
     </row>
     <row r="1248" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1248" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1248" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1248" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1248" s="49" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="E1248" s="49" t="s">
         <v>89</v>
@@ -32180,34 +32180,34 @@
         <v>89</v>
       </c>
       <c r="G1248" s="49" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1248" s="49" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1248" s="49" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1248" s="49"/>
     </row>
     <row r="1249" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1249" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1249" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1249" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1249" s="49" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="E1249" s="49" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="F1249" s="49" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="G1249" s="49" t="s">
         <v>89</v>
@@ -32224,28 +32224,28 @@
     </row>
     <row r="1250" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1250" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1250" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1250" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1250" s="49" t="s">
+        <v>1398</v>
+      </c>
+      <c r="E1250" s="49" t="s">
         <v>1399</v>
       </c>
-      <c r="E1250" s="49" t="s">
-        <v>1400</v>
-      </c>
       <c r="F1250" s="49" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="G1250" s="49" t="s">
         <v>81</v>
       </c>
       <c r="H1250" s="49" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="I1250" s="49" t="s">
         <v>81</v>
@@ -32256,19 +32256,19 @@
     </row>
     <row r="1251" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1251" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1251" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1251" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1251" s="49" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E1251" s="49" t="s">
         <v>1402</v>
-      </c>
-      <c r="E1251" s="49" t="s">
-        <v>1403</v>
       </c>
       <c r="F1251" s="49"/>
       <c r="G1251" s="49"/>
@@ -32282,13 +32282,13 @@
     </row>
     <row r="1252" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1252" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1252" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1252" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1252" s="49" t="s">
         <v>242</v>
@@ -32312,16 +32312,16 @@
     </row>
     <row r="1253" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1253" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1253" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1253" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1253" s="49" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E1253" s="49" t="s">
         <v>89</v>
@@ -32330,28 +32330,28 @@
         <v>89</v>
       </c>
       <c r="G1253" s="49" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1253" s="49" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1253" s="49" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1253" s="49"/>
     </row>
     <row r="1254" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1254" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1254" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1254" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1254" s="49" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="E1254" s="49" t="s">
         <v>218</v>
@@ -32360,10 +32360,10 @@
         <v>219</v>
       </c>
       <c r="G1254" s="49" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1254" s="49" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="I1254" s="49" t="s">
         <v>227</v>
@@ -32374,25 +32374,25 @@
     </row>
     <row r="1255" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1255" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1255" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1255" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1255" s="49" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E1255" s="49" t="s">
         <v>1406</v>
-      </c>
-      <c r="E1255" s="49" t="s">
-        <v>1407</v>
       </c>
       <c r="F1255" s="49" t="s">
         <v>827</v>
       </c>
       <c r="G1255" s="49" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1255" s="49" t="s">
         <v>81</v>
@@ -32406,13 +32406,13 @@
     </row>
     <row r="1256" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1256" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1256" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1256" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1256" s="49" t="s">
         <v>242</v>
@@ -32438,19 +32438,19 @@
     </row>
     <row r="1257" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1257" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1257" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1257" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1257" s="49" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E1257" s="49" t="s">
         <v>1408</v>
-      </c>
-      <c r="E1257" s="49" t="s">
-        <v>1409</v>
       </c>
       <c r="F1257" s="49" t="s">
         <v>999</v>
@@ -32459,7 +32459,7 @@
         <v>89</v>
       </c>
       <c r="H1257" s="49" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="I1257" s="49" t="s">
         <v>89</v>
@@ -32470,16 +32470,16 @@
     </row>
     <row r="1258" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1258" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1258" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1258" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1258" s="49" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="E1258" s="49" t="s">
         <v>977</v>
@@ -32488,10 +32488,10 @@
         <v>81</v>
       </c>
       <c r="G1258" s="49" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="H1258" s="49" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="I1258" s="49" t="s">
         <v>977</v>
@@ -32500,16 +32500,16 @@
     </row>
     <row r="1259" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1259" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1259" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1259" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1259" s="49" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="E1259" s="49" t="s">
         <v>81</v>
@@ -32521,7 +32521,7 @@
         <v>81</v>
       </c>
       <c r="H1259" s="49" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="I1259" s="49" t="s">
         <v>81</v>
@@ -32532,16 +32532,16 @@
     </row>
     <row r="1260" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1260" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1260" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1260" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1260" s="49" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="E1260" s="49" t="s">
         <v>808</v>
@@ -32562,16 +32562,16 @@
     </row>
     <row r="1261" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1261" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1261" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1261" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1261" s="49" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="E1261" s="49" t="s">
         <v>808</v>
@@ -32592,16 +32592,16 @@
     </row>
     <row r="1262" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1262" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1262" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1262" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1262" s="49" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="E1262" s="49" t="s">
         <v>89</v>
@@ -32622,16 +32622,16 @@
     </row>
     <row r="1263" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1263" s="49" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B1263" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1263" s="50" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="D1263" s="49" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="E1263" s="49" t="s">
         <v>89</v>
@@ -32658,13 +32658,13 @@
         <v>11</v>
       </c>
       <c r="C1264" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1264" s="32" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="E1264" s="32" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="F1264" s="32" t="s">
         <v>81</v>
@@ -32690,7 +32690,7 @@
         <v>11</v>
       </c>
       <c r="C1265" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1265" s="32" t="s">
         <v>108</v>
@@ -32702,7 +32702,7 @@
         <v>89</v>
       </c>
       <c r="G1265" s="32" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1265" s="32" t="s">
         <v>108</v>
@@ -32722,7 +32722,7 @@
         <v>11</v>
       </c>
       <c r="C1266" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1266" s="33" t="s">
         <v>143</v>
@@ -32754,10 +32754,10 @@
         <v>11</v>
       </c>
       <c r="C1267" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1267" s="32" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="E1267" s="32" t="s">
         <v>108</v>
@@ -32784,7 +32784,7 @@
         <v>11</v>
       </c>
       <c r="C1268" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1268" s="32" t="s">
         <v>50</v>
@@ -32816,7 +32816,7 @@
         <v>11</v>
       </c>
       <c r="C1269" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1269" s="32" t="s">
         <v>409</v>
@@ -32825,7 +32825,7 @@
         <v>847</v>
       </c>
       <c r="F1269" s="32" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="G1269" s="32" t="s">
         <v>89</v>
@@ -32848,7 +32848,7 @@
         <v>11</v>
       </c>
       <c r="C1270" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1270" s="32" t="s">
         <v>20</v>
@@ -32880,10 +32880,10 @@
         <v>11</v>
       </c>
       <c r="C1271" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1271" s="32" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="E1271" s="32" t="s">
         <v>89</v>
@@ -32898,7 +32898,7 @@
         <v>89</v>
       </c>
       <c r="I1271" s="32" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1271" s="32" t="s">
         <v>941</v>
@@ -32912,22 +32912,22 @@
         <v>11</v>
       </c>
       <c r="C1272" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1272" s="32" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="E1272" s="32" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="F1272" s="32" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="G1272" s="32" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H1272" s="32" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="I1272" s="32" t="s">
         <v>81</v>
@@ -32944,19 +32944,19 @@
         <v>11</v>
       </c>
       <c r="C1273" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1273" s="32" t="s">
+        <v>1420</v>
+      </c>
+      <c r="E1273" s="32" t="s">
         <v>1421</v>
-      </c>
-      <c r="E1273" s="32" t="s">
-        <v>1422</v>
       </c>
       <c r="F1273" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G1273" s="32" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H1273" s="32" t="s">
         <v>89</v>
@@ -32974,10 +32974,10 @@
         <v>11</v>
       </c>
       <c r="C1274" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1274" s="32" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="E1274" s="32" t="s">
         <v>941</v>
@@ -33006,22 +33006,22 @@
         <v>11</v>
       </c>
       <c r="C1275" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1275" s="32" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E1275" s="32" t="s">
         <v>1424</v>
       </c>
-      <c r="E1275" s="32" t="s">
+      <c r="F1275" s="32" t="s">
         <v>1425</v>
       </c>
-      <c r="F1275" s="32" t="s">
+      <c r="G1275" s="32" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H1275" s="32" t="s">
         <v>1426</v>
-      </c>
-      <c r="G1275" s="32" t="s">
-        <v>1183</v>
-      </c>
-      <c r="H1275" s="32" t="s">
-        <v>1427</v>
       </c>
       <c r="I1275" s="32" t="s">
         <v>81</v>
@@ -33038,7 +33038,7 @@
         <v>11</v>
       </c>
       <c r="C1276" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1276" s="32" t="s">
         <v>50</v>
@@ -33068,7 +33068,7 @@
         <v>11</v>
       </c>
       <c r="C1277" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1277" s="32" t="s">
         <v>50</v>
@@ -33098,7 +33098,7 @@
         <v>11</v>
       </c>
       <c r="C1278" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1278" s="32" t="s">
         <v>458</v>
@@ -33116,7 +33116,7 @@
         <v>89</v>
       </c>
       <c r="I1278" s="32" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1278" s="32"/>
     </row>
@@ -33128,7 +33128,7 @@
         <v>11</v>
       </c>
       <c r="C1279" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1279" s="32" t="s">
         <v>149</v>
@@ -33158,7 +33158,7 @@
         <v>11</v>
       </c>
       <c r="C1280" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1280" s="32" t="s">
         <v>20</v>
@@ -33190,7 +33190,7 @@
         <v>11</v>
       </c>
       <c r="C1281" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1281" s="32" t="s">
         <v>108</v>
@@ -33205,7 +33205,7 @@
         <v>89</v>
       </c>
       <c r="H1281" s="32" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1281" s="32" t="s">
         <v>89</v>
@@ -33222,7 +33222,7 @@
         <v>11</v>
       </c>
       <c r="C1282" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1282" s="32" t="s">
         <v>101</v>
@@ -33254,13 +33254,13 @@
         <v>11</v>
       </c>
       <c r="C1283" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1283" s="32" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="E1283" s="32" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F1283" s="32" t="s">
         <v>938</v>
@@ -33286,28 +33286,28 @@
         <v>11</v>
       </c>
       <c r="C1284" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1284" s="32" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E1284" s="32" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F1284" s="32" t="s">
+        <v>1167</v>
+      </c>
+      <c r="G1284" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1284" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1284" s="32" t="s">
         <v>1429</v>
       </c>
-      <c r="E1284" s="32" t="s">
-        <v>1373</v>
-      </c>
-      <c r="F1284" s="32" t="s">
-        <v>1168</v>
-      </c>
-      <c r="G1284" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="H1284" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="I1284" s="32" t="s">
-        <v>1430</v>
-      </c>
       <c r="J1284" s="32" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="1285" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -33318,7 +33318,7 @@
         <v>11</v>
       </c>
       <c r="C1285" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1285" s="32" t="s">
         <v>108</v>
@@ -33336,7 +33336,7 @@
         <v>89</v>
       </c>
       <c r="I1285" s="32" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1285" s="32" t="s">
         <v>89</v>
@@ -33350,7 +33350,7 @@
         <v>11</v>
       </c>
       <c r="C1286" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1286" s="32" t="s">
         <v>227</v>
@@ -33382,10 +33382,10 @@
         <v>11</v>
       </c>
       <c r="C1287" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1287" s="32" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="E1287" s="32" t="s">
         <v>101</v>
@@ -33414,7 +33414,7 @@
         <v>11</v>
       </c>
       <c r="C1288" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1288" s="32" t="s">
         <v>116</v>
@@ -33446,19 +33446,19 @@
         <v>11</v>
       </c>
       <c r="C1289" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1289" s="32" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E1289" s="32" t="s">
         <v>1432</v>
       </c>
-      <c r="E1289" s="32" t="s">
+      <c r="F1289" s="32" t="s">
         <v>1433</v>
       </c>
-      <c r="F1289" s="32" t="s">
-        <v>1434</v>
-      </c>
       <c r="G1289" s="32" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1289" s="32" t="s">
         <v>81</v>
@@ -33478,7 +33478,7 @@
         <v>11</v>
       </c>
       <c r="C1290" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1290" s="32" t="s">
         <v>108</v>
@@ -33510,22 +33510,22 @@
         <v>11</v>
       </c>
       <c r="C1291" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1291" s="32" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="E1291" s="32" t="s">
         <v>33</v>
       </c>
       <c r="F1291" s="32" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="G1291" s="32" t="s">
         <v>108</v>
       </c>
       <c r="H1291" s="32" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="I1291" s="32"/>
       <c r="J1291" s="32" t="s">
@@ -33540,7 +33540,7 @@
         <v>11</v>
       </c>
       <c r="C1292" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1292" s="32" t="s">
         <v>116</v>
@@ -33572,13 +33572,13 @@
         <v>11</v>
       </c>
       <c r="C1293" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1293" s="32" t="s">
         <v>108</v>
       </c>
       <c r="E1293" s="32" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F1293" s="32" t="s">
         <v>81</v>
@@ -33590,7 +33590,7 @@
         <v>89</v>
       </c>
       <c r="I1293" s="32" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="J1293" s="32"/>
     </row>
@@ -33602,7 +33602,7 @@
         <v>11</v>
       </c>
       <c r="C1294" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1294" s="32" t="s">
         <v>204</v>
@@ -33614,7 +33614,7 @@
         <v>89</v>
       </c>
       <c r="G1294" s="32" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1294" s="32" t="s">
         <v>204</v>
@@ -33632,7 +33632,7 @@
         <v>11</v>
       </c>
       <c r="C1295" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1295" s="32" t="s">
         <v>108</v>
@@ -33662,10 +33662,10 @@
         <v>11</v>
       </c>
       <c r="C1296" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1296" s="32" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="E1296" s="32" t="s">
         <v>81</v>
@@ -33680,7 +33680,7 @@
         <v>81</v>
       </c>
       <c r="I1296" s="32" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="J1296" s="32"/>
     </row>
@@ -33692,7 +33692,7 @@
         <v>11</v>
       </c>
       <c r="C1297" s="32" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="D1297" s="32" t="s">
         <v>108</v>
@@ -33716,78 +33716,78 @@
     </row>
     <row r="1298" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1298" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1298" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1298" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1298" s="31" t="s">
+        <v>1437</v>
+      </c>
+      <c r="E1298" s="26" t="s">
         <v>1438</v>
       </c>
-      <c r="E1298" s="26" t="s">
+      <c r="F1298" s="26" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G1298" s="31" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H1298" s="26" t="s">
         <v>1439</v>
       </c>
-      <c r="F1298" s="26" t="s">
-        <v>1439</v>
-      </c>
-      <c r="G1298" s="31" t="s">
-        <v>1183</v>
-      </c>
-      <c r="H1298" s="26" t="s">
-        <v>1440</v>
-      </c>
       <c r="I1298" s="26" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="J1298" s="26" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="1299" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1299" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1299" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1299" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1299" s="26" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="E1299" s="26" t="s">
         <v>1088</v>
       </c>
       <c r="F1299" s="26" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G1299" s="26" t="s">
+        <v>1182</v>
+      </c>
+      <c r="H1299" s="26" t="s">
         <v>1442</v>
       </c>
-      <c r="G1299" s="26" t="s">
-        <v>1183</v>
-      </c>
-      <c r="H1299" s="26" t="s">
-        <v>1443</v>
-      </c>
       <c r="I1299" s="26" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="J1299" s="26"/>
     </row>
     <row r="1300" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1300" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1300" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1300" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1300" s="31" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="E1300" s="27" t="s">
         <v>19</v>
@@ -33799,10 +33799,10 @@
         <v>81</v>
       </c>
       <c r="H1300" s="27" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="I1300" s="27" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="J1300" s="26" t="s">
         <v>19</v>
@@ -33810,16 +33810,16 @@
     </row>
     <row r="1301" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1301" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1301" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1301" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1301" s="26" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="E1301" s="26" t="s">
         <v>161</v>
@@ -33834,7 +33834,7 @@
         <v>455</v>
       </c>
       <c r="I1301" s="26" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="J1301" s="26" t="s">
         <v>82</v>
@@ -33842,13 +33842,13 @@
     </row>
     <row r="1302" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1302" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1302" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1302" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1302" s="26" t="s">
         <v>50</v>
@@ -33860,10 +33860,10 @@
         <v>89</v>
       </c>
       <c r="G1302" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1302" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1302" s="26" t="s">
         <v>81</v>
@@ -33872,16 +33872,16 @@
     </row>
     <row r="1303" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1303" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1303" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1303" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1303" s="26" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="E1303" s="26" t="s">
         <v>847</v>
@@ -33896,7 +33896,7 @@
         <v>81</v>
       </c>
       <c r="I1303" s="26" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="J1303" s="26" t="s">
         <v>847</v>
@@ -33904,13 +33904,13 @@
     </row>
     <row r="1304" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1304" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1304" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1304" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1304" s="26" t="s">
         <v>284</v>
@@ -33925,10 +33925,10 @@
         <v>89</v>
       </c>
       <c r="H1304" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I1304" s="26" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="J1304" s="26" t="s">
         <v>141</v>
@@ -33936,16 +33936,16 @@
     </row>
     <row r="1305" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1305" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1305" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1305" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1305" s="26" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="E1305" s="26" t="s">
         <v>1021</v>
@@ -33954,25 +33954,25 @@
         <v>1021</v>
       </c>
       <c r="G1305" s="26" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H1305" s="26" t="s">
         <v>81</v>
       </c>
       <c r="I1305" s="26" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="J1305" s="26"/>
     </row>
     <row r="1306" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1306" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1306" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1306" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1306" s="26" t="s">
         <v>39</v>
@@ -33998,46 +33998,46 @@
     </row>
     <row r="1307" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1307" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1307" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1307" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1307" s="26" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E1307" s="26" t="s">
         <v>1447</v>
       </c>
-      <c r="E1307" s="26" t="s">
-        <v>1448</v>
-      </c>
       <c r="F1307" s="26" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="G1307" s="26" t="s">
         <v>81</v>
       </c>
       <c r="H1307" s="26" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="I1307" s="26" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="J1307" s="26"/>
     </row>
     <row r="1308" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1308" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1308" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1308" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1308" s="31" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="E1308" s="26" t="s">
         <v>847</v>
@@ -34046,13 +34046,13 @@
         <v>847</v>
       </c>
       <c r="G1308" s="26" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="H1308" s="26" t="s">
+        <v>1336</v>
+      </c>
+      <c r="I1308" s="26" t="s">
         <v>1337</v>
-      </c>
-      <c r="I1308" s="26" t="s">
-        <v>1338</v>
       </c>
       <c r="J1308" s="26" t="s">
         <v>847</v>
@@ -34060,16 +34060,16 @@
     </row>
     <row r="1309" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1309" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1309" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1309" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1309" s="26" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="E1309" s="26" t="s">
         <v>841</v>
@@ -34081,25 +34081,25 @@
         <v>81</v>
       </c>
       <c r="H1309" s="26" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="I1309" s="26" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="J1309" s="26"/>
     </row>
     <row r="1310" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1310" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1310" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1310" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1310" s="26" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="E1310" s="26" t="s">
         <v>832</v>
@@ -34108,27 +34108,27 @@
         <v>832</v>
       </c>
       <c r="G1310" s="26" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="H1310" s="26" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="I1310" s="26" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="J1310" s="26" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="1311" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1311" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1311" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1311" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1311" s="26" t="s">
         <v>218</v>
@@ -34152,16 +34152,16 @@
     </row>
     <row r="1312" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1312" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1312" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1312" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1312" s="26" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="E1312" s="26" t="s">
         <v>924</v>
@@ -34173,10 +34173,10 @@
         <v>81</v>
       </c>
       <c r="H1312" s="31" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="I1312" s="26" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="J1312" s="26" t="s">
         <v>924</v>
@@ -34184,31 +34184,31 @@
     </row>
     <row r="1313" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1313" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1313" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1313" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1313" s="31" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E1313" s="26" t="s">
         <v>1454</v>
       </c>
-      <c r="E1313" s="26" t="s">
-        <v>1455</v>
-      </c>
       <c r="F1313" s="26" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="G1313" s="31" t="s">
         <v>81</v>
       </c>
       <c r="H1313" s="26" t="s">
+        <v>1455</v>
+      </c>
+      <c r="I1313" s="26" t="s">
         <v>1456</v>
-      </c>
-      <c r="I1313" s="26" t="s">
-        <v>1457</v>
       </c>
       <c r="J1313" s="26" t="s">
         <v>895</v>
@@ -34216,31 +34216,31 @@
     </row>
     <row r="1314" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1314" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1314" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1314" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1314" s="26" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="E1314" s="26" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F1314" s="26" t="s">
+        <v>1457</v>
+      </c>
+      <c r="G1314" s="26" t="s">
         <v>1458</v>
       </c>
-      <c r="F1314" s="26" t="s">
+      <c r="H1314" s="26" t="s">
         <v>1458</v>
       </c>
-      <c r="G1314" s="26" t="s">
-        <v>1459</v>
-      </c>
-      <c r="H1314" s="26" t="s">
-        <v>1459</v>
-      </c>
       <c r="I1314" s="26" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="J1314" s="26" t="s">
         <v>902</v>
@@ -34248,13 +34248,13 @@
     </row>
     <row r="1315" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1315" s="24" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B1315" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1315" s="25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D1315" s="26" t="s">
         <v>334</v>
@@ -36043,117 +36043,117 @@
     </row>
     <row r="135" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="58" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B135" s="58" t="s">
         <v>1142</v>
       </c>
-      <c r="B135" s="58" t="s">
+      <c r="C135" s="58" t="s">
         <v>1143</v>
-      </c>
-      <c r="C135" s="58" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="22" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B136" s="22" t="s">
         <v>1145</v>
       </c>
-      <c r="B136" s="22" t="s">
+      <c r="C136" s="22" t="s">
         <v>1146</v>
-      </c>
-      <c r="C136" s="22" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="57" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B137" s="57" t="s">
         <v>1148</v>
       </c>
-      <c r="B137" s="57" t="s">
+      <c r="C137" s="57" t="s">
         <v>1149</v>
-      </c>
-      <c r="C137" s="57" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="59" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B138" s="57" t="s">
         <v>1151</v>
       </c>
-      <c r="B138" s="57" t="s">
+      <c r="C138" s="57" t="s">
         <v>1152</v>
-      </c>
-      <c r="C138" s="57" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="22" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B139" s="22" t="s">
         <v>1154</v>
       </c>
-      <c r="B139" s="22" t="s">
+      <c r="C139" s="22" t="s">
         <v>1155</v>
-      </c>
-      <c r="C139" s="22" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="22" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B140" s="22" t="s">
         <v>1157</v>
       </c>
-      <c r="B140" s="22" t="s">
+      <c r="C140" s="22" t="s">
         <v>1158</v>
-      </c>
-      <c r="C140" s="22" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="22" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B141" s="22" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C141" s="22" t="s">
         <v>1160</v>
-      </c>
-      <c r="C141" s="22" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="22" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B142" s="22" t="s">
         <v>1162</v>
       </c>
-      <c r="B142" s="22" t="s">
-        <v>1163</v>
-      </c>
       <c r="C142" s="22" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="22" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B143" s="60" t="s">
         <v>1164</v>
       </c>
-      <c r="B143" s="60" t="s">
-        <v>1165</v>
-      </c>
       <c r="C143" s="60" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="22" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B144" s="22" t="s">
         <v>1166</v>
       </c>
-      <c r="B144" s="22" t="s">
-        <v>1167</v>
-      </c>
       <c r="C144" s="22" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="22" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B145" s="22" t="s">
         <v>1033</v>
@@ -36164,35 +36164,35 @@
     </row>
     <row r="146" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="22" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B146" s="22" t="s">
         <v>1169</v>
       </c>
-      <c r="B146" s="22" t="s">
+      <c r="C146" s="22" t="s">
         <v>1170</v>
-      </c>
-      <c r="C146" s="22" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="22" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B147" s="22" t="s">
         <v>1172</v>
       </c>
-      <c r="B147" s="22" t="s">
+      <c r="C147" s="61" t="s">
         <v>1173</v>
-      </c>
-      <c r="C147" s="61" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="22" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B148" s="22" t="s">
         <v>1175</v>
       </c>
-      <c r="B148" s="22" t="s">
-        <v>1176</v>
-      </c>
       <c r="C148" s="22" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
   </sheetData>
@@ -37030,10 +37030,10 @@
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="52" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B59" s="52" t="s">
         <v>1122</v>
-      </c>
-      <c r="B59" s="52" t="s">
-        <v>1123</v>
       </c>
       <c r="C59" s="52" t="s">
         <v>425</v>
@@ -37044,10 +37044,10 @@
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="53" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="C60" s="20" t="s">
         <v>413</v>
@@ -37058,10 +37058,10 @@
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="20" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B61" s="20" t="s">
         <v>1125</v>
-      </c>
-      <c r="B61" s="20" t="s">
-        <v>1126</v>
       </c>
       <c r="C61" s="20" t="s">
         <v>482</v>
@@ -37072,10 +37072,10 @@
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="54" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B62" s="20" t="s">
         <v>1127</v>
-      </c>
-      <c r="B62" s="20" t="s">
-        <v>1128</v>
       </c>
       <c r="C62" s="20" t="s">
         <v>317</v>
@@ -37086,10 +37086,10 @@
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="55" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B63" s="55" t="s">
         <v>1129</v>
-      </c>
-      <c r="B63" s="55" t="s">
-        <v>1130</v>
       </c>
       <c r="C63" s="20" t="s">
         <v>155</v>
@@ -37100,10 +37100,10 @@
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="54" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B64" s="20" t="s">
         <v>1131</v>
-      </c>
-      <c r="B64" s="20" t="s">
-        <v>1132</v>
       </c>
       <c r="C64" s="20" t="s">
         <v>317</v>
@@ -37114,10 +37114,10 @@
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="56" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B65" s="56" t="s">
         <v>1133</v>
-      </c>
-      <c r="B65" s="56" t="s">
-        <v>1134</v>
       </c>
       <c r="C65" s="56" t="s">
         <v>425</v>
@@ -37128,10 +37128,10 @@
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="57" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B66" s="20" t="s">
         <v>1135</v>
-      </c>
-      <c r="B66" s="20" t="s">
-        <v>1136</v>
       </c>
       <c r="C66" s="20" t="s">
         <v>413</v>

--- a/static/TALENKAART_DATA/talenkaart_data.xlsx
+++ b/static/TALENKAART_DATA/talenkaart_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amsuni-my.sharepoint.com/personal/kylie_mansour_student_uva_nl/Documents/Documents/MA/Internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{D6D6DB9B-1825-0E4C-A6B9-EC4CA1933FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9582289-DC86-BE47-B4F1-7C39349B2275}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{D6D6DB9B-1825-0E4C-A6B9-EC4CA1933FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5738FDB0-FA52-454E-87F9-7B2563C22F75}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respondenten" sheetId="2" r:id="rId1"/>
@@ -30194,7 +30194,7 @@
     </row>
     <row r="1183" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1183" s="24" t="s">
-        <v>1176</v>
+        <v>1460</v>
       </c>
       <c r="B1183" s="25" t="s">
         <v>425</v>
@@ -37030,7 +37030,7 @@
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="52" t="s">
-        <v>1460</v>
+        <v>1176</v>
       </c>
       <c r="B59" s="52" t="s">
         <v>1122</v>

--- a/static/TALENKAART_DATA/talenkaart_data.xlsx
+++ b/static/TALENKAART_DATA/talenkaart_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amsuni-my.sharepoint.com/personal/kylie_mansour_student_uva_nl/Documents/Documents/MA/Internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{D6D6DB9B-1825-0E4C-A6B9-EC4CA1933FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5738FDB0-FA52-454E-87F9-7B2563C22F75}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{D6D6DB9B-1825-0E4C-A6B9-EC4CA1933FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD23FD8E-2C6D-1945-93F4-429B5C42A6D5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6927" uniqueCount="1461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6927" uniqueCount="1459">
   <si>
     <t>Locatie</t>
   </si>
@@ -3399,12 +3399,6 @@
   </si>
   <si>
     <t>eng,nld,yue</t>
-  </si>
-  <si>
-    <t>52.358203766879825</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 4.926217857436223</t>
   </si>
   <si>
     <t>52.367097743814796, 4.86875051064426</t>
@@ -15041,7 +15035,7 @@
       </c>
       <c r="C475" s="2"/>
       <c r="D475" s="2" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="E475" s="6"/>
       <c r="F475" s="3"/>
@@ -15167,7 +15161,7 @@
       </c>
       <c r="C482" s="2"/>
       <c r="D482" s="2" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="E482" s="6"/>
       <c r="F482" s="3"/>
@@ -18659,7 +18653,7 @@
       </c>
       <c r="C676" s="2"/>
       <c r="D676" s="2" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="E676" s="6"/>
       <c r="F676" s="3"/>
@@ -21827,7 +21821,7 @@
       </c>
       <c r="C852" s="2"/>
       <c r="D852" s="2" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="E852" s="6"/>
       <c r="F852" s="3"/>
@@ -24095,7 +24089,7 @@
       </c>
       <c r="C978" s="2"/>
       <c r="D978" s="2" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="E978" s="6"/>
       <c r="F978" s="3"/>
@@ -24556,13 +24550,13 @@
     </row>
     <row r="999" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A999" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B999" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C999" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D999" s="25" t="s">
         <v>227</v>
@@ -24586,13 +24580,13 @@
     </row>
     <row r="1000" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1000" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1000" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1000" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1000" s="25" t="s">
         <v>227</v>
@@ -24604,7 +24598,7 @@
         <v>218</v>
       </c>
       <c r="G1000" s="25" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="H1000" s="25" t="s">
         <v>34</v>
@@ -24616,16 +24610,16 @@
     </row>
     <row r="1001" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1001" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1001" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1001" s="25" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D1001" s="25" t="s">
         <v>1177</v>
-      </c>
-      <c r="D1001" s="25" t="s">
-        <v>1179</v>
       </c>
       <c r="E1001" s="25" t="s">
         <v>89</v>
@@ -24637,10 +24631,10 @@
         <v>204</v>
       </c>
       <c r="H1001" s="25" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="I1001" s="25" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="J1001" s="25" t="s">
         <v>108</v>
@@ -24648,13 +24642,13 @@
     </row>
     <row r="1002" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1002" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1002" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1002" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1002" s="25" t="s">
         <v>140</v>
@@ -24666,28 +24660,28 @@
         <v>141</v>
       </c>
       <c r="G1002" s="25" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1002" s="25" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1002" s="25" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1002" s="25"/>
     </row>
     <row r="1003" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1003" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1003" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1003" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1003" s="25" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="E1003" s="25" t="s">
         <v>89</v>
@@ -24708,16 +24702,16 @@
     </row>
     <row r="1004" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1004" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1004" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1004" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1004" s="25" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="E1004" s="25" t="s">
         <v>242</v>
@@ -24726,28 +24720,28 @@
         <v>242</v>
       </c>
       <c r="G1004" s="25" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="H1004" s="25" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="I1004" s="25" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="J1004" s="25"/>
     </row>
     <row r="1005" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1005" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1005" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1005" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1005" s="25" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="E1005" s="25" t="s">
         <v>219</v>
@@ -24756,10 +24750,10 @@
         <v>218</v>
       </c>
       <c r="G1005" s="25" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="H1005" s="25" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="I1005" s="25" t="s">
         <v>218</v>
@@ -24768,16 +24762,16 @@
     </row>
     <row r="1006" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1006" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1006" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1006" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1006" s="26" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="E1006" s="26" t="s">
         <v>81</v>
@@ -24798,16 +24792,16 @@
     </row>
     <row r="1007" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1007" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1007" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1007" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1007" s="26" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="E1007" s="27" t="s">
         <v>284</v>
@@ -24819,7 +24813,7 @@
         <v>108</v>
       </c>
       <c r="H1007" s="27" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1007" s="27" t="s">
         <v>81</v>
@@ -24828,19 +24822,19 @@
     </row>
     <row r="1008" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1008" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1008" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1008" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1008" s="26" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="E1008" s="27" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="F1008" s="27" t="s">
         <v>1005</v>
@@ -24849,22 +24843,22 @@
         <v>81</v>
       </c>
       <c r="H1008" s="27" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="I1008" s="27" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="J1008" s="26"/>
     </row>
     <row r="1009" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1009" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1009" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1009" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1009" s="26" t="s">
         <v>34</v>
@@ -24888,13 +24882,13 @@
     </row>
     <row r="1010" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1010" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1010" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1010" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1010" s="26" t="s">
         <v>108</v>
@@ -24906,7 +24900,7 @@
         <v>89</v>
       </c>
       <c r="G1010" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1010" s="26" t="s">
         <v>89</v>
@@ -24918,13 +24912,13 @@
     </row>
     <row r="1011" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1011" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1011" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1011" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1011" s="26" t="s">
         <v>204</v>
@@ -24942,22 +24936,22 @@
         <v>89</v>
       </c>
       <c r="I1011" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1011" s="26"/>
     </row>
     <row r="1012" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1012" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1012" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1012" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1012" s="26" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="E1012" s="26" t="s">
         <v>969</v>
@@ -24966,7 +24960,7 @@
         <v>969</v>
       </c>
       <c r="G1012" s="26" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="H1012" s="26" t="s">
         <v>81</v>
@@ -24978,16 +24972,16 @@
     </row>
     <row r="1013" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1013" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1013" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1013" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1013" s="27" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="E1013" s="27" t="s">
         <v>143</v>
@@ -24999,24 +24993,24 @@
         <v>108</v>
       </c>
       <c r="H1013" s="27" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1013" s="27" t="s">
         <v>81</v>
       </c>
       <c r="J1013" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="1014" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1014" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1014" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1014" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1014" s="26" t="s">
         <v>338</v>
@@ -25042,16 +25036,16 @@
     </row>
     <row r="1015" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1015" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1015" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1015" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1015" s="26" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="E1015" s="26" t="s">
         <v>108</v>
@@ -25078,7 +25072,7 @@
         <v>155</v>
       </c>
       <c r="C1016" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1016" s="28" t="s">
         <v>232</v>
@@ -25110,13 +25104,13 @@
         <v>155</v>
       </c>
       <c r="C1017" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1017" s="28" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="E1017" s="28" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F1017" s="28" t="s">
         <v>219</v>
@@ -25140,7 +25134,7 @@
         <v>155</v>
       </c>
       <c r="C1018" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1018" s="29" t="s">
         <v>796</v>
@@ -25152,13 +25146,13 @@
         <v>89</v>
       </c>
       <c r="G1018" s="29" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1018" s="29" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1018" s="29" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1018" s="28"/>
     </row>
@@ -25170,7 +25164,7 @@
         <v>155</v>
       </c>
       <c r="C1019" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1019" s="28" t="s">
         <v>206</v>
@@ -25198,25 +25192,25 @@
         <v>155</v>
       </c>
       <c r="C1020" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1020" s="28" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="E1020" s="28" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="F1020" s="28" t="s">
         <v>89</v>
       </c>
       <c r="G1020" s="28" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1020" s="28" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1020" s="28" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1020" s="28"/>
     </row>
@@ -25228,16 +25222,16 @@
         <v>155</v>
       </c>
       <c r="C1021" s="28" t="s">
+        <v>1195</v>
+      </c>
+      <c r="D1021" s="28" t="s">
         <v>1197</v>
-      </c>
-      <c r="D1021" s="28" t="s">
-        <v>1199</v>
       </c>
       <c r="E1021" s="28" t="s">
         <v>82</v>
       </c>
       <c r="F1021" s="28" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="G1021" s="28" t="s">
         <v>89</v>
@@ -25246,7 +25240,7 @@
         <v>89</v>
       </c>
       <c r="I1021" s="28" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1021" s="28" t="s">
         <v>281</v>
@@ -25260,7 +25254,7 @@
         <v>155</v>
       </c>
       <c r="C1022" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1022" s="28" t="s">
         <v>31</v>
@@ -25278,7 +25272,7 @@
         <v>89</v>
       </c>
       <c r="I1022" s="28" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1022" s="28" t="s">
         <v>89</v>
@@ -25292,7 +25286,7 @@
         <v>155</v>
       </c>
       <c r="C1023" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1023" s="28" t="s">
         <v>796</v>
@@ -25324,10 +25318,10 @@
         <v>155</v>
       </c>
       <c r="C1024" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1024" s="28" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="E1024" s="28" t="s">
         <v>89</v>
@@ -25356,7 +25350,7 @@
         <v>155</v>
       </c>
       <c r="C1025" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1025" s="28" t="s">
         <v>281</v>
@@ -25388,22 +25382,22 @@
         <v>155</v>
       </c>
       <c r="C1026" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1026" s="28" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E1026" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1026" s="28" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G1026" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1026" s="28" t="s">
         <v>1200</v>
-      </c>
-      <c r="E1026" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1026" s="28" t="s">
-        <v>1201</v>
-      </c>
-      <c r="G1026" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="H1026" s="28" t="s">
-        <v>1202</v>
       </c>
       <c r="I1026" s="28" t="s">
         <v>89</v>
@@ -25420,25 +25414,25 @@
         <v>155</v>
       </c>
       <c r="C1027" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1027" s="28" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="E1027" s="28" t="s">
         <v>81</v>
       </c>
       <c r="F1027" s="28" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="G1027" s="28" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1027" s="28" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="I1027" s="28" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="J1027" s="28"/>
     </row>
@@ -25450,10 +25444,10 @@
         <v>155</v>
       </c>
       <c r="C1028" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1028" s="28" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="E1028" s="28" t="s">
         <v>16</v>
@@ -25465,10 +25459,10 @@
         <v>89</v>
       </c>
       <c r="H1028" s="28" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="I1028" s="28" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="J1028" s="28" t="s">
         <v>15</v>
@@ -25482,7 +25476,7 @@
         <v>155</v>
       </c>
       <c r="C1029" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1029" s="28" t="s">
         <v>281</v>
@@ -25514,7 +25508,7 @@
         <v>155</v>
       </c>
       <c r="C1030" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1030" s="28" t="s">
         <v>89</v>
@@ -25536,16 +25530,16 @@
     </row>
     <row r="1031" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1031" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1031" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1031" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1031" s="26" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="E1031" s="26" t="s">
         <v>902</v>
@@ -25557,22 +25551,22 @@
         <v>81</v>
       </c>
       <c r="H1031" s="26" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="I1031" s="26" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="J1031" s="26"/>
     </row>
     <row r="1032" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1032" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1032" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1032" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1032" s="26" t="s">
         <v>108</v>
@@ -25590,7 +25584,7 @@
         <v>89</v>
       </c>
       <c r="I1032" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1032" s="26" t="s">
         <v>89</v>
@@ -25598,13 +25592,13 @@
     </row>
     <row r="1033" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1033" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1033" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1033" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1033" s="27" t="s">
         <v>50</v>
@@ -25616,13 +25610,13 @@
         <v>89</v>
       </c>
       <c r="G1033" s="27" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1033" s="27" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1033" s="27" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1033" s="26" t="s">
         <v>89</v>
@@ -25630,13 +25624,13 @@
     </row>
     <row r="1034" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1034" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1034" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1034" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1034" s="26" t="s">
         <v>204</v>
@@ -25648,7 +25642,7 @@
         <v>89</v>
       </c>
       <c r="G1034" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1034" s="26" t="s">
         <v>89</v>
@@ -25662,13 +25656,13 @@
     </row>
     <row r="1035" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1035" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1035" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1035" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1035" s="26" t="s">
         <v>81</v>
@@ -25686,16 +25680,16 @@
     </row>
     <row r="1036" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1036" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1036" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1036" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1036" s="26" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="E1036" s="26" t="s">
         <v>892</v>
@@ -25707,10 +25701,10 @@
         <v>81</v>
       </c>
       <c r="H1036" s="26" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="I1036" s="26" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="J1036" s="26" t="s">
         <v>892</v>
@@ -25718,22 +25712,22 @@
     </row>
     <row r="1037" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1037" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1037" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1037" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1037" s="26" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="E1037" s="26" t="s">
         <v>89</v>
       </c>
       <c r="F1037" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="G1037" s="26" t="s">
         <v>81</v>
@@ -25742,7 +25736,7 @@
         <v>89</v>
       </c>
       <c r="I1037" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1037" s="26" t="s">
         <v>89</v>
@@ -25750,19 +25744,19 @@
     </row>
     <row r="1038" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1038" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1038" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1038" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1038" s="26" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="E1038" s="26" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="F1038" s="26" t="s">
         <v>969</v>
@@ -25782,13 +25776,13 @@
     </row>
     <row r="1039" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1039" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1039" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1039" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1039" s="26" t="s">
         <v>204</v>
@@ -25803,7 +25797,7 @@
         <v>22</v>
       </c>
       <c r="H1039" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1039" s="26" t="s">
         <v>22</v>
@@ -25812,16 +25806,16 @@
     </row>
     <row r="1040" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1040" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1040" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1040" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1040" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="E1040" s="26" t="s">
         <v>89</v>
@@ -25830,28 +25824,28 @@
         <v>89</v>
       </c>
       <c r="G1040" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1040" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1040" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1040" s="26"/>
     </row>
     <row r="1041" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1041" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1041" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1041" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1041" s="30" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="E1041" s="30" t="s">
         <v>89</v>
@@ -25860,30 +25854,30 @@
         <v>153</v>
       </c>
       <c r="G1041" s="30" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1041" s="30" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1041" s="30" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1041" s="30" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="1042" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1042" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1042" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1042" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1042" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="E1042" s="26" t="s">
         <v>89</v>
@@ -25904,13 +25898,13 @@
     </row>
     <row r="1043" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1043" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1043" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1043" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1043" s="26" t="s">
         <v>31</v>
@@ -25934,16 +25928,16 @@
     </row>
     <row r="1044" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1044" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1044" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1044" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1044" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="E1044" s="26" t="s">
         <v>81</v>
@@ -25955,7 +25949,7 @@
         <v>89</v>
       </c>
       <c r="H1044" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1044" s="26" t="s">
         <v>81</v>
@@ -25964,28 +25958,28 @@
     </row>
     <row r="1045" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1045" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1045" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1045" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1045" s="26" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="E1045" s="26" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="F1045" s="26" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="G1045" s="26" t="s">
         <v>108</v>
       </c>
       <c r="H1045" s="26" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="I1045" s="26" t="s">
         <v>81</v>
@@ -25994,13 +25988,13 @@
     </row>
     <row r="1046" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1046" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1046" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1046" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1046" s="26" t="s">
         <v>1119</v>
@@ -26024,16 +26018,16 @@
     </row>
     <row r="1047" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1047" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1047" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1047" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1047" s="26" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="E1047" s="26" t="s">
         <v>37</v>
@@ -26054,16 +26048,16 @@
     </row>
     <row r="1048" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1048" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1048" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1048" s="26" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="E1048" s="26" t="s">
         <v>892</v>
@@ -26075,7 +26069,7 @@
         <v>81</v>
       </c>
       <c r="H1048" s="26" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="I1048" s="26" t="s">
         <v>81</v>
@@ -26086,13 +26080,13 @@
     </row>
     <row r="1049" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1049" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1049" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1049" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1049" s="26" t="s">
         <v>142</v>
@@ -26118,13 +26112,13 @@
     </row>
     <row r="1050" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1050" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1050" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1050" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1050" s="26" t="s">
         <v>142</v>
@@ -26150,16 +26144,16 @@
     </row>
     <row r="1051" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1051" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1051" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1051" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1051" s="26" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="E1051" s="26" t="s">
         <v>865</v>
@@ -26174,22 +26168,22 @@
         <v>81</v>
       </c>
       <c r="I1051" s="26" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="J1051" s="26"/>
     </row>
     <row r="1052" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1052" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1052" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1052" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1052" s="26" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="E1052" s="26" t="s">
         <v>81</v>
@@ -26201,7 +26195,7 @@
         <v>81</v>
       </c>
       <c r="H1052" s="26" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="I1052" s="26" t="s">
         <v>81</v>
@@ -26212,16 +26206,16 @@
     </row>
     <row r="1053" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1053" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1053" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1053" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1053" s="26" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="E1053" s="26" t="s">
         <v>81</v>
@@ -26233,7 +26227,7 @@
         <v>81</v>
       </c>
       <c r="H1053" s="26" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="I1053" s="26" t="s">
         <v>81</v>
@@ -26244,16 +26238,16 @@
     </row>
     <row r="1054" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1054" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1054" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1054" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1054" s="26" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E1054" s="26" t="s">
         <v>219</v>
@@ -26274,16 +26268,16 @@
     </row>
     <row r="1055" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1055" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1055" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1055" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1055" s="26" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="E1055" s="26" t="s">
         <v>248</v>
@@ -26292,7 +26286,7 @@
         <v>248</v>
       </c>
       <c r="G1055" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1055" s="26" t="s">
         <v>89</v>
@@ -26306,16 +26300,16 @@
     </row>
     <row r="1056" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1056" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1056" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1056" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1056" s="26" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="E1056" s="26" t="s">
         <v>28</v>
@@ -26324,58 +26318,58 @@
         <v>28</v>
       </c>
       <c r="G1056" s="26" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="H1056" s="26" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="I1056" s="26" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="J1056" s="26" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="1057" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1057" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1057" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1057" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1057" s="26" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="E1057" s="26" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="F1057" s="26"/>
       <c r="G1057" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1057" s="26" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="I1057" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1057" s="26"/>
     </row>
     <row r="1058" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1058" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1058" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1058" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1058" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="E1058" s="26" t="s">
         <v>108</v>
@@ -26390,34 +26384,34 @@
         <v>89</v>
       </c>
       <c r="I1058" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1058" s="26"/>
     </row>
     <row r="1059" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1059" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1059" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1059" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1059" s="26" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="E1059" s="26" t="s">
         <v>81</v>
       </c>
       <c r="F1059" s="26" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="G1059" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1059" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1059" s="26" t="s">
         <v>81</v>
@@ -26426,16 +26420,16 @@
     </row>
     <row r="1060" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1060" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1060" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1060" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1060" s="26" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="E1060" s="26" t="s">
         <v>1041</v>
@@ -26456,13 +26450,13 @@
     </row>
     <row r="1061" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1061" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1061" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1061" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1061" s="26" t="s">
         <v>338</v>
@@ -26474,25 +26468,25 @@
         <v>89</v>
       </c>
       <c r="G1061" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1061" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1061" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1061" s="26"/>
     </row>
     <row r="1062" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1062" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1062" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1062" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1062" s="26" t="s">
         <v>204</v>
@@ -26504,25 +26498,25 @@
         <v>89</v>
       </c>
       <c r="G1062" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1062" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1062" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1062" s="26"/>
     </row>
     <row r="1063" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1063" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1063" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1063" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1063" s="26" t="s">
         <v>108</v>
@@ -26534,28 +26528,28 @@
         <v>89</v>
       </c>
       <c r="G1063" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1063" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1063" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1063" s="26"/>
     </row>
     <row r="1064" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1064" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1064" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1064" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1064" s="26" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="E1064" s="26" t="s">
         <v>859</v>
@@ -26567,25 +26561,25 @@
         <v>81</v>
       </c>
       <c r="H1064" s="26" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="I1064" s="26" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="J1064" s="26"/>
     </row>
     <row r="1065" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1065" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1065" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1065" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1065" s="26" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="E1065" s="26" t="s">
         <v>19</v>
@@ -26597,25 +26591,25 @@
         <v>81</v>
       </c>
       <c r="H1065" s="26" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="I1065" s="26" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="J1065" s="26"/>
     </row>
     <row r="1066" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1066" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1066" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1066" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1066" s="26" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="E1066" s="26" t="s">
         <v>81</v>
@@ -26630,22 +26624,22 @@
         <v>81</v>
       </c>
       <c r="I1066" s="26" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="J1066" s="26"/>
     </row>
     <row r="1067" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1067" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1067" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1067" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1067" s="26" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="E1067" s="26" t="s">
         <v>89</v>
@@ -26654,7 +26648,7 @@
         <v>89</v>
       </c>
       <c r="G1067" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1067" s="26" t="s">
         <v>108</v>
@@ -26666,13 +26660,13 @@
     </row>
     <row r="1068" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1068" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1068" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1068" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1068" s="26" t="s">
         <v>796</v>
@@ -26684,7 +26678,7 @@
         <v>89</v>
       </c>
       <c r="G1068" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1068" s="26" t="s">
         <v>108</v>
@@ -26696,28 +26690,28 @@
     </row>
     <row r="1069" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1069" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1069" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1069" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1069" s="26" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="E1069" s="26" t="s">
         <v>81</v>
       </c>
       <c r="F1069" s="26" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="G1069" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1069" s="26" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="I1069" s="26" t="s">
         <v>81</v>
@@ -26726,16 +26720,16 @@
     </row>
     <row r="1070" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1070" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1070" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1070" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1070" s="26" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="E1070" s="26" t="s">
         <v>81</v>
@@ -26750,31 +26744,31 @@
         <v>81</v>
       </c>
       <c r="I1070" s="26" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="J1070" s="26"/>
     </row>
     <row r="1071" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1071" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1071" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1071" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1071" s="26" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="E1071" s="26" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="F1071" s="26" t="s">
         <v>97</v>
       </c>
       <c r="G1071" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1071" s="26" t="s">
         <v>81</v>
@@ -26786,16 +26780,16 @@
     </row>
     <row r="1072" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1072" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1072" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1072" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1072" s="26" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="E1072" s="26" t="s">
         <v>81</v>
@@ -26810,28 +26804,28 @@
         <v>81</v>
       </c>
       <c r="I1072" s="26" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="J1072" s="26"/>
     </row>
     <row r="1073" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1073" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1073" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1073" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1073" s="31" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="E1073" s="26" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="F1073" s="26" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="G1073" s="26" t="s">
         <v>81</v>
@@ -26846,16 +26840,16 @@
     </row>
     <row r="1074" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1074" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1074" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1074" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1074" s="26" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="E1074" s="26" t="s">
         <v>990</v>
@@ -26876,13 +26870,13 @@
     </row>
     <row r="1075" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1075" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1075" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1075" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1075" s="26" t="s">
         <v>218</v>
@@ -26906,13 +26900,13 @@
     </row>
     <row r="1076" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1076" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1076" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1076" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1076" s="26" t="s">
         <v>796</v>
@@ -26936,13 +26930,13 @@
     </row>
     <row r="1077" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1077" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1077" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1077" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1077" s="26" t="s">
         <v>594</v>
@@ -26968,13 +26962,13 @@
     </row>
     <row r="1078" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1078" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1078" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1078" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1078" s="26" t="s">
         <v>338</v>
@@ -26992,7 +26986,7 @@
         <v>89</v>
       </c>
       <c r="I1078" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1078" s="26" t="s">
         <v>89</v>
@@ -27000,16 +26994,16 @@
     </row>
     <row r="1079" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1079" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1079" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1079" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1079" s="26" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="E1079" s="26" t="s">
         <v>1021</v>
@@ -27021,10 +27015,10 @@
         <v>81</v>
       </c>
       <c r="H1079" s="26" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="I1079" s="26" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="J1079" s="26" t="s">
         <v>1021</v>
@@ -27032,19 +27026,19 @@
     </row>
     <row r="1080" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1080" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1080" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1080" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1080" s="26" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="E1080" s="26" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="F1080" s="26" t="s">
         <v>924</v>
@@ -27064,16 +27058,16 @@
     </row>
     <row r="1081" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1081" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1081" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1081" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1081" s="26" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E1081" s="26" t="s">
         <v>811</v>
@@ -27082,28 +27076,28 @@
         <v>811</v>
       </c>
       <c r="G1081" s="26" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="H1081" s="26" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="I1081" s="26" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="J1081" s="26"/>
     </row>
     <row r="1082" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1082" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1082" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1082" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1082" s="26" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="E1082" s="26" t="s">
         <v>28</v>
@@ -27115,25 +27109,25 @@
         <v>28</v>
       </c>
       <c r="H1082" s="26" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="I1082" s="26" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="J1082" s="26"/>
     </row>
     <row r="1083" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1083" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1083" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1083" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1083" s="26" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="E1083" s="26" t="s">
         <v>28</v>
@@ -27154,16 +27148,16 @@
     </row>
     <row r="1084" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1084" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1084" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1084" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1084" s="26" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="E1084" s="26" t="s">
         <v>808</v>
@@ -27178,19 +27172,19 @@
         <v>81</v>
       </c>
       <c r="I1084" s="26" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="J1084" s="26"/>
     </row>
     <row r="1085" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1085" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1085" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1085" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1085" s="26" t="s">
         <v>108</v>
@@ -27208,22 +27202,22 @@
         <v>89</v>
       </c>
       <c r="I1085" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1085" s="26"/>
     </row>
     <row r="1086" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1086" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1086" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1086" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1086" s="26" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="E1086" s="26" t="s">
         <v>946</v>
@@ -27235,7 +27229,7 @@
         <v>81</v>
       </c>
       <c r="H1086" s="26" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="I1086" s="26" t="s">
         <v>81</v>
@@ -27246,16 +27240,16 @@
     </row>
     <row r="1087" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1087" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1087" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1087" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1087" s="26" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="E1087" s="26" t="s">
         <v>89</v>
@@ -27276,16 +27270,16 @@
     </row>
     <row r="1088" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1088" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1088" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1088" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1088" s="26" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E1088" s="26" t="s">
         <v>89</v>
@@ -27306,13 +27300,13 @@
     </row>
     <row r="1089" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1089" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1089" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1089" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1089" s="26" t="s">
         <v>50</v>
@@ -27321,7 +27315,7 @@
         <v>392</v>
       </c>
       <c r="F1089" s="26" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="G1089" s="26" t="s">
         <v>108</v>
@@ -27336,13 +27330,13 @@
     </row>
     <row r="1090" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1090" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1090" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1090" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1090" s="26" t="s">
         <v>233</v>
@@ -27368,16 +27362,16 @@
     </row>
     <row r="1091" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1091" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1091" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1091" s="32" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D1091" s="32" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="E1091" s="32" t="s">
         <v>89</v>
@@ -27396,22 +27390,22 @@
     </row>
     <row r="1092" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1092" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1092" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1092" s="32" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D1092" s="32" t="s">
         <v>1262</v>
-      </c>
-      <c r="D1092" s="32" t="s">
-        <v>1264</v>
       </c>
       <c r="E1092" s="32" t="s">
         <v>108</v>
       </c>
       <c r="F1092" s="32" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="G1092" s="32" t="s">
         <v>89</v>
@@ -27428,43 +27422,43 @@
     </row>
     <row r="1093" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1093" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1093" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1093" s="32" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D1093" s="33" t="s">
         <v>348</v>
       </c>
       <c r="E1093" s="33" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="F1093" s="33" t="s">
         <v>89</v>
       </c>
       <c r="G1093" s="33" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1093" s="33" t="s">
         <v>108</v>
       </c>
       <c r="I1093" s="33" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1093" s="32"/>
     </row>
     <row r="1094" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1094" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1094" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1094" s="32" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D1094" s="32" t="s">
         <v>50</v>
@@ -27473,31 +27467,31 @@
         <v>808</v>
       </c>
       <c r="F1094" s="32" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="G1094" s="32" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1094" s="32" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="I1094" s="32" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="J1094" s="32"/>
     </row>
     <row r="1095" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1095" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1095" s="32" t="s">
         <v>482</v>
       </c>
       <c r="C1095" s="32" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D1095" s="32" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="E1095" s="32" t="s">
         <v>401</v>
@@ -27515,18 +27509,18 @@
         <v>108</v>
       </c>
       <c r="J1095" s="32" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="1096" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1096" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1096" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1096" s="32" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D1096" s="34" t="s">
         <v>34</v>
@@ -27552,16 +27546,16 @@
     </row>
     <row r="1097" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1097" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1097" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1097" s="32" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D1097" s="34" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="E1097" s="34" t="s">
         <v>81</v>
@@ -27573,24 +27567,24 @@
         <v>81</v>
       </c>
       <c r="H1097" s="34" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="I1097" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J1097" s="34" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="1098" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1098" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1098" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1098" s="32" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D1098" s="34" t="s">
         <v>50</v>
@@ -27616,28 +27610,28 @@
     </row>
     <row r="1099" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1099" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1099" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1099" s="32" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D1099" s="34" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="E1099" s="34" t="s">
         <v>50</v>
       </c>
       <c r="F1099" s="34" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="G1099" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1099" s="34" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="I1099" s="34" t="s">
         <v>50</v>
@@ -27646,13 +27640,13 @@
     </row>
     <row r="1100" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1100" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1100" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1100" s="32" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D1100" s="34" t="s">
         <v>108</v>
@@ -27676,22 +27670,22 @@
     </row>
     <row r="1101" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1101" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1101" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1101" s="32" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D1101" s="34" t="s">
         <v>496</v>
       </c>
       <c r="E1101" s="34" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="F1101" s="34" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="G1101" s="34" t="s">
         <v>89</v>
@@ -27706,13 +27700,13 @@
     </row>
     <row r="1102" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1102" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1102" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1102" s="32" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D1102" s="34" t="s">
         <v>204</v>
@@ -27736,13 +27730,13 @@
     </row>
     <row r="1103" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1103" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1103" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1103" s="32" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D1103" s="34" t="s">
         <v>149</v>
@@ -27766,16 +27760,16 @@
     </row>
     <row r="1104" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1104" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1104" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1104" s="32" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D1104" s="34" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="E1104" s="34" t="s">
         <v>144</v>
@@ -27784,7 +27778,7 @@
         <v>144</v>
       </c>
       <c r="G1104" s="34" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="H1104" s="34" t="s">
         <v>89</v>
@@ -27793,27 +27787,27 @@
         <v>89</v>
       </c>
       <c r="J1104" s="34" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="1105" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1105" s="32" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B1105" s="34" t="s">
         <v>482</v>
       </c>
       <c r="C1105" s="32" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D1105" s="34" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="E1105" s="34" t="s">
         <v>81</v>
       </c>
       <c r="F1105" s="34" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="G1105" s="34" t="s">
         <v>81</v>
@@ -27834,19 +27828,19 @@
         <v>155</v>
       </c>
       <c r="C1106" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1106" s="34" t="s">
         <v>319</v>
       </c>
       <c r="E1106" s="34" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="F1106" s="34" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="G1106" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="H1106" s="34" t="s">
         <v>143</v>
@@ -27864,28 +27858,28 @@
         <v>155</v>
       </c>
       <c r="C1107" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1107" s="34" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="E1107" s="34" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="F1107" s="34" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="G1107" s="34" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1107" s="34" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1107" s="34" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1107" s="34" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1108" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27896,25 +27890,25 @@
         <v>155</v>
       </c>
       <c r="C1108" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1108" s="35" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="E1108" s="35" t="s">
         <v>16</v>
       </c>
       <c r="F1108" s="35" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="G1108" s="35" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H1108" s="35" t="s">
         <v>1281</v>
       </c>
-      <c r="H1108" s="35" t="s">
-        <v>1283</v>
-      </c>
       <c r="I1108" s="35" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="J1108" s="34"/>
     </row>
@@ -27926,22 +27920,22 @@
         <v>155</v>
       </c>
       <c r="C1109" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1109" s="34" t="s">
         <v>108</v>
       </c>
       <c r="E1109" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="F1109" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="G1109" s="34" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="H1109" s="34" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="I1109" s="34" t="s">
         <v>108</v>
@@ -27956,28 +27950,28 @@
         <v>155</v>
       </c>
       <c r="C1110" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1110" s="34" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="E1110" s="34" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F1110" s="34" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="G1110" s="34" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="H1110" s="34" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="I1110" s="34" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="J1110" s="34" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="1111" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27988,28 +27982,28 @@
         <v>155</v>
       </c>
       <c r="C1111" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1111" s="34" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="E1111" s="34" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F1111" s="34" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="G1111" s="34" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="H1111" s="34" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="I1111" s="34" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="J1111" s="34" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="1112" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28020,7 +28014,7 @@
         <v>155</v>
       </c>
       <c r="C1112" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1112" s="34" t="s">
         <v>275</v>
@@ -28029,7 +28023,7 @@
         <v>281</v>
       </c>
       <c r="F1112" s="34" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="G1112" s="34" t="s">
         <v>281</v>
@@ -28041,7 +28035,7 @@
         <v>281</v>
       </c>
       <c r="J1112" s="34" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="1113" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28052,25 +28046,25 @@
         <v>155</v>
       </c>
       <c r="C1113" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1113" s="34" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="E1113" s="34" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="F1113" s="34" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="G1113" s="34" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="H1113" s="34" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="I1113" s="34" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="J1113" s="34"/>
     </row>
@@ -28082,19 +28076,19 @@
         <v>155</v>
       </c>
       <c r="C1114" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1114" s="34" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="E1114" s="34" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="F1114" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="G1114" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="H1114" s="34" t="s">
         <v>227</v>
@@ -28103,7 +28097,7 @@
         <v>227</v>
       </c>
       <c r="J1114" s="34" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1115" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28114,16 +28108,16 @@
         <v>155</v>
       </c>
       <c r="C1115" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1115" s="34" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E1115" s="34" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="F1115" s="34" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="G1115" s="34" t="s">
         <v>281</v>
@@ -28132,10 +28126,10 @@
         <v>157</v>
       </c>
       <c r="I1115" s="34" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="J1115" s="34" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="1116" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28146,28 +28140,28 @@
         <v>155</v>
       </c>
       <c r="C1116" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1116" s="34" t="s">
         <v>337</v>
       </c>
       <c r="E1116" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="F1116" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="G1116" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="H1116" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I1116" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="J1116" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="1117" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28178,28 +28172,28 @@
         <v>155</v>
       </c>
       <c r="C1117" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1117" s="34" t="s">
         <v>337</v>
       </c>
       <c r="E1117" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="F1117" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="G1117" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="H1117" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I1117" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="J1117" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="1118" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28210,28 +28204,28 @@
         <v>155</v>
       </c>
       <c r="C1118" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1118" s="34" t="s">
         <v>437</v>
       </c>
       <c r="E1118" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="F1118" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="G1118" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="H1118" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I1118" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="J1118" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="1119" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28242,28 +28236,28 @@
         <v>155</v>
       </c>
       <c r="C1119" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1119" s="34" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="E1119" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="F1119" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="G1119" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="H1119" s="34" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="I1119" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="J1119" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="1120" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28274,25 +28268,25 @@
         <v>155</v>
       </c>
       <c r="C1120" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1120" s="34" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="E1120" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="F1120" s="34" t="s">
         <v>108</v>
       </c>
       <c r="G1120" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="H1120" s="34" t="s">
         <v>108</v>
       </c>
       <c r="I1120" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="J1120" s="34"/>
     </row>
@@ -28304,19 +28298,19 @@
         <v>155</v>
       </c>
       <c r="C1121" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1121" s="36" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="E1121" s="36" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="F1121" s="36" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="G1121" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="H1121" s="34" t="s">
         <v>108</v>
@@ -28334,28 +28328,28 @@
         <v>155</v>
       </c>
       <c r="C1122" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1122" s="34" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="E1122" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="F1122" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="G1122" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1122" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I1122" s="34" t="s">
         <v>108</v>
       </c>
       <c r="J1122" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="1123" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28366,28 +28360,28 @@
         <v>155</v>
       </c>
       <c r="C1123" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1123" s="34" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="E1123" s="34" t="s">
         <v>143</v>
       </c>
       <c r="F1123" s="34" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="G1123" s="34" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1123" s="34" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1123" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="J1123" s="34" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="1124" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28398,28 +28392,28 @@
         <v>155</v>
       </c>
       <c r="C1124" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1124" s="34" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="E1124" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="F1124" s="34" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="G1124" s="34" t="s">
         <v>228</v>
       </c>
       <c r="H1124" s="34" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="I1124" s="34" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="J1124" s="34" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="1125" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28430,40 +28424,40 @@
         <v>155</v>
       </c>
       <c r="C1125" s="28" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="D1125" s="34" t="s">
         <v>111</v>
       </c>
       <c r="E1125" s="34" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="F1125" s="34" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="G1125" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1125" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="I1125" s="34" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="J1125" s="34"/>
     </row>
     <row r="1126" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1126" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1126" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1126" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1126" s="34" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="E1126" s="34" t="s">
         <v>808</v>
@@ -28472,10 +28466,10 @@
         <v>808</v>
       </c>
       <c r="G1126" s="34" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1126" s="34" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1126" s="34" t="s">
         <v>81</v>
@@ -28484,16 +28478,16 @@
     </row>
     <row r="1127" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1127" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1127" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1127" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1127" s="34" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="E1127" s="34" t="s">
         <v>969</v>
@@ -28514,16 +28508,16 @@
     </row>
     <row r="1128" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1128" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1128" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1128" s="34" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D1128" s="34" t="s">
         <v>1301</v>
-      </c>
-      <c r="D1128" s="34" t="s">
-        <v>1303</v>
       </c>
       <c r="E1128" s="34" t="s">
         <v>242</v>
@@ -28546,16 +28540,16 @@
     </row>
     <row r="1129" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1129" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1129" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1129" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1129" s="34" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="E1129" s="34" t="s">
         <v>14</v>
@@ -28576,13 +28570,13 @@
     </row>
     <row r="1130" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1130" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1130" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1130" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1130" s="34" t="s">
         <v>142</v>
@@ -28606,16 +28600,16 @@
     </row>
     <row r="1131" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1131" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1131" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1131" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1131" s="34" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="E1131" s="34" t="s">
         <v>19</v>
@@ -28627,7 +28621,7 @@
         <v>81</v>
       </c>
       <c r="H1131" s="34" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="I1131" s="34" t="s">
         <v>34</v>
@@ -28636,16 +28630,16 @@
     </row>
     <row r="1132" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1132" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1132" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1132" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1132" s="34" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="E1132" s="34" t="s">
         <v>242</v>
@@ -28660,19 +28654,19 @@
         <v>98</v>
       </c>
       <c r="I1132" s="34" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="J1132" s="34"/>
     </row>
     <row r="1133" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1133" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1133" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1133" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1133" s="34" t="s">
         <v>321</v>
@@ -28696,13 +28690,13 @@
     </row>
     <row r="1134" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1134" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1134" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1134" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1134" s="34" t="s">
         <v>204</v>
@@ -28726,19 +28720,19 @@
     </row>
     <row r="1135" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1135" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1135" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1135" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1135" s="34" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="E1135" s="34" t="s">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="F1135" s="34" t="s">
         <v>89</v>
@@ -28758,16 +28752,16 @@
     </row>
     <row r="1136" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1136" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1136" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1136" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1136" s="34" t="s">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="E1136" s="34" t="s">
         <v>34</v>
@@ -28788,13 +28782,13 @@
     </row>
     <row r="1137" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1137" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1137" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1137" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1137" s="34" t="s">
         <v>204</v>
@@ -28818,13 +28812,13 @@
     </row>
     <row r="1138" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1138" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1138" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1138" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1138" s="34" t="s">
         <v>149</v>
@@ -28848,16 +28842,16 @@
     </row>
     <row r="1139" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1139" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1139" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1139" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1139" s="34" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="E1139" s="34" t="s">
         <v>89</v>
@@ -28878,28 +28872,28 @@
     </row>
     <row r="1140" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1140" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1140" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1140" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1140" s="34" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="E1140" s="34" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="F1140" s="34" t="s">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="G1140" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1140" s="34" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1140" s="34" t="s">
         <v>81</v>
@@ -28908,16 +28902,16 @@
     </row>
     <row r="1141" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1141" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1141" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1141" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1141" s="34" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="E1141" s="34" t="s">
         <v>54</v>
@@ -28938,13 +28932,13 @@
     </row>
     <row r="1142" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1142" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1142" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1142" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1142" s="34" t="s">
         <v>204</v>
@@ -28968,13 +28962,13 @@
     </row>
     <row r="1143" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1143" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1143" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1143" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1143" s="34" t="s">
         <v>206</v>
@@ -29000,16 +28994,16 @@
     </row>
     <row r="1144" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1144" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1144" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1144" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1144" s="34" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="E1144" s="34" t="s">
         <v>242</v>
@@ -29018,7 +29012,7 @@
         <v>89</v>
       </c>
       <c r="G1144" s="34" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1144" s="34" t="s">
         <v>89</v>
@@ -29030,16 +29024,16 @@
     </row>
     <row r="1145" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1145" s="34" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B1145" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1145" s="34" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D1145" s="34" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="E1145" s="34" t="s">
         <v>141</v>
@@ -29062,13 +29056,13 @@
     </row>
     <row r="1146" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1146" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1146" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1146" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1146" s="38" t="s">
         <v>81</v>
@@ -29092,13 +29086,13 @@
     </row>
     <row r="1147" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1147" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1147" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1147" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1147" s="38" t="s">
         <v>81</v>
@@ -29122,13 +29116,13 @@
     </row>
     <row r="1148" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1148" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1148" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1148" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1148" s="38" t="s">
         <v>108</v>
@@ -29152,28 +29146,28 @@
     </row>
     <row r="1149" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1149" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1149" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1149" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1149" s="38" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="E1149" s="37" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="F1149" s="38" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="G1149" s="37" t="s">
         <v>108</v>
       </c>
       <c r="H1149" s="38" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="I1149" s="37" t="s">
         <v>22</v>
@@ -29184,22 +29178,22 @@
     </row>
     <row r="1150" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1150" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1150" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1150" s="37" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D1150" s="38" t="s">
         <v>1315</v>
       </c>
-      <c r="D1150" s="38" t="s">
+      <c r="E1150" s="37" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F1150" s="38" t="s">
         <v>1317</v>
-      </c>
-      <c r="E1150" s="37" t="s">
-        <v>1318</v>
-      </c>
-      <c r="F1150" s="38" t="s">
-        <v>1319</v>
       </c>
       <c r="G1150" s="37" t="s">
         <v>89</v>
@@ -29214,16 +29208,16 @@
     </row>
     <row r="1151" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1151" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1151" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1151" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1151" s="38" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="E1151" s="37" t="s">
         <v>141</v>
@@ -29238,22 +29232,22 @@
         <v>54</v>
       </c>
       <c r="I1151" s="37" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="J1151" s="38"/>
     </row>
     <row r="1152" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1152" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1152" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1152" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1152" s="38" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="E1152" s="37" t="s">
         <v>89</v>
@@ -29268,34 +29262,34 @@
         <v>89</v>
       </c>
       <c r="I1152" s="37" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="J1152" s="38"/>
     </row>
     <row r="1153" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1153" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1153" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1153" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1153" s="38" t="s">
         <v>204</v>
       </c>
       <c r="E1153" s="37" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="F1153" s="38" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="G1153" s="37" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1153" s="38" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1153" s="37" t="s">
         <v>204</v>
@@ -29304,91 +29298,91 @@
     </row>
     <row r="1154" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1154" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1154" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1154" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1154" s="38" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="E1154" s="37" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="F1154" s="38" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="G1154" s="37" t="s">
         <v>108</v>
       </c>
       <c r="H1154" s="38" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="I1154" s="37" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="J1154" s="38"/>
     </row>
     <row r="1155" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1155" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1155" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1155" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1155" s="38" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="E1155" s="37" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="F1155" s="38" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="G1155" s="37" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="H1155" s="38" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="I1155" s="37" t="s">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="J1155" s="38"/>
     </row>
     <row r="1156" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1156" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1156" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1156" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1156" s="38" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="E1156" s="37" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="F1156" s="38" t="s">
         <v>219</v>
       </c>
       <c r="G1156" s="37" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1156" s="38" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="I1156" s="37" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="J1156" s="38" t="s">
         <v>219</v>
@@ -29396,19 +29390,19 @@
     </row>
     <row r="1157" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1157" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1157" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1157" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1157" s="38" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E1157" s="37" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="F1157" s="38" t="s">
         <v>902</v>
@@ -29417,28 +29411,28 @@
         <v>81</v>
       </c>
       <c r="H1157" s="38" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="I1157" s="37" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="J1157" s="38"/>
     </row>
     <row r="1158" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1158" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1158" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1158" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1158" s="38" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="E1158" s="37" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="F1158" s="38" t="s">
         <v>902</v>
@@ -29450,67 +29444,67 @@
         <v>81</v>
       </c>
       <c r="I1158" s="37" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="J1158" s="38"/>
     </row>
     <row r="1159" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1159" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1159" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1159" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1159" s="38" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="E1159" s="37" t="s">
         <v>34</v>
       </c>
       <c r="F1159" s="38" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="G1159" s="37" t="s">
         <v>81</v>
       </c>
       <c r="H1159" s="38" t="s">
-        <v>1330</v>
+        <v>1328</v>
       </c>
       <c r="I1159" s="37" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="J1159" s="38"/>
     </row>
     <row r="1160" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1160" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1160" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1160" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1160" s="38" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E1160" s="37" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="F1160" s="38" t="s">
         <v>832</v>
       </c>
       <c r="G1160" s="37" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="H1160" s="38" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="I1160" s="37" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="J1160" s="38" t="s">
         <v>81</v>
@@ -29518,16 +29512,16 @@
     </row>
     <row r="1161" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1161" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1161" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1161" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1161" s="38" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="E1161" s="37" t="s">
         <v>847</v>
@@ -29536,43 +29530,43 @@
         <v>847</v>
       </c>
       <c r="G1161" s="37" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="H1161" s="38" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I1161" s="37" t="s">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="J1161" s="38"/>
     </row>
     <row r="1162" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1162" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1162" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1162" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1162" s="38" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E1162" s="37" t="s">
+        <v>1337</v>
+      </c>
+      <c r="F1162" s="38" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G1162" s="37" t="s">
         <v>1338</v>
-      </c>
-      <c r="E1162" s="37" t="s">
-        <v>1339</v>
-      </c>
-      <c r="F1162" s="38" t="s">
-        <v>1339</v>
-      </c>
-      <c r="G1162" s="37" t="s">
-        <v>1340</v>
       </c>
       <c r="H1162" s="38" t="s">
         <v>81</v>
       </c>
       <c r="I1162" s="37" t="s">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="J1162" s="38" t="s">
         <v>81</v>
@@ -29580,13 +29574,13 @@
     </row>
     <row r="1163" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1163" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1163" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1163" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1163" s="38" t="s">
         <v>108</v>
@@ -29610,13 +29604,13 @@
     </row>
     <row r="1164" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1164" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1164" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1164" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1164" s="38" t="s">
         <v>108</v>
@@ -29640,31 +29634,31 @@
     </row>
     <row r="1165" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1165" s="37" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B1165" s="38" t="s">
         <v>155</v>
       </c>
       <c r="C1165" s="37" t="s">
-        <v>1315</v>
+        <v>1313</v>
       </c>
       <c r="D1165" s="38" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="E1165" s="37" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="F1165" s="38" t="s">
         <v>219</v>
       </c>
       <c r="G1165" s="37" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1165" s="38" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="I1165" s="37" t="s">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="J1165" s="38" t="s">
         <v>219</v>
@@ -29672,13 +29666,13 @@
     </row>
     <row r="1166" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1166" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1166" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1166" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1166" s="34" t="s">
         <v>108</v>
@@ -29702,16 +29696,16 @@
     </row>
     <row r="1167" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1167" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1167" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1167" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1167" s="34" t="s">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="E1167" s="34" t="s">
         <v>143</v>
@@ -29732,19 +29726,19 @@
     </row>
     <row r="1168" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1168" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1168" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1168" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1168" s="35" t="s">
         <v>338</v>
       </c>
       <c r="E1168" s="35" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="F1168" s="35" t="s">
         <v>89</v>
@@ -29762,13 +29756,13 @@
     </row>
     <row r="1169" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1169" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1169" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1169" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1169" s="34" t="s">
         <v>108</v>
@@ -29792,13 +29786,13 @@
     </row>
     <row r="1170" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1170" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1170" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1170" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1170" s="34" t="s">
         <v>114</v>
@@ -29824,19 +29818,19 @@
     </row>
     <row r="1171" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1171" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1171" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1171" s="34" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D1171" s="34" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E1171" s="34" t="s">
         <v>1341</v>
-      </c>
-      <c r="D1171" s="34" t="s">
-        <v>1342</v>
-      </c>
-      <c r="E1171" s="34" t="s">
-        <v>1343</v>
       </c>
       <c r="F1171" s="34" t="s">
         <v>832</v>
@@ -29854,13 +29848,13 @@
     </row>
     <row r="1172" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1172" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1172" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1172" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1172" s="34" t="s">
         <v>338</v>
@@ -29884,13 +29878,13 @@
     </row>
     <row r="1173" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1173" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1173" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1173" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1173" s="34" t="s">
         <v>458</v>
@@ -29916,16 +29910,16 @@
     </row>
     <row r="1174" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1174" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1174" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1174" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1174" s="34" t="s">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="E1174" s="34" t="s">
         <v>82</v>
@@ -29948,22 +29942,22 @@
     </row>
     <row r="1175" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1175" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1175" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1175" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1175" s="34" t="s">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="E1175" s="34" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="F1175" s="34" t="s">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="G1175" s="34" t="s">
         <v>108</v>
@@ -29980,22 +29974,22 @@
     </row>
     <row r="1176" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1176" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1176" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1176" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1176" s="34" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="E1176" s="34" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="F1176" s="34" t="s">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="G1176" s="34" t="s">
         <v>81</v>
@@ -30012,16 +30006,16 @@
     </row>
     <row r="1177" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1177" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1177" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1177" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1177" s="34" t="s">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="E1177" s="34" t="s">
         <v>89</v>
@@ -30042,13 +30036,13 @@
     </row>
     <row r="1178" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1178" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1178" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1178" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1178" s="34" t="s">
         <v>334</v>
@@ -30072,13 +30066,13 @@
     </row>
     <row r="1179" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1179" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1179" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1179" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1179" s="34" t="s">
         <v>280</v>
@@ -30102,16 +30096,16 @@
     </row>
     <row r="1180" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1180" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1180" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1180" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1180" s="34" t="s">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="E1180" s="34" t="s">
         <v>89</v>
@@ -30132,16 +30126,16 @@
     </row>
     <row r="1181" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1181" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1181" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1181" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1181" s="34" t="s">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="E1181" s="34" t="s">
         <v>51</v>
@@ -30164,16 +30158,16 @@
     </row>
     <row r="1182" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1182" s="34" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B1182" s="34" t="s">
         <v>317</v>
       </c>
       <c r="C1182" s="34" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D1182" s="34" t="s">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="E1182" s="34" t="s">
         <v>89</v>
@@ -30185,7 +30179,7 @@
         <v>89</v>
       </c>
       <c r="H1182" s="34" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="I1182" s="34" t="s">
         <v>108</v>
@@ -30194,13 +30188,13 @@
     </row>
     <row r="1183" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1183" s="24" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="B1183" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1183" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1183" s="39" t="s">
         <v>410</v>
@@ -30224,16 +30218,16 @@
     </row>
     <row r="1184" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1184" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1184" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1184" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1184" s="39" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="E1184" s="39" t="s">
         <v>89</v>
@@ -30252,25 +30246,25 @@
     </row>
     <row r="1185" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1185" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1185" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1185" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1185" s="39" t="s">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="E1185" s="39" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="F1185" s="39" t="s">
         <v>89</v>
       </c>
       <c r="G1185" s="39" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="H1185" s="39" t="s">
         <v>89</v>
@@ -30282,43 +30276,43 @@
     </row>
     <row r="1186" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1186" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1186" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1186" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1186" s="39" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="E1186" s="39" t="s">
         <v>832</v>
       </c>
       <c r="F1186" s="39" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="G1186" s="39" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1186" s="39" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="I1186" s="39" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="J1186" s="39"/>
     </row>
     <row r="1187" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1187" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1187" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1187" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1187" s="40" t="s">
         <v>594</v>
@@ -30342,13 +30336,13 @@
     </row>
     <row r="1188" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1188" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1188" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1188" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1188" s="40" t="s">
         <v>108</v>
@@ -30372,13 +30366,13 @@
     </row>
     <row r="1189" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1189" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1189" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1189" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1189" s="40" t="s">
         <v>204</v>
@@ -30402,19 +30396,19 @@
     </row>
     <row r="1190" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1190" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1190" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1190" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1190" s="40" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="E1190" s="40" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="F1190" s="40" t="s">
         <v>808</v>
@@ -30423,7 +30417,7 @@
         <v>81</v>
       </c>
       <c r="H1190" s="40" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="I1190" s="40" t="s">
         <v>81</v>
@@ -30432,13 +30426,13 @@
     </row>
     <row r="1191" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1191" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1191" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1191" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1191" s="40" t="s">
         <v>108</v>
@@ -30450,7 +30444,7 @@
         <v>89</v>
       </c>
       <c r="G1191" s="40" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1191" s="40" t="s">
         <v>89</v>
@@ -30462,16 +30456,16 @@
     </row>
     <row r="1192" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1192" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1192" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1192" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1192" s="40" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="E1192" s="40" t="s">
         <v>169</v>
@@ -30494,13 +30488,13 @@
     </row>
     <row r="1193" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1193" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1193" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1193" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1193" s="40" t="s">
         <v>495</v>
@@ -30526,13 +30520,13 @@
     </row>
     <row r="1194" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1194" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1194" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1194" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1194" s="40" t="s">
         <v>50</v>
@@ -30558,13 +30552,13 @@
     </row>
     <row r="1195" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1195" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1195" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1195" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1195" s="40" t="s">
         <v>393</v>
@@ -30580,25 +30574,25 @@
         <v>108</v>
       </c>
       <c r="I1195" s="40" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1195" s="40"/>
     </row>
     <row r="1196" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1196" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1196" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1196" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1196" s="40" t="s">
         <v>321</v>
       </c>
       <c r="E1196" s="40" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="F1196" s="40" t="s">
         <v>89</v>
@@ -30616,13 +30610,13 @@
     </row>
     <row r="1197" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1197" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1197" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1197" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1197" s="40" t="s">
         <v>108</v>
@@ -30646,13 +30640,13 @@
     </row>
     <row r="1198" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1198" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1198" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1198" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1198" s="40" t="s">
         <v>204</v>
@@ -30674,16 +30668,16 @@
     </row>
     <row r="1199" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1199" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1199" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1199" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1199" s="40" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="E1199" s="40" t="s">
         <v>89</v>
@@ -30702,13 +30696,13 @@
     </row>
     <row r="1200" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1200" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1200" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1200" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1200" s="40" t="s">
         <v>108</v>
@@ -30720,7 +30714,7 @@
         <v>89</v>
       </c>
       <c r="G1200" s="40" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1200" s="40" t="s">
         <v>108</v>
@@ -30732,16 +30726,16 @@
     </row>
     <row r="1201" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1201" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1201" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1201" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1201" s="40" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E1201" s="40" t="s">
         <v>16</v>
@@ -30753,7 +30747,7 @@
         <v>81</v>
       </c>
       <c r="H1201" s="40" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="I1201" s="40" t="s">
         <v>81</v>
@@ -30762,16 +30756,16 @@
     </row>
     <row r="1202" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1202" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1202" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1202" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1202" s="40" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="E1202" s="40" t="s">
         <v>89</v>
@@ -30792,16 +30786,16 @@
     </row>
     <row r="1203" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1203" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1203" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1203" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1203" s="40" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="E1203" s="40" t="s">
         <v>94</v>
@@ -30824,13 +30818,13 @@
     </row>
     <row r="1204" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1204" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1204" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1204" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1204" s="40" t="s">
         <v>338</v>
@@ -30842,10 +30836,10 @@
         <v>89</v>
       </c>
       <c r="G1204" s="40" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="H1204" s="40" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="I1204" s="40" t="s">
         <v>89</v>
@@ -30854,13 +30848,13 @@
     </row>
     <row r="1205" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1205" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1205" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1205" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1205" s="40" t="s">
         <v>392</v>
@@ -30882,13 +30876,13 @@
     </row>
     <row r="1206" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1206" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1206" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1206" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1206" s="40" t="s">
         <v>108</v>
@@ -30910,16 +30904,16 @@
     </row>
     <row r="1207" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1207" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1207" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1207" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1207" s="40" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E1207" s="40" t="s">
         <v>89</v>
@@ -30928,34 +30922,34 @@
         <v>89</v>
       </c>
       <c r="G1207" s="40" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1207" s="40" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1207" s="40" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1207" s="40"/>
     </row>
     <row r="1208" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1208" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1208" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1208" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1208" s="40" t="s">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="E1208" s="40" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="F1208" s="40" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="G1208" s="40" t="s">
         <v>89</v>
@@ -30964,7 +30958,7 @@
         <v>108</v>
       </c>
       <c r="I1208" s="40" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1208" s="40" t="s">
         <v>955</v>
@@ -30972,16 +30966,16 @@
     </row>
     <row r="1209" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1209" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1209" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1209" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1209" s="40" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="E1209" s="40" t="s">
         <v>141</v>
@@ -31004,16 +30998,16 @@
     </row>
     <row r="1210" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1210" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1210" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1210" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1210" s="40" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="E1210" s="40" t="s">
         <v>141</v>
@@ -31034,16 +31028,16 @@
     </row>
     <row r="1211" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1211" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1211" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1211" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1211" s="40" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="E1211" s="40" t="s">
         <v>847</v>
@@ -31055,22 +31049,22 @@
         <v>81</v>
       </c>
       <c r="H1211" s="40" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="I1211" s="40" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="J1211" s="40"/>
     </row>
     <row r="1212" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1212" s="27" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B1212" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1212" s="26" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D1212" s="41" t="s">
         <v>676</v>
@@ -31098,7 +31092,7 @@
         <v>11</v>
       </c>
       <c r="C1213" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1213" s="32" t="s">
         <v>108</v>
@@ -31128,10 +31122,10 @@
         <v>11</v>
       </c>
       <c r="C1214" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1214" s="32" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="E1214" s="32" t="s">
         <v>89</v>
@@ -31160,16 +31154,16 @@
         <v>11</v>
       </c>
       <c r="C1215" s="32" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D1215" s="32" t="s">
         <v>1366</v>
-      </c>
-      <c r="D1215" s="32" t="s">
-        <v>1368</v>
       </c>
       <c r="E1215" s="32" t="s">
         <v>847</v>
       </c>
       <c r="F1215" s="32" t="s">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="G1215" s="32" t="s">
         <v>89</v>
@@ -31192,16 +31186,16 @@
         <v>11</v>
       </c>
       <c r="C1216" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1216" s="32" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="E1216" s="32" t="s">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="F1216" s="32" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="G1216" s="32" t="s">
         <v>50</v>
@@ -31222,7 +31216,7 @@
         <v>11</v>
       </c>
       <c r="C1217" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1217" s="32" t="s">
         <v>146</v>
@@ -31254,7 +31248,7 @@
         <v>11</v>
       </c>
       <c r="C1218" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1218" s="32" t="s">
         <v>108</v>
@@ -31284,7 +31278,7 @@
         <v>11</v>
       </c>
       <c r="C1219" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1219" s="32" t="s">
         <v>351</v>
@@ -31293,7 +31287,7 @@
         <v>89</v>
       </c>
       <c r="F1219" s="32" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="G1219" s="32" t="s">
         <v>108</v>
@@ -31314,28 +31308,28 @@
         <v>11</v>
       </c>
       <c r="C1220" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1220" s="32" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="E1220" s="32" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="F1220" s="32" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="G1220" s="32" t="s">
         <v>89</v>
       </c>
       <c r="H1220" s="32" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="I1220" s="32" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="J1220" s="32" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="1221" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31346,7 +31340,7 @@
         <v>11</v>
       </c>
       <c r="C1221" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1221" s="32" t="s">
         <v>297</v>
@@ -31378,16 +31372,16 @@
         <v>11</v>
       </c>
       <c r="C1222" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1222" s="32" t="s">
-        <v>1373</v>
+        <v>1371</v>
       </c>
       <c r="E1222" s="32" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="F1222" s="32" t="s">
-        <v>1374</v>
+        <v>1372</v>
       </c>
       <c r="G1222" s="32" t="s">
         <v>89</v>
@@ -31408,7 +31402,7 @@
         <v>11</v>
       </c>
       <c r="C1223" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1223" s="32" t="s">
         <v>108</v>
@@ -31438,7 +31432,7 @@
         <v>11</v>
       </c>
       <c r="C1224" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1224" s="32" t="s">
         <v>334</v>
@@ -31468,7 +31462,7 @@
         <v>11</v>
       </c>
       <c r="C1225" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1225" s="32" t="s">
         <v>51</v>
@@ -31489,7 +31483,7 @@
         <v>81</v>
       </c>
       <c r="J1225" s="32" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="1226" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31500,10 +31494,10 @@
         <v>11</v>
       </c>
       <c r="C1226" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1226" s="32" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="E1226" s="32" t="s">
         <v>983</v>
@@ -31530,10 +31524,10 @@
         <v>11</v>
       </c>
       <c r="C1227" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1227" s="32" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="E1227" s="32" t="s">
         <v>16</v>
@@ -31554,13 +31548,13 @@
     </row>
     <row r="1228" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1228" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1228" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1228" s="43" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D1228" s="42" t="s">
         <v>108</v>
@@ -31586,13 +31580,13 @@
     </row>
     <row r="1229" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1229" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1229" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1229" s="43" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D1229" s="42" t="s">
         <v>50</v>
@@ -31616,13 +31610,13 @@
     </row>
     <row r="1230" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1230" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1230" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1230" s="43" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D1230" s="42" t="s">
         <v>411</v>
@@ -31637,22 +31631,22 @@
         <v>108</v>
       </c>
       <c r="H1230" s="42" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="I1230" s="42" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="J1230" s="43"/>
     </row>
     <row r="1231" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1231" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1231" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1231" s="43" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D1231" s="42" t="s">
         <v>351</v>
@@ -31661,7 +31655,7 @@
         <v>89</v>
       </c>
       <c r="F1231" s="42" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="G1231" s="42" t="s">
         <v>108</v>
@@ -31676,13 +31670,13 @@
     </row>
     <row r="1232" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1232" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1232" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1232" s="43" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D1232" s="42" t="s">
         <v>338</v>
@@ -31708,16 +31702,16 @@
     </row>
     <row r="1233" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1233" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1233" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1233" s="43" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D1233" s="42" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="E1233" s="42" t="s">
         <v>89</v>
@@ -31740,13 +31734,13 @@
     </row>
     <row r="1234" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1234" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1234" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1234" s="43" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D1234" s="42" t="s">
         <v>458</v>
@@ -31770,22 +31764,22 @@
     </row>
     <row r="1235" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1235" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1235" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1235" s="43" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D1235" s="44" t="s">
         <v>1377</v>
-      </c>
-      <c r="D1235" s="44" t="s">
-        <v>1379</v>
       </c>
       <c r="E1235" s="42" t="s">
         <v>81</v>
       </c>
       <c r="F1235" s="42" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="G1235" s="42" t="s">
         <v>108</v>
@@ -31795,51 +31789,51 @@
       </c>
       <c r="I1235" s="43"/>
       <c r="J1235" s="42" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="1236" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1236" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1236" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1236" s="43" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D1236" s="45" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="E1236" s="42" t="s">
         <v>325</v>
       </c>
       <c r="F1236" s="42" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="G1236" s="42" t="s">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="H1236" s="42" t="s">
         <v>89</v>
       </c>
       <c r="I1236" s="42" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="J1236" s="43"/>
     </row>
     <row r="1237" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1237" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1237" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1237" s="43" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D1237" s="46" t="s">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="E1237" s="42" t="s">
         <v>108</v>
@@ -31862,22 +31856,22 @@
     </row>
     <row r="1238" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1238" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1238" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1238" s="43" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D1238" s="47" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="E1238" s="42" t="s">
         <v>89</v>
       </c>
       <c r="F1238" s="42" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="G1238" s="42" t="s">
         <v>108</v>
@@ -31892,16 +31886,16 @@
     </row>
     <row r="1239" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1239" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1239" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1239" s="43" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D1239" s="42" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="E1239" s="42" t="s">
         <v>26</v>
@@ -31922,16 +31916,16 @@
     </row>
     <row r="1240" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1240" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1240" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1240" s="43" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D1240" s="48" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="E1240" s="42" t="s">
         <v>89</v>
@@ -31954,28 +31948,28 @@
     </row>
     <row r="1241" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1241" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1241" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1241" s="43" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D1241" s="42" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="E1241" s="42" t="s">
         <v>847</v>
       </c>
       <c r="F1241" s="42" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="G1241" s="42" t="s">
         <v>81</v>
       </c>
       <c r="H1241" s="42" t="s">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="I1241" s="42" t="s">
         <v>81</v>
@@ -31984,16 +31978,16 @@
     </row>
     <row r="1242" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1242" s="42" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B1242" s="26" t="s">
         <v>413</v>
       </c>
       <c r="C1242" s="43" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="D1242" s="42" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="E1242" s="42" t="s">
         <v>19</v>
@@ -32005,22 +31999,22 @@
         <v>81</v>
       </c>
       <c r="H1242" s="42" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="I1242" s="42" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="J1242" s="43"/>
     </row>
     <row r="1243" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1243" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1243" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1243" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1243" s="50" t="s">
         <v>50</v>
@@ -32032,7 +32026,7 @@
         <v>89</v>
       </c>
       <c r="G1243" s="50" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="H1243" s="50" t="s">
         <v>89</v>
@@ -32044,16 +32038,16 @@
     </row>
     <row r="1244" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1244" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1244" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1244" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1244" s="49" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="E1244" s="49" t="s">
         <v>89</v>
@@ -32072,19 +32066,19 @@
     </row>
     <row r="1245" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1245" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1245" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1245" s="50" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D1245" s="49" t="s">
         <v>1393</v>
       </c>
-      <c r="D1245" s="49" t="s">
-        <v>1395</v>
-      </c>
       <c r="E1245" s="49" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="F1245" s="49" t="s">
         <v>19</v>
@@ -32102,16 +32096,16 @@
     </row>
     <row r="1246" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1246" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1246" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1246" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1246" s="51" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="E1246" s="51" t="s">
         <v>89</v>
@@ -32132,13 +32126,13 @@
     </row>
     <row r="1247" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1247" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1247" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1247" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1247" s="49" t="s">
         <v>384</v>
@@ -32150,28 +32144,28 @@
         <v>89</v>
       </c>
       <c r="G1247" s="49" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1247" s="49" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1247" s="49" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1247" s="49"/>
     </row>
     <row r="1248" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1248" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1248" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1248" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1248" s="49" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="E1248" s="49" t="s">
         <v>89</v>
@@ -32180,34 +32174,34 @@
         <v>89</v>
       </c>
       <c r="G1248" s="49" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1248" s="49" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1248" s="49" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1248" s="49"/>
     </row>
     <row r="1249" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1249" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1249" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1249" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1249" s="49" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="E1249" s="49" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="F1249" s="49" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="G1249" s="49" t="s">
         <v>89</v>
@@ -32224,28 +32218,28 @@
     </row>
     <row r="1250" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1250" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1250" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1250" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1250" s="49" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="E1250" s="49" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="F1250" s="49" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="G1250" s="49" t="s">
         <v>81</v>
       </c>
       <c r="H1250" s="49" t="s">
-        <v>1400</v>
+        <v>1398</v>
       </c>
       <c r="I1250" s="49" t="s">
         <v>81</v>
@@ -32256,19 +32250,19 @@
     </row>
     <row r="1251" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1251" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1251" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1251" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1251" s="49" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="E1251" s="49" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="F1251" s="49"/>
       <c r="G1251" s="49"/>
@@ -32282,13 +32276,13 @@
     </row>
     <row r="1252" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1252" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1252" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1252" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1252" s="49" t="s">
         <v>242</v>
@@ -32312,16 +32306,16 @@
     </row>
     <row r="1253" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1253" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1253" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1253" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1253" s="49" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="E1253" s="49" t="s">
         <v>89</v>
@@ -32330,28 +32324,28 @@
         <v>89</v>
       </c>
       <c r="G1253" s="49" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1253" s="49" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1253" s="49" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1253" s="49"/>
     </row>
     <row r="1254" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1254" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1254" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1254" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1254" s="49" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="E1254" s="49" t="s">
         <v>218</v>
@@ -32360,10 +32354,10 @@
         <v>219</v>
       </c>
       <c r="G1254" s="49" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1254" s="49" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="I1254" s="49" t="s">
         <v>227</v>
@@ -32374,25 +32368,25 @@
     </row>
     <row r="1255" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1255" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1255" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1255" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1255" s="49" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="E1255" s="49" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="F1255" s="49" t="s">
         <v>827</v>
       </c>
       <c r="G1255" s="49" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1255" s="49" t="s">
         <v>81</v>
@@ -32406,13 +32400,13 @@
     </row>
     <row r="1256" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1256" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1256" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1256" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1256" s="49" t="s">
         <v>242</v>
@@ -32438,19 +32432,19 @@
     </row>
     <row r="1257" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1257" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1257" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1257" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1257" s="49" t="s">
-        <v>1407</v>
+        <v>1405</v>
       </c>
       <c r="E1257" s="49" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="F1257" s="49" t="s">
         <v>999</v>
@@ -32459,7 +32453,7 @@
         <v>89</v>
       </c>
       <c r="H1257" s="49" t="s">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="I1257" s="49" t="s">
         <v>89</v>
@@ -32470,16 +32464,16 @@
     </row>
     <row r="1258" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1258" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1258" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1258" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1258" s="49" t="s">
-        <v>1409</v>
+        <v>1407</v>
       </c>
       <c r="E1258" s="49" t="s">
         <v>977</v>
@@ -32488,10 +32482,10 @@
         <v>81</v>
       </c>
       <c r="G1258" s="49" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="H1258" s="49" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="I1258" s="49" t="s">
         <v>977</v>
@@ -32500,16 +32494,16 @@
     </row>
     <row r="1259" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1259" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1259" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1259" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1259" s="49" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="E1259" s="49" t="s">
         <v>81</v>
@@ -32521,7 +32515,7 @@
         <v>81</v>
       </c>
       <c r="H1259" s="49" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="I1259" s="49" t="s">
         <v>81</v>
@@ -32532,16 +32526,16 @@
     </row>
     <row r="1260" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1260" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1260" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1260" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1260" s="49" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E1260" s="49" t="s">
         <v>808</v>
@@ -32562,16 +32556,16 @@
     </row>
     <row r="1261" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1261" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1261" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1261" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1261" s="49" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="E1261" s="49" t="s">
         <v>808</v>
@@ -32592,16 +32586,16 @@
     </row>
     <row r="1262" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1262" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1262" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1262" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1262" s="49" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="E1262" s="49" t="s">
         <v>89</v>
@@ -32622,16 +32616,16 @@
     </row>
     <row r="1263" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1263" s="49" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B1263" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1263" s="50" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D1263" s="49" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="E1263" s="49" t="s">
         <v>89</v>
@@ -32658,13 +32652,13 @@
         <v>11</v>
       </c>
       <c r="C1264" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1264" s="32" t="s">
-        <v>1416</v>
+        <v>1414</v>
       </c>
       <c r="E1264" s="32" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="F1264" s="32" t="s">
         <v>81</v>
@@ -32690,7 +32684,7 @@
         <v>11</v>
       </c>
       <c r="C1265" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1265" s="32" t="s">
         <v>108</v>
@@ -32702,7 +32696,7 @@
         <v>89</v>
       </c>
       <c r="G1265" s="32" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1265" s="32" t="s">
         <v>108</v>
@@ -32722,7 +32716,7 @@
         <v>11</v>
       </c>
       <c r="C1266" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1266" s="33" t="s">
         <v>143</v>
@@ -32754,10 +32748,10 @@
         <v>11</v>
       </c>
       <c r="C1267" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1267" s="32" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="E1267" s="32" t="s">
         <v>108</v>
@@ -32784,7 +32778,7 @@
         <v>11</v>
       </c>
       <c r="C1268" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1268" s="32" t="s">
         <v>50</v>
@@ -32816,7 +32810,7 @@
         <v>11</v>
       </c>
       <c r="C1269" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1269" s="32" t="s">
         <v>409</v>
@@ -32825,7 +32819,7 @@
         <v>847</v>
       </c>
       <c r="F1269" s="32" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="G1269" s="32" t="s">
         <v>89</v>
@@ -32848,7 +32842,7 @@
         <v>11</v>
       </c>
       <c r="C1270" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1270" s="32" t="s">
         <v>20</v>
@@ -32880,10 +32874,10 @@
         <v>11</v>
       </c>
       <c r="C1271" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1271" s="32" t="s">
-        <v>1418</v>
+        <v>1416</v>
       </c>
       <c r="E1271" s="32" t="s">
         <v>89</v>
@@ -32898,7 +32892,7 @@
         <v>89</v>
       </c>
       <c r="I1271" s="32" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1271" s="32" t="s">
         <v>941</v>
@@ -32912,22 +32906,22 @@
         <v>11</v>
       </c>
       <c r="C1272" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1272" s="32" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="E1272" s="32" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="F1272" s="32" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="G1272" s="32" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="H1272" s="32" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="I1272" s="32" t="s">
         <v>81</v>
@@ -32944,19 +32938,19 @@
         <v>11</v>
       </c>
       <c r="C1273" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1273" s="32" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="E1273" s="32" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="F1273" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G1273" s="32" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="H1273" s="32" t="s">
         <v>89</v>
@@ -32974,10 +32968,10 @@
         <v>11</v>
       </c>
       <c r="C1274" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1274" s="32" t="s">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="E1274" s="32" t="s">
         <v>941</v>
@@ -33006,22 +33000,22 @@
         <v>11</v>
       </c>
       <c r="C1275" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1275" s="32" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E1275" s="32" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F1275" s="32" t="s">
         <v>1423</v>
       </c>
-      <c r="E1275" s="32" t="s">
+      <c r="G1275" s="32" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H1275" s="32" t="s">
         <v>1424</v>
-      </c>
-      <c r="F1275" s="32" t="s">
-        <v>1425</v>
-      </c>
-      <c r="G1275" s="32" t="s">
-        <v>1182</v>
-      </c>
-      <c r="H1275" s="32" t="s">
-        <v>1426</v>
       </c>
       <c r="I1275" s="32" t="s">
         <v>81</v>
@@ -33038,7 +33032,7 @@
         <v>11</v>
       </c>
       <c r="C1276" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1276" s="32" t="s">
         <v>50</v>
@@ -33068,7 +33062,7 @@
         <v>11</v>
       </c>
       <c r="C1277" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1277" s="32" t="s">
         <v>50</v>
@@ -33098,7 +33092,7 @@
         <v>11</v>
       </c>
       <c r="C1278" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1278" s="32" t="s">
         <v>458</v>
@@ -33116,7 +33110,7 @@
         <v>89</v>
       </c>
       <c r="I1278" s="32" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1278" s="32"/>
     </row>
@@ -33128,7 +33122,7 @@
         <v>11</v>
       </c>
       <c r="C1279" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1279" s="32" t="s">
         <v>149</v>
@@ -33158,7 +33152,7 @@
         <v>11</v>
       </c>
       <c r="C1280" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1280" s="32" t="s">
         <v>20</v>
@@ -33190,7 +33184,7 @@
         <v>11</v>
       </c>
       <c r="C1281" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1281" s="32" t="s">
         <v>108</v>
@@ -33205,7 +33199,7 @@
         <v>89</v>
       </c>
       <c r="H1281" s="32" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1281" s="32" t="s">
         <v>89</v>
@@ -33222,7 +33216,7 @@
         <v>11</v>
       </c>
       <c r="C1282" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1282" s="32" t="s">
         <v>101</v>
@@ -33254,13 +33248,13 @@
         <v>11</v>
       </c>
       <c r="C1283" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1283" s="32" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="E1283" s="32" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="F1283" s="32" t="s">
         <v>938</v>
@@ -33286,16 +33280,16 @@
         <v>11</v>
       </c>
       <c r="C1284" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1284" s="32" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="E1284" s="32" t="s">
-        <v>1372</v>
+        <v>1370</v>
       </c>
       <c r="F1284" s="32" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="G1284" s="32" t="s">
         <v>89</v>
@@ -33304,10 +33298,10 @@
         <v>89</v>
       </c>
       <c r="I1284" s="32" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="J1284" s="32" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="1285" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -33318,7 +33312,7 @@
         <v>11</v>
       </c>
       <c r="C1285" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1285" s="32" t="s">
         <v>108</v>
@@ -33336,7 +33330,7 @@
         <v>89</v>
       </c>
       <c r="I1285" s="32" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1285" s="32" t="s">
         <v>89</v>
@@ -33350,7 +33344,7 @@
         <v>11</v>
       </c>
       <c r="C1286" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1286" s="32" t="s">
         <v>227</v>
@@ -33382,10 +33376,10 @@
         <v>11</v>
       </c>
       <c r="C1287" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1287" s="32" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="E1287" s="32" t="s">
         <v>101</v>
@@ -33414,7 +33408,7 @@
         <v>11</v>
       </c>
       <c r="C1288" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1288" s="32" t="s">
         <v>116</v>
@@ -33446,19 +33440,19 @@
         <v>11</v>
       </c>
       <c r="C1289" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1289" s="32" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E1289" s="32" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F1289" s="32" t="s">
         <v>1431</v>
       </c>
-      <c r="E1289" s="32" t="s">
-        <v>1432</v>
-      </c>
-      <c r="F1289" s="32" t="s">
-        <v>1433</v>
-      </c>
       <c r="G1289" s="32" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1289" s="32" t="s">
         <v>81</v>
@@ -33478,7 +33472,7 @@
         <v>11</v>
       </c>
       <c r="C1290" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1290" s="32" t="s">
         <v>108</v>
@@ -33510,22 +33504,22 @@
         <v>11</v>
       </c>
       <c r="C1291" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1291" s="32" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="E1291" s="32" t="s">
         <v>33</v>
       </c>
       <c r="F1291" s="32" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="G1291" s="32" t="s">
         <v>108</v>
       </c>
       <c r="H1291" s="32" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="I1291" s="32"/>
       <c r="J1291" s="32" t="s">
@@ -33540,7 +33534,7 @@
         <v>11</v>
       </c>
       <c r="C1292" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1292" s="32" t="s">
         <v>116</v>
@@ -33572,13 +33566,13 @@
         <v>11</v>
       </c>
       <c r="C1293" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1293" s="32" t="s">
         <v>108</v>
       </c>
       <c r="E1293" s="32" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="F1293" s="32" t="s">
         <v>81</v>
@@ -33590,7 +33584,7 @@
         <v>89</v>
       </c>
       <c r="I1293" s="32" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="J1293" s="32"/>
     </row>
@@ -33602,7 +33596,7 @@
         <v>11</v>
       </c>
       <c r="C1294" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1294" s="32" t="s">
         <v>204</v>
@@ -33614,7 +33608,7 @@
         <v>89</v>
       </c>
       <c r="G1294" s="32" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1294" s="32" t="s">
         <v>204</v>
@@ -33632,7 +33626,7 @@
         <v>11</v>
       </c>
       <c r="C1295" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1295" s="32" t="s">
         <v>108</v>
@@ -33662,10 +33656,10 @@
         <v>11</v>
       </c>
       <c r="C1296" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1296" s="32" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="E1296" s="32" t="s">
         <v>81</v>
@@ -33680,7 +33674,7 @@
         <v>81</v>
       </c>
       <c r="I1296" s="32" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="J1296" s="32"/>
     </row>
@@ -33692,7 +33686,7 @@
         <v>11</v>
       </c>
       <c r="C1297" s="32" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="D1297" s="32" t="s">
         <v>108</v>
@@ -33716,78 +33710,78 @@
     </row>
     <row r="1298" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1298" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1298" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1298" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1298" s="31" t="s">
+        <v>1435</v>
+      </c>
+      <c r="E1298" s="26" t="s">
+        <v>1436</v>
+      </c>
+      <c r="F1298" s="26" t="s">
+        <v>1436</v>
+      </c>
+      <c r="G1298" s="31" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H1298" s="26" t="s">
         <v>1437</v>
       </c>
-      <c r="E1298" s="26" t="s">
-        <v>1438</v>
-      </c>
-      <c r="F1298" s="26" t="s">
-        <v>1438</v>
-      </c>
-      <c r="G1298" s="31" t="s">
-        <v>1182</v>
-      </c>
-      <c r="H1298" s="26" t="s">
-        <v>1439</v>
-      </c>
       <c r="I1298" s="26" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="J1298" s="26" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="1299" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1299" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1299" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1299" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1299" s="26" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="E1299" s="26" t="s">
         <v>1088</v>
       </c>
       <c r="F1299" s="26" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="G1299" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1299" s="26" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="I1299" s="26" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="J1299" s="26"/>
     </row>
     <row r="1300" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1300" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1300" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1300" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1300" s="31" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E1300" s="27" t="s">
         <v>19</v>
@@ -33799,10 +33793,10 @@
         <v>81</v>
       </c>
       <c r="H1300" s="27" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="I1300" s="27" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="J1300" s="26" t="s">
         <v>19</v>
@@ -33810,16 +33804,16 @@
     </row>
     <row r="1301" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1301" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1301" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1301" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1301" s="26" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="E1301" s="26" t="s">
         <v>161</v>
@@ -33834,7 +33828,7 @@
         <v>455</v>
       </c>
       <c r="I1301" s="26" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="J1301" s="26" t="s">
         <v>82</v>
@@ -33842,13 +33836,13 @@
     </row>
     <row r="1302" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1302" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1302" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1302" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1302" s="26" t="s">
         <v>50</v>
@@ -33860,10 +33854,10 @@
         <v>89</v>
       </c>
       <c r="G1302" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1302" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1302" s="26" t="s">
         <v>81</v>
@@ -33872,16 +33866,16 @@
     </row>
     <row r="1303" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1303" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1303" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1303" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1303" s="26" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="E1303" s="26" t="s">
         <v>847</v>
@@ -33896,7 +33890,7 @@
         <v>81</v>
       </c>
       <c r="I1303" s="26" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="J1303" s="26" t="s">
         <v>847</v>
@@ -33904,13 +33898,13 @@
     </row>
     <row r="1304" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1304" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1304" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1304" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1304" s="26" t="s">
         <v>284</v>
@@ -33925,10 +33919,10 @@
         <v>89</v>
       </c>
       <c r="H1304" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="I1304" s="26" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="J1304" s="26" t="s">
         <v>141</v>
@@ -33936,16 +33930,16 @@
     </row>
     <row r="1305" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1305" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1305" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1305" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1305" s="26" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="E1305" s="26" t="s">
         <v>1021</v>
@@ -33954,25 +33948,25 @@
         <v>1021</v>
       </c>
       <c r="G1305" s="26" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="H1305" s="26" t="s">
         <v>81</v>
       </c>
       <c r="I1305" s="26" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="J1305" s="26"/>
     </row>
     <row r="1306" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1306" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1306" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1306" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1306" s="26" t="s">
         <v>39</v>
@@ -33998,46 +33992,46 @@
     </row>
     <row r="1307" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1307" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1307" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1307" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1307" s="26" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="E1307" s="26" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="F1307" s="26" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="G1307" s="26" t="s">
         <v>81</v>
       </c>
       <c r="H1307" s="26" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="I1307" s="26" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="J1307" s="26"/>
     </row>
     <row r="1308" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1308" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1308" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1308" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1308" s="31" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="E1308" s="26" t="s">
         <v>847</v>
@@ -34046,13 +34040,13 @@
         <v>847</v>
       </c>
       <c r="G1308" s="26" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="H1308" s="26" t="s">
-        <v>1336</v>
+        <v>1334</v>
       </c>
       <c r="I1308" s="26" t="s">
-        <v>1337</v>
+        <v>1335</v>
       </c>
       <c r="J1308" s="26" t="s">
         <v>847</v>
@@ -34060,16 +34054,16 @@
     </row>
     <row r="1309" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1309" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1309" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1309" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1309" s="26" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="E1309" s="26" t="s">
         <v>841</v>
@@ -34081,25 +34075,25 @@
         <v>81</v>
       </c>
       <c r="H1309" s="26" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="I1309" s="26" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="J1309" s="26"/>
     </row>
     <row r="1310" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1310" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1310" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1310" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1310" s="26" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="E1310" s="26" t="s">
         <v>832</v>
@@ -34108,27 +34102,27 @@
         <v>832</v>
       </c>
       <c r="G1310" s="26" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="H1310" s="26" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="I1310" s="26" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="J1310" s="26" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="1311" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1311" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1311" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1311" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1311" s="26" t="s">
         <v>218</v>
@@ -34152,16 +34146,16 @@
     </row>
     <row r="1312" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1312" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1312" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1312" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1312" s="26" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="E1312" s="26" t="s">
         <v>924</v>
@@ -34173,10 +34167,10 @@
         <v>81</v>
       </c>
       <c r="H1312" s="31" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="I1312" s="26" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="J1312" s="26" t="s">
         <v>924</v>
@@ -34184,31 +34178,31 @@
     </row>
     <row r="1313" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1313" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1313" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1313" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1313" s="31" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="E1313" s="26" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="F1313" s="26" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="G1313" s="31" t="s">
         <v>81</v>
       </c>
       <c r="H1313" s="26" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="I1313" s="26" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="J1313" s="26" t="s">
         <v>895</v>
@@ -34216,31 +34210,31 @@
     </row>
     <row r="1314" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1314" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1314" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1314" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1314" s="26" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="E1314" s="26" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="F1314" s="26" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="G1314" s="26" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="H1314" s="26" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="I1314" s="26" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="J1314" s="26" t="s">
         <v>902</v>
@@ -34248,13 +34242,13 @@
     </row>
     <row r="1315" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1315" s="24" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B1315" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1315" s="25" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="D1315" s="26" t="s">
         <v>334</v>
@@ -36043,117 +36037,117 @@
     </row>
     <row r="135" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="58" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B135" s="58" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C135" s="58" t="s">
         <v>1141</v>
-      </c>
-      <c r="B135" s="58" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C135" s="58" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="22" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B136" s="22" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C136" s="22" t="s">
         <v>1144</v>
-      </c>
-      <c r="B136" s="22" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C136" s="22" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="57" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B137" s="57" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C137" s="57" t="s">
         <v>1147</v>
-      </c>
-      <c r="B137" s="57" t="s">
-        <v>1148</v>
-      </c>
-      <c r="C137" s="57" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="59" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B138" s="57" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C138" s="57" t="s">
         <v>1150</v>
-      </c>
-      <c r="B138" s="57" t="s">
-        <v>1151</v>
-      </c>
-      <c r="C138" s="57" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="22" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B139" s="22" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C139" s="22" t="s">
         <v>1153</v>
-      </c>
-      <c r="B139" s="22" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C139" s="22" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="22" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B140" s="22" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C140" s="22" t="s">
         <v>1156</v>
-      </c>
-      <c r="B140" s="22" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C140" s="22" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="22" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="B141" s="22" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C141" s="22" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="22" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="B142" s="22" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="C142" s="22" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="22" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="B143" s="60" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="C143" s="60" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="22" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="B144" s="22" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="C144" s="22" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="22" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="B145" s="22" t="s">
         <v>1033</v>
@@ -36164,35 +36158,35 @@
     </row>
     <row r="146" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="22" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B146" s="22" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C146" s="22" t="s">
         <v>1168</v>
-      </c>
-      <c r="B146" s="22" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C146" s="22" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="22" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B147" s="22" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C147" s="61" t="s">
         <v>1171</v>
-      </c>
-      <c r="B147" s="22" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C147" s="61" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="22" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="B148" s="22" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="C148" s="22" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
     </row>
   </sheetData>
@@ -36347,10 +36341,10 @@
         <v>514</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>1120</v>
+        <v>1129</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1121</v>
+        <v>155</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>727</v>
@@ -37030,10 +37024,10 @@
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="52" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="B59" s="52" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="C59" s="52" t="s">
         <v>425</v>
@@ -37044,10 +37038,10 @@
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="53" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="C60" s="20" t="s">
         <v>413</v>
@@ -37058,10 +37052,10 @@
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="20" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="C61" s="20" t="s">
         <v>482</v>
@@ -37072,10 +37066,10 @@
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="54" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="C62" s="20" t="s">
         <v>317</v>
@@ -37086,10 +37080,10 @@
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="55" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="B63" s="55" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="C63" s="20" t="s">
         <v>155</v>
@@ -37100,10 +37094,10 @@
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="54" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="C64" s="20" t="s">
         <v>317</v>
@@ -37114,10 +37108,10 @@
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="56" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
       <c r="B65" s="56" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="C65" s="56" t="s">
         <v>425</v>
@@ -37128,10 +37122,10 @@
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="57" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="C66" s="20" t="s">
         <v>413</v>

--- a/static/TALENKAART_DATA/talenkaart_data.xlsx
+++ b/static/TALENKAART_DATA/talenkaart_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amsuni-my.sharepoint.com/personal/kylie_mansour_student_uva_nl/Documents/Documents/MA/Internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{D6D6DB9B-1825-0E4C-A6B9-EC4CA1933FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD23FD8E-2C6D-1945-93F4-429B5C42A6D5}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{D6D6DB9B-1825-0E4C-A6B9-EC4CA1933FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75D2AE43-EF18-4041-A7D3-05D24502DBAE}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respondenten" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6927" uniqueCount="1459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6930" uniqueCount="1462">
   <si>
     <t>Locatie</t>
   </si>
@@ -4427,6 +4427,15 @@
   </si>
   <si>
     <t xml:space="preserve">OBA De Hallen </t>
+  </si>
+  <si>
+    <t>srv</t>
+  </si>
+  <si>
+    <t>Zuid-Sorsoganon</t>
+  </si>
+  <si>
+    <t>Southern Sorsoganon</t>
   </si>
 </sst>
 </file>
@@ -34284,7 +34293,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E149"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="12.6640625" style="22" customWidth="1"/>
@@ -36187,6 +36196,17 @@
       </c>
       <c r="C148" s="22" t="s">
         <v>1173</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A149" s="22" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B149" s="22" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C149" s="22" t="s">
+        <v>1461</v>
       </c>
     </row>
   </sheetData>

--- a/static/TALENKAART_DATA/talenkaart_data.xlsx
+++ b/static/TALENKAART_DATA/talenkaart_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amsuni-my.sharepoint.com/personal/kylie_mansour_student_uva_nl/Documents/Documents/MA/Internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{D6D6DB9B-1825-0E4C-A6B9-EC4CA1933FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75D2AE43-EF18-4041-A7D3-05D24502DBAE}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{4E206D19-195A-944F-8DDD-B7F1A58C2269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D09ED4B8-3D17-2E45-91BB-8E4153E710D8}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Respondenten" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6930" uniqueCount="1462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6924" uniqueCount="1458">
   <si>
     <t>Locatie</t>
   </si>
@@ -3516,18 +3516,6 @@
   </si>
   <si>
     <t>Ethiopian sign language</t>
-  </si>
-  <si>
-    <t>sra</t>
-  </si>
-  <si>
-    <t>Saruga</t>
-  </si>
-  <si>
-    <t>ant</t>
-  </si>
-  <si>
-    <t>Antakarinya</t>
   </si>
   <si>
     <t>kok</t>
@@ -4198,9 +4186,6 @@
     <t>nld,eng,por,hin,spa</t>
   </si>
   <si>
-    <t>nld,eng,sra,ant,deu</t>
-  </si>
-  <si>
     <t>nld,eng,afr,heb</t>
   </si>
   <si>
@@ -4436,6 +4421,9 @@
   </si>
   <si>
     <t>Southern Sorsoganon</t>
+  </si>
+  <si>
+    <t>nld,eng,srn,pap,deu</t>
   </si>
 </sst>
 </file>
@@ -4780,7 +4768,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -4901,7 +4889,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="11" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4995,10 +4982,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6062,34 +6045,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64" t="s">
+      <c r="B1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="64" t="s">
+      <c r="C1" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="64" t="s">
+      <c r="D1" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="64" t="s">
+      <c r="E1" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="65" t="s">
+      <c r="F1" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="66" t="s">
+      <c r="H1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="66" t="s">
+      <c r="I1" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="67" t="s">
+      <c r="J1" s="66" t="s">
         <v>9</v>
       </c>
     </row>
@@ -24559,13 +24542,13 @@
     </row>
     <row r="999" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A999" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B999" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C999" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D999" s="25" t="s">
         <v>227</v>
@@ -24589,13 +24572,13 @@
     </row>
     <row r="1000" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1000" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1000" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1000" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1000" s="25" t="s">
         <v>227</v>
@@ -24607,7 +24590,7 @@
         <v>218</v>
       </c>
       <c r="G1000" s="25" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="H1000" s="25" t="s">
         <v>34</v>
@@ -24619,16 +24602,16 @@
     </row>
     <row r="1001" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1001" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1001" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1001" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1001" s="25" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="E1001" s="25" t="s">
         <v>89</v>
@@ -24640,10 +24623,10 @@
         <v>204</v>
       </c>
       <c r="H1001" s="25" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="I1001" s="25" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="J1001" s="25" t="s">
         <v>108</v>
@@ -24651,13 +24634,13 @@
     </row>
     <row r="1002" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1002" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1002" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1002" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1002" s="25" t="s">
         <v>140</v>
@@ -24669,28 +24652,28 @@
         <v>141</v>
       </c>
       <c r="G1002" s="25" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1002" s="25" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1002" s="25" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1002" s="25"/>
     </row>
     <row r="1003" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1003" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1003" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1003" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1003" s="25" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="E1003" s="25" t="s">
         <v>89</v>
@@ -24711,16 +24694,16 @@
     </row>
     <row r="1004" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1004" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1004" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1004" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1004" s="25" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="E1004" s="25" t="s">
         <v>242</v>
@@ -24729,28 +24712,28 @@
         <v>242</v>
       </c>
       <c r="G1004" s="25" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="H1004" s="25" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="I1004" s="25" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="J1004" s="25"/>
     </row>
     <row r="1005" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1005" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1005" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1005" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1005" s="25" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="E1005" s="25" t="s">
         <v>219</v>
@@ -24759,10 +24742,10 @@
         <v>218</v>
       </c>
       <c r="G1005" s="25" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="H1005" s="25" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="I1005" s="25" t="s">
         <v>218</v>
@@ -24771,16 +24754,16 @@
     </row>
     <row r="1006" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1006" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1006" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1006" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1006" s="26" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="E1006" s="26" t="s">
         <v>81</v>
@@ -24801,16 +24784,16 @@
     </row>
     <row r="1007" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1007" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1007" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1007" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1007" s="26" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="E1007" s="27" t="s">
         <v>284</v>
@@ -24822,7 +24805,7 @@
         <v>108</v>
       </c>
       <c r="H1007" s="27" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1007" s="27" t="s">
         <v>81</v>
@@ -24831,19 +24814,19 @@
     </row>
     <row r="1008" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1008" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1008" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1008" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1008" s="26" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="E1008" s="27" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="F1008" s="27" t="s">
         <v>1005</v>
@@ -24852,22 +24835,22 @@
         <v>81</v>
       </c>
       <c r="H1008" s="27" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="I1008" s="27" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="J1008" s="26"/>
     </row>
     <row r="1009" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1009" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1009" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1009" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1009" s="26" t="s">
         <v>34</v>
@@ -24891,13 +24874,13 @@
     </row>
     <row r="1010" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1010" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1010" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1010" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1010" s="26" t="s">
         <v>108</v>
@@ -24909,7 +24892,7 @@
         <v>89</v>
       </c>
       <c r="G1010" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1010" s="26" t="s">
         <v>89</v>
@@ -24921,13 +24904,13 @@
     </row>
     <row r="1011" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1011" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1011" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1011" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1011" s="26" t="s">
         <v>204</v>
@@ -24945,22 +24928,22 @@
         <v>89</v>
       </c>
       <c r="I1011" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1011" s="26"/>
     </row>
     <row r="1012" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1012" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1012" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1012" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1012" s="26" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="E1012" s="26" t="s">
         <v>969</v>
@@ -24969,7 +24952,7 @@
         <v>969</v>
       </c>
       <c r="G1012" s="26" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="H1012" s="26" t="s">
         <v>81</v>
@@ -24981,16 +24964,16 @@
     </row>
     <row r="1013" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1013" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1013" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1013" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1013" s="27" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="E1013" s="27" t="s">
         <v>143</v>
@@ -25002,24 +24985,24 @@
         <v>108</v>
       </c>
       <c r="H1013" s="27" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1013" s="27" t="s">
         <v>81</v>
       </c>
       <c r="J1013" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="1014" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1014" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1014" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1014" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1014" s="26" t="s">
         <v>338</v>
@@ -25045,16 +25028,16 @@
     </row>
     <row r="1015" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1015" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1015" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1015" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1015" s="26" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="E1015" s="26" t="s">
         <v>108</v>
@@ -25081,7 +25064,7 @@
         <v>155</v>
       </c>
       <c r="C1016" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1016" s="28" t="s">
         <v>232</v>
@@ -25113,13 +25096,13 @@
         <v>155</v>
       </c>
       <c r="C1017" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1017" s="28" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="E1017" s="28" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="F1017" s="28" t="s">
         <v>219</v>
@@ -25143,7 +25126,7 @@
         <v>155</v>
       </c>
       <c r="C1018" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1018" s="29" t="s">
         <v>796</v>
@@ -25155,13 +25138,13 @@
         <v>89</v>
       </c>
       <c r="G1018" s="29" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1018" s="29" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1018" s="29" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1018" s="28"/>
     </row>
@@ -25173,7 +25156,7 @@
         <v>155</v>
       </c>
       <c r="C1019" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1019" s="28" t="s">
         <v>206</v>
@@ -25201,25 +25184,25 @@
         <v>155</v>
       </c>
       <c r="C1020" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1020" s="28" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="E1020" s="28" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="F1020" s="28" t="s">
         <v>89</v>
       </c>
       <c r="G1020" s="28" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1020" s="28" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1020" s="28" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1020" s="28"/>
     </row>
@@ -25231,16 +25214,16 @@
         <v>155</v>
       </c>
       <c r="C1021" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1021" s="28" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="E1021" s="28" t="s">
         <v>82</v>
       </c>
       <c r="F1021" s="28" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="G1021" s="28" t="s">
         <v>89</v>
@@ -25249,7 +25232,7 @@
         <v>89</v>
       </c>
       <c r="I1021" s="28" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1021" s="28" t="s">
         <v>281</v>
@@ -25263,7 +25246,7 @@
         <v>155</v>
       </c>
       <c r="C1022" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1022" s="28" t="s">
         <v>31</v>
@@ -25281,7 +25264,7 @@
         <v>89</v>
       </c>
       <c r="I1022" s="28" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1022" s="28" t="s">
         <v>89</v>
@@ -25295,7 +25278,7 @@
         <v>155</v>
       </c>
       <c r="C1023" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1023" s="28" t="s">
         <v>796</v>
@@ -25327,10 +25310,10 @@
         <v>155</v>
       </c>
       <c r="C1024" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1024" s="28" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="E1024" s="28" t="s">
         <v>89</v>
@@ -25359,7 +25342,7 @@
         <v>155</v>
       </c>
       <c r="C1025" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1025" s="28" t="s">
         <v>281</v>
@@ -25391,22 +25374,22 @@
         <v>155</v>
       </c>
       <c r="C1026" s="28" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D1026" s="28" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E1026" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1026" s="28" t="s">
         <v>1195</v>
       </c>
-      <c r="D1026" s="28" t="s">
-        <v>1198</v>
-      </c>
-      <c r="E1026" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="F1026" s="28" t="s">
-        <v>1199</v>
-      </c>
       <c r="G1026" s="28" t="s">
         <v>89</v>
       </c>
       <c r="H1026" s="28" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="I1026" s="28" t="s">
         <v>89</v>
@@ -25423,25 +25406,25 @@
         <v>155</v>
       </c>
       <c r="C1027" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1027" s="28" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="E1027" s="28" t="s">
         <v>81</v>
       </c>
       <c r="F1027" s="28" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="G1027" s="28" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1027" s="28" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="I1027" s="28" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="J1027" s="28"/>
     </row>
@@ -25453,10 +25436,10 @@
         <v>155</v>
       </c>
       <c r="C1028" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1028" s="28" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="E1028" s="28" t="s">
         <v>16</v>
@@ -25468,10 +25451,10 @@
         <v>89</v>
       </c>
       <c r="H1028" s="28" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="I1028" s="28" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="J1028" s="28" t="s">
         <v>15</v>
@@ -25485,7 +25468,7 @@
         <v>155</v>
       </c>
       <c r="C1029" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1029" s="28" t="s">
         <v>281</v>
@@ -25517,7 +25500,7 @@
         <v>155</v>
       </c>
       <c r="C1030" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1030" s="28" t="s">
         <v>89</v>
@@ -25545,10 +25528,10 @@
         <v>413</v>
       </c>
       <c r="C1031" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1031" s="26" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="E1031" s="26" t="s">
         <v>902</v>
@@ -25560,10 +25543,10 @@
         <v>81</v>
       </c>
       <c r="H1031" s="26" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="I1031" s="26" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="J1031" s="26"/>
     </row>
@@ -25575,7 +25558,7 @@
         <v>413</v>
       </c>
       <c r="C1032" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1032" s="26" t="s">
         <v>108</v>
@@ -25593,7 +25576,7 @@
         <v>89</v>
       </c>
       <c r="I1032" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1032" s="26" t="s">
         <v>89</v>
@@ -25607,7 +25590,7 @@
         <v>413</v>
       </c>
       <c r="C1033" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1033" s="27" t="s">
         <v>50</v>
@@ -25619,13 +25602,13 @@
         <v>89</v>
       </c>
       <c r="G1033" s="27" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1033" s="27" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1033" s="27" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1033" s="26" t="s">
         <v>89</v>
@@ -25639,7 +25622,7 @@
         <v>413</v>
       </c>
       <c r="C1034" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1034" s="26" t="s">
         <v>204</v>
@@ -25651,7 +25634,7 @@
         <v>89</v>
       </c>
       <c r="G1034" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1034" s="26" t="s">
         <v>89</v>
@@ -25671,7 +25654,7 @@
         <v>413</v>
       </c>
       <c r="C1035" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1035" s="26" t="s">
         <v>81</v>
@@ -25695,10 +25678,10 @@
         <v>413</v>
       </c>
       <c r="C1036" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1036" s="26" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="E1036" s="26" t="s">
         <v>892</v>
@@ -25710,10 +25693,10 @@
         <v>81</v>
       </c>
       <c r="H1036" s="26" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="I1036" s="26" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="J1036" s="26" t="s">
         <v>892</v>
@@ -25727,16 +25710,16 @@
         <v>413</v>
       </c>
       <c r="C1037" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1037" s="26" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="E1037" s="26" t="s">
         <v>89</v>
       </c>
       <c r="F1037" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="G1037" s="26" t="s">
         <v>81</v>
@@ -25745,7 +25728,7 @@
         <v>89</v>
       </c>
       <c r="I1037" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1037" s="26" t="s">
         <v>89</v>
@@ -25759,13 +25742,13 @@
         <v>413</v>
       </c>
       <c r="C1038" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1038" s="26" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="E1038" s="26" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="F1038" s="26" t="s">
         <v>969</v>
@@ -25791,7 +25774,7 @@
         <v>413</v>
       </c>
       <c r="C1039" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1039" s="26" t="s">
         <v>204</v>
@@ -25806,7 +25789,7 @@
         <v>22</v>
       </c>
       <c r="H1039" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1039" s="26" t="s">
         <v>22</v>
@@ -25821,10 +25804,10 @@
         <v>413</v>
       </c>
       <c r="C1040" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1040" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="E1040" s="26" t="s">
         <v>89</v>
@@ -25833,13 +25816,13 @@
         <v>89</v>
       </c>
       <c r="G1040" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1040" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1040" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1040" s="26"/>
     </row>
@@ -25851,10 +25834,10 @@
         <v>413</v>
       </c>
       <c r="C1041" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1041" s="30" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="E1041" s="30" t="s">
         <v>89</v>
@@ -25863,16 +25846,16 @@
         <v>153</v>
       </c>
       <c r="G1041" s="30" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1041" s="30" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1041" s="30" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1041" s="30" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="1042" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -25883,10 +25866,10 @@
         <v>413</v>
       </c>
       <c r="C1042" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1042" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="E1042" s="26" t="s">
         <v>89</v>
@@ -25913,7 +25896,7 @@
         <v>413</v>
       </c>
       <c r="C1043" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1043" s="26" t="s">
         <v>31</v>
@@ -25943,10 +25926,10 @@
         <v>413</v>
       </c>
       <c r="C1044" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1044" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="E1044" s="26" t="s">
         <v>81</v>
@@ -25958,7 +25941,7 @@
         <v>89</v>
       </c>
       <c r="H1044" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1044" s="26" t="s">
         <v>81</v>
@@ -25973,22 +25956,22 @@
         <v>413</v>
       </c>
       <c r="C1045" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1045" s="26" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="E1045" s="26" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="F1045" s="26" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="G1045" s="26" t="s">
         <v>108</v>
       </c>
       <c r="H1045" s="26" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="I1045" s="26" t="s">
         <v>81</v>
@@ -26003,7 +25986,7 @@
         <v>413</v>
       </c>
       <c r="C1046" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1046" s="26" t="s">
         <v>1119</v>
@@ -26033,10 +26016,10 @@
         <v>413</v>
       </c>
       <c r="C1047" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1047" s="26" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="E1047" s="26" t="s">
         <v>37</v>
@@ -26063,10 +26046,10 @@
         <v>413</v>
       </c>
       <c r="C1048" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1048" s="26" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="E1048" s="26" t="s">
         <v>892</v>
@@ -26078,7 +26061,7 @@
         <v>81</v>
       </c>
       <c r="H1048" s="26" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="I1048" s="26" t="s">
         <v>81</v>
@@ -26095,7 +26078,7 @@
         <v>413</v>
       </c>
       <c r="C1049" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1049" s="26" t="s">
         <v>142</v>
@@ -26127,7 +26110,7 @@
         <v>413</v>
       </c>
       <c r="C1050" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1050" s="26" t="s">
         <v>142</v>
@@ -26159,10 +26142,10 @@
         <v>413</v>
       </c>
       <c r="C1051" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1051" s="26" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="E1051" s="26" t="s">
         <v>865</v>
@@ -26177,7 +26160,7 @@
         <v>81</v>
       </c>
       <c r="I1051" s="26" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="J1051" s="26"/>
     </row>
@@ -26189,10 +26172,10 @@
         <v>413</v>
       </c>
       <c r="C1052" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1052" s="26" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="E1052" s="26" t="s">
         <v>81</v>
@@ -26204,7 +26187,7 @@
         <v>81</v>
       </c>
       <c r="H1052" s="26" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="I1052" s="26" t="s">
         <v>81</v>
@@ -26221,10 +26204,10 @@
         <v>413</v>
       </c>
       <c r="C1053" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1053" s="26" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="E1053" s="26" t="s">
         <v>81</v>
@@ -26236,7 +26219,7 @@
         <v>81</v>
       </c>
       <c r="H1053" s="26" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="I1053" s="26" t="s">
         <v>81</v>
@@ -26253,10 +26236,10 @@
         <v>413</v>
       </c>
       <c r="C1054" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1054" s="26" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="E1054" s="26" t="s">
         <v>219</v>
@@ -26283,10 +26266,10 @@
         <v>413</v>
       </c>
       <c r="C1055" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1055" s="26" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="E1055" s="26" t="s">
         <v>248</v>
@@ -26295,7 +26278,7 @@
         <v>248</v>
       </c>
       <c r="G1055" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1055" s="26" t="s">
         <v>89</v>
@@ -26315,10 +26298,10 @@
         <v>413</v>
       </c>
       <c r="C1056" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1056" s="26" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="E1056" s="26" t="s">
         <v>28</v>
@@ -26327,16 +26310,16 @@
         <v>28</v>
       </c>
       <c r="G1056" s="26" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="H1056" s="26" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="I1056" s="26" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="J1056" s="26" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="1057" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -26347,23 +26330,23 @@
         <v>413</v>
       </c>
       <c r="C1057" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1057" s="26" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="E1057" s="26" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="F1057" s="26"/>
       <c r="G1057" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1057" s="26" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="I1057" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1057" s="26"/>
     </row>
@@ -26375,10 +26358,10 @@
         <v>413</v>
       </c>
       <c r="C1058" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1058" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="E1058" s="26" t="s">
         <v>108</v>
@@ -26393,7 +26376,7 @@
         <v>89</v>
       </c>
       <c r="I1058" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1058" s="26"/>
     </row>
@@ -26405,22 +26388,22 @@
         <v>413</v>
       </c>
       <c r="C1059" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1059" s="26" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="E1059" s="26" t="s">
         <v>81</v>
       </c>
       <c r="F1059" s="26" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="G1059" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1059" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1059" s="26" t="s">
         <v>81</v>
@@ -26435,10 +26418,10 @@
         <v>413</v>
       </c>
       <c r="C1060" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1060" s="26" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="E1060" s="26" t="s">
         <v>1041</v>
@@ -26465,7 +26448,7 @@
         <v>413</v>
       </c>
       <c r="C1061" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1061" s="26" t="s">
         <v>338</v>
@@ -26477,13 +26460,13 @@
         <v>89</v>
       </c>
       <c r="G1061" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1061" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1061" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1061" s="26"/>
     </row>
@@ -26495,7 +26478,7 @@
         <v>413</v>
       </c>
       <c r="C1062" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1062" s="26" t="s">
         <v>204</v>
@@ -26507,13 +26490,13 @@
         <v>89</v>
       </c>
       <c r="G1062" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1062" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1062" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1062" s="26"/>
     </row>
@@ -26525,7 +26508,7 @@
         <v>413</v>
       </c>
       <c r="C1063" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1063" s="26" t="s">
         <v>108</v>
@@ -26537,13 +26520,13 @@
         <v>89</v>
       </c>
       <c r="G1063" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1063" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1063" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1063" s="26"/>
     </row>
@@ -26555,10 +26538,10 @@
         <v>413</v>
       </c>
       <c r="C1064" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1064" s="26" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="E1064" s="26" t="s">
         <v>859</v>
@@ -26570,10 +26553,10 @@
         <v>81</v>
       </c>
       <c r="H1064" s="26" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="I1064" s="26" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="J1064" s="26"/>
     </row>
@@ -26585,10 +26568,10 @@
         <v>413</v>
       </c>
       <c r="C1065" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1065" s="26" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="E1065" s="26" t="s">
         <v>19</v>
@@ -26600,10 +26583,10 @@
         <v>81</v>
       </c>
       <c r="H1065" s="26" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="I1065" s="26" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="J1065" s="26"/>
     </row>
@@ -26615,10 +26598,10 @@
         <v>413</v>
       </c>
       <c r="C1066" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1066" s="26" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="E1066" s="26" t="s">
         <v>81</v>
@@ -26633,7 +26616,7 @@
         <v>81</v>
       </c>
       <c r="I1066" s="26" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="J1066" s="26"/>
     </row>
@@ -26645,10 +26628,10 @@
         <v>413</v>
       </c>
       <c r="C1067" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1067" s="26" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="E1067" s="26" t="s">
         <v>89</v>
@@ -26657,7 +26640,7 @@
         <v>89</v>
       </c>
       <c r="G1067" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1067" s="26" t="s">
         <v>108</v>
@@ -26675,7 +26658,7 @@
         <v>413</v>
       </c>
       <c r="C1068" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1068" s="26" t="s">
         <v>796</v>
@@ -26687,7 +26670,7 @@
         <v>89</v>
       </c>
       <c r="G1068" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1068" s="26" t="s">
         <v>108</v>
@@ -26705,22 +26688,22 @@
         <v>413</v>
       </c>
       <c r="C1069" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1069" s="26" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="E1069" s="26" t="s">
         <v>81</v>
       </c>
       <c r="F1069" s="26" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="G1069" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1069" s="26" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="I1069" s="26" t="s">
         <v>81</v>
@@ -26735,10 +26718,10 @@
         <v>413</v>
       </c>
       <c r="C1070" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1070" s="26" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="E1070" s="26" t="s">
         <v>81</v>
@@ -26753,7 +26736,7 @@
         <v>81</v>
       </c>
       <c r="I1070" s="26" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="J1070" s="26"/>
     </row>
@@ -26765,19 +26748,19 @@
         <v>413</v>
       </c>
       <c r="C1071" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1071" s="26" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="E1071" s="26" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="F1071" s="26" t="s">
         <v>97</v>
       </c>
       <c r="G1071" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1071" s="26" t="s">
         <v>81</v>
@@ -26795,10 +26778,10 @@
         <v>413</v>
       </c>
       <c r="C1072" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1072" s="26" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="E1072" s="26" t="s">
         <v>81</v>
@@ -26813,7 +26796,7 @@
         <v>81</v>
       </c>
       <c r="I1072" s="26" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="J1072" s="26"/>
     </row>
@@ -26825,16 +26808,16 @@
         <v>413</v>
       </c>
       <c r="C1073" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1073" s="31" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="E1073" s="26" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="F1073" s="26" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="G1073" s="26" t="s">
         <v>81</v>
@@ -26855,10 +26838,10 @@
         <v>413</v>
       </c>
       <c r="C1074" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1074" s="26" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E1074" s="26" t="s">
         <v>990</v>
@@ -26885,7 +26868,7 @@
         <v>413</v>
       </c>
       <c r="C1075" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1075" s="26" t="s">
         <v>218</v>
@@ -26915,7 +26898,7 @@
         <v>413</v>
       </c>
       <c r="C1076" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1076" s="26" t="s">
         <v>796</v>
@@ -26945,7 +26928,7 @@
         <v>413</v>
       </c>
       <c r="C1077" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1077" s="26" t="s">
         <v>594</v>
@@ -26977,7 +26960,7 @@
         <v>413</v>
       </c>
       <c r="C1078" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1078" s="26" t="s">
         <v>338</v>
@@ -26995,7 +26978,7 @@
         <v>89</v>
       </c>
       <c r="I1078" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1078" s="26" t="s">
         <v>89</v>
@@ -27009,10 +26992,10 @@
         <v>413</v>
       </c>
       <c r="C1079" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1079" s="26" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="E1079" s="26" t="s">
         <v>1021</v>
@@ -27024,10 +27007,10 @@
         <v>81</v>
       </c>
       <c r="H1079" s="26" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="I1079" s="26" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="J1079" s="26" t="s">
         <v>1021</v>
@@ -27041,13 +27024,13 @@
         <v>413</v>
       </c>
       <c r="C1080" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1080" s="26" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="E1080" s="26" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="F1080" s="26" t="s">
         <v>924</v>
@@ -27073,10 +27056,10 @@
         <v>413</v>
       </c>
       <c r="C1081" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1081" s="26" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="E1081" s="26" t="s">
         <v>811</v>
@@ -27085,13 +27068,13 @@
         <v>811</v>
       </c>
       <c r="G1081" s="26" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="H1081" s="26" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="I1081" s="26" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="J1081" s="26"/>
     </row>
@@ -27103,10 +27086,10 @@
         <v>413</v>
       </c>
       <c r="C1082" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1082" s="26" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="E1082" s="26" t="s">
         <v>28</v>
@@ -27118,10 +27101,10 @@
         <v>28</v>
       </c>
       <c r="H1082" s="26" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="I1082" s="26" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="J1082" s="26"/>
     </row>
@@ -27133,10 +27116,10 @@
         <v>413</v>
       </c>
       <c r="C1083" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1083" s="26" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="E1083" s="26" t="s">
         <v>28</v>
@@ -27163,10 +27146,10 @@
         <v>413</v>
       </c>
       <c r="C1084" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1084" s="26" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="E1084" s="26" t="s">
         <v>808</v>
@@ -27181,7 +27164,7 @@
         <v>81</v>
       </c>
       <c r="I1084" s="26" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="J1084" s="26"/>
     </row>
@@ -27193,7 +27176,7 @@
         <v>413</v>
       </c>
       <c r="C1085" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1085" s="26" t="s">
         <v>108</v>
@@ -27211,7 +27194,7 @@
         <v>89</v>
       </c>
       <c r="I1085" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1085" s="26"/>
     </row>
@@ -27223,10 +27206,10 @@
         <v>413</v>
       </c>
       <c r="C1086" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1086" s="26" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="E1086" s="26" t="s">
         <v>946</v>
@@ -27238,7 +27221,7 @@
         <v>81</v>
       </c>
       <c r="H1086" s="26" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="I1086" s="26" t="s">
         <v>81</v>
@@ -27255,10 +27238,10 @@
         <v>413</v>
       </c>
       <c r="C1087" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1087" s="26" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="E1087" s="26" t="s">
         <v>89</v>
@@ -27285,10 +27268,10 @@
         <v>413</v>
       </c>
       <c r="C1088" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1088" s="26" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="E1088" s="26" t="s">
         <v>89</v>
@@ -27315,7 +27298,7 @@
         <v>413</v>
       </c>
       <c r="C1089" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1089" s="26" t="s">
         <v>50</v>
@@ -27324,7 +27307,7 @@
         <v>392</v>
       </c>
       <c r="F1089" s="26" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="G1089" s="26" t="s">
         <v>108</v>
@@ -27345,7 +27328,7 @@
         <v>413</v>
       </c>
       <c r="C1090" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1090" s="26" t="s">
         <v>233</v>
@@ -27377,10 +27360,10 @@
         <v>482</v>
       </c>
       <c r="C1091" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1091" s="32" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="E1091" s="32" t="s">
         <v>89</v>
@@ -27405,16 +27388,16 @@
         <v>482</v>
       </c>
       <c r="C1092" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1092" s="32" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="E1092" s="32" t="s">
         <v>108</v>
       </c>
       <c r="F1092" s="32" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="G1092" s="32" t="s">
         <v>89</v>
@@ -27437,25 +27420,25 @@
         <v>482</v>
       </c>
       <c r="C1093" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1093" s="33" t="s">
         <v>348</v>
       </c>
       <c r="E1093" s="33" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="F1093" s="33" t="s">
         <v>89</v>
       </c>
       <c r="G1093" s="33" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1093" s="33" t="s">
         <v>108</v>
       </c>
       <c r="I1093" s="33" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1093" s="32"/>
     </row>
@@ -27467,7 +27450,7 @@
         <v>482</v>
       </c>
       <c r="C1094" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1094" s="32" t="s">
         <v>50</v>
@@ -27476,16 +27459,16 @@
         <v>808</v>
       </c>
       <c r="F1094" s="32" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="G1094" s="32" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1094" s="32" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="I1094" s="32" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="J1094" s="32"/>
     </row>
@@ -27497,10 +27480,10 @@
         <v>482</v>
       </c>
       <c r="C1095" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1095" s="32" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="E1095" s="32" t="s">
         <v>401</v>
@@ -27518,7 +27501,7 @@
         <v>108</v>
       </c>
       <c r="J1095" s="32" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="1096" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27529,7 +27512,7 @@
         <v>482</v>
       </c>
       <c r="C1096" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1096" s="34" t="s">
         <v>34</v>
@@ -27561,10 +27544,10 @@
         <v>482</v>
       </c>
       <c r="C1097" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1097" s="34" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="E1097" s="34" t="s">
         <v>81</v>
@@ -27576,13 +27559,13 @@
         <v>81</v>
       </c>
       <c r="H1097" s="34" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="I1097" s="34" t="s">
         <v>81</v>
       </c>
       <c r="J1097" s="34" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="1098" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27593,7 +27576,7 @@
         <v>482</v>
       </c>
       <c r="C1098" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1098" s="34" t="s">
         <v>50</v>
@@ -27625,22 +27608,22 @@
         <v>482</v>
       </c>
       <c r="C1099" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1099" s="34" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="E1099" s="34" t="s">
         <v>50</v>
       </c>
       <c r="F1099" s="34" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="G1099" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1099" s="34" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="I1099" s="34" t="s">
         <v>50</v>
@@ -27655,7 +27638,7 @@
         <v>482</v>
       </c>
       <c r="C1100" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1100" s="34" t="s">
         <v>108</v>
@@ -27685,16 +27668,16 @@
         <v>482</v>
       </c>
       <c r="C1101" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1101" s="34" t="s">
         <v>496</v>
       </c>
       <c r="E1101" s="34" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="F1101" s="34" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="G1101" s="34" t="s">
         <v>89</v>
@@ -27715,7 +27698,7 @@
         <v>482</v>
       </c>
       <c r="C1102" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1102" s="34" t="s">
         <v>204</v>
@@ -27745,7 +27728,7 @@
         <v>482</v>
       </c>
       <c r="C1103" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1103" s="34" t="s">
         <v>149</v>
@@ -27775,10 +27758,10 @@
         <v>482</v>
       </c>
       <c r="C1104" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1104" s="34" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="E1104" s="34" t="s">
         <v>144</v>
@@ -27787,7 +27770,7 @@
         <v>144</v>
       </c>
       <c r="G1104" s="34" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="H1104" s="34" t="s">
         <v>89</v>
@@ -27796,7 +27779,7 @@
         <v>89</v>
       </c>
       <c r="J1104" s="34" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="1105" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27807,16 +27790,16 @@
         <v>482</v>
       </c>
       <c r="C1105" s="32" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D1105" s="34" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="E1105" s="34" t="s">
         <v>81</v>
       </c>
       <c r="F1105" s="34" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="G1105" s="34" t="s">
         <v>81</v>
@@ -27837,19 +27820,19 @@
         <v>155</v>
       </c>
       <c r="C1106" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1106" s="34" t="s">
         <v>319</v>
       </c>
       <c r="E1106" s="34" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F1106" s="34" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="G1106" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="H1106" s="34" t="s">
         <v>143</v>
@@ -27867,28 +27850,28 @@
         <v>155</v>
       </c>
       <c r="C1107" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1107" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="E1107" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="F1107" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="G1107" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1107" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1107" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1107" s="34" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="1108" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27899,25 +27882,25 @@
         <v>155</v>
       </c>
       <c r="C1108" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1108" s="35" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="E1108" s="35" t="s">
         <v>16</v>
       </c>
       <c r="F1108" s="35" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="G1108" s="35" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="H1108" s="35" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="I1108" s="35" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="J1108" s="34"/>
     </row>
@@ -27929,22 +27912,22 @@
         <v>155</v>
       </c>
       <c r="C1109" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1109" s="34" t="s">
         <v>108</v>
       </c>
       <c r="E1109" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="F1109" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="G1109" s="34" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="H1109" s="34" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="I1109" s="34" t="s">
         <v>108</v>
@@ -27959,28 +27942,28 @@
         <v>155</v>
       </c>
       <c r="C1110" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1110" s="34" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E1110" s="34" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="F1110" s="34" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="G1110" s="34" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="H1110" s="34" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="I1110" s="34" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="J1110" s="34" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1111" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -27991,28 +27974,28 @@
         <v>155</v>
       </c>
       <c r="C1111" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1111" s="34" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E1111" s="34" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="F1111" s="34" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="G1111" s="34" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="H1111" s="34" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="I1111" s="34" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="J1111" s="34" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1112" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28023,7 +28006,7 @@
         <v>155</v>
       </c>
       <c r="C1112" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1112" s="34" t="s">
         <v>275</v>
@@ -28032,7 +28015,7 @@
         <v>281</v>
       </c>
       <c r="F1112" s="34" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="G1112" s="34" t="s">
         <v>281</v>
@@ -28044,7 +28027,7 @@
         <v>281</v>
       </c>
       <c r="J1112" s="34" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="1113" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28055,25 +28038,25 @@
         <v>155</v>
       </c>
       <c r="C1113" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1113" s="34" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="E1113" s="34" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="F1113" s="34" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="G1113" s="34" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="H1113" s="34" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="I1113" s="34" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="J1113" s="34"/>
     </row>
@@ -28085,19 +28068,19 @@
         <v>155</v>
       </c>
       <c r="C1114" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1114" s="34" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="E1114" s="34" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="F1114" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="G1114" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="H1114" s="34" t="s">
         <v>227</v>
@@ -28106,7 +28089,7 @@
         <v>227</v>
       </c>
       <c r="J1114" s="34" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="1115" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28117,16 +28100,16 @@
         <v>155</v>
       </c>
       <c r="C1115" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1115" s="34" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="E1115" s="34" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="F1115" s="34" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="G1115" s="34" t="s">
         <v>281</v>
@@ -28135,10 +28118,10 @@
         <v>157</v>
       </c>
       <c r="I1115" s="34" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J1115" s="34" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="1116" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28149,28 +28132,28 @@
         <v>155</v>
       </c>
       <c r="C1116" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1116" s="34" t="s">
         <v>337</v>
       </c>
       <c r="E1116" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="F1116" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="G1116" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="H1116" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="I1116" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J1116" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="1117" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28181,28 +28164,28 @@
         <v>155</v>
       </c>
       <c r="C1117" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1117" s="34" t="s">
         <v>337</v>
       </c>
       <c r="E1117" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="F1117" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="G1117" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="H1117" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="I1117" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J1117" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="1118" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28213,28 +28196,28 @@
         <v>155</v>
       </c>
       <c r="C1118" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1118" s="34" t="s">
         <v>437</v>
       </c>
       <c r="E1118" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="F1118" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="G1118" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="H1118" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="I1118" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J1118" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="1119" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28245,28 +28228,28 @@
         <v>155</v>
       </c>
       <c r="C1119" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1119" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="E1119" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="F1119" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="G1119" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="H1119" s="34" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="I1119" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J1119" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="1120" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28277,25 +28260,25 @@
         <v>155</v>
       </c>
       <c r="C1120" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1120" s="34" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="E1120" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="F1120" s="34" t="s">
         <v>108</v>
       </c>
       <c r="G1120" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="H1120" s="34" t="s">
         <v>108</v>
       </c>
       <c r="I1120" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J1120" s="34"/>
     </row>
@@ -28307,19 +28290,19 @@
         <v>155</v>
       </c>
       <c r="C1121" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1121" s="36" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="E1121" s="36" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="F1121" s="36" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="G1121" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="H1121" s="34" t="s">
         <v>108</v>
@@ -28337,28 +28320,28 @@
         <v>155</v>
       </c>
       <c r="C1122" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1122" s="34" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="E1122" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="F1122" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="G1122" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1122" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="I1122" s="34" t="s">
         <v>108</v>
       </c>
       <c r="J1122" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="1123" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28369,28 +28352,28 @@
         <v>155</v>
       </c>
       <c r="C1123" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1123" s="34" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="E1123" s="34" t="s">
         <v>143</v>
       </c>
       <c r="F1123" s="34" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="G1123" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1123" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1123" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J1123" s="34" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="1124" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28401,28 +28384,28 @@
         <v>155</v>
       </c>
       <c r="C1124" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1124" s="34" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="E1124" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="F1124" s="34" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="G1124" s="34" t="s">
         <v>228</v>
       </c>
       <c r="H1124" s="34" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="I1124" s="34" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="J1124" s="34" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="1125" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28433,25 +28416,25 @@
         <v>155</v>
       </c>
       <c r="C1125" s="28" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="D1125" s="34" t="s">
         <v>111</v>
       </c>
       <c r="E1125" s="34" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="F1125" s="34" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="G1125" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1125" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="I1125" s="34" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="J1125" s="34"/>
     </row>
@@ -28463,10 +28446,10 @@
         <v>317</v>
       </c>
       <c r="C1126" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1126" s="34" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="E1126" s="34" t="s">
         <v>808</v>
@@ -28475,10 +28458,10 @@
         <v>808</v>
       </c>
       <c r="G1126" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1126" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1126" s="34" t="s">
         <v>81</v>
@@ -28493,10 +28476,10 @@
         <v>317</v>
       </c>
       <c r="C1127" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1127" s="34" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="E1127" s="34" t="s">
         <v>969</v>
@@ -28523,10 +28506,10 @@
         <v>317</v>
       </c>
       <c r="C1128" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1128" s="34" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="E1128" s="34" t="s">
         <v>242</v>
@@ -28555,10 +28538,10 @@
         <v>317</v>
       </c>
       <c r="C1129" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1129" s="34" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="E1129" s="34" t="s">
         <v>14</v>
@@ -28585,7 +28568,7 @@
         <v>317</v>
       </c>
       <c r="C1130" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1130" s="34" t="s">
         <v>142</v>
@@ -28615,10 +28598,10 @@
         <v>317</v>
       </c>
       <c r="C1131" s="34" t="s">
+        <v>1295</v>
+      </c>
+      <c r="D1131" s="34" t="s">
         <v>1299</v>
-      </c>
-      <c r="D1131" s="34" t="s">
-        <v>1303</v>
       </c>
       <c r="E1131" s="34" t="s">
         <v>19</v>
@@ -28630,7 +28613,7 @@
         <v>81</v>
       </c>
       <c r="H1131" s="34" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="I1131" s="34" t="s">
         <v>34</v>
@@ -28645,10 +28628,10 @@
         <v>317</v>
       </c>
       <c r="C1132" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1132" s="34" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="E1132" s="34" t="s">
         <v>242</v>
@@ -28663,7 +28646,7 @@
         <v>98</v>
       </c>
       <c r="I1132" s="34" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="J1132" s="34"/>
     </row>
@@ -28675,7 +28658,7 @@
         <v>317</v>
       </c>
       <c r="C1133" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1133" s="34" t="s">
         <v>321</v>
@@ -28705,7 +28688,7 @@
         <v>317</v>
       </c>
       <c r="C1134" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1134" s="34" t="s">
         <v>204</v>
@@ -28735,13 +28718,13 @@
         <v>317</v>
       </c>
       <c r="C1135" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1135" s="34" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="E1135" s="34" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="F1135" s="34" t="s">
         <v>89</v>
@@ -28767,10 +28750,10 @@
         <v>317</v>
       </c>
       <c r="C1136" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1136" s="34" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="E1136" s="34" t="s">
         <v>34</v>
@@ -28797,7 +28780,7 @@
         <v>317</v>
       </c>
       <c r="C1137" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1137" s="34" t="s">
         <v>204</v>
@@ -28827,7 +28810,7 @@
         <v>317</v>
       </c>
       <c r="C1138" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1138" s="34" t="s">
         <v>149</v>
@@ -28857,10 +28840,10 @@
         <v>317</v>
       </c>
       <c r="C1139" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1139" s="34" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="E1139" s="34" t="s">
         <v>89</v>
@@ -28887,22 +28870,22 @@
         <v>317</v>
       </c>
       <c r="C1140" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1140" s="34" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="E1140" s="34" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="F1140" s="34" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="G1140" s="34" t="s">
         <v>108</v>
       </c>
       <c r="H1140" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1140" s="34" t="s">
         <v>81</v>
@@ -28917,10 +28900,10 @@
         <v>317</v>
       </c>
       <c r="C1141" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1141" s="34" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="E1141" s="34" t="s">
         <v>54</v>
@@ -28947,7 +28930,7 @@
         <v>317</v>
       </c>
       <c r="C1142" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1142" s="34" t="s">
         <v>204</v>
@@ -28977,7 +28960,7 @@
         <v>317</v>
       </c>
       <c r="C1143" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1143" s="34" t="s">
         <v>206</v>
@@ -29009,10 +28992,10 @@
         <v>317</v>
       </c>
       <c r="C1144" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1144" s="34" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="E1144" s="34" t="s">
         <v>242</v>
@@ -29021,7 +29004,7 @@
         <v>89</v>
       </c>
       <c r="G1144" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1144" s="34" t="s">
         <v>89</v>
@@ -29039,10 +29022,10 @@
         <v>317</v>
       </c>
       <c r="C1145" s="34" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D1145" s="34" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="E1145" s="34" t="s">
         <v>141</v>
@@ -29071,7 +29054,7 @@
         <v>155</v>
       </c>
       <c r="C1146" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1146" s="38" t="s">
         <v>81</v>
@@ -29101,7 +29084,7 @@
         <v>155</v>
       </c>
       <c r="C1147" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1147" s="38" t="s">
         <v>81</v>
@@ -29131,7 +29114,7 @@
         <v>155</v>
       </c>
       <c r="C1148" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1148" s="38" t="s">
         <v>108</v>
@@ -29161,22 +29144,22 @@
         <v>155</v>
       </c>
       <c r="C1149" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1149" s="38" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="E1149" s="37" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="F1149" s="38" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="G1149" s="37" t="s">
         <v>108</v>
       </c>
       <c r="H1149" s="38" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="I1149" s="37" t="s">
         <v>22</v>
@@ -29193,16 +29176,16 @@
         <v>155</v>
       </c>
       <c r="C1150" s="37" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D1150" s="38" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E1150" s="37" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F1150" s="38" t="s">
         <v>1313</v>
-      </c>
-      <c r="D1150" s="38" t="s">
-        <v>1315</v>
-      </c>
-      <c r="E1150" s="37" t="s">
-        <v>1316</v>
-      </c>
-      <c r="F1150" s="38" t="s">
-        <v>1317</v>
       </c>
       <c r="G1150" s="37" t="s">
         <v>89</v>
@@ -29223,10 +29206,10 @@
         <v>155</v>
       </c>
       <c r="C1151" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1151" s="38" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="E1151" s="37" t="s">
         <v>141</v>
@@ -29241,7 +29224,7 @@
         <v>54</v>
       </c>
       <c r="I1151" s="37" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="J1151" s="38"/>
     </row>
@@ -29253,10 +29236,10 @@
         <v>155</v>
       </c>
       <c r="C1152" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1152" s="38" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E1152" s="37" t="s">
         <v>89</v>
@@ -29271,7 +29254,7 @@
         <v>89</v>
       </c>
       <c r="I1152" s="37" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="J1152" s="38"/>
     </row>
@@ -29283,22 +29266,22 @@
         <v>155</v>
       </c>
       <c r="C1153" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1153" s="38" t="s">
         <v>204</v>
       </c>
       <c r="E1153" s="37" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="F1153" s="38" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="G1153" s="37" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1153" s="38" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1153" s="37" t="s">
         <v>204</v>
@@ -29313,25 +29296,25 @@
         <v>155</v>
       </c>
       <c r="C1154" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1154" s="38" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="E1154" s="37" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="F1154" s="38" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="G1154" s="37" t="s">
         <v>108</v>
       </c>
       <c r="H1154" s="38" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="I1154" s="37" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="J1154" s="38"/>
     </row>
@@ -29343,25 +29326,25 @@
         <v>155</v>
       </c>
       <c r="C1155" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1155" s="38" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="E1155" s="37" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="F1155" s="38" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="G1155" s="37" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="H1155" s="38" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="I1155" s="37" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="J1155" s="38"/>
     </row>
@@ -29373,25 +29356,25 @@
         <v>155</v>
       </c>
       <c r="C1156" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1156" s="38" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="E1156" s="37" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="F1156" s="38" t="s">
         <v>219</v>
       </c>
       <c r="G1156" s="37" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1156" s="38" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="I1156" s="37" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="J1156" s="38" t="s">
         <v>219</v>
@@ -29405,13 +29388,13 @@
         <v>155</v>
       </c>
       <c r="C1157" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1157" s="38" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="E1157" s="37" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="F1157" s="38" t="s">
         <v>902</v>
@@ -29420,10 +29403,10 @@
         <v>81</v>
       </c>
       <c r="H1157" s="38" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="I1157" s="37" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="J1157" s="38"/>
     </row>
@@ -29435,13 +29418,13 @@
         <v>155</v>
       </c>
       <c r="C1158" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1158" s="38" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="E1158" s="37" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="F1158" s="38" t="s">
         <v>902</v>
@@ -29453,7 +29436,7 @@
         <v>81</v>
       </c>
       <c r="I1158" s="37" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="J1158" s="38"/>
     </row>
@@ -29465,25 +29448,25 @@
         <v>155</v>
       </c>
       <c r="C1159" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1159" s="38" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="E1159" s="37" t="s">
         <v>34</v>
       </c>
       <c r="F1159" s="38" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="G1159" s="37" t="s">
         <v>81</v>
       </c>
       <c r="H1159" s="38" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="I1159" s="37" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="J1159" s="38"/>
     </row>
@@ -29495,25 +29478,25 @@
         <v>155</v>
       </c>
       <c r="C1160" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1160" s="38" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="E1160" s="37" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="F1160" s="38" t="s">
         <v>832</v>
       </c>
       <c r="G1160" s="37" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="H1160" s="38" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="I1160" s="37" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="J1160" s="38" t="s">
         <v>81</v>
@@ -29527,10 +29510,10 @@
         <v>155</v>
       </c>
       <c r="C1161" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1161" s="38" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="E1161" s="37" t="s">
         <v>847</v>
@@ -29539,13 +29522,13 @@
         <v>847</v>
       </c>
       <c r="G1161" s="37" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="H1161" s="38" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="I1161" s="37" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="J1161" s="38"/>
     </row>
@@ -29557,25 +29540,25 @@
         <v>155</v>
       </c>
       <c r="C1162" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1162" s="38" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="E1162" s="37" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="F1162" s="38" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="G1162" s="37" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="H1162" s="38" t="s">
         <v>81</v>
       </c>
       <c r="I1162" s="37" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="J1162" s="38" t="s">
         <v>81</v>
@@ -29589,7 +29572,7 @@
         <v>155</v>
       </c>
       <c r="C1163" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1163" s="38" t="s">
         <v>108</v>
@@ -29619,7 +29602,7 @@
         <v>155</v>
       </c>
       <c r="C1164" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1164" s="38" t="s">
         <v>108</v>
@@ -29649,25 +29632,25 @@
         <v>155</v>
       </c>
       <c r="C1165" s="37" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="D1165" s="38" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="E1165" s="37" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="F1165" s="38" t="s">
         <v>219</v>
       </c>
       <c r="G1165" s="37" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1165" s="38" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="I1165" s="37" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="J1165" s="38" t="s">
         <v>219</v>
@@ -29681,7 +29664,7 @@
         <v>317</v>
       </c>
       <c r="C1166" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1166" s="34" t="s">
         <v>108</v>
@@ -29711,10 +29694,10 @@
         <v>317</v>
       </c>
       <c r="C1167" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1167" s="34" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="E1167" s="34" t="s">
         <v>143</v>
@@ -29741,13 +29724,13 @@
         <v>317</v>
       </c>
       <c r="C1168" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1168" s="35" t="s">
         <v>338</v>
       </c>
       <c r="E1168" s="35" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="F1168" s="35" t="s">
         <v>89</v>
@@ -29771,7 +29754,7 @@
         <v>317</v>
       </c>
       <c r="C1169" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1169" s="34" t="s">
         <v>108</v>
@@ -29801,7 +29784,7 @@
         <v>317</v>
       </c>
       <c r="C1170" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1170" s="34" t="s">
         <v>114</v>
@@ -29833,13 +29816,13 @@
         <v>317</v>
       </c>
       <c r="C1171" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1171" s="34" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="E1171" s="34" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="F1171" s="34" t="s">
         <v>832</v>
@@ -29863,7 +29846,7 @@
         <v>317</v>
       </c>
       <c r="C1172" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1172" s="34" t="s">
         <v>338</v>
@@ -29893,7 +29876,7 @@
         <v>317</v>
       </c>
       <c r="C1173" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1173" s="34" t="s">
         <v>458</v>
@@ -29925,10 +29908,10 @@
         <v>317</v>
       </c>
       <c r="C1174" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1174" s="34" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="E1174" s="34" t="s">
         <v>82</v>
@@ -29957,16 +29940,16 @@
         <v>317</v>
       </c>
       <c r="C1175" s="34" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D1175" s="34" t="s">
         <v>1339</v>
       </c>
-      <c r="D1175" s="34" t="s">
-        <v>1343</v>
-      </c>
       <c r="E1175" s="34" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="F1175" s="34" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="G1175" s="34" t="s">
         <v>108</v>
@@ -29989,16 +29972,16 @@
         <v>317</v>
       </c>
       <c r="C1176" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1176" s="34" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="E1176" s="34" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="F1176" s="34" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="G1176" s="34" t="s">
         <v>81</v>
@@ -30021,10 +30004,10 @@
         <v>317</v>
       </c>
       <c r="C1177" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1177" s="34" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="E1177" s="34" t="s">
         <v>89</v>
@@ -30051,7 +30034,7 @@
         <v>317</v>
       </c>
       <c r="C1178" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1178" s="34" t="s">
         <v>334</v>
@@ -30081,7 +30064,7 @@
         <v>317</v>
       </c>
       <c r="C1179" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1179" s="34" t="s">
         <v>280</v>
@@ -30111,10 +30094,10 @@
         <v>317</v>
       </c>
       <c r="C1180" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1180" s="34" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="E1180" s="34" t="s">
         <v>89</v>
@@ -30141,10 +30124,10 @@
         <v>317</v>
       </c>
       <c r="C1181" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1181" s="34" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="E1181" s="34" t="s">
         <v>51</v>
@@ -30173,10 +30156,10 @@
         <v>317</v>
       </c>
       <c r="C1182" s="34" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="D1182" s="34" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="E1182" s="34" t="s">
         <v>89</v>
@@ -30188,7 +30171,7 @@
         <v>89</v>
       </c>
       <c r="H1182" s="34" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="I1182" s="34" t="s">
         <v>108</v>
@@ -30197,13 +30180,13 @@
     </row>
     <row r="1183" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1183" s="24" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="B1183" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1183" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1183" s="39" t="s">
         <v>410</v>
@@ -30227,16 +30210,16 @@
     </row>
     <row r="1184" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1184" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1184" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1184" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1184" s="39" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="E1184" s="39" t="s">
         <v>89</v>
@@ -30255,25 +30238,25 @@
     </row>
     <row r="1185" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1185" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1185" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1185" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1185" s="39" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="E1185" s="39" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="F1185" s="39" t="s">
         <v>89</v>
       </c>
       <c r="G1185" s="39" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="H1185" s="39" t="s">
         <v>89</v>
@@ -30285,43 +30268,43 @@
     </row>
     <row r="1186" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1186" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1186" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1186" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1186" s="39" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="E1186" s="39" t="s">
         <v>832</v>
       </c>
       <c r="F1186" s="39" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="G1186" s="39" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1186" s="39" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="I1186" s="39" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="J1186" s="39"/>
     </row>
     <row r="1187" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1187" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1187" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1187" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1187" s="40" t="s">
         <v>594</v>
@@ -30345,13 +30328,13 @@
     </row>
     <row r="1188" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1188" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1188" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1188" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1188" s="40" t="s">
         <v>108</v>
@@ -30375,13 +30358,13 @@
     </row>
     <row r="1189" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1189" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1189" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1189" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1189" s="40" t="s">
         <v>204</v>
@@ -30405,19 +30388,19 @@
     </row>
     <row r="1190" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1190" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1190" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1190" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1190" s="40" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="E1190" s="40" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="F1190" s="40" t="s">
         <v>808</v>
@@ -30426,7 +30409,7 @@
         <v>81</v>
       </c>
       <c r="H1190" s="40" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="I1190" s="40" t="s">
         <v>81</v>
@@ -30435,13 +30418,13 @@
     </row>
     <row r="1191" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1191" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1191" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1191" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1191" s="40" t="s">
         <v>108</v>
@@ -30453,7 +30436,7 @@
         <v>89</v>
       </c>
       <c r="G1191" s="40" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1191" s="40" t="s">
         <v>89</v>
@@ -30465,16 +30448,16 @@
     </row>
     <row r="1192" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1192" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1192" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1192" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1192" s="40" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="E1192" s="40" t="s">
         <v>169</v>
@@ -30497,13 +30480,13 @@
     </row>
     <row r="1193" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1193" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1193" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1193" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1193" s="40" t="s">
         <v>495</v>
@@ -30529,13 +30512,13 @@
     </row>
     <row r="1194" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1194" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1194" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1194" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1194" s="40" t="s">
         <v>50</v>
@@ -30561,13 +30544,13 @@
     </row>
     <row r="1195" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1195" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1195" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1195" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1195" s="40" t="s">
         <v>393</v>
@@ -30583,25 +30566,25 @@
         <v>108</v>
       </c>
       <c r="I1195" s="40" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1195" s="40"/>
     </row>
     <row r="1196" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1196" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1196" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1196" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1196" s="40" t="s">
         <v>321</v>
       </c>
       <c r="E1196" s="40" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="F1196" s="40" t="s">
         <v>89</v>
@@ -30619,13 +30602,13 @@
     </row>
     <row r="1197" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1197" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1197" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1197" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1197" s="40" t="s">
         <v>108</v>
@@ -30655,7 +30638,7 @@
         <v>413</v>
       </c>
       <c r="C1198" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1198" s="40" t="s">
         <v>204</v>
@@ -30683,10 +30666,10 @@
         <v>413</v>
       </c>
       <c r="C1199" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1199" s="40" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="E1199" s="40" t="s">
         <v>89</v>
@@ -30711,7 +30694,7 @@
         <v>413</v>
       </c>
       <c r="C1200" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1200" s="40" t="s">
         <v>108</v>
@@ -30723,7 +30706,7 @@
         <v>89</v>
       </c>
       <c r="G1200" s="40" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1200" s="40" t="s">
         <v>108</v>
@@ -30741,10 +30724,10 @@
         <v>413</v>
       </c>
       <c r="C1201" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1201" s="40" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="E1201" s="40" t="s">
         <v>16</v>
@@ -30756,7 +30739,7 @@
         <v>81</v>
       </c>
       <c r="H1201" s="40" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="I1201" s="40" t="s">
         <v>81</v>
@@ -30771,10 +30754,10 @@
         <v>413</v>
       </c>
       <c r="C1202" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1202" s="40" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="E1202" s="40" t="s">
         <v>89</v>
@@ -30801,10 +30784,10 @@
         <v>413</v>
       </c>
       <c r="C1203" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1203" s="40" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="E1203" s="40" t="s">
         <v>94</v>
@@ -30833,7 +30816,7 @@
         <v>413</v>
       </c>
       <c r="C1204" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1204" s="40" t="s">
         <v>338</v>
@@ -30845,10 +30828,10 @@
         <v>89</v>
       </c>
       <c r="G1204" s="40" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="H1204" s="40" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="I1204" s="40" t="s">
         <v>89</v>
@@ -30863,7 +30846,7 @@
         <v>413</v>
       </c>
       <c r="C1205" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1205" s="40" t="s">
         <v>392</v>
@@ -30891,7 +30874,7 @@
         <v>413</v>
       </c>
       <c r="C1206" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1206" s="40" t="s">
         <v>108</v>
@@ -30919,10 +30902,10 @@
         <v>413</v>
       </c>
       <c r="C1207" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1207" s="40" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="E1207" s="40" t="s">
         <v>89</v>
@@ -30931,13 +30914,13 @@
         <v>89</v>
       </c>
       <c r="G1207" s="40" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1207" s="40" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1207" s="40" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1207" s="40"/>
     </row>
@@ -30949,16 +30932,16 @@
         <v>413</v>
       </c>
       <c r="C1208" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1208" s="40" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="E1208" s="40" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="F1208" s="40" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="G1208" s="40" t="s">
         <v>89</v>
@@ -30967,7 +30950,7 @@
         <v>108</v>
       </c>
       <c r="I1208" s="40" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1208" s="40" t="s">
         <v>955</v>
@@ -30981,10 +30964,10 @@
         <v>413</v>
       </c>
       <c r="C1209" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1209" s="40" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="E1209" s="40" t="s">
         <v>141</v>
@@ -31013,10 +30996,10 @@
         <v>413</v>
       </c>
       <c r="C1210" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1210" s="40" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="E1210" s="40" t="s">
         <v>141</v>
@@ -31043,10 +31026,10 @@
         <v>413</v>
       </c>
       <c r="C1211" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1211" s="40" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="E1211" s="40" t="s">
         <v>847</v>
@@ -31058,10 +31041,10 @@
         <v>81</v>
       </c>
       <c r="H1211" s="40" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="I1211" s="40" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="J1211" s="40"/>
     </row>
@@ -31073,7 +31056,7 @@
         <v>413</v>
       </c>
       <c r="C1212" s="26" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D1212" s="41" t="s">
         <v>676</v>
@@ -31101,7 +31084,7 @@
         <v>11</v>
       </c>
       <c r="C1213" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1213" s="32" t="s">
         <v>108</v>
@@ -31131,10 +31114,10 @@
         <v>11</v>
       </c>
       <c r="C1214" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1214" s="32" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="E1214" s="32" t="s">
         <v>89</v>
@@ -31163,16 +31146,16 @@
         <v>11</v>
       </c>
       <c r="C1215" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1215" s="32" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="E1215" s="32" t="s">
         <v>847</v>
       </c>
       <c r="F1215" s="32" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="G1215" s="32" t="s">
         <v>89</v>
@@ -31195,16 +31178,16 @@
         <v>11</v>
       </c>
       <c r="C1216" s="32" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D1216" s="32" t="s">
         <v>1364</v>
       </c>
-      <c r="D1216" s="32" t="s">
-        <v>1368</v>
-      </c>
       <c r="E1216" s="32" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="F1216" s="32" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="G1216" s="32" t="s">
         <v>50</v>
@@ -31225,7 +31208,7 @@
         <v>11</v>
       </c>
       <c r="C1217" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1217" s="32" t="s">
         <v>146</v>
@@ -31257,7 +31240,7 @@
         <v>11</v>
       </c>
       <c r="C1218" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1218" s="32" t="s">
         <v>108</v>
@@ -31287,7 +31270,7 @@
         <v>11</v>
       </c>
       <c r="C1219" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1219" s="32" t="s">
         <v>351</v>
@@ -31296,7 +31279,7 @@
         <v>89</v>
       </c>
       <c r="F1219" s="32" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="G1219" s="32" t="s">
         <v>108</v>
@@ -31317,28 +31300,28 @@
         <v>11</v>
       </c>
       <c r="C1220" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1220" s="32" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="E1220" s="32" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="F1220" s="32" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="G1220" s="32" t="s">
         <v>89</v>
       </c>
       <c r="H1220" s="32" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="I1220" s="32" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="J1220" s="32" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="1221" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31349,7 +31332,7 @@
         <v>11</v>
       </c>
       <c r="C1221" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1221" s="32" t="s">
         <v>297</v>
@@ -31381,16 +31364,16 @@
         <v>11</v>
       </c>
       <c r="C1222" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1222" s="32" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="E1222" s="32" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="F1222" s="32" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="G1222" s="32" t="s">
         <v>89</v>
@@ -31411,7 +31394,7 @@
         <v>11</v>
       </c>
       <c r="C1223" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1223" s="32" t="s">
         <v>108</v>
@@ -31441,7 +31424,7 @@
         <v>11</v>
       </c>
       <c r="C1224" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1224" s="32" t="s">
         <v>334</v>
@@ -31471,7 +31454,7 @@
         <v>11</v>
       </c>
       <c r="C1225" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1225" s="32" t="s">
         <v>51</v>
@@ -31492,7 +31475,7 @@
         <v>81</v>
       </c>
       <c r="J1225" s="32" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="1226" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31503,10 +31486,10 @@
         <v>11</v>
       </c>
       <c r="C1226" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1226" s="32" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="E1226" s="32" t="s">
         <v>983</v>
@@ -31533,10 +31516,10 @@
         <v>11</v>
       </c>
       <c r="C1227" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1227" s="32" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E1227" s="32" t="s">
         <v>16</v>
@@ -31563,7 +31546,7 @@
         <v>413</v>
       </c>
       <c r="C1228" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1228" s="42" t="s">
         <v>108</v>
@@ -31595,7 +31578,7 @@
         <v>413</v>
       </c>
       <c r="C1229" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1229" s="42" t="s">
         <v>50</v>
@@ -31625,7 +31608,7 @@
         <v>413</v>
       </c>
       <c r="C1230" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1230" s="42" t="s">
         <v>411</v>
@@ -31640,10 +31623,10 @@
         <v>108</v>
       </c>
       <c r="H1230" s="42" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="I1230" s="42" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="J1230" s="43"/>
     </row>
@@ -31655,7 +31638,7 @@
         <v>413</v>
       </c>
       <c r="C1231" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1231" s="42" t="s">
         <v>351</v>
@@ -31664,7 +31647,7 @@
         <v>89</v>
       </c>
       <c r="F1231" s="42" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="G1231" s="42" t="s">
         <v>108</v>
@@ -31685,7 +31668,7 @@
         <v>413</v>
       </c>
       <c r="C1232" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1232" s="42" t="s">
         <v>338</v>
@@ -31717,10 +31700,10 @@
         <v>413</v>
       </c>
       <c r="C1233" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1233" s="42" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="E1233" s="42" t="s">
         <v>89</v>
@@ -31749,7 +31732,7 @@
         <v>413</v>
       </c>
       <c r="C1234" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1234" s="42" t="s">
         <v>458</v>
@@ -31779,16 +31762,16 @@
         <v>413</v>
       </c>
       <c r="C1235" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1235" s="44" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="E1235" s="42" t="s">
         <v>81</v>
       </c>
       <c r="F1235" s="42" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="G1235" s="42" t="s">
         <v>108</v>
@@ -31798,7 +31781,7 @@
       </c>
       <c r="I1235" s="43"/>
       <c r="J1235" s="42" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="1236" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -31809,25 +31792,25 @@
         <v>413</v>
       </c>
       <c r="C1236" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1236" s="45" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="E1236" s="42" t="s">
         <v>325</v>
       </c>
       <c r="F1236" s="42" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="G1236" s="42" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="H1236" s="42" t="s">
         <v>89</v>
       </c>
       <c r="I1236" s="42" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="J1236" s="43"/>
     </row>
@@ -31839,10 +31822,10 @@
         <v>413</v>
       </c>
       <c r="C1237" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1237" s="46" t="s">
-        <v>1382</v>
+        <v>1457</v>
       </c>
       <c r="E1237" s="42" t="s">
         <v>108</v>
@@ -31871,16 +31854,16 @@
         <v>413</v>
       </c>
       <c r="C1238" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1238" s="47" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="E1238" s="42" t="s">
         <v>89</v>
       </c>
       <c r="F1238" s="42" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
       <c r="G1238" s="42" t="s">
         <v>108</v>
@@ -31901,10 +31884,10 @@
         <v>413</v>
       </c>
       <c r="C1239" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1239" s="42" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="E1239" s="42" t="s">
         <v>26</v>
@@ -31931,10 +31914,10 @@
         <v>413</v>
       </c>
       <c r="C1240" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1240" s="48" t="s">
-        <v>1386</v>
+        <v>1381</v>
       </c>
       <c r="E1240" s="42" t="s">
         <v>89</v>
@@ -31963,22 +31946,22 @@
         <v>413</v>
       </c>
       <c r="C1241" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1241" s="42" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="E1241" s="42" t="s">
         <v>847</v>
       </c>
       <c r="F1241" s="42" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="G1241" s="42" t="s">
         <v>81</v>
       </c>
       <c r="H1241" s="42" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="I1241" s="42" t="s">
         <v>81</v>
@@ -31993,10 +31976,10 @@
         <v>413</v>
       </c>
       <c r="C1242" s="43" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D1242" s="42" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="E1242" s="42" t="s">
         <v>19</v>
@@ -32008,10 +31991,10 @@
         <v>81</v>
       </c>
       <c r="H1242" s="42" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="I1242" s="42" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="J1242" s="43"/>
     </row>
@@ -32023,7 +32006,7 @@
         <v>425</v>
       </c>
       <c r="C1243" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1243" s="50" t="s">
         <v>50</v>
@@ -32035,7 +32018,7 @@
         <v>89</v>
       </c>
       <c r="G1243" s="50" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="H1243" s="50" t="s">
         <v>89</v>
@@ -32053,10 +32036,10 @@
         <v>425</v>
       </c>
       <c r="C1244" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1244" s="49" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="E1244" s="49" t="s">
         <v>89</v>
@@ -32081,13 +32064,13 @@
         <v>425</v>
       </c>
       <c r="C1245" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1245" s="49" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="E1245" s="49" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="F1245" s="49" t="s">
         <v>19</v>
@@ -32111,10 +32094,10 @@
         <v>425</v>
       </c>
       <c r="C1246" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1246" s="51" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="E1246" s="51" t="s">
         <v>89</v>
@@ -32141,7 +32124,7 @@
         <v>425</v>
       </c>
       <c r="C1247" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1247" s="49" t="s">
         <v>384</v>
@@ -32153,13 +32136,13 @@
         <v>89</v>
       </c>
       <c r="G1247" s="49" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1247" s="49" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1247" s="49" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1247" s="49"/>
     </row>
@@ -32171,10 +32154,10 @@
         <v>425</v>
       </c>
       <c r="C1248" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1248" s="49" t="s">
-        <v>1394</v>
+        <v>1389</v>
       </c>
       <c r="E1248" s="49" t="s">
         <v>89</v>
@@ -32183,13 +32166,13 @@
         <v>89</v>
       </c>
       <c r="G1248" s="49" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1248" s="49" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1248" s="49" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1248" s="49"/>
     </row>
@@ -32201,16 +32184,16 @@
         <v>425</v>
       </c>
       <c r="C1249" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1249" s="49" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="E1249" s="49" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="F1249" s="49" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="G1249" s="49" t="s">
         <v>89</v>
@@ -32233,22 +32216,22 @@
         <v>425</v>
       </c>
       <c r="C1250" s="50" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D1250" s="49" t="s">
         <v>1391</v>
       </c>
-      <c r="D1250" s="49" t="s">
-        <v>1396</v>
-      </c>
       <c r="E1250" s="49" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="F1250" s="49" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="G1250" s="49" t="s">
         <v>81</v>
       </c>
       <c r="H1250" s="49" t="s">
-        <v>1398</v>
+        <v>1393</v>
       </c>
       <c r="I1250" s="49" t="s">
         <v>81</v>
@@ -32265,13 +32248,13 @@
         <v>425</v>
       </c>
       <c r="C1251" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1251" s="49" t="s">
-        <v>1399</v>
+        <v>1394</v>
       </c>
       <c r="E1251" s="49" t="s">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="F1251" s="49"/>
       <c r="G1251" s="49"/>
@@ -32291,7 +32274,7 @@
         <v>425</v>
       </c>
       <c r="C1252" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1252" s="49" t="s">
         <v>242</v>
@@ -32321,10 +32304,10 @@
         <v>425</v>
       </c>
       <c r="C1253" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1253" s="49" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="E1253" s="49" t="s">
         <v>89</v>
@@ -32333,13 +32316,13 @@
         <v>89</v>
       </c>
       <c r="G1253" s="49" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1253" s="49" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1253" s="49" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1253" s="49"/>
     </row>
@@ -32351,10 +32334,10 @@
         <v>425</v>
       </c>
       <c r="C1254" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1254" s="49" t="s">
-        <v>1401</v>
+        <v>1396</v>
       </c>
       <c r="E1254" s="49" t="s">
         <v>218</v>
@@ -32363,10 +32346,10 @@
         <v>219</v>
       </c>
       <c r="G1254" s="49" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1254" s="49" t="s">
-        <v>1402</v>
+        <v>1397</v>
       </c>
       <c r="I1254" s="49" t="s">
         <v>227</v>
@@ -32383,19 +32366,19 @@
         <v>425</v>
       </c>
       <c r="C1255" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1255" s="49" t="s">
-        <v>1403</v>
+        <v>1398</v>
       </c>
       <c r="E1255" s="49" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="F1255" s="49" t="s">
         <v>827</v>
       </c>
       <c r="G1255" s="49" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1255" s="49" t="s">
         <v>81</v>
@@ -32415,7 +32398,7 @@
         <v>425</v>
       </c>
       <c r="C1256" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1256" s="49" t="s">
         <v>242</v>
@@ -32447,13 +32430,13 @@
         <v>425</v>
       </c>
       <c r="C1257" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1257" s="49" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="E1257" s="49" t="s">
-        <v>1406</v>
+        <v>1401</v>
       </c>
       <c r="F1257" s="49" t="s">
         <v>999</v>
@@ -32462,7 +32445,7 @@
         <v>89</v>
       </c>
       <c r="H1257" s="49" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="I1257" s="49" t="s">
         <v>89</v>
@@ -32479,10 +32462,10 @@
         <v>425</v>
       </c>
       <c r="C1258" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1258" s="49" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="E1258" s="49" t="s">
         <v>977</v>
@@ -32491,10 +32474,10 @@
         <v>81</v>
       </c>
       <c r="G1258" s="49" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="H1258" s="49" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="I1258" s="49" t="s">
         <v>977</v>
@@ -32509,10 +32492,10 @@
         <v>425</v>
       </c>
       <c r="C1259" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1259" s="49" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="E1259" s="49" t="s">
         <v>81</v>
@@ -32524,7 +32507,7 @@
         <v>81</v>
       </c>
       <c r="H1259" s="49" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="I1259" s="49" t="s">
         <v>81</v>
@@ -32541,10 +32524,10 @@
         <v>425</v>
       </c>
       <c r="C1260" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1260" s="49" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="E1260" s="49" t="s">
         <v>808</v>
@@ -32571,10 +32554,10 @@
         <v>425</v>
       </c>
       <c r="C1261" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1261" s="49" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="E1261" s="49" t="s">
         <v>808</v>
@@ -32601,10 +32584,10 @@
         <v>425</v>
       </c>
       <c r="C1262" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1262" s="49" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="E1262" s="49" t="s">
         <v>89</v>
@@ -32631,10 +32614,10 @@
         <v>425</v>
       </c>
       <c r="C1263" s="50" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="D1263" s="49" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="E1263" s="49" t="s">
         <v>89</v>
@@ -32661,13 +32644,13 @@
         <v>11</v>
       </c>
       <c r="C1264" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1264" s="32" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="E1264" s="32" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="F1264" s="32" t="s">
         <v>81</v>
@@ -32693,7 +32676,7 @@
         <v>11</v>
       </c>
       <c r="C1265" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1265" s="32" t="s">
         <v>108</v>
@@ -32705,7 +32688,7 @@
         <v>89</v>
       </c>
       <c r="G1265" s="32" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1265" s="32" t="s">
         <v>108</v>
@@ -32725,7 +32708,7 @@
         <v>11</v>
       </c>
       <c r="C1266" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1266" s="33" t="s">
         <v>143</v>
@@ -32757,10 +32740,10 @@
         <v>11</v>
       </c>
       <c r="C1267" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1267" s="32" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="E1267" s="32" t="s">
         <v>108</v>
@@ -32787,7 +32770,7 @@
         <v>11</v>
       </c>
       <c r="C1268" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1268" s="32" t="s">
         <v>50</v>
@@ -32819,7 +32802,7 @@
         <v>11</v>
       </c>
       <c r="C1269" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1269" s="32" t="s">
         <v>409</v>
@@ -32828,7 +32811,7 @@
         <v>847</v>
       </c>
       <c r="F1269" s="32" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="G1269" s="32" t="s">
         <v>89</v>
@@ -32851,7 +32834,7 @@
         <v>11</v>
       </c>
       <c r="C1270" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1270" s="32" t="s">
         <v>20</v>
@@ -32883,10 +32866,10 @@
         <v>11</v>
       </c>
       <c r="C1271" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1271" s="32" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
       <c r="E1271" s="32" t="s">
         <v>89</v>
@@ -32901,7 +32884,7 @@
         <v>89</v>
       </c>
       <c r="I1271" s="32" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1271" s="32" t="s">
         <v>941</v>
@@ -32915,22 +32898,22 @@
         <v>11</v>
       </c>
       <c r="C1272" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1272" s="32" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="E1272" s="32" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="F1272" s="32" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="G1272" s="32" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="H1272" s="32" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="I1272" s="32" t="s">
         <v>81</v>
@@ -32947,19 +32930,19 @@
         <v>11</v>
       </c>
       <c r="C1273" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1273" s="32" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
       <c r="E1273" s="32" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="F1273" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G1273" s="32" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="H1273" s="32" t="s">
         <v>89</v>
@@ -32977,10 +32960,10 @@
         <v>11</v>
       </c>
       <c r="C1274" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1274" s="32" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="E1274" s="32" t="s">
         <v>941</v>
@@ -33009,22 +32992,22 @@
         <v>11</v>
       </c>
       <c r="C1275" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1275" s="32" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="E1275" s="32" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="F1275" s="32" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="G1275" s="32" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1275" s="32" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="I1275" s="32" t="s">
         <v>81</v>
@@ -33041,7 +33024,7 @@
         <v>11</v>
       </c>
       <c r="C1276" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1276" s="32" t="s">
         <v>50</v>
@@ -33071,7 +33054,7 @@
         <v>11</v>
       </c>
       <c r="C1277" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1277" s="32" t="s">
         <v>50</v>
@@ -33101,7 +33084,7 @@
         <v>11</v>
       </c>
       <c r="C1278" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1278" s="32" t="s">
         <v>458</v>
@@ -33119,7 +33102,7 @@
         <v>89</v>
       </c>
       <c r="I1278" s="32" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1278" s="32"/>
     </row>
@@ -33131,7 +33114,7 @@
         <v>11</v>
       </c>
       <c r="C1279" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1279" s="32" t="s">
         <v>149</v>
@@ -33161,7 +33144,7 @@
         <v>11</v>
       </c>
       <c r="C1280" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1280" s="32" t="s">
         <v>20</v>
@@ -33193,7 +33176,7 @@
         <v>11</v>
       </c>
       <c r="C1281" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1281" s="32" t="s">
         <v>108</v>
@@ -33208,7 +33191,7 @@
         <v>89</v>
       </c>
       <c r="H1281" s="32" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1281" s="32" t="s">
         <v>89</v>
@@ -33225,7 +33208,7 @@
         <v>11</v>
       </c>
       <c r="C1282" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1282" s="32" t="s">
         <v>101</v>
@@ -33257,13 +33240,13 @@
         <v>11</v>
       </c>
       <c r="C1283" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1283" s="32" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
       <c r="E1283" s="32" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="F1283" s="32" t="s">
         <v>938</v>
@@ -33289,16 +33272,16 @@
         <v>11</v>
       </c>
       <c r="C1284" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1284" s="32" t="s">
-        <v>1426</v>
+        <v>1421</v>
       </c>
       <c r="E1284" s="32" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="F1284" s="32" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="G1284" s="32" t="s">
         <v>89</v>
@@ -33307,10 +33290,10 @@
         <v>89</v>
       </c>
       <c r="I1284" s="32" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
       <c r="J1284" s="32" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="1285" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -33321,7 +33304,7 @@
         <v>11</v>
       </c>
       <c r="C1285" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1285" s="32" t="s">
         <v>108</v>
@@ -33339,7 +33322,7 @@
         <v>89</v>
       </c>
       <c r="I1285" s="32" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1285" s="32" t="s">
         <v>89</v>
@@ -33353,7 +33336,7 @@
         <v>11</v>
       </c>
       <c r="C1286" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1286" s="32" t="s">
         <v>227</v>
@@ -33385,10 +33368,10 @@
         <v>11</v>
       </c>
       <c r="C1287" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1287" s="32" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="E1287" s="32" t="s">
         <v>101</v>
@@ -33417,7 +33400,7 @@
         <v>11</v>
       </c>
       <c r="C1288" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1288" s="32" t="s">
         <v>116</v>
@@ -33449,19 +33432,19 @@
         <v>11</v>
       </c>
       <c r="C1289" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1289" s="32" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="E1289" s="32" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="F1289" s="32" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
       <c r="G1289" s="32" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1289" s="32" t="s">
         <v>81</v>
@@ -33481,7 +33464,7 @@
         <v>11</v>
       </c>
       <c r="C1290" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1290" s="32" t="s">
         <v>108</v>
@@ -33513,22 +33496,22 @@
         <v>11</v>
       </c>
       <c r="C1291" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1291" s="32" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="E1291" s="32" t="s">
         <v>33</v>
       </c>
       <c r="F1291" s="32" t="s">
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="G1291" s="32" t="s">
         <v>108</v>
       </c>
       <c r="H1291" s="32" t="s">
-        <v>1434</v>
+        <v>1429</v>
       </c>
       <c r="I1291" s="32"/>
       <c r="J1291" s="32" t="s">
@@ -33543,7 +33526,7 @@
         <v>11</v>
       </c>
       <c r="C1292" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1292" s="32" t="s">
         <v>116</v>
@@ -33575,13 +33558,13 @@
         <v>11</v>
       </c>
       <c r="C1293" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1293" s="32" t="s">
         <v>108</v>
       </c>
       <c r="E1293" s="32" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="F1293" s="32" t="s">
         <v>81</v>
@@ -33593,7 +33576,7 @@
         <v>89</v>
       </c>
       <c r="I1293" s="32" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="J1293" s="32"/>
     </row>
@@ -33605,7 +33588,7 @@
         <v>11</v>
       </c>
       <c r="C1294" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1294" s="32" t="s">
         <v>204</v>
@@ -33617,7 +33600,7 @@
         <v>89</v>
       </c>
       <c r="G1294" s="32" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1294" s="32" t="s">
         <v>204</v>
@@ -33635,7 +33618,7 @@
         <v>11</v>
       </c>
       <c r="C1295" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1295" s="32" t="s">
         <v>108</v>
@@ -33665,10 +33648,10 @@
         <v>11</v>
       </c>
       <c r="C1296" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1296" s="32" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="E1296" s="32" t="s">
         <v>81</v>
@@ -33683,7 +33666,7 @@
         <v>81</v>
       </c>
       <c r="I1296" s="32" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="J1296" s="32"/>
     </row>
@@ -33695,7 +33678,7 @@
         <v>11</v>
       </c>
       <c r="C1297" s="32" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D1297" s="32" t="s">
         <v>108</v>
@@ -33719,31 +33702,31 @@
     </row>
     <row r="1298" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1298" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1298" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1298" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1298" s="31" t="s">
-        <v>1435</v>
+        <v>1430</v>
       </c>
       <c r="E1298" s="26" t="s">
-        <v>1436</v>
+        <v>1431</v>
       </c>
       <c r="F1298" s="26" t="s">
-        <v>1436</v>
+        <v>1431</v>
       </c>
       <c r="G1298" s="31" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1298" s="26" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
       <c r="I1298" s="26" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="J1298" s="26" t="s">
         <v>1148</v>
@@ -33751,46 +33734,46 @@
     </row>
     <row r="1299" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1299" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1299" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1299" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1299" s="26" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
       <c r="E1299" s="26" t="s">
         <v>1088</v>
       </c>
       <c r="F1299" s="26" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="G1299" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1299" s="26" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="I1299" s="26" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="J1299" s="26"/>
     </row>
     <row r="1300" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1300" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1300" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1300" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1300" s="31" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="E1300" s="27" t="s">
         <v>19</v>
@@ -33802,10 +33785,10 @@
         <v>81</v>
       </c>
       <c r="H1300" s="27" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="I1300" s="27" t="s">
-        <v>1390</v>
+        <v>1385</v>
       </c>
       <c r="J1300" s="26" t="s">
         <v>19</v>
@@ -33813,16 +33796,16 @@
     </row>
     <row r="1301" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1301" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1301" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1301" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1301" s="26" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="E1301" s="26" t="s">
         <v>161</v>
@@ -33837,7 +33820,7 @@
         <v>455</v>
       </c>
       <c r="I1301" s="26" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="J1301" s="26" t="s">
         <v>82</v>
@@ -33845,13 +33828,13 @@
     </row>
     <row r="1302" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1302" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1302" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1302" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1302" s="26" t="s">
         <v>50</v>
@@ -33863,10 +33846,10 @@
         <v>89</v>
       </c>
       <c r="G1302" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1302" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1302" s="26" t="s">
         <v>81</v>
@@ -33875,16 +33858,16 @@
     </row>
     <row r="1303" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1303" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1303" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1303" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1303" s="26" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="E1303" s="26" t="s">
         <v>847</v>
@@ -33899,7 +33882,7 @@
         <v>81</v>
       </c>
       <c r="I1303" s="26" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="J1303" s="26" t="s">
         <v>847</v>
@@ -33907,13 +33890,13 @@
     </row>
     <row r="1304" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1304" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1304" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1304" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1304" s="26" t="s">
         <v>284</v>
@@ -33928,10 +33911,10 @@
         <v>89</v>
       </c>
       <c r="H1304" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="I1304" s="26" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="J1304" s="26" t="s">
         <v>141</v>
@@ -33939,16 +33922,16 @@
     </row>
     <row r="1305" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1305" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1305" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1305" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1305" s="26" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="E1305" s="26" t="s">
         <v>1021</v>
@@ -33957,25 +33940,25 @@
         <v>1021</v>
       </c>
       <c r="G1305" s="26" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="H1305" s="26" t="s">
         <v>81</v>
       </c>
       <c r="I1305" s="26" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="J1305" s="26"/>
     </row>
     <row r="1306" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1306" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1306" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1306" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1306" s="26" t="s">
         <v>39</v>
@@ -34001,46 +33984,46 @@
     </row>
     <row r="1307" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1307" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1307" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1307" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1307" s="26" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="E1307" s="26" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="F1307" s="26" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="G1307" s="26" t="s">
         <v>81</v>
       </c>
       <c r="H1307" s="26" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="I1307" s="26" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="J1307" s="26"/>
     </row>
     <row r="1308" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1308" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1308" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1308" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1308" s="31" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="E1308" s="26" t="s">
         <v>847</v>
@@ -34049,13 +34032,13 @@
         <v>847</v>
       </c>
       <c r="G1308" s="26" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="H1308" s="26" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="I1308" s="26" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="J1308" s="26" t="s">
         <v>847</v>
@@ -34063,16 +34046,16 @@
     </row>
     <row r="1309" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1309" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1309" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1309" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1309" s="26" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="E1309" s="26" t="s">
         <v>841</v>
@@ -34084,25 +34067,25 @@
         <v>81</v>
       </c>
       <c r="H1309" s="26" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="I1309" s="26" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="J1309" s="26"/>
     </row>
     <row r="1310" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1310" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1310" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1310" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1310" s="26" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="E1310" s="26" t="s">
         <v>832</v>
@@ -34111,27 +34094,27 @@
         <v>832</v>
       </c>
       <c r="G1310" s="26" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="H1310" s="26" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="I1310" s="26" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="J1310" s="26" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="1311" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1311" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1311" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1311" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1311" s="26" t="s">
         <v>218</v>
@@ -34155,16 +34138,16 @@
     </row>
     <row r="1312" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1312" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1312" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1312" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1312" s="26" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="E1312" s="26" t="s">
         <v>924</v>
@@ -34176,10 +34159,10 @@
         <v>81</v>
       </c>
       <c r="H1312" s="31" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="I1312" s="26" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
       <c r="J1312" s="26" t="s">
         <v>924</v>
@@ -34187,31 +34170,31 @@
     </row>
     <row r="1313" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1313" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1313" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1313" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1313" s="31" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="E1313" s="26" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="F1313" s="26" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="G1313" s="31" t="s">
         <v>81</v>
       </c>
       <c r="H1313" s="26" t="s">
-        <v>1453</v>
+        <v>1448</v>
       </c>
       <c r="I1313" s="26" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="J1313" s="26" t="s">
         <v>895</v>
@@ -34219,31 +34202,31 @@
     </row>
     <row r="1314" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1314" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1314" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1314" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1314" s="26" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="E1314" s="26" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="F1314" s="26" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="G1314" s="26" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="H1314" s="26" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="I1314" s="26" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="J1314" s="26" t="s">
         <v>902</v>
@@ -34251,13 +34234,13 @@
     </row>
     <row r="1315" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1315" s="24" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B1315" s="25" t="s">
         <v>425</v>
       </c>
       <c r="C1315" s="25" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="D1315" s="26" t="s">
         <v>334</v>
@@ -34293,7 +34276,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E147"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="12.6640625" style="22" customWidth="1"/>
@@ -34303,13 +34286,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="13.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="61" t="s">
         <v>799</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="61" t="s">
         <v>800</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="61" t="s">
         <v>801</v>
       </c>
       <c r="D1" s="17"/>
@@ -36136,19 +36119,19 @@
       <c r="A143" s="22" t="s">
         <v>1161</v>
       </c>
-      <c r="B143" s="60" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C143" s="60" t="s">
-        <v>1162</v>
+      <c r="B143" s="22" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C143" s="22" t="s">
+        <v>1034</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="22" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B144" s="22" t="s">
         <v>1163</v>
-      </c>
-      <c r="B144" s="22" t="s">
-        <v>1164</v>
       </c>
       <c r="C144" s="22" t="s">
         <v>1164</v>
@@ -36159,54 +36142,32 @@
         <v>1165</v>
       </c>
       <c r="B145" s="22" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C145" s="22" t="s">
-        <v>1034</v>
+        <v>1166</v>
+      </c>
+      <c r="C145" s="60" t="s">
+        <v>1167</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="22" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="B146" s="22" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="C146" s="22" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="22" t="s">
-        <v>1169</v>
+        <v>1454</v>
       </c>
       <c r="B147" s="22" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C147" s="61" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A148" s="22" t="s">
-        <v>1172</v>
-      </c>
-      <c r="B148" s="22" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C148" s="22" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A149" s="22" t="s">
-        <v>1459</v>
-      </c>
-      <c r="B149" s="22" t="s">
-        <v>1460</v>
-      </c>
-      <c r="C149" s="22" t="s">
-        <v>1461</v>
+        <v>1455</v>
+      </c>
+      <c r="C147" s="22" t="s">
+        <v>1456</v>
       </c>
     </row>
   </sheetData>
@@ -36231,16 +36192,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="62" t="s">
         <v>720</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="62" t="s">
         <v>721</v>
       </c>
-      <c r="C1" s="63" t="s">
+      <c r="C1" s="62" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="63" t="s">
+      <c r="D1" s="62" t="s">
         <v>722</v>
       </c>
     </row>
@@ -37044,7 +37005,7 @@
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="52" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="B59" s="52" t="s">
         <v>1120</v>
@@ -37061,7 +37022,7 @@
         <v>1121</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1457</v>
+        <v>1452</v>
       </c>
       <c r="C60" s="20" t="s">
         <v>413</v>
